--- a/data/JNJ_data.xlsx
+++ b/data/JNJ_data.xlsx
@@ -5096,7 +5096,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-09-06 05:35:06</t>
+          <t>2026-09-06 05:42:07</t>
         </is>
       </c>
     </row>

--- a/data/JNJ_data.xlsx
+++ b/data/JNJ_data.xlsx
@@ -4851,7 +4851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB2"/>
+  <dimension ref="A1:AF2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4972,25 +4972,45 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>book_value</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>price_to_book</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>earnings_growth</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>shares_outstanding</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>industry</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>website</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>last_updated</t>
         </is>
@@ -5050,7 +5070,7 @@
         <v>0.235</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -5074,29 +5094,41 @@
       <c r="W2" t="n">
         <v>1.089</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X2" t="n">
+        <v>35.284</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>7.80042</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-0.008999999999999999</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2409898597</v>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>Drug Manufacturers - General</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>https://www.jnj.com</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>Johnson &amp; Johnson, together with its subsidiaries, engages in the research and development, manufacture, and sale of a range of products in the healthcare field worldwide. It operates in two segments, Innovative Medicine and MedTech. The Innovative Medicine segment offers products for various therapeutic areas, such as oncology, immunology, neuroscience, pulmonary hypertension, infectious diseases, and cardiovascular and metabolism distributed through retailers, wholesalers, distributors, hospitals, and healthcare professionals for prescription use. The MedTech segment provides a portfolio of products used in the surgery, orthopedic, cardiovascular, and vision fields distributed through wholesalers, hospitals and retailers, and used in the professional fields by physicians, nurses, hospitals, eye care professionals and clinics. This segment also offers products and enabling technologies that support joint reconstruction, trauma, spine, sports related injuries, and others, as well as open, laparoscopic, and robotic surgical procedures; instrumentation, energy devices, stapling systems, wound closure, biosurgery products, and digital and robotic technologies; breast aesthetics and reconstruction; contact lenses under the ACUVUE brand; intraocular lenses for cataract surgery, and other products used in cataract and refractive procedures under the TECNIS brand. The company was founded in 1886 and is based in New Brunswick, New Jersey.</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>2026-09-06 05:42:07</t>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>2026-09-06 16:10:09</t>
         </is>
       </c>
     </row>

--- a/data/JNJ_data.xlsx
+++ b/data/JNJ_data.xlsx
@@ -5128,7 +5128,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:10:09</t>
+          <t>2026-09-06 16:24:45</t>
         </is>
       </c>
     </row>

--- a/data/JNJ_data.xlsx
+++ b/data/JNJ_data.xlsx
@@ -5128,7 +5128,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:24:45</t>
+          <t>2026-09-06 16:34:40</t>
         </is>
       </c>
     </row>

--- a/data/JNJ_data.xlsx
+++ b/data/JNJ_data.xlsx
@@ -5128,7 +5128,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:34:40</t>
+          <t>2026-09-06 16:49:14</t>
         </is>
       </c>
     </row>

--- a/data/JNJ_data.xlsx
+++ b/data/JNJ_data.xlsx
@@ -5072,15 +5072,11 @@
       <c r="Q2" t="n">
         <v>1.95</v>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="R2" t="n">
+        <v>0.21482</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.2919</v>
       </c>
       <c r="T2" t="n">
         <v>0.25742</v>
@@ -5128,7 +5124,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:49:14</t>
+          <t>2026-09-06 16:59:44</t>
         </is>
       </c>
     </row>

--- a/data/JNJ_data.xlsx
+++ b/data/JNJ_data.xlsx
@@ -4851,7 +4851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF2"/>
+  <dimension ref="A1:AI2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4992,25 +4992,40 @@
       </c>
       <c r="AB1" t="inlineStr">
         <is>
+          <t>total_revenue</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>industry</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>website</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>last_updated</t>
         </is>
@@ -5102,29 +5117,38 @@
       <c r="AA2" t="n">
         <v>2409898597</v>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB2" t="n">
+        <v>97929003008</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>691554418688</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>34872000512</v>
+      </c>
+      <c r="AE2" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>Drug Manufacturers - General</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>https://www.jnj.com</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>Johnson &amp; Johnson, together with its subsidiaries, engages in the research and development, manufacture, and sale of a range of products in the healthcare field worldwide. It operates in two segments, Innovative Medicine and MedTech. The Innovative Medicine segment offers products for various therapeutic areas, such as oncology, immunology, neuroscience, pulmonary hypertension, infectious diseases, and cardiovascular and metabolism distributed through retailers, wholesalers, distributors, hospitals, and healthcare professionals for prescription use. The MedTech segment provides a portfolio of products used in the surgery, orthopedic, cardiovascular, and vision fields distributed through wholesalers, hospitals and retailers, and used in the professional fields by physicians, nurses, hospitals, eye care professionals and clinics. This segment also offers products and enabling technologies that support joint reconstruction, trauma, spine, sports related injuries, and others, as well as open, laparoscopic, and robotic surgical procedures; instrumentation, energy devices, stapling systems, wound closure, biosurgery products, and digital and robotic technologies; breast aesthetics and reconstruction; contact lenses under the ACUVUE brand; intraocular lenses for cataract surgery, and other products used in cataract and refractive procedures under the TECNIS brand. The company was founded in 1886 and is based in New Brunswick, New Jersey.</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>2026-09-06 16:59:44</t>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2026-09-06 22:20:49</t>
         </is>
       </c>
     </row>

--- a/data/JNJ_data.xlsx
+++ b/data/JNJ_data.xlsx
@@ -5148,7 +5148,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-06 22:20:49</t>
+          <t>2026-09-06 22:41:44</t>
         </is>
       </c>
     </row>

--- a/data/JNJ_data.xlsx
+++ b/data/JNJ_data.xlsx
@@ -5148,7 +5148,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-06 22:41:44</t>
+          <t>2026-09-06 22:59:39</t>
         </is>
       </c>
     </row>

--- a/data/JNJ_data.xlsx
+++ b/data/JNJ_data.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46239</v>
+        <v>45905</v>
       </c>
       <c r="B2" t="n">
-        <v>253.9972934738065</v>
+        <v>174.0770425638393</v>
       </c>
       <c r="C2" t="n">
-        <v>258.0473261663437</v>
+        <v>175.5537581707923</v>
       </c>
       <c r="D2" t="n">
-        <v>253.2211227437212</v>
+        <v>172.6687764611162</v>
       </c>
       <c r="E2" t="n">
-        <v>256.3258056640625</v>
+        <v>174.49755859375</v>
       </c>
       <c r="F2" t="n">
-        <v>6472600</v>
+        <v>9733800</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46240</v>
+        <v>45908</v>
       </c>
       <c r="B3" t="n">
-        <v>260.425593365904</v>
+        <v>173.4511589867753</v>
       </c>
       <c r="C3" t="n">
-        <v>260.8236242062839</v>
+        <v>175.4950938415212</v>
       </c>
       <c r="D3" t="n">
-        <v>254.0271572625725</v>
+        <v>172.8057011623818</v>
       </c>
       <c r="E3" t="n">
-        <v>255.7188262939453</v>
+        <v>174.2041931152344</v>
       </c>
       <c r="F3" t="n">
-        <v>6931800</v>
+        <v>8382500</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46241</v>
+        <v>45909</v>
       </c>
       <c r="B4" t="n">
-        <v>254.6341623817563</v>
+        <v>174.0770398088306</v>
       </c>
       <c r="C4" t="n">
-        <v>258.3259614136433</v>
+        <v>174.165052708233</v>
       </c>
       <c r="D4" t="n">
-        <v>253.8679370762885</v>
+        <v>172.561197432737</v>
       </c>
       <c r="E4" t="n">
-        <v>257.9677124023438</v>
+        <v>173.0599670410156</v>
       </c>
       <c r="F4" t="n">
-        <v>6532100</v>
+        <v>6005700</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46244</v>
+        <v>45910</v>
       </c>
       <c r="B5" t="n">
-        <v>257.7886121067854</v>
+        <v>172.4145258819289</v>
       </c>
       <c r="C5" t="n">
-        <v>260.7141859356404</v>
+        <v>172.7176914018626</v>
       </c>
       <c r="D5" t="n">
-        <v>257.281105309594</v>
+        <v>170.4879415338014</v>
       </c>
       <c r="E5" t="n">
-        <v>260.5251159667969</v>
+        <v>171.9157562255859</v>
       </c>
       <c r="F5" t="n">
-        <v>8985100</v>
+        <v>6891600</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46245</v>
+        <v>45911</v>
       </c>
       <c r="B6" t="n">
-        <v>259.9479684253454</v>
+        <v>171.8766472653515</v>
       </c>
       <c r="C6" t="n">
-        <v>262.853620890259</v>
+        <v>174.9083323610806</v>
       </c>
       <c r="D6" t="n">
-        <v>257.0920280597301</v>
+        <v>171.759296719517</v>
       </c>
       <c r="E6" t="n">
-        <v>258.5249633789062</v>
+        <v>174.5660400390625</v>
       </c>
       <c r="F6" t="n">
-        <v>5945900</v>
+        <v>5792500</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46246</v>
+        <v>45912</v>
       </c>
       <c r="B7" t="n">
-        <v>254.7436088096904</v>
+        <v>173.7934495446803</v>
       </c>
       <c r="C7" t="n">
-        <v>260.1270613743755</v>
+        <v>174.8594234144472</v>
       </c>
       <c r="D7" t="n">
-        <v>254.00723509927</v>
+        <v>172.8252628178507</v>
       </c>
       <c r="E7" t="n">
-        <v>259.5797424316406</v>
+        <v>174.1357269287109</v>
       </c>
       <c r="F7" t="n">
-        <v>4629300</v>
+        <v>7220200</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46247</v>
+        <v>45915</v>
       </c>
       <c r="B8" t="n">
-        <v>260.4455042155265</v>
+        <v>173.8423161383384</v>
       </c>
       <c r="C8" t="n">
-        <v>261.3311205223152</v>
+        <v>175.0452187336727</v>
       </c>
       <c r="D8" t="n">
-        <v>258.3756953399613</v>
+        <v>173.0306068383358</v>
       </c>
       <c r="E8" t="n">
-        <v>260.7937622070312</v>
+        <v>173.4902496337891</v>
       </c>
       <c r="F8" t="n">
-        <v>4852700</v>
+        <v>4768100</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46248</v>
+        <v>45916</v>
       </c>
       <c r="B9" t="n">
-        <v>259.3707811439639</v>
+        <v>173.6565364179341</v>
       </c>
       <c r="C9" t="n">
-        <v>260.4255764680427</v>
+        <v>173.7054225283811</v>
       </c>
       <c r="D9" t="n">
-        <v>257.8881034534354</v>
+        <v>171.7788382257642</v>
       </c>
       <c r="E9" t="n">
-        <v>259.072265625</v>
+        <v>172.5709991455078</v>
       </c>
       <c r="F9" t="n">
-        <v>4998100</v>
+        <v>7959300</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46251</v>
+        <v>45917</v>
       </c>
       <c r="B10" t="n">
-        <v>257.5995438259766</v>
+        <v>172.8154864182272</v>
       </c>
       <c r="C10" t="n">
-        <v>262.9829969172681</v>
+        <v>174.5758041940759</v>
       </c>
       <c r="D10" t="n">
-        <v>256.7437790079673</v>
+        <v>172.6981209566707</v>
       </c>
       <c r="E10" t="n">
-        <v>261.0823669433594</v>
+        <v>173.294677734375</v>
       </c>
       <c r="F10" t="n">
-        <v>5515500</v>
+        <v>6714900</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46252</v>
+        <v>45918</v>
       </c>
       <c r="B11" t="n">
-        <v>266.3563600087168</v>
+        <v>172.7078974682877</v>
       </c>
       <c r="C11" t="n">
-        <v>270.3964321763198</v>
+        <v>173.1186392474049</v>
       </c>
       <c r="D11" t="n">
-        <v>265.0229096495755</v>
+        <v>170.0380535202773</v>
       </c>
       <c r="E11" t="n">
-        <v>269.7794494628906</v>
+        <v>170.3216705322266</v>
       </c>
       <c r="F11" t="n">
-        <v>7838200</v>
+        <v>8200900</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46253</v>
+        <v>45919</v>
       </c>
       <c r="B12" t="n">
-        <v>271.6601848020655</v>
+        <v>170.8400043448543</v>
       </c>
       <c r="C12" t="n">
-        <v>275.1131561312948</v>
+        <v>173.2555691360807</v>
       </c>
       <c r="D12" t="n">
-        <v>269.2321572777068</v>
+        <v>169.5099768279138</v>
       </c>
       <c r="E12" t="n">
-        <v>272.0681762695312</v>
+        <v>172.3069458007812</v>
       </c>
       <c r="F12" t="n">
-        <v>7728500</v>
+        <v>25621000</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46254</v>
+        <v>45922</v>
       </c>
       <c r="B13" t="n">
-        <v>272.0582363321417</v>
+        <v>172.2091312958323</v>
       </c>
       <c r="C13" t="n">
-        <v>272.0582363321417</v>
+        <v>172.7470127753203</v>
       </c>
       <c r="D13" t="n">
-        <v>266.0578308105469</v>
+        <v>170.2825471290745</v>
       </c>
       <c r="E13" t="n">
-        <v>266.0578308105469</v>
+        <v>170.3705749511719</v>
       </c>
       <c r="F13" t="n">
-        <v>6475900</v>
+        <v>7193900</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46255</v>
+        <v>45923</v>
       </c>
       <c r="B14" t="n">
-        <v>266.5155507786093</v>
+        <v>171.0355980210813</v>
       </c>
       <c r="C14" t="n">
-        <v>271.3218634751246</v>
+        <v>173.0697586837889</v>
       </c>
       <c r="D14" t="n">
-        <v>265.6896375517999</v>
+        <v>170.9769227489119</v>
       </c>
       <c r="E14" t="n">
-        <v>268.9137268066406</v>
+        <v>172.6883544921875</v>
       </c>
       <c r="F14" t="n">
-        <v>6186800</v>
+        <v>8350400</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46258</v>
+        <v>45924</v>
       </c>
       <c r="B15" t="n">
-        <v>268.4161893708204</v>
+        <v>172.2580322171388</v>
       </c>
       <c r="C15" t="n">
-        <v>272.635401405727</v>
+        <v>173.0501781580241</v>
       </c>
       <c r="D15" t="n">
-        <v>267.2519483767422</v>
+        <v>171.8668538263927</v>
       </c>
       <c r="E15" t="n">
-        <v>271.7000122070312</v>
+        <v>172.7959136962891</v>
       </c>
       <c r="F15" t="n">
-        <v>5436100</v>
+        <v>6676800</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,25 +833,25 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46259</v>
+        <v>45925</v>
       </c>
       <c r="B16" t="n">
-        <v>271</v>
+        <v>173.2946701929729</v>
       </c>
       <c r="C16" t="n">
-        <v>273.7999877929688</v>
+        <v>174.4682202999683</v>
       </c>
       <c r="D16" t="n">
-        <v>270.1799926757812</v>
+        <v>172.0331071855151</v>
       </c>
       <c r="E16" t="n">
-        <v>273.1400146484375</v>
+        <v>173.81298828125</v>
       </c>
       <c r="F16" t="n">
-        <v>4687000</v>
+        <v>8475000</v>
       </c>
       <c r="G16" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46260</v>
+        <v>45926</v>
       </c>
       <c r="B17" t="n">
-        <v>271.9700012207031</v>
+        <v>174.6638219397404</v>
       </c>
       <c r="C17" t="n">
-        <v>272.9100036621094</v>
+        <v>175.9449483254981</v>
       </c>
       <c r="D17" t="n">
-        <v>269.5499877929688</v>
+        <v>173.4120331870535</v>
       </c>
       <c r="E17" t="n">
-        <v>270</v>
+        <v>175.7493591308594</v>
       </c>
       <c r="F17" t="n">
-        <v>7214100</v>
+        <v>8634400</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46261</v>
+        <v>45929</v>
       </c>
       <c r="B18" t="n">
-        <v>268.4500122070312</v>
+        <v>175.8667202511636</v>
       </c>
       <c r="C18" t="n">
-        <v>268.4500122070312</v>
+        <v>177.861754032588</v>
       </c>
       <c r="D18" t="n">
-        <v>263.8299865722656</v>
+        <v>175.8373826163265</v>
       </c>
       <c r="E18" t="n">
-        <v>265.7699890136719</v>
+        <v>177.6172637939453</v>
       </c>
       <c r="F18" t="n">
-        <v>7306200</v>
+        <v>8597100</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46262</v>
+        <v>45930</v>
       </c>
       <c r="B19" t="n">
-        <v>265.7799987792969</v>
+        <v>177.6954955492426</v>
       </c>
       <c r="C19" t="n">
-        <v>268.3800048828125</v>
+        <v>181.8909562377616</v>
       </c>
       <c r="D19" t="n">
-        <v>264.2699890136719</v>
+        <v>177.0793903191274</v>
       </c>
       <c r="E19" t="n">
-        <v>268.0400085449219</v>
+        <v>181.3335113525391</v>
       </c>
       <c r="F19" t="n">
-        <v>5765600</v>
+        <v>11569000</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46265</v>
+        <v>45931</v>
       </c>
       <c r="B20" t="n">
-        <v>267.1300048828125</v>
+        <v>181.9007297071846</v>
       </c>
       <c r="C20" t="n">
-        <v>267.7699890136719</v>
+        <v>182.4483854305311</v>
       </c>
       <c r="D20" t="n">
-        <v>265.1700134277344</v>
+        <v>179.8567949816596</v>
       </c>
       <c r="E20" t="n">
-        <v>265.8500061035156</v>
+        <v>181.9496307373047</v>
       </c>
       <c r="F20" t="n">
-        <v>7900100</v>
+        <v>13063800</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46266</v>
+        <v>45932</v>
       </c>
       <c r="B21" t="n">
-        <v>270.8299865722656</v>
+        <v>180.1306362123439</v>
       </c>
       <c r="C21" t="n">
-        <v>271.9100036621094</v>
+        <v>182.4777366073124</v>
       </c>
       <c r="D21" t="n">
-        <v>267.0199890136719</v>
+        <v>180.032834144845</v>
       </c>
       <c r="E21" t="n">
-        <v>271.1900024414062</v>
+        <v>181.8811798095703</v>
       </c>
       <c r="F21" t="n">
-        <v>6033600</v>
+        <v>7728100</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46267</v>
+        <v>45933</v>
       </c>
       <c r="B22" t="n">
-        <v>274.739990234375</v>
+        <v>182.9373639295453</v>
       </c>
       <c r="C22" t="n">
-        <v>281.0700073242188</v>
+        <v>185.5974187766257</v>
       </c>
       <c r="D22" t="n">
-        <v>273.5299987792969</v>
+        <v>182.7906757632537</v>
       </c>
       <c r="E22" t="n">
-        <v>275.2099914550781</v>
+        <v>184.4825439453125</v>
       </c>
       <c r="F22" t="n">
-        <v>7910600</v>
+        <v>8675100</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46268</v>
+        <v>45936</v>
       </c>
       <c r="B23" t="n">
-        <v>277.3200073242188</v>
+        <v>183.8566604823808</v>
       </c>
       <c r="C23" t="n">
-        <v>278.8900146484375</v>
+        <v>185.7343437349051</v>
       </c>
       <c r="D23" t="n">
-        <v>273.1600036621094</v>
+        <v>183.2405403023728</v>
       </c>
       <c r="E23" t="n">
-        <v>278.4299926757812</v>
+        <v>184.0131378173828</v>
       </c>
       <c r="F23" t="n">
-        <v>5940300</v>
+        <v>5806100</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,27 +1041,5981 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
+        <v>45937</v>
+      </c>
+      <c r="B24" t="n">
+        <v>179.7198952882722</v>
+      </c>
+      <c r="C24" t="n">
+        <v>185.0595539364086</v>
+      </c>
+      <c r="D24" t="n">
+        <v>178.908185875973</v>
+      </c>
+      <c r="E24" t="n">
+        <v>184.72705078125</v>
+      </c>
+      <c r="F24" t="n">
+        <v>8776800</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>45938</v>
+      </c>
+      <c r="B25" t="n">
+        <v>184.7074643396089</v>
+      </c>
+      <c r="C25" t="n">
+        <v>186.0277174802343</v>
+      </c>
+      <c r="D25" t="n">
+        <v>184.1206967723854</v>
+      </c>
+      <c r="E25" t="n">
+        <v>185.5093994140625</v>
+      </c>
+      <c r="F25" t="n">
+        <v>5751200</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>45939</v>
+      </c>
+      <c r="B26" t="n">
+        <v>185.8125748295944</v>
+      </c>
+      <c r="C26" t="n">
+        <v>187.8662987309212</v>
+      </c>
+      <c r="D26" t="n">
+        <v>185.5485212028525</v>
+      </c>
+      <c r="E26" t="n">
+        <v>186.8687744140625</v>
+      </c>
+      <c r="F26" t="n">
+        <v>7484800</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>45940</v>
+      </c>
+      <c r="B27" t="n">
+        <v>187.7782713984262</v>
+      </c>
+      <c r="C27" t="n">
+        <v>187.8369615886886</v>
+      </c>
+      <c r="D27" t="n">
+        <v>185.6658871464611</v>
+      </c>
+      <c r="E27" t="n">
+        <v>186.5167083740234</v>
+      </c>
+      <c r="F27" t="n">
+        <v>9598000</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>45943</v>
+      </c>
+      <c r="B28" t="n">
+        <v>185.646323339356</v>
+      </c>
+      <c r="C28" t="n">
+        <v>187.0839270863694</v>
+      </c>
+      <c r="D28" t="n">
+        <v>185.1084418485517</v>
+      </c>
+      <c r="E28" t="n">
+        <v>186.6927337646484</v>
+      </c>
+      <c r="F28" t="n">
+        <v>7979500</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B29" t="n">
+        <v>188.6682159172342</v>
+      </c>
+      <c r="C29" t="n">
+        <v>190.1155938776849</v>
+      </c>
+      <c r="D29" t="n">
+        <v>181.7833777150234</v>
+      </c>
+      <c r="E29" t="n">
+        <v>186.6438446044922</v>
+      </c>
+      <c r="F29" t="n">
+        <v>13613300</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B30" t="n">
+        <v>187.2599526066892</v>
+      </c>
+      <c r="C30" t="n">
+        <v>189.303902268661</v>
+      </c>
+      <c r="D30" t="n">
+        <v>185.1280049658996</v>
+      </c>
+      <c r="E30" t="n">
+        <v>186.956787109375</v>
+      </c>
+      <c r="F30" t="n">
+        <v>9473000</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>45946</v>
+      </c>
+      <c r="B31" t="n">
+        <v>187.1230558646578</v>
+      </c>
+      <c r="C31" t="n">
+        <v>188.7953757558051</v>
+      </c>
+      <c r="D31" t="n">
+        <v>186.2331077651437</v>
+      </c>
+      <c r="E31" t="n">
+        <v>187.8858642578125</v>
+      </c>
+      <c r="F31" t="n">
+        <v>10611800</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B32" t="n">
+        <v>188.2574758352493</v>
+      </c>
+      <c r="C32" t="n">
+        <v>189.3332388090219</v>
+      </c>
+      <c r="D32" t="n">
+        <v>187.4555407234371</v>
+      </c>
+      <c r="E32" t="n">
+        <v>188.9616088867188</v>
+      </c>
+      <c r="F32" t="n">
+        <v>7764400</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B33" t="n">
+        <v>189.2354242017374</v>
+      </c>
+      <c r="C33" t="n">
+        <v>190.1938216550539</v>
+      </c>
+      <c r="D33" t="n">
+        <v>188.0912117995895</v>
+      </c>
+      <c r="E33" t="n">
+        <v>189.4505767822266</v>
+      </c>
+      <c r="F33" t="n">
+        <v>8034700</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>45951</v>
+      </c>
+      <c r="B34" t="n">
+        <v>188.756223952035</v>
+      </c>
+      <c r="C34" t="n">
+        <v>189.2843311834856</v>
+      </c>
+      <c r="D34" t="n">
+        <v>187.5435620120352</v>
+      </c>
+      <c r="E34" t="n">
+        <v>187.6511383056641</v>
+      </c>
+      <c r="F34" t="n">
+        <v>6716000</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>45952</v>
+      </c>
+      <c r="B35" t="n">
+        <v>187.768489042997</v>
+      </c>
+      <c r="C35" t="n">
+        <v>189.186529335124</v>
+      </c>
+      <c r="D35" t="n">
+        <v>187.553336455502</v>
+      </c>
+      <c r="E35" t="n">
+        <v>188.6877746582031</v>
+      </c>
+      <c r="F35" t="n">
+        <v>6343100</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>45953</v>
+      </c>
+      <c r="B36" t="n">
+        <v>188.3161623201141</v>
+      </c>
+      <c r="C36" t="n">
+        <v>189.7244285069409</v>
+      </c>
+      <c r="D36" t="n">
+        <v>187.3186379506951</v>
+      </c>
+      <c r="E36" t="n">
+        <v>188.2281494140625</v>
+      </c>
+      <c r="F36" t="n">
+        <v>8882500</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B37" t="n">
+        <v>187.9640832263789</v>
+      </c>
+      <c r="C37" t="n">
+        <v>188.0716595229833</v>
+      </c>
+      <c r="D37" t="n">
+        <v>185.2453531003753</v>
+      </c>
+      <c r="E37" t="n">
+        <v>186.2037506103516</v>
+      </c>
+      <c r="F37" t="n">
+        <v>6903400</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>45957</v>
+      </c>
+      <c r="B38" t="n">
+        <v>185.8027915483585</v>
+      </c>
+      <c r="C38" t="n">
+        <v>186.5949374675263</v>
+      </c>
+      <c r="D38" t="n">
+        <v>185.3529229810849</v>
+      </c>
+      <c r="E38" t="n">
+        <v>186.10595703125</v>
+      </c>
+      <c r="F38" t="n">
+        <v>7126000</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B39" t="n">
+        <v>185.0888771601165</v>
+      </c>
+      <c r="C39" t="n">
+        <v>185.3333673885486</v>
+      </c>
+      <c r="D39" t="n">
+        <v>182.5070609447738</v>
+      </c>
+      <c r="E39" t="n">
+        <v>182.8102264404297</v>
+      </c>
+      <c r="F39" t="n">
+        <v>8329500</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>45959</v>
+      </c>
+      <c r="B40" t="n">
+        <v>182.5852901845839</v>
+      </c>
+      <c r="C40" t="n">
+        <v>182.9764834833836</v>
+      </c>
+      <c r="D40" t="n">
+        <v>180.5902565894498</v>
+      </c>
+      <c r="E40" t="n">
+        <v>182.4875030517578</v>
+      </c>
+      <c r="F40" t="n">
+        <v>10551100</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B41" t="n">
+        <v>182.9569302033718</v>
+      </c>
+      <c r="C41" t="n">
+        <v>185.2062432977132</v>
+      </c>
+      <c r="D41" t="n">
+        <v>182.7906786381269</v>
+      </c>
+      <c r="E41" t="n">
+        <v>184.8835144042969</v>
+      </c>
+      <c r="F41" t="n">
+        <v>7072500</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B42" t="n">
+        <v>183.3285602019948</v>
+      </c>
+      <c r="C42" t="n">
+        <v>185.3235939082472</v>
+      </c>
+      <c r="D42" t="n">
+        <v>182.6439756215902</v>
+      </c>
+      <c r="E42" t="n">
+        <v>184.7074737548828</v>
+      </c>
+      <c r="F42" t="n">
+        <v>8791700</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B43" t="n">
+        <v>184.8346326024117</v>
+      </c>
+      <c r="C43" t="n">
+        <v>184.8639702391834</v>
+      </c>
+      <c r="D43" t="n">
+        <v>181.4313324343818</v>
+      </c>
+      <c r="E43" t="n">
+        <v>182.1550140380859</v>
+      </c>
+      <c r="F43" t="n">
+        <v>7542600</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B44" t="n">
+        <v>182.7124378793119</v>
+      </c>
+      <c r="C44" t="n">
+        <v>183.680624548461</v>
+      </c>
+      <c r="D44" t="n">
+        <v>181.5290986170187</v>
+      </c>
+      <c r="E44" t="n">
+        <v>182.7417755126953</v>
+      </c>
+      <c r="F44" t="n">
+        <v>7209400</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B45" t="n">
+        <v>182.5266206937376</v>
+      </c>
+      <c r="C45" t="n">
+        <v>183.6903965454173</v>
+      </c>
+      <c r="D45" t="n">
+        <v>181.3139438128489</v>
+      </c>
+      <c r="E45" t="n">
+        <v>181.9007263183594</v>
+      </c>
+      <c r="F45" t="n">
+        <v>5049400</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B46" t="n">
+        <v>182.6439716214627</v>
+      </c>
+      <c r="C46" t="n">
+        <v>183.3872314530524</v>
+      </c>
+      <c r="D46" t="n">
+        <v>181.2846065725014</v>
+      </c>
+      <c r="E46" t="n">
+        <v>182.8493499755859</v>
+      </c>
+      <c r="F46" t="n">
+        <v>6767400</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>45968</v>
+      </c>
+      <c r="B47" t="n">
+        <v>183.6023881426973</v>
+      </c>
+      <c r="C47" t="n">
+        <v>184.1989448996594</v>
+      </c>
+      <c r="D47" t="n">
+        <v>181.607339513103</v>
+      </c>
+      <c r="E47" t="n">
+        <v>182.4581756591797</v>
+      </c>
+      <c r="F47" t="n">
+        <v>6959200</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B48" t="n">
+        <v>181.9007248187872</v>
+      </c>
+      <c r="C48" t="n">
+        <v>184.2673883725038</v>
+      </c>
+      <c r="D48" t="n">
+        <v>181.0401144637998</v>
+      </c>
+      <c r="E48" t="n">
+        <v>184.2576141357422</v>
+      </c>
+      <c r="F48" t="n">
+        <v>5323800</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>45972</v>
+      </c>
+      <c r="B49" t="n">
+        <v>185.2160176409071</v>
+      </c>
+      <c r="C49" t="n">
+        <v>189.6461794051158</v>
+      </c>
+      <c r="D49" t="n">
+        <v>184.8835145102268</v>
+      </c>
+      <c r="E49" t="n">
+        <v>189.5581665039062</v>
+      </c>
+      <c r="F49" t="n">
+        <v>7465600</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B50" t="n">
+        <v>189.0985363418636</v>
+      </c>
+      <c r="C50" t="n">
+        <v>191.24027328305</v>
+      </c>
+      <c r="D50" t="n">
+        <v>188.8149342225856</v>
+      </c>
+      <c r="E50" t="n">
+        <v>190.1058349609375</v>
+      </c>
+      <c r="F50" t="n">
+        <v>8803000</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>45974</v>
+      </c>
+      <c r="B51" t="n">
+        <v>189.9297961094911</v>
+      </c>
+      <c r="C51" t="n">
+        <v>191.6803395836668</v>
+      </c>
+      <c r="D51" t="n">
+        <v>189.1865362627468</v>
+      </c>
+      <c r="E51" t="n">
+        <v>190.9468688964844</v>
+      </c>
+      <c r="F51" t="n">
+        <v>8631600</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>45975</v>
+      </c>
+      <c r="B52" t="n">
+        <v>190.7023657548931</v>
+      </c>
+      <c r="C52" t="n">
+        <v>192.8343132451486</v>
+      </c>
+      <c r="D52" t="n">
+        <v>189.2843255068563</v>
+      </c>
+      <c r="E52" t="n">
+        <v>191.6118621826172</v>
+      </c>
+      <c r="F52" t="n">
+        <v>8824800</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>45978</v>
+      </c>
+      <c r="B53" t="n">
+        <v>192.619189424801</v>
+      </c>
+      <c r="C53" t="n">
+        <v>195.8660119204403</v>
+      </c>
+      <c r="D53" t="n">
+        <v>191.5825383144018</v>
+      </c>
+      <c r="E53" t="n">
+        <v>195.1814422607422</v>
+      </c>
+      <c r="F53" t="n">
+        <v>13257000</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>45979</v>
+      </c>
+      <c r="B54" t="n">
+        <v>194.6239916898205</v>
+      </c>
+      <c r="C54" t="n">
+        <v>195.8855695967434</v>
+      </c>
+      <c r="D54" t="n">
+        <v>194.1545746400929</v>
+      </c>
+      <c r="E54" t="n">
+        <v>195.5921783447266</v>
+      </c>
+      <c r="F54" t="n">
+        <v>12468600</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>45980</v>
+      </c>
+      <c r="B55" t="n">
+        <v>195.5921832139753</v>
+      </c>
+      <c r="C55" t="n">
+        <v>198.9954830235987</v>
+      </c>
+      <c r="D55" t="n">
+        <v>194.9858522212118</v>
+      </c>
+      <c r="E55" t="n">
+        <v>198.0468597412109</v>
+      </c>
+      <c r="F55" t="n">
+        <v>14690800</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>45981</v>
+      </c>
+      <c r="B56" t="n">
+        <v>197.5480876884036</v>
+      </c>
+      <c r="C56" t="n">
+        <v>200.0027639999573</v>
+      </c>
+      <c r="D56" t="n">
+        <v>197.1275716942422</v>
+      </c>
+      <c r="E56" t="n">
+        <v>198.5945129394531</v>
+      </c>
+      <c r="F56" t="n">
+        <v>10612600</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>45982</v>
+      </c>
+      <c r="B57" t="n">
+        <v>199.4649249339953</v>
+      </c>
+      <c r="C57" t="n">
+        <v>202.3792444306165</v>
+      </c>
+      <c r="D57" t="n">
+        <v>198.5163016043988</v>
+      </c>
+      <c r="E57" t="n">
+        <v>199.4062347412109</v>
+      </c>
+      <c r="F57" t="n">
+        <v>13189100</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>45985</v>
+      </c>
+      <c r="B58" t="n">
+        <v>199.2204251313988</v>
+      </c>
+      <c r="C58" t="n">
+        <v>201.5772996022027</v>
+      </c>
+      <c r="D58" t="n">
+        <v>198.5260663138595</v>
+      </c>
+      <c r="E58" t="n">
+        <v>201.5088500976562</v>
+      </c>
+      <c r="F58" t="n">
+        <v>14803900</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>45986</v>
+      </c>
+      <c r="B59" t="n">
+        <v>201.9320337594338</v>
+      </c>
+      <c r="C59" t="n">
+        <v>204.4318344688182</v>
+      </c>
+      <c r="D59" t="n">
+        <v>201.9320337594338</v>
+      </c>
+      <c r="E59" t="n">
+        <v>203.3984527587891</v>
+      </c>
+      <c r="F59" t="n">
+        <v>10275300</v>
+      </c>
+      <c r="G59" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>45987</v>
+      </c>
+      <c r="B60" t="n">
+        <v>203.2213139605992</v>
+      </c>
+      <c r="C60" t="n">
+        <v>204.5204108409229</v>
+      </c>
+      <c r="D60" t="n">
+        <v>202.6800173366119</v>
+      </c>
+      <c r="E60" t="n">
+        <v>204.2743682861328</v>
+      </c>
+      <c r="F60" t="n">
+        <v>6729000</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>45989</v>
+      </c>
+      <c r="B61" t="n">
+        <v>203.723236152328</v>
+      </c>
+      <c r="C61" t="n">
+        <v>204.1759610624769</v>
+      </c>
+      <c r="D61" t="n">
+        <v>201.390757529436</v>
+      </c>
+      <c r="E61" t="n">
+        <v>203.6445007324219</v>
+      </c>
+      <c r="F61" t="n">
+        <v>5638300</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B62" t="n">
+        <v>203.2311491085565</v>
+      </c>
+      <c r="C62" t="n">
+        <v>204.4121503614282</v>
+      </c>
+      <c r="D62" t="n">
+        <v>202.0895080566406</v>
+      </c>
+      <c r="E62" t="n">
+        <v>202.0895080566406</v>
+      </c>
+      <c r="F62" t="n">
+        <v>8473700</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B63" t="n">
+        <v>201.9910999780921</v>
+      </c>
+      <c r="C63" t="n">
+        <v>202.3552381514841</v>
+      </c>
+      <c r="D63" t="n">
+        <v>199.8849763223805</v>
+      </c>
+      <c r="E63" t="n">
+        <v>202.1682434082031</v>
+      </c>
+      <c r="F63" t="n">
+        <v>8393600</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>45994</v>
+      </c>
+      <c r="B64" t="n">
+        <v>202.6406353348706</v>
+      </c>
+      <c r="C64" t="n">
+        <v>203.7429161551587</v>
+      </c>
+      <c r="D64" t="n">
+        <v>201.7450518785209</v>
+      </c>
+      <c r="E64" t="n">
+        <v>202.0796661376953</v>
+      </c>
+      <c r="F64" t="n">
+        <v>8363300</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B65" t="n">
+        <v>201.3513800209524</v>
+      </c>
+      <c r="C65" t="n">
+        <v>201.6171101829578</v>
+      </c>
+      <c r="D65" t="n">
+        <v>198.516980022795</v>
+      </c>
+      <c r="E65" t="n">
+        <v>199.2747802734375</v>
+      </c>
+      <c r="F65" t="n">
+        <v>9049900</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>45996</v>
+      </c>
+      <c r="B66" t="n">
+        <v>199.7668717489871</v>
+      </c>
+      <c r="C66" t="n">
+        <v>200.2294329646455</v>
+      </c>
+      <c r="D66" t="n">
+        <v>197.6312241234294</v>
+      </c>
+      <c r="E66" t="n">
+        <v>198.7334899902344</v>
+      </c>
+      <c r="F66" t="n">
+        <v>7785300</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B67" t="n">
+        <v>199.4519359184436</v>
+      </c>
+      <c r="C67" t="n">
+        <v>200.0424290268597</v>
+      </c>
+      <c r="D67" t="n">
+        <v>197.8083734899551</v>
+      </c>
+      <c r="E67" t="n">
+        <v>198.4283905029297</v>
+      </c>
+      <c r="F67" t="n">
+        <v>7785700</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B68" t="n">
+        <v>199.7078130861464</v>
+      </c>
+      <c r="C68" t="n">
+        <v>202.2863341775681</v>
+      </c>
+      <c r="D68" t="n">
+        <v>196.7454662214423</v>
+      </c>
+      <c r="E68" t="n">
+        <v>196.794677734375</v>
+      </c>
+      <c r="F68" t="n">
+        <v>7509400</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>46001</v>
+      </c>
+      <c r="B69" t="n">
+        <v>197.4146980881505</v>
+      </c>
+      <c r="C69" t="n">
+        <v>203.5264016771889</v>
+      </c>
+      <c r="D69" t="n">
+        <v>197.011184699407</v>
+      </c>
+      <c r="E69" t="n">
+        <v>203.2705078125</v>
+      </c>
+      <c r="F69" t="n">
+        <v>11599800</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>46002</v>
+      </c>
+      <c r="B70" t="n">
+        <v>204.608977678963</v>
+      </c>
+      <c r="C70" t="n">
+        <v>207.8961175457048</v>
+      </c>
+      <c r="D70" t="n">
+        <v>204.5400935742317</v>
+      </c>
+      <c r="E70" t="n">
+        <v>206.6855773925781</v>
+      </c>
+      <c r="F70" t="n">
+        <v>9009000</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>46003</v>
+      </c>
+      <c r="B71" t="n">
+        <v>206.951319079071</v>
+      </c>
+      <c r="C71" t="n">
+        <v>208.9098232838249</v>
+      </c>
+      <c r="D71" t="n">
+        <v>205.6522221573458</v>
+      </c>
+      <c r="E71" t="n">
+        <v>208.2307434082031</v>
+      </c>
+      <c r="F71" t="n">
+        <v>6922700</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B72" t="n">
+        <v>207.0202168563343</v>
+      </c>
+      <c r="C72" t="n">
+        <v>211.7835972337083</v>
+      </c>
+      <c r="D72" t="n">
+        <v>205.7014173161141</v>
+      </c>
+      <c r="E72" t="n">
+        <v>210.7797393798828</v>
+      </c>
+      <c r="F72" t="n">
+        <v>8467000</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>46007</v>
+      </c>
+      <c r="B73" t="n">
+        <v>210.612413130432</v>
+      </c>
+      <c r="C73" t="n">
+        <v>211.3308531386185</v>
+      </c>
+      <c r="D73" t="n">
+        <v>205.5045676241825</v>
+      </c>
+      <c r="E73" t="n">
+        <v>205.98681640625</v>
+      </c>
+      <c r="F73" t="n">
+        <v>9949800</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B74" t="n">
+        <v>206.0753964132944</v>
+      </c>
+      <c r="C74" t="n">
+        <v>208.1716837329721</v>
+      </c>
+      <c r="D74" t="n">
+        <v>205.1601253407421</v>
+      </c>
+      <c r="E74" t="n">
+        <v>207.0005187988281</v>
+      </c>
+      <c r="F74" t="n">
+        <v>8457600</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B75" t="n">
+        <v>206.478915988136</v>
+      </c>
+      <c r="C75" t="n">
+        <v>207.7189650641044</v>
+      </c>
+      <c r="D75" t="n">
+        <v>204.4712003216206</v>
+      </c>
+      <c r="E75" t="n">
+        <v>205.0124969482422</v>
+      </c>
+      <c r="F75" t="n">
+        <v>7499900</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B76" t="n">
+        <v>204.2743754538735</v>
+      </c>
+      <c r="C76" t="n">
+        <v>205.9277892890467</v>
+      </c>
+      <c r="D76" t="n">
+        <v>202.768596167102</v>
+      </c>
+      <c r="E76" t="n">
+        <v>203.1032104492188</v>
+      </c>
+      <c r="F76" t="n">
+        <v>24803900</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B77" t="n">
+        <v>202.8670125241163</v>
+      </c>
+      <c r="C77" t="n">
+        <v>204.7861414522214</v>
+      </c>
+      <c r="D77" t="n">
+        <v>202.2469804791725</v>
+      </c>
+      <c r="E77" t="n">
+        <v>204.0381774902344</v>
+      </c>
+      <c r="F77" t="n">
+        <v>8187800</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>46014</v>
+      </c>
+      <c r="B78" t="n">
+        <v>201.7745733053134</v>
+      </c>
+      <c r="C78" t="n">
+        <v>203.2606648620441</v>
+      </c>
+      <c r="D78" t="n">
+        <v>200.062111796116</v>
+      </c>
+      <c r="E78" t="n">
+        <v>202.5225372314453</v>
+      </c>
+      <c r="F78" t="n">
+        <v>7047300</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>46015</v>
+      </c>
+      <c r="B79" t="n">
+        <v>202.739053555574</v>
+      </c>
+      <c r="C79" t="n">
+        <v>204.648346074342</v>
+      </c>
+      <c r="D79" t="n">
+        <v>202.3158675938084</v>
+      </c>
+      <c r="E79" t="n">
+        <v>204.4908752441406</v>
+      </c>
+      <c r="F79" t="n">
+        <v>2376500</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>46017</v>
+      </c>
+      <c r="B80" t="n">
+        <v>204.2448386926768</v>
+      </c>
+      <c r="C80" t="n">
+        <v>204.7467600842614</v>
+      </c>
+      <c r="D80" t="n">
+        <v>203.4378269444086</v>
+      </c>
+      <c r="E80" t="n">
+        <v>204.34326171875</v>
+      </c>
+      <c r="F80" t="n">
+        <v>2316700</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>46020</v>
+      </c>
+      <c r="B81" t="n">
+        <v>204.7074055853226</v>
+      </c>
+      <c r="C81" t="n">
+        <v>206.1541370088678</v>
+      </c>
+      <c r="D81" t="n">
+        <v>204.097224854962</v>
+      </c>
+      <c r="E81" t="n">
+        <v>204.2743682861328</v>
+      </c>
+      <c r="F81" t="n">
+        <v>4348900</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>46021</v>
+      </c>
+      <c r="B82" t="n">
+        <v>204.2251519205988</v>
+      </c>
+      <c r="C82" t="n">
+        <v>204.4023103648072</v>
+      </c>
+      <c r="D82" t="n">
+        <v>203.2508330378112</v>
+      </c>
+      <c r="E82" t="n">
+        <v>203.6346588134766</v>
+      </c>
+      <c r="F82" t="n">
+        <v>3937400</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B83" t="n">
+        <v>203.6346510317296</v>
+      </c>
+      <c r="C83" t="n">
+        <v>204.2153078209129</v>
+      </c>
+      <c r="D83" t="n">
+        <v>203.103190736659</v>
+      </c>
+      <c r="E83" t="n">
+        <v>203.6740112304688</v>
+      </c>
+      <c r="F83" t="n">
+        <v>4083800</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>46024</v>
+      </c>
+      <c r="B84" t="n">
+        <v>203.546094226423</v>
+      </c>
+      <c r="C84" t="n">
+        <v>204.1070634486917</v>
+      </c>
+      <c r="D84" t="n">
+        <v>200.4557852869147</v>
+      </c>
+      <c r="E84" t="n">
+        <v>204.0677032470703</v>
+      </c>
+      <c r="F84" t="n">
+        <v>6325500</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>46027</v>
+      </c>
+      <c r="B85" t="n">
+        <v>202.6111087313451</v>
+      </c>
+      <c r="C85" t="n">
+        <v>202.68000785174</v>
+      </c>
+      <c r="D85" t="n">
+        <v>197.7296330824079</v>
+      </c>
+      <c r="E85" t="n">
+        <v>201.0758056640625</v>
+      </c>
+      <c r="F85" t="n">
+        <v>9477000</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>46028</v>
+      </c>
+      <c r="B86" t="n">
+        <v>201.3612227968269</v>
+      </c>
+      <c r="C86" t="n">
+        <v>203.4378224562984</v>
+      </c>
+      <c r="D86" t="n">
+        <v>200.8888103027919</v>
+      </c>
+      <c r="E86" t="n">
+        <v>201.5482025146484</v>
+      </c>
+      <c r="F86" t="n">
+        <v>8107900</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>46029</v>
+      </c>
+      <c r="B87" t="n">
+        <v>202.0107645526058</v>
+      </c>
+      <c r="C87" t="n">
+        <v>204.9632750752426</v>
+      </c>
+      <c r="D87" t="n">
+        <v>201.7844096173656</v>
+      </c>
+      <c r="E87" t="n">
+        <v>204.2054748535156</v>
+      </c>
+      <c r="F87" t="n">
+        <v>7545900</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>46030</v>
+      </c>
+      <c r="B88" t="n">
+        <v>203.6543250611801</v>
+      </c>
+      <c r="C88" t="n">
+        <v>205.6718769031367</v>
+      </c>
+      <c r="D88" t="n">
+        <v>201.7253599471909</v>
+      </c>
+      <c r="E88" t="n">
+        <v>202.4930114746094</v>
+      </c>
+      <c r="F88" t="n">
+        <v>6557800</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B89" t="n">
+        <v>202.6504838830927</v>
+      </c>
+      <c r="C89" t="n">
+        <v>203.4279717120081</v>
+      </c>
+      <c r="D89" t="n">
+        <v>200.7805515444468</v>
+      </c>
+      <c r="E89" t="n">
+        <v>201.154541015625</v>
+      </c>
+      <c r="F89" t="n">
+        <v>6154300</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>46034</v>
+      </c>
+      <c r="B90" t="n">
+        <v>202.2961890410606</v>
+      </c>
+      <c r="C90" t="n">
+        <v>206.5773204309254</v>
+      </c>
+      <c r="D90" t="n">
+        <v>200.6231026927027</v>
+      </c>
+      <c r="E90" t="n">
+        <v>206.4001770019531</v>
+      </c>
+      <c r="F90" t="n">
+        <v>11794300</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B91" t="n">
+        <v>206.5871726162479</v>
+      </c>
+      <c r="C91" t="n">
+        <v>210.9962509571494</v>
+      </c>
+      <c r="D91" t="n">
+        <v>205.5537908911432</v>
+      </c>
+      <c r="E91" t="n">
+        <v>210.2679595947266</v>
+      </c>
+      <c r="F91" t="n">
+        <v>11379600</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>46036</v>
+      </c>
+      <c r="B92" t="n">
+        <v>211.3308558190507</v>
+      </c>
+      <c r="C92" t="n">
+        <v>215.3954834155094</v>
+      </c>
+      <c r="D92" t="n">
+        <v>210.7600353199485</v>
+      </c>
+      <c r="E92" t="n">
+        <v>215.0903930664062</v>
+      </c>
+      <c r="F92" t="n">
+        <v>11858800</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>46037</v>
+      </c>
+      <c r="B93" t="n">
+        <v>214.7754540862871</v>
+      </c>
+      <c r="C93" t="n">
+        <v>216.2713969640869</v>
+      </c>
+      <c r="D93" t="n">
+        <v>212.4921870786144</v>
+      </c>
+      <c r="E93" t="n">
+        <v>216.0942535400391</v>
+      </c>
+      <c r="F93" t="n">
+        <v>8492100</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B94" t="n">
+        <v>215.5726286297608</v>
+      </c>
+      <c r="C94" t="n">
+        <v>216.6256979258031</v>
+      </c>
+      <c r="D94" t="n">
+        <v>214.686881478726</v>
+      </c>
+      <c r="E94" t="n">
+        <v>215.1986541748047</v>
+      </c>
+      <c r="F94" t="n">
+        <v>10021500</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B95" t="n">
+        <v>213.6535022600511</v>
+      </c>
+      <c r="C95" t="n">
+        <v>215.2675407658023</v>
+      </c>
+      <c r="D95" t="n">
+        <v>211.1045050802375</v>
+      </c>
+      <c r="E95" t="n">
+        <v>214.7557830810547</v>
+      </c>
+      <c r="F95" t="n">
+        <v>14057100</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>46043</v>
+      </c>
+      <c r="B96" t="n">
+        <v>207.6599020836601</v>
+      </c>
+      <c r="C96" t="n">
+        <v>215.218321643167</v>
+      </c>
+      <c r="D96" t="n">
+        <v>207.1678170076325</v>
+      </c>
+      <c r="E96" t="n">
+        <v>214.5589294433594</v>
+      </c>
+      <c r="F96" t="n">
+        <v>14762900</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B97" t="n">
+        <v>215.3069079934484</v>
+      </c>
+      <c r="C97" t="n">
+        <v>218.6530804976869</v>
+      </c>
+      <c r="D97" t="n">
+        <v>214.6475157947938</v>
+      </c>
+      <c r="E97" t="n">
+        <v>215.0313415527344</v>
+      </c>
+      <c r="F97" t="n">
+        <v>13160000</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B98" t="n">
+        <v>216.3206133966017</v>
+      </c>
+      <c r="C98" t="n">
+        <v>217.7082969855193</v>
+      </c>
+      <c r="D98" t="n">
+        <v>214.3916331931512</v>
+      </c>
+      <c r="E98" t="n">
+        <v>216.6552276611328</v>
+      </c>
+      <c r="F98" t="n">
+        <v>6950600</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B99" t="n">
+        <v>216.7241347564745</v>
+      </c>
+      <c r="C99" t="n">
+        <v>218.5153167809881</v>
+      </c>
+      <c r="D99" t="n">
+        <v>216.5174523988691</v>
+      </c>
+      <c r="E99" t="n">
+        <v>217.9838714599609</v>
+      </c>
+      <c r="F99" t="n">
+        <v>6856700</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B100" t="n">
+        <v>218.4857835732108</v>
+      </c>
+      <c r="C100" t="n">
+        <v>221.9303792601758</v>
+      </c>
+      <c r="D100" t="n">
+        <v>217.2063593146032</v>
+      </c>
+      <c r="E100" t="n">
+        <v>220.8871612548828</v>
+      </c>
+      <c r="F100" t="n">
+        <v>8154100</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B101" t="n">
+        <v>222.8161377007139</v>
+      </c>
+      <c r="C101" t="n">
+        <v>224.9518003498371</v>
+      </c>
+      <c r="D101" t="n">
+        <v>222.5012110309432</v>
+      </c>
+      <c r="E101" t="n">
+        <v>224.1152496337891</v>
+      </c>
+      <c r="F101" t="n">
+        <v>9026500</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B102" t="n">
+        <v>225.1879747271155</v>
+      </c>
+      <c r="C102" t="n">
+        <v>226.3591396349424</v>
+      </c>
+      <c r="D102" t="n">
+        <v>223.4853645338204</v>
+      </c>
+      <c r="E102" t="n">
+        <v>223.6920318603516</v>
+      </c>
+      <c r="F102" t="n">
+        <v>9645300</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B103" t="n">
+        <v>224.6466859457881</v>
+      </c>
+      <c r="C103" t="n">
+        <v>224.8828922015737</v>
+      </c>
+      <c r="D103" t="n">
+        <v>221.7630744488117</v>
+      </c>
+      <c r="E103" t="n">
+        <v>223.6526794433594</v>
+      </c>
+      <c r="F103" t="n">
+        <v>11045500</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B104" t="n">
+        <v>224.7057483906486</v>
+      </c>
+      <c r="C104" t="n">
+        <v>227.530312073188</v>
+      </c>
+      <c r="D104" t="n">
+        <v>223.6526790631295</v>
+      </c>
+      <c r="E104" t="n">
+        <v>227.0972747802734</v>
+      </c>
+      <c r="F104" t="n">
+        <v>8187500</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B105" t="n">
+        <v>227.8354016268972</v>
+      </c>
+      <c r="C105" t="n">
+        <v>231.4768283686728</v>
+      </c>
+      <c r="D105" t="n">
+        <v>226.8315438166281</v>
+      </c>
+      <c r="E105" t="n">
+        <v>229.4100799560547</v>
+      </c>
+      <c r="F105" t="n">
+        <v>9346600</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B106" t="n">
+        <v>231.2800013484118</v>
+      </c>
+      <c r="C106" t="n">
+        <v>232.0968644318395</v>
+      </c>
+      <c r="D106" t="n">
+        <v>229.2526131010531</v>
+      </c>
+      <c r="E106" t="n">
+        <v>230.7583923339844</v>
+      </c>
+      <c r="F106" t="n">
+        <v>8641400</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>46058</v>
+      </c>
+      <c r="B107" t="n">
+        <v>231.2799897072634</v>
+      </c>
+      <c r="C107" t="n">
+        <v>235.787490883202</v>
+      </c>
+      <c r="D107" t="n">
+        <v>231.2701534117819</v>
+      </c>
+      <c r="E107" t="n">
+        <v>234.0258178710938</v>
+      </c>
+      <c r="F107" t="n">
+        <v>10267500</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B108" t="n">
+        <v>235.1773154262319</v>
+      </c>
+      <c r="C108" t="n">
+        <v>237.125968199395</v>
+      </c>
+      <c r="D108" t="n">
+        <v>234.2128178267284</v>
+      </c>
+      <c r="E108" t="n">
+        <v>236.1910095214844</v>
+      </c>
+      <c r="F108" t="n">
+        <v>8274000</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>46062</v>
+      </c>
+      <c r="B109" t="n">
+        <v>236.4468956382332</v>
+      </c>
+      <c r="C109" t="n">
+        <v>236.9291444528193</v>
+      </c>
+      <c r="D109" t="n">
+        <v>233.2877026206608</v>
+      </c>
+      <c r="E109" t="n">
+        <v>234.8623809814453</v>
+      </c>
+      <c r="F109" t="n">
+        <v>9378500</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B110" t="n">
+        <v>236.1811678557945</v>
+      </c>
+      <c r="C110" t="n">
+        <v>236.6929405807981</v>
+      </c>
+      <c r="D110" t="n">
+        <v>234.1144193808212</v>
+      </c>
+      <c r="E110" t="n">
+        <v>234.5769805908203</v>
+      </c>
+      <c r="F110" t="n">
+        <v>6723300</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B111" t="n">
+        <v>235.5512982627408</v>
+      </c>
+      <c r="C111" t="n">
+        <v>237.4409032943991</v>
+      </c>
+      <c r="D111" t="n">
+        <v>233.6420056217357</v>
+      </c>
+      <c r="E111" t="n">
+        <v>237.0472412109375</v>
+      </c>
+      <c r="F111" t="n">
+        <v>6803900</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>46065</v>
+      </c>
+      <c r="B112" t="n">
+        <v>236.6732529591429</v>
+      </c>
+      <c r="C112" t="n">
+        <v>242.4503424271597</v>
+      </c>
+      <c r="D112" t="n">
+        <v>235.8859137708501</v>
+      </c>
+      <c r="E112" t="n">
+        <v>240.6788330078125</v>
+      </c>
+      <c r="F112" t="n">
+        <v>10254300</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>46066</v>
+      </c>
+      <c r="B113" t="n">
+        <v>240.7181753030812</v>
+      </c>
+      <c r="C113" t="n">
+        <v>241.0724771605951</v>
+      </c>
+      <c r="D113" t="n">
+        <v>238.7695225953774</v>
+      </c>
+      <c r="E113" t="n">
+        <v>239.5962219238281</v>
+      </c>
+      <c r="F113" t="n">
+        <v>13268500</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>46070</v>
+      </c>
+      <c r="B114" t="n">
+        <v>240.2654733107899</v>
+      </c>
+      <c r="C114" t="n">
+        <v>240.6197751799101</v>
+      </c>
+      <c r="D114" t="n">
+        <v>238.0412390701625</v>
+      </c>
+      <c r="E114" t="n">
+        <v>239.4781341552734</v>
+      </c>
+      <c r="F114" t="n">
+        <v>12703000</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>46071</v>
+      </c>
+      <c r="B115" t="n">
+        <v>239.389564336343</v>
+      </c>
+      <c r="C115" t="n">
+        <v>241.1905976005163</v>
+      </c>
+      <c r="D115" t="n">
+        <v>238.9762146553066</v>
+      </c>
+      <c r="E115" t="n">
+        <v>241.1118621826172</v>
+      </c>
+      <c r="F115" t="n">
+        <v>8129700</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>46072</v>
+      </c>
+      <c r="B116" t="n">
+        <v>240.7477067024548</v>
+      </c>
+      <c r="C116" t="n">
+        <v>243.0506763566235</v>
+      </c>
+      <c r="D116" t="n">
+        <v>240.4032561468311</v>
+      </c>
+      <c r="E116" t="n">
+        <v>243.00146484375</v>
+      </c>
+      <c r="F116" t="n">
+        <v>7553900</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B117" t="n">
+        <v>242.568421266413</v>
+      </c>
+      <c r="C117" t="n">
+        <v>242.9719346373659</v>
+      </c>
+      <c r="D117" t="n">
+        <v>236.4764055549244</v>
+      </c>
+      <c r="E117" t="n">
+        <v>238.6514282226562</v>
+      </c>
+      <c r="F117" t="n">
+        <v>13565800</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B118" t="n">
+        <v>239.7733870753068</v>
+      </c>
+      <c r="C118" t="n">
+        <v>242.9030410566114</v>
+      </c>
+      <c r="D118" t="n">
+        <v>238.7596929857211</v>
+      </c>
+      <c r="E118" t="n">
+        <v>241.9483947753906</v>
+      </c>
+      <c r="F118" t="n">
+        <v>9622700</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B119" t="n">
+        <v>242.7498156695138</v>
+      </c>
+      <c r="C119" t="n">
+        <v>244.6296736547229</v>
+      </c>
+      <c r="D119" t="n">
+        <v>241.9483872724562</v>
+      </c>
+      <c r="E119" t="n">
+        <v>243.6699523925781</v>
+      </c>
+      <c r="F119" t="n">
+        <v>7246300</v>
+      </c>
+      <c r="G119" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B120" t="n">
+        <v>242.2650040664713</v>
+      </c>
+      <c r="C120" t="n">
+        <v>244.629674532896</v>
+      </c>
+      <c r="D120" t="n">
+        <v>241.1370862518812</v>
+      </c>
+      <c r="E120" t="n">
+        <v>242.5717163085938</v>
+      </c>
+      <c r="F120" t="n">
+        <v>7698200</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B121" t="n">
+        <v>242.5123588943122</v>
+      </c>
+      <c r="C121" t="n">
+        <v>242.8685442682355</v>
+      </c>
+      <c r="D121" t="n">
+        <v>239.4551099080992</v>
+      </c>
+      <c r="E121" t="n">
+        <v>240.8897399902344</v>
+      </c>
+      <c r="F121" t="n">
+        <v>7172600</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B122" t="n">
+        <v>241.4438165545137</v>
+      </c>
+      <c r="C122" t="n">
+        <v>246.3017849576054</v>
+      </c>
+      <c r="D122" t="n">
+        <v>239.9300324032001</v>
+      </c>
+      <c r="E122" t="n">
+        <v>245.7971801757812</v>
+      </c>
+      <c r="F122" t="n">
+        <v>16428600</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B123" t="n">
+        <v>246.549124695673</v>
+      </c>
+      <c r="C123" t="n">
+        <v>249.0424223461303</v>
+      </c>
+      <c r="D123" t="n">
+        <v>244.2537044562187</v>
+      </c>
+      <c r="E123" t="n">
+        <v>245.9257965087891</v>
+      </c>
+      <c r="F123" t="n">
+        <v>9042400</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B124" t="n">
+        <v>243.8480592687475</v>
+      </c>
+      <c r="C124" t="n">
+        <v>245.2530085028214</v>
+      </c>
+      <c r="D124" t="n">
+        <v>241.7703087256774</v>
+      </c>
+      <c r="E124" t="n">
+        <v>244.1349792480469</v>
+      </c>
+      <c r="F124" t="n">
+        <v>6178700</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B125" t="n">
+        <v>243.145575843863</v>
+      </c>
+      <c r="C125" t="n">
+        <v>243.9568928450567</v>
+      </c>
+      <c r="D125" t="n">
+        <v>240.6028050981046</v>
+      </c>
+      <c r="E125" t="n">
+        <v>242.7003479003906</v>
+      </c>
+      <c r="F125" t="n">
+        <v>5768000</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B126" t="n">
+        <v>240.0586452528019</v>
+      </c>
+      <c r="C126" t="n">
+        <v>240.424719212307</v>
+      </c>
+      <c r="D126" t="n">
+        <v>233.4296388594088</v>
+      </c>
+      <c r="E126" t="n">
+        <v>237.0904388427734</v>
+      </c>
+      <c r="F126" t="n">
+        <v>9375400</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B127" t="n">
+        <v>235.596428770922</v>
+      </c>
+      <c r="C127" t="n">
+        <v>238.2381306285037</v>
+      </c>
+      <c r="D127" t="n">
+        <v>232.9349346436922</v>
+      </c>
+      <c r="E127" t="n">
+        <v>237.8522644042969</v>
+      </c>
+      <c r="F127" t="n">
+        <v>7179800</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B128" t="n">
+        <v>238.3173005129137</v>
+      </c>
+      <c r="C128" t="n">
+        <v>241.5031767703235</v>
+      </c>
+      <c r="D128" t="n">
+        <v>237.4960948841201</v>
+      </c>
+      <c r="E128" t="n">
+        <v>240.0190734863281</v>
+      </c>
+      <c r="F128" t="n">
+        <v>7844000</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B129" t="n">
+        <v>239.732151823879</v>
+      </c>
+      <c r="C129" t="n">
+        <v>242.4035346970428</v>
+      </c>
+      <c r="D129" t="n">
+        <v>238.2678408210546</v>
+      </c>
+      <c r="E129" t="n">
+        <v>241.1272125244141</v>
+      </c>
+      <c r="F129" t="n">
+        <v>7214100</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B130" t="n">
+        <v>240.2960869196001</v>
+      </c>
+      <c r="C130" t="n">
+        <v>241.1074039007698</v>
+      </c>
+      <c r="D130" t="n">
+        <v>238.802095160397</v>
+      </c>
+      <c r="E130" t="n">
+        <v>240.4148254394531</v>
+      </c>
+      <c r="F130" t="n">
+        <v>6933200</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B131" t="n">
+        <v>238.9010593075404</v>
+      </c>
+      <c r="C131" t="n">
+        <v>241.8098890629796</v>
+      </c>
+      <c r="D131" t="n">
+        <v>237.7533491444783</v>
+      </c>
+      <c r="E131" t="n">
+        <v>239.4748992919922</v>
+      </c>
+      <c r="F131" t="n">
+        <v>7710200</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B132" t="n">
+        <v>241.6219129804633</v>
+      </c>
+      <c r="C132" t="n">
+        <v>242.9872777226232</v>
+      </c>
+      <c r="D132" t="n">
+        <v>238.940626430393</v>
+      </c>
+      <c r="E132" t="n">
+        <v>238.9604187011719</v>
+      </c>
+      <c r="F132" t="n">
+        <v>6415300</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B133" t="n">
+        <v>241.3349760333344</v>
+      </c>
+      <c r="C133" t="n">
+        <v>242.4628939057684</v>
+      </c>
+      <c r="D133" t="n">
+        <v>239.1088211458664</v>
+      </c>
+      <c r="E133" t="n">
+        <v>240.6127166748047</v>
+      </c>
+      <c r="F133" t="n">
+        <v>7571500</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B134" t="n">
+        <v>240.99857884995</v>
+      </c>
+      <c r="C134" t="n">
+        <v>241.5526416415011</v>
+      </c>
+      <c r="D134" t="n">
+        <v>234.7059805370448</v>
+      </c>
+      <c r="E134" t="n">
+        <v>235.5865478515625</v>
+      </c>
+      <c r="F134" t="n">
+        <v>7281800</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B135" t="n">
+        <v>235.349094010365</v>
+      </c>
+      <c r="C135" t="n">
+        <v>236.5759581604242</v>
+      </c>
+      <c r="D135" t="n">
+        <v>232.9250616652477</v>
+      </c>
+      <c r="E135" t="n">
+        <v>234.7653503417969</v>
+      </c>
+      <c r="F135" t="n">
+        <v>6811500</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B136" t="n">
+        <v>235.814102878936</v>
+      </c>
+      <c r="C136" t="n">
+        <v>236.7243510378414</v>
+      </c>
+      <c r="D136" t="n">
+        <v>233.80561773863</v>
+      </c>
+      <c r="E136" t="n">
+        <v>235.0819549560547</v>
+      </c>
+      <c r="F136" t="n">
+        <v>7511500</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B137" t="n">
+        <v>234.3201136195421</v>
+      </c>
+      <c r="C137" t="n">
+        <v>235.764632308021</v>
+      </c>
+      <c r="D137" t="n">
+        <v>232.0148047922595</v>
+      </c>
+      <c r="E137" t="n">
+        <v>232.8755798339844</v>
+      </c>
+      <c r="F137" t="n">
+        <v>17156600</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B138" t="n">
+        <v>234.884060828395</v>
+      </c>
+      <c r="C138" t="n">
+        <v>235.7844203946137</v>
+      </c>
+      <c r="D138" t="n">
+        <v>231.7674501417346</v>
+      </c>
+      <c r="E138" t="n">
+        <v>232.925048828125</v>
+      </c>
+      <c r="F138" t="n">
+        <v>7313700</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B139" t="n">
+        <v>231.6586126149741</v>
+      </c>
+      <c r="C139" t="n">
+        <v>233.4989011687466</v>
+      </c>
+      <c r="D139" t="n">
+        <v>229.7787546189723</v>
+      </c>
+      <c r="E139" t="n">
+        <v>232.7766418457031</v>
+      </c>
+      <c r="F139" t="n">
+        <v>9046200</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B140" t="n">
+        <v>234.2904343153693</v>
+      </c>
+      <c r="C140" t="n">
+        <v>238.9010520004889</v>
+      </c>
+      <c r="D140" t="n">
+        <v>233.2317667584392</v>
+      </c>
+      <c r="E140" t="n">
+        <v>237.3872528076172</v>
+      </c>
+      <c r="F140" t="n">
+        <v>6456400</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B141" t="n">
+        <v>237.4565300874115</v>
+      </c>
+      <c r="C141" t="n">
+        <v>239.0890376929306</v>
+      </c>
+      <c r="D141" t="n">
+        <v>236.3978624775069</v>
+      </c>
+      <c r="E141" t="n">
+        <v>236.70458984375</v>
+      </c>
+      <c r="F141" t="n">
+        <v>5171400</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B142" t="n">
+        <v>238.6339116976677</v>
+      </c>
+      <c r="C142" t="n">
+        <v>240.1081112682183</v>
+      </c>
+      <c r="D142" t="n">
+        <v>236.5957456438558</v>
+      </c>
+      <c r="E142" t="n">
+        <v>237.9017486572266</v>
+      </c>
+      <c r="F142" t="n">
+        <v>7617600</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B143" t="n">
+        <v>240.9095376592209</v>
+      </c>
+      <c r="C143" t="n">
+        <v>241.6219084230326</v>
+      </c>
+      <c r="D143" t="n">
+        <v>237.9611083490254</v>
+      </c>
+      <c r="E143" t="n">
+        <v>239.9201354980469</v>
+      </c>
+      <c r="F143" t="n">
+        <v>7241300</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B144" t="n">
+        <v>240.4346190736229</v>
+      </c>
+      <c r="C144" t="n">
+        <v>242.7300393849503</v>
+      </c>
+      <c r="D144" t="n">
+        <v>240.0784336838334</v>
+      </c>
+      <c r="E144" t="n">
+        <v>241.8494720458984</v>
+      </c>
+      <c r="F144" t="n">
+        <v>7554200</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B145" t="n">
+        <v>242.9971782498834</v>
+      </c>
+      <c r="C145" t="n">
+        <v>244.580212658809</v>
+      </c>
+      <c r="D145" t="n">
+        <v>241.1568896154117</v>
+      </c>
+      <c r="E145" t="n">
+        <v>241.5328521728516</v>
+      </c>
+      <c r="F145" t="n">
+        <v>6314600</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B146" t="n">
+        <v>242.5123641523277</v>
+      </c>
+      <c r="C146" t="n">
+        <v>244.5901147281089</v>
+      </c>
+      <c r="D146" t="n">
+        <v>239.3066957175141</v>
+      </c>
+      <c r="E146" t="n">
+        <v>240.4642944335938</v>
+      </c>
+      <c r="F146" t="n">
+        <v>6878700</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>46118</v>
+      </c>
+      <c r="B147" t="n">
+        <v>240.0784329225297</v>
+      </c>
+      <c r="C147" t="n">
+        <v>240.9392230850874</v>
+      </c>
+      <c r="D147" t="n">
+        <v>237.9512242744999</v>
+      </c>
+      <c r="E147" t="n">
+        <v>238.4162445068359</v>
+      </c>
+      <c r="F147" t="n">
+        <v>4442400</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B148" t="n">
+        <v>238.2282554079276</v>
+      </c>
+      <c r="C148" t="n">
+        <v>238.2282554079276</v>
+      </c>
+      <c r="D148" t="n">
+        <v>233.5088027877857</v>
+      </c>
+      <c r="E148" t="n">
+        <v>235.8833770751953</v>
+      </c>
+      <c r="F148" t="n">
+        <v>6241100</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>46120</v>
+      </c>
+      <c r="B149" t="n">
+        <v>234.1321342347395</v>
+      </c>
+      <c r="C149" t="n">
+        <v>238.7724329332046</v>
+      </c>
+      <c r="D149" t="n">
+        <v>231.4211667922781</v>
+      </c>
+      <c r="E149" t="n">
+        <v>238.7427520751953</v>
+      </c>
+      <c r="F149" t="n">
+        <v>8771100</v>
+      </c>
+      <c r="G149" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="B150" t="n">
+        <v>238.7427511835681</v>
+      </c>
+      <c r="C150" t="n">
+        <v>241.612011492337</v>
+      </c>
+      <c r="D150" t="n">
+        <v>237.9907958579282</v>
+      </c>
+      <c r="E150" t="n">
+        <v>238.7526397705078</v>
+      </c>
+      <c r="F150" t="n">
+        <v>6216500</v>
+      </c>
+      <c r="G150" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="B151" t="n">
+        <v>239.4353230782619</v>
+      </c>
+      <c r="C151" t="n">
+        <v>239.6925622052984</v>
+      </c>
+      <c r="D151" t="n">
+        <v>235.3886718611059</v>
+      </c>
+      <c r="E151" t="n">
+        <v>235.9328460693359</v>
+      </c>
+      <c r="F151" t="n">
+        <v>7354500</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B152" t="n">
+        <v>235.1907903330984</v>
+      </c>
+      <c r="C152" t="n">
+        <v>235.8635765445355</v>
+      </c>
+      <c r="D152" t="n">
+        <v>232.6875890190388</v>
+      </c>
+      <c r="E152" t="n">
+        <v>235.4381408691406</v>
+      </c>
+      <c r="F152" t="n">
+        <v>7663600</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>46126</v>
+      </c>
+      <c r="B153" t="n">
+        <v>232.5193972079424</v>
+      </c>
+      <c r="C153" t="n">
+        <v>239.6233125984258</v>
+      </c>
+      <c r="D153" t="n">
+        <v>230.7780548336423</v>
+      </c>
+      <c r="E153" t="n">
+        <v>237.5554656982422</v>
+      </c>
+      <c r="F153" t="n">
+        <v>10318700</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>46127</v>
+      </c>
+      <c r="B154" t="n">
+        <v>237.3971547010872</v>
+      </c>
+      <c r="C154" t="n">
+        <v>237.8720635067345</v>
+      </c>
+      <c r="D154" t="n">
+        <v>234.2409594215431</v>
+      </c>
+      <c r="E154" t="n">
+        <v>236.1406097412109</v>
+      </c>
+      <c r="F154" t="n">
+        <v>6463500</v>
+      </c>
+      <c r="G154" t="n">
+        <v>0</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="B155" t="n">
+        <v>234.9038500080299</v>
+      </c>
+      <c r="C155" t="n">
+        <v>235.6162207436799</v>
+      </c>
+      <c r="D155" t="n">
+        <v>229.6600157416919</v>
+      </c>
+      <c r="E155" t="n">
+        <v>232.0543670654297</v>
+      </c>
+      <c r="F155" t="n">
+        <v>8668900</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0</v>
+      </c>
+      <c r="H155" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B156" t="n">
+        <v>231.8762966548944</v>
+      </c>
+      <c r="C156" t="n">
+        <v>233.0437839864675</v>
+      </c>
+      <c r="D156" t="n">
+        <v>229.5808763393496</v>
+      </c>
+      <c r="E156" t="n">
+        <v>231.6981964111328</v>
+      </c>
+      <c r="F156" t="n">
+        <v>8946300</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B157" t="n">
+        <v>232.321525670587</v>
+      </c>
+      <c r="C157" t="n">
+        <v>232.7667536363879</v>
+      </c>
+      <c r="D157" t="n">
+        <v>227.0974833184763</v>
+      </c>
+      <c r="E157" t="n">
+        <v>228.2451934814453</v>
+      </c>
+      <c r="F157" t="n">
+        <v>7810500</v>
+      </c>
+      <c r="G157" t="n">
+        <v>0</v>
+      </c>
+      <c r="H157" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B158" t="n">
+        <v>226.9193941968888</v>
+      </c>
+      <c r="C158" t="n">
+        <v>227.2557873120845</v>
+      </c>
+      <c r="D158" t="n">
+        <v>222.3186650386415</v>
+      </c>
+      <c r="E158" t="n">
+        <v>223.7631988525391</v>
+      </c>
+      <c r="F158" t="n">
+        <v>11681200</v>
+      </c>
+      <c r="G158" t="n">
+        <v>0</v>
+      </c>
+      <c r="H158" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B159" t="n">
+        <v>223.7829810531976</v>
+      </c>
+      <c r="C159" t="n">
+        <v>225.0692069251634</v>
+      </c>
+      <c r="D159" t="n">
+        <v>221.4084218257834</v>
+      </c>
+      <c r="E159" t="n">
+        <v>223.7038421630859</v>
+      </c>
+      <c r="F159" t="n">
+        <v>9003400</v>
+      </c>
+      <c r="G159" t="n">
+        <v>0</v>
+      </c>
+      <c r="H159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B160" t="n">
+        <v>224.8416356959219</v>
+      </c>
+      <c r="C160" t="n">
+        <v>228.9377599403605</v>
+      </c>
+      <c r="D160" t="n">
+        <v>224.6239660179549</v>
+      </c>
+      <c r="E160" t="n">
+        <v>228.2055969238281</v>
+      </c>
+      <c r="F160" t="n">
+        <v>7097600</v>
+      </c>
+      <c r="G160" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B161" t="n">
+        <v>226.6027887018479</v>
+      </c>
+      <c r="C161" t="n">
+        <v>227.5526214735122</v>
+      </c>
+      <c r="D161" t="n">
+        <v>224.6140956793093</v>
+      </c>
+      <c r="E161" t="n">
+        <v>225.0890045166016</v>
+      </c>
+      <c r="F161" t="n">
+        <v>6067500</v>
+      </c>
+      <c r="G161" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B162" t="n">
+        <v>223.3773245484034</v>
+      </c>
+      <c r="C162" t="n">
+        <v>225.4946445162854</v>
+      </c>
+      <c r="D162" t="n">
+        <v>221.9723753264516</v>
+      </c>
+      <c r="E162" t="n">
+        <v>222.9518737792969</v>
+      </c>
+      <c r="F162" t="n">
+        <v>7897800</v>
+      </c>
+      <c r="G162" t="n">
+        <v>0</v>
+      </c>
+      <c r="H162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B163" t="n">
+        <v>225.316553812185</v>
+      </c>
+      <c r="C163" t="n">
+        <v>228.5815840196301</v>
+      </c>
+      <c r="D163" t="n">
+        <v>223.9709662459624</v>
+      </c>
+      <c r="E163" t="n">
+        <v>225.3759155273438</v>
+      </c>
+      <c r="F163" t="n">
+        <v>7179800</v>
+      </c>
+      <c r="G163" t="n">
+        <v>0</v>
+      </c>
+      <c r="H163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B164" t="n">
+        <v>223.1299896858621</v>
+      </c>
+      <c r="C164" t="n">
+        <v>226.2861851379911</v>
+      </c>
+      <c r="D164" t="n">
+        <v>222.4769806067155</v>
+      </c>
+      <c r="E164" t="n">
+        <v>224.9405975341797</v>
+      </c>
+      <c r="F164" t="n">
+        <v>7071100</v>
+      </c>
+      <c r="G164" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B165" t="n">
+        <v>225.534219851175</v>
+      </c>
+      <c r="C165" t="n">
+        <v>228.7102074345108</v>
+      </c>
+      <c r="D165" t="n">
+        <v>225.3957041523519</v>
+      </c>
+      <c r="E165" t="n">
+        <v>227.4140930175781</v>
+      </c>
+      <c r="F165" t="n">
+        <v>8157200</v>
+      </c>
+      <c r="G165" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B166" t="n">
+        <v>226.6324494909732</v>
+      </c>
+      <c r="C166" t="n">
+        <v>227.3349316460146</v>
+      </c>
+      <c r="D166" t="n">
+        <v>224.6140757884101</v>
+      </c>
+      <c r="E166" t="n">
+        <v>224.7822723388672</v>
+      </c>
+      <c r="F166" t="n">
+        <v>6863600</v>
+      </c>
+      <c r="G166" t="n">
+        <v>0</v>
+      </c>
+      <c r="H166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B167" t="n">
+        <v>223.12007375354</v>
+      </c>
+      <c r="C167" t="n">
+        <v>224.6635537914519</v>
+      </c>
+      <c r="D167" t="n">
+        <v>221.2105348477109</v>
+      </c>
+      <c r="E167" t="n">
+        <v>221.8239593505859</v>
+      </c>
+      <c r="F167" t="n">
+        <v>8215200</v>
+      </c>
+      <c r="G167" t="n">
+        <v>0</v>
+      </c>
+      <c r="H167" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B168" t="n">
+        <v>223.0013599943453</v>
+      </c>
+      <c r="C168" t="n">
+        <v>224.1292778920903</v>
+      </c>
+      <c r="D168" t="n">
+        <v>222.5165474841354</v>
+      </c>
+      <c r="E168" t="n">
+        <v>223.15966796875</v>
+      </c>
+      <c r="F168" t="n">
+        <v>5556700</v>
+      </c>
+      <c r="G168" t="n">
+        <v>0</v>
+      </c>
+      <c r="H168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B169" t="n">
+        <v>222.86284542864</v>
+      </c>
+      <c r="C169" t="n">
+        <v>223.9412902027537</v>
+      </c>
+      <c r="D169" t="n">
+        <v>220.5872173504634</v>
+      </c>
+      <c r="E169" t="n">
+        <v>222.2395172119141</v>
+      </c>
+      <c r="F169" t="n">
+        <v>7982300</v>
+      </c>
+      <c r="G169" t="n">
+        <v>0</v>
+      </c>
+      <c r="H169" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B170" t="n">
+        <v>222.3978024591847</v>
+      </c>
+      <c r="C170" t="n">
+        <v>222.3978024591847</v>
+      </c>
+      <c r="D170" t="n">
+        <v>218.2917897898664</v>
+      </c>
+      <c r="E170" t="n">
+        <v>220.15185546875</v>
+      </c>
+      <c r="F170" t="n">
+        <v>7269700</v>
+      </c>
+      <c r="G170" t="n">
+        <v>0</v>
+      </c>
+      <c r="H170" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B171" t="n">
+        <v>220.5773139289545</v>
+      </c>
+      <c r="C171" t="n">
+        <v>221.0027495995129</v>
+      </c>
+      <c r="D171" t="n">
+        <v>218.578717393272</v>
+      </c>
+      <c r="E171" t="n">
+        <v>218.9744873046875</v>
+      </c>
+      <c r="F171" t="n">
+        <v>5550600</v>
+      </c>
+      <c r="G171" t="n">
+        <v>0</v>
+      </c>
+      <c r="H171" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B172" t="n">
+        <v>218.9744932439037</v>
+      </c>
+      <c r="C172" t="n">
+        <v>220.9137130226623</v>
+      </c>
+      <c r="D172" t="n">
+        <v>218.034549114472</v>
+      </c>
+      <c r="E172" t="n">
+        <v>219.0833129882812</v>
+      </c>
+      <c r="F172" t="n">
+        <v>6223200</v>
+      </c>
+      <c r="G172" t="n">
+        <v>0</v>
+      </c>
+      <c r="H172" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B173" t="n">
+        <v>220.6366899653626</v>
+      </c>
+      <c r="C173" t="n">
+        <v>225.2374041432973</v>
+      </c>
+      <c r="D173" t="n">
+        <v>219.3009909603728</v>
+      </c>
+      <c r="E173" t="n">
+        <v>221.8833312988281</v>
+      </c>
+      <c r="F173" t="n">
+        <v>8632500</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0</v>
+      </c>
+      <c r="H173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B174" t="n">
+        <v>223.4268017505994</v>
+      </c>
+      <c r="C174" t="n">
+        <v>228.3540202522719</v>
+      </c>
+      <c r="D174" t="n">
+        <v>223.0508241008666</v>
+      </c>
+      <c r="E174" t="n">
+        <v>227.9780426025391</v>
+      </c>
+      <c r="F174" t="n">
+        <v>7464500</v>
+      </c>
+      <c r="G174" t="n">
+        <v>0</v>
+      </c>
+      <c r="H174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B175" t="n">
+        <v>228.5518965755589</v>
+      </c>
+      <c r="C175" t="n">
+        <v>229.3038367743656</v>
+      </c>
+      <c r="D175" t="n">
+        <v>226.7314002434507</v>
+      </c>
+      <c r="E175" t="n">
+        <v>228.3540191650391</v>
+      </c>
+      <c r="F175" t="n">
+        <v>6974400</v>
+      </c>
+      <c r="G175" t="n">
+        <v>0</v>
+      </c>
+      <c r="H175" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B176" t="n">
+        <v>228.324343449484</v>
+      </c>
+      <c r="C176" t="n">
+        <v>229.6798195939985</v>
+      </c>
+      <c r="D176" t="n">
+        <v>224.0402302332647</v>
+      </c>
+      <c r="E176" t="n">
+        <v>224.307373046875</v>
+      </c>
+      <c r="F176" t="n">
+        <v>12167000</v>
+      </c>
+      <c r="G176" t="n">
+        <v>0</v>
+      </c>
+      <c r="H176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B177" t="n">
+        <v>224.3073719260098</v>
+      </c>
+      <c r="C177" t="n">
+        <v>227.2656747432453</v>
+      </c>
+      <c r="D177" t="n">
+        <v>223.466374045218</v>
+      </c>
+      <c r="E177" t="n">
+        <v>226.4939422607422</v>
+      </c>
+      <c r="F177" t="n">
+        <v>10141600</v>
+      </c>
+      <c r="G177" t="n">
+        <v>0</v>
+      </c>
+      <c r="H177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B178" t="n">
+        <v>226.5137209227187</v>
+      </c>
+      <c r="C178" t="n">
+        <v>228.4034825714771</v>
+      </c>
+      <c r="D178" t="n">
+        <v>225.6232499676584</v>
+      </c>
+      <c r="E178" t="n">
+        <v>227.5624847412109</v>
+      </c>
+      <c r="F178" t="n">
+        <v>9677900</v>
+      </c>
+      <c r="G178" t="n">
+        <v>0</v>
+      </c>
+      <c r="H178" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B179" t="n">
+        <v>229.2345877493695</v>
+      </c>
+      <c r="C179" t="n">
+        <v>229.5413000019429</v>
+      </c>
+      <c r="D179" t="n">
+        <v>226.7412900911319</v>
+      </c>
+      <c r="E179" t="n">
+        <v>226.8897094726562</v>
+      </c>
+      <c r="F179" t="n">
+        <v>7353800</v>
+      </c>
+      <c r="G179" t="n">
+        <v>0</v>
+      </c>
+      <c r="H179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B180" t="n">
+        <v>226.8897069691897</v>
+      </c>
+      <c r="C180" t="n">
+        <v>229.432462629467</v>
+      </c>
+      <c r="D180" t="n">
+        <v>224.9405835372236</v>
+      </c>
+      <c r="E180" t="n">
+        <v>229.2741546630859</v>
+      </c>
+      <c r="F180" t="n">
+        <v>5239000</v>
+      </c>
+      <c r="G180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H180" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B181" t="n">
+        <v>230.5307110319731</v>
+      </c>
+      <c r="C181" t="n">
+        <v>233.0042165151488</v>
+      </c>
+      <c r="D181" t="n">
+        <v>230.2536796256238</v>
+      </c>
+      <c r="E181" t="n">
+        <v>231.8565063476562</v>
+      </c>
+      <c r="F181" t="n">
+        <v>5462300</v>
+      </c>
+      <c r="G181" t="n">
+        <v>0</v>
+      </c>
+      <c r="H181" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B182" t="n">
+        <v>231.856506324529</v>
+      </c>
+      <c r="C182" t="n">
+        <v>232.0953339431715</v>
+      </c>
+      <c r="D182" t="n">
+        <v>227.9557463234551</v>
+      </c>
+      <c r="E182" t="n">
+        <v>229.0503387451172</v>
+      </c>
+      <c r="F182" t="n">
+        <v>6619600</v>
+      </c>
+      <c r="G182" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="H182" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="n">
+        <v>46169</v>
+      </c>
+      <c r="B183" t="n">
+        <v>228.8513234809034</v>
+      </c>
+      <c r="C183" t="n">
+        <v>231.7470457253588</v>
+      </c>
+      <c r="D183" t="n">
+        <v>227.896043373475</v>
+      </c>
+      <c r="E183" t="n">
+        <v>230.1548919677734</v>
+      </c>
+      <c r="F183" t="n">
+        <v>5835500</v>
+      </c>
+      <c r="G183" t="n">
+        <v>0</v>
+      </c>
+      <c r="H183" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B184" t="n">
+        <v>228.9010720691913</v>
+      </c>
+      <c r="C184" t="n">
+        <v>230.7320381891827</v>
+      </c>
+      <c r="D184" t="n">
+        <v>228.6025413534768</v>
+      </c>
+      <c r="E184" t="n">
+        <v>229.6672973632812</v>
+      </c>
+      <c r="F184" t="n">
+        <v>7193400</v>
+      </c>
+      <c r="G184" t="n">
+        <v>0</v>
+      </c>
+      <c r="H184" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B185" t="n">
+        <v>230.0951744973679</v>
+      </c>
+      <c r="C185" t="n">
+        <v>230.36385365377</v>
+      </c>
+      <c r="D185" t="n">
+        <v>223.4877626284344</v>
+      </c>
+      <c r="E185" t="n">
+        <v>224.2241363525391</v>
+      </c>
+      <c r="F185" t="n">
+        <v>13897700</v>
+      </c>
+      <c r="G185" t="n">
+        <v>0</v>
+      </c>
+      <c r="H185" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B186" t="n">
+        <v>222.1045945004449</v>
+      </c>
+      <c r="C186" t="n">
+        <v>223.3385143974124</v>
+      </c>
+      <c r="D186" t="n">
+        <v>219.7561761055088</v>
+      </c>
+      <c r="E186" t="n">
+        <v>222.4130706787109</v>
+      </c>
+      <c r="F186" t="n">
+        <v>8041000</v>
+      </c>
+      <c r="G186" t="n">
+        <v>0</v>
+      </c>
+      <c r="H186" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B187" t="n">
+        <v>221.4876358909895</v>
+      </c>
+      <c r="C187" t="n">
+        <v>224.3933034528787</v>
+      </c>
+      <c r="D187" t="n">
+        <v>220.0845521676131</v>
+      </c>
+      <c r="E187" t="n">
+        <v>221.7961120605469</v>
+      </c>
+      <c r="F187" t="n">
+        <v>5669000</v>
+      </c>
+      <c r="G187" t="n">
+        <v>0</v>
+      </c>
+      <c r="H187" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B188" t="n">
+        <v>221.3582777644383</v>
+      </c>
+      <c r="C188" t="n">
+        <v>223.8261024020756</v>
+      </c>
+      <c r="D188" t="n">
+        <v>220.9104892689172</v>
+      </c>
+      <c r="E188" t="n">
+        <v>222.1444091796875</v>
+      </c>
+      <c r="F188" t="n">
+        <v>6507200</v>
+      </c>
+      <c r="G188" t="n">
+        <v>0</v>
+      </c>
+      <c r="H188" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B189" t="n">
+        <v>225.9754999423843</v>
+      </c>
+      <c r="C189" t="n">
+        <v>227.5477475509985</v>
+      </c>
+      <c r="D189" t="n">
+        <v>224.7913377117005</v>
+      </c>
+      <c r="E189" t="n">
+        <v>227.0502014160156</v>
+      </c>
+      <c r="F189" t="n">
+        <v>7274800</v>
+      </c>
+      <c r="G189" t="n">
+        <v>0</v>
+      </c>
+      <c r="H189" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="B190" t="n">
+        <v>228.8712298379233</v>
+      </c>
+      <c r="C190" t="n">
+        <v>234.0656128776528</v>
+      </c>
+      <c r="D190" t="n">
+        <v>227.8761375342802</v>
+      </c>
+      <c r="E190" t="n">
+        <v>231.6276397705078</v>
+      </c>
+      <c r="F190" t="n">
+        <v>8034900</v>
+      </c>
+      <c r="G190" t="n">
+        <v>0</v>
+      </c>
+      <c r="H190" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B191" t="n">
+        <v>231.6276367875738</v>
+      </c>
+      <c r="C191" t="n">
+        <v>233.7969306933057</v>
+      </c>
+      <c r="D191" t="n">
+        <v>229.428476143926</v>
+      </c>
+      <c r="E191" t="n">
+        <v>231.0206298828125</v>
+      </c>
+      <c r="F191" t="n">
+        <v>7559800</v>
+      </c>
+      <c r="G191" t="n">
+        <v>0</v>
+      </c>
+      <c r="H191" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="B192" t="n">
+        <v>231.2395468518091</v>
+      </c>
+      <c r="C192" t="n">
+        <v>236.5433904796373</v>
+      </c>
+      <c r="D192" t="n">
+        <v>229.2792138627353</v>
+      </c>
+      <c r="E192" t="n">
+        <v>235.8368682861328</v>
+      </c>
+      <c r="F192" t="n">
+        <v>8354500</v>
+      </c>
+      <c r="G192" t="n">
+        <v>0</v>
+      </c>
+      <c r="H192" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B193" t="n">
+        <v>237.6777986497502</v>
+      </c>
+      <c r="C193" t="n">
+        <v>239.7475772433621</v>
+      </c>
+      <c r="D193" t="n">
+        <v>235.886629497679</v>
+      </c>
+      <c r="E193" t="n">
+        <v>237.3195648193359</v>
+      </c>
+      <c r="F193" t="n">
+        <v>8350800</v>
+      </c>
+      <c r="G193" t="n">
+        <v>0</v>
+      </c>
+      <c r="H193" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B194" t="n">
+        <v>238.822141602048</v>
+      </c>
+      <c r="C194" t="n">
+        <v>240.4142952862894</v>
+      </c>
+      <c r="D194" t="n">
+        <v>236.971269397276</v>
+      </c>
+      <c r="E194" t="n">
+        <v>237.1603393554688</v>
+      </c>
+      <c r="F194" t="n">
+        <v>7399000</v>
+      </c>
+      <c r="G194" t="n">
+        <v>0</v>
+      </c>
+      <c r="H194" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B195" t="n">
+        <v>238.8221408093525</v>
+      </c>
+      <c r="C195" t="n">
+        <v>239.7276784040579</v>
+      </c>
+      <c r="D195" t="n">
+        <v>236.354316272482</v>
+      </c>
+      <c r="E195" t="n">
+        <v>239.6878662109375</v>
+      </c>
+      <c r="F195" t="n">
+        <v>6459400</v>
+      </c>
+      <c r="G195" t="n">
+        <v>0</v>
+      </c>
+      <c r="H195" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B196" t="n">
+        <v>237.8270530309927</v>
+      </c>
+      <c r="C196" t="n">
+        <v>238.3245991670408</v>
+      </c>
+      <c r="D196" t="n">
+        <v>232.4336547382997</v>
+      </c>
+      <c r="E196" t="n">
+        <v>234.5034484863281</v>
+      </c>
+      <c r="F196" t="n">
+        <v>7732000</v>
+      </c>
+      <c r="G196" t="n">
+        <v>0</v>
+      </c>
+      <c r="H196" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="B197" t="n">
+        <v>235.2099495568312</v>
+      </c>
+      <c r="C197" t="n">
+        <v>235.2099495568312</v>
+      </c>
+      <c r="D197" t="n">
+        <v>229.8862151458974</v>
+      </c>
+      <c r="E197" t="n">
+        <v>234.0257873535156</v>
+      </c>
+      <c r="F197" t="n">
+        <v>7718100</v>
+      </c>
+      <c r="G197" t="n">
+        <v>0</v>
+      </c>
+      <c r="H197" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B198" t="n">
+        <v>232.8814495345484</v>
+      </c>
+      <c r="C198" t="n">
+        <v>234.2745726796724</v>
+      </c>
+      <c r="D198" t="n">
+        <v>229.5677903566066</v>
+      </c>
+      <c r="E198" t="n">
+        <v>233.0506134033203</v>
+      </c>
+      <c r="F198" t="n">
+        <v>8548000</v>
+      </c>
+      <c r="G198" t="n">
+        <v>0</v>
+      </c>
+      <c r="H198" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B199" t="n">
+        <v>230.6424813960874</v>
+      </c>
+      <c r="C199" t="n">
+        <v>231.6077220970904</v>
+      </c>
+      <c r="D199" t="n">
+        <v>226.4830030630252</v>
+      </c>
+      <c r="E199" t="n">
+        <v>227.2691192626953</v>
+      </c>
+      <c r="F199" t="n">
+        <v>18989800</v>
+      </c>
+      <c r="G199" t="n">
+        <v>0</v>
+      </c>
+      <c r="H199" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="B200" t="n">
+        <v>227.8263796240252</v>
+      </c>
+      <c r="C200" t="n">
+        <v>230.3141103803127</v>
+      </c>
+      <c r="D200" t="n">
+        <v>226.3834988221592</v>
+      </c>
+      <c r="E200" t="n">
+        <v>230.1548919677734</v>
+      </c>
+      <c r="F200" t="n">
+        <v>8518300</v>
+      </c>
+      <c r="G200" t="n">
+        <v>0</v>
+      </c>
+      <c r="H200" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="n">
+        <v>46196</v>
+      </c>
+      <c r="B201" t="n">
+        <v>234.4835421454308</v>
+      </c>
+      <c r="C201" t="n">
+        <v>238.6231296371808</v>
+      </c>
+      <c r="D201" t="n">
+        <v>233.1998797966796</v>
+      </c>
+      <c r="E201" t="n">
+        <v>237.9066619873047</v>
+      </c>
+      <c r="F201" t="n">
+        <v>11802000</v>
+      </c>
+      <c r="G201" t="n">
+        <v>0</v>
+      </c>
+      <c r="H201" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B202" t="n">
+        <v>238.7126772290818</v>
+      </c>
+      <c r="C202" t="n">
+        <v>241.8472117165478</v>
+      </c>
+      <c r="D202" t="n">
+        <v>237.5782726810186</v>
+      </c>
+      <c r="E202" t="n">
+        <v>239.8172302246094</v>
+      </c>
+      <c r="F202" t="n">
+        <v>8139200</v>
+      </c>
+      <c r="G202" t="n">
+        <v>0</v>
+      </c>
+      <c r="H202" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B203" t="n">
+        <v>240.0859235854152</v>
+      </c>
+      <c r="C203" t="n">
+        <v>246.9719604825856</v>
+      </c>
+      <c r="D203" t="n">
+        <v>239.7077836523882</v>
+      </c>
+      <c r="E203" t="n">
+        <v>243.6782073974609</v>
+      </c>
+      <c r="F203" t="n">
+        <v>10130400</v>
+      </c>
+      <c r="G203" t="n">
+        <v>0</v>
+      </c>
+      <c r="H203" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="B204" t="n">
+        <v>247.0515630057391</v>
+      </c>
+      <c r="C204" t="n">
+        <v>253.857990512684</v>
+      </c>
+      <c r="D204" t="n">
+        <v>246.6535169859773</v>
+      </c>
+      <c r="E204" t="n">
+        <v>253.4102020263672</v>
+      </c>
+      <c r="F204" t="n">
+        <v>16316800</v>
+      </c>
+      <c r="G204" t="n">
+        <v>0</v>
+      </c>
+      <c r="H204" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B205" t="n">
+        <v>251.9474045302274</v>
+      </c>
+      <c r="C205" t="n">
+        <v>257.3109358669097</v>
+      </c>
+      <c r="D205" t="n">
+        <v>250.7930938975173</v>
+      </c>
+      <c r="E205" t="n">
+        <v>257.2413024902344</v>
+      </c>
+      <c r="F205" t="n">
+        <v>8608400</v>
+      </c>
+      <c r="G205" t="n">
+        <v>0</v>
+      </c>
+      <c r="H205" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B206" t="n">
+        <v>257.7288999793201</v>
+      </c>
+      <c r="C206" t="n">
+        <v>258.62447695588</v>
+      </c>
+      <c r="D206" t="n">
+        <v>251.9275101770222</v>
+      </c>
+      <c r="E206" t="n">
+        <v>252.7235870361328</v>
+      </c>
+      <c r="F206" t="n">
+        <v>8469500</v>
+      </c>
+      <c r="G206" t="n">
+        <v>0</v>
+      </c>
+      <c r="H206" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B207" t="n">
+        <v>252.0071226458085</v>
+      </c>
+      <c r="C207" t="n">
+        <v>252.9524572852904</v>
+      </c>
+      <c r="D207" t="n">
+        <v>249.8477741968348</v>
+      </c>
+      <c r="E207" t="n">
+        <v>252.7335357666016</v>
+      </c>
+      <c r="F207" t="n">
+        <v>6516500</v>
+      </c>
+      <c r="G207" t="n">
+        <v>0</v>
+      </c>
+      <c r="H207" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B208" t="n">
+        <v>254.5247047293354</v>
+      </c>
+      <c r="C208" t="n">
+        <v>261.8087875806335</v>
+      </c>
+      <c r="D208" t="n">
+        <v>252.753441667793</v>
+      </c>
+      <c r="E208" t="n">
+        <v>261.7490844726562</v>
+      </c>
+      <c r="F208" t="n">
+        <v>7998700</v>
+      </c>
+      <c r="G208" t="n">
+        <v>0</v>
+      </c>
+      <c r="H208" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B209" t="n">
+        <v>258.9528582650781</v>
+      </c>
+      <c r="C209" t="n">
+        <v>260.0972082397536</v>
+      </c>
+      <c r="D209" t="n">
+        <v>254.673943516207</v>
+      </c>
+      <c r="E209" t="n">
+        <v>258.0572509765625</v>
+      </c>
+      <c r="F209" t="n">
+        <v>6803700</v>
+      </c>
+      <c r="G209" t="n">
+        <v>0</v>
+      </c>
+      <c r="H209" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B210" t="n">
+        <v>263.5899938466549</v>
+      </c>
+      <c r="C210" t="n">
+        <v>268.1076906797339</v>
+      </c>
+      <c r="D210" t="n">
+        <v>262.7540896546532</v>
+      </c>
+      <c r="E210" t="n">
+        <v>265.9284362792969</v>
+      </c>
+      <c r="F210" t="n">
+        <v>9089700</v>
+      </c>
+      <c r="G210" t="n">
+        <v>0</v>
+      </c>
+      <c r="H210" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B211" t="n">
+        <v>267.2817917945089</v>
+      </c>
+      <c r="C211" t="n">
+        <v>267.2817917945089</v>
+      </c>
+      <c r="D211" t="n">
+        <v>261.8386358221884</v>
+      </c>
+      <c r="E211" t="n">
+        <v>262.1072998046875</v>
+      </c>
+      <c r="F211" t="n">
+        <v>6769400</v>
+      </c>
+      <c r="G211" t="n">
+        <v>0</v>
+      </c>
+      <c r="H211" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B212" t="n">
+        <v>259.3508895364454</v>
+      </c>
+      <c r="C212" t="n">
+        <v>262.1570568783993</v>
+      </c>
+      <c r="D212" t="n">
+        <v>256.8631589924022</v>
+      </c>
+      <c r="E212" t="n">
+        <v>257.8283996582031</v>
+      </c>
+      <c r="F212" t="n">
+        <v>6426100</v>
+      </c>
+      <c r="G212" t="n">
+        <v>0</v>
+      </c>
+      <c r="H212" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B213" t="n">
+        <v>258.9130640253377</v>
+      </c>
+      <c r="C213" t="n">
+        <v>260.0176018849775</v>
+      </c>
+      <c r="D213" t="n">
+        <v>254.2659848771424</v>
+      </c>
+      <c r="E213" t="n">
+        <v>255.7188262939453</v>
+      </c>
+      <c r="F213" t="n">
+        <v>6534700</v>
+      </c>
+      <c r="G213" t="n">
+        <v>0</v>
+      </c>
+      <c r="H213" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B214" t="n">
+        <v>256.6840530111044</v>
+      </c>
+      <c r="C214" t="n">
+        <v>258.2562853735001</v>
+      </c>
+      <c r="D214" t="n">
+        <v>254.892868775476</v>
+      </c>
+      <c r="E214" t="n">
+        <v>256.5049133300781</v>
+      </c>
+      <c r="F214" t="n">
+        <v>5272200</v>
+      </c>
+      <c r="G214" t="n">
+        <v>0</v>
+      </c>
+      <c r="H214" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B215" t="n">
+        <v>254.2759347913044</v>
+      </c>
+      <c r="C215" t="n">
+        <v>255.1317299625397</v>
+      </c>
+      <c r="D215" t="n">
+        <v>250.9025724938729</v>
+      </c>
+      <c r="E215" t="n">
+        <v>252.6041870117188</v>
+      </c>
+      <c r="F215" t="n">
+        <v>8770600</v>
+      </c>
+      <c r="G215" t="n">
+        <v>0</v>
+      </c>
+      <c r="H215" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B216" t="n">
+        <v>248.8626188136353</v>
+      </c>
+      <c r="C216" t="n">
+        <v>255.5695309055475</v>
+      </c>
+      <c r="D216" t="n">
+        <v>244.842452777813</v>
+      </c>
+      <c r="E216" t="n">
+        <v>245.8076934814453</v>
+      </c>
+      <c r="F216" t="n">
+        <v>10547300</v>
+      </c>
+      <c r="G216" t="n">
+        <v>0</v>
+      </c>
+      <c r="H216" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B217" t="n">
+        <v>247.6784538478382</v>
+      </c>
+      <c r="C217" t="n">
+        <v>252.3056419000621</v>
+      </c>
+      <c r="D217" t="n">
+        <v>245.091223119708</v>
+      </c>
+      <c r="E217" t="n">
+        <v>248.7432098388672</v>
+      </c>
+      <c r="F217" t="n">
+        <v>11097600</v>
+      </c>
+      <c r="G217" t="n">
+        <v>0</v>
+      </c>
+      <c r="H217" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B218" t="n">
+        <v>251.350352994489</v>
+      </c>
+      <c r="C218" t="n">
+        <v>254.4052935535989</v>
+      </c>
+      <c r="D218" t="n">
+        <v>250.7134945486414</v>
+      </c>
+      <c r="E218" t="n">
+        <v>251.7981414794922</v>
+      </c>
+      <c r="F218" t="n">
+        <v>10167700</v>
+      </c>
+      <c r="G218" t="n">
+        <v>0</v>
+      </c>
+      <c r="H218" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B219" t="n">
+        <v>250.7731932271148</v>
+      </c>
+      <c r="C219" t="n">
+        <v>252.9325415941838</v>
+      </c>
+      <c r="D219" t="n">
+        <v>247.4097917368304</v>
+      </c>
+      <c r="E219" t="n">
+        <v>247.5988616943359</v>
+      </c>
+      <c r="F219" t="n">
+        <v>8114700</v>
+      </c>
+      <c r="G219" t="n">
+        <v>0</v>
+      </c>
+      <c r="H219" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B220" t="n">
+        <v>246.2355858738711</v>
+      </c>
+      <c r="C220" t="n">
+        <v>250.1064943021279</v>
+      </c>
+      <c r="D220" t="n">
+        <v>244.2852134745944</v>
+      </c>
+      <c r="E220" t="n">
+        <v>249.3800811767578</v>
+      </c>
+      <c r="F220" t="n">
+        <v>7793100</v>
+      </c>
+      <c r="G220" t="n">
+        <v>0</v>
+      </c>
+      <c r="H220" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B221" t="n">
+        <v>251.5195173574522</v>
+      </c>
+      <c r="C221" t="n">
+        <v>255.0322070489389</v>
+      </c>
+      <c r="D221" t="n">
+        <v>249.9771364820368</v>
+      </c>
+      <c r="E221" t="n">
+        <v>254.3754425048828</v>
+      </c>
+      <c r="F221" t="n">
+        <v>9100200</v>
+      </c>
+      <c r="G221" t="n">
+        <v>0</v>
+      </c>
+      <c r="H221" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B222" t="n">
+        <v>253.9873531958193</v>
+      </c>
+      <c r="C222" t="n">
+        <v>258.9230174724852</v>
+      </c>
+      <c r="D222" t="n">
+        <v>253.1713702566359</v>
+      </c>
+      <c r="E222" t="n">
+        <v>257.99755859375</v>
+      </c>
+      <c r="F222" t="n">
+        <v>8063300</v>
+      </c>
+      <c r="G222" t="n">
+        <v>0</v>
+      </c>
+      <c r="H222" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B223" t="n">
+        <v>260.1469668034143</v>
+      </c>
+      <c r="C223" t="n">
+        <v>262.41577598127</v>
+      </c>
+      <c r="D223" t="n">
+        <v>258.3358915701962</v>
+      </c>
+      <c r="E223" t="n">
+        <v>262.1072998046875</v>
+      </c>
+      <c r="F223" t="n">
+        <v>6351800</v>
+      </c>
+      <c r="G223" t="n">
+        <v>0</v>
+      </c>
+      <c r="H223" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B224" t="n">
+        <v>261.2614678377304</v>
+      </c>
+      <c r="C224" t="n">
+        <v>267.4807946322661</v>
+      </c>
+      <c r="D224" t="n">
+        <v>260.0673753138636</v>
+      </c>
+      <c r="E224" t="n">
+        <v>264.6448059082031</v>
+      </c>
+      <c r="F224" t="n">
+        <v>9647900</v>
+      </c>
+      <c r="G224" t="n">
+        <v>0</v>
+      </c>
+      <c r="H224" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B225" t="n">
+        <v>268.6749001082239</v>
+      </c>
+      <c r="C225" t="n">
+        <v>273.5508459255159</v>
+      </c>
+      <c r="D225" t="n">
+        <v>264.8736405295307</v>
+      </c>
+      <c r="E225" t="n">
+        <v>265.4209594726562</v>
+      </c>
+      <c r="F225" t="n">
+        <v>10491000</v>
+      </c>
+      <c r="G225" t="n">
+        <v>0</v>
+      </c>
+      <c r="H225" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B226" t="n">
+        <v>267.1822622796963</v>
+      </c>
+      <c r="C226" t="n">
+        <v>268.0181361041443</v>
+      </c>
+      <c r="D226" t="n">
+        <v>263.4904786297666</v>
+      </c>
+      <c r="E226" t="n">
+        <v>264.2268371582031</v>
+      </c>
+      <c r="F226" t="n">
+        <v>6105600</v>
+      </c>
+      <c r="G226" t="n">
+        <v>0</v>
+      </c>
+      <c r="H226" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B227" t="n">
+        <v>257.7587518734895</v>
+      </c>
+      <c r="C227" t="n">
+        <v>259.2414296518399</v>
+      </c>
+      <c r="D227" t="n">
+        <v>253.310688170632</v>
+      </c>
+      <c r="E227" t="n">
+        <v>254.5645141601562</v>
+      </c>
+      <c r="F227" t="n">
+        <v>8216500</v>
+      </c>
+      <c r="G227" t="n">
+        <v>0</v>
+      </c>
+      <c r="H227" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B228" t="n">
+        <v>254.7535759665547</v>
+      </c>
+      <c r="C228" t="n">
+        <v>257.2114550322676</v>
+      </c>
+      <c r="D228" t="n">
+        <v>252.046908655097</v>
+      </c>
+      <c r="E228" t="n">
+        <v>255.0919036865234</v>
+      </c>
+      <c r="F228" t="n">
+        <v>6782100</v>
+      </c>
+      <c r="G228" t="n">
+        <v>0</v>
+      </c>
+      <c r="H228" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B229" t="n">
+        <v>253.7186719595458</v>
+      </c>
+      <c r="C229" t="n">
+        <v>256.4850271972422</v>
+      </c>
+      <c r="D229" t="n">
+        <v>249.6785998577546</v>
+      </c>
+      <c r="E229" t="n">
+        <v>253.1614227294922</v>
+      </c>
+      <c r="F229" t="n">
+        <v>8136300</v>
+      </c>
+      <c r="G229" t="n">
+        <v>0</v>
+      </c>
+      <c r="H229" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B230" t="n">
+        <v>253.1614264806184</v>
+      </c>
+      <c r="C230" t="n">
+        <v>254.2659795008061</v>
+      </c>
+      <c r="D230" t="n">
+        <v>249.2109089785714</v>
+      </c>
+      <c r="E230" t="n">
+        <v>253.6788635253906</v>
+      </c>
+      <c r="F230" t="n">
+        <v>7362400</v>
+      </c>
+      <c r="G230" t="n">
+        <v>0</v>
+      </c>
+      <c r="H230" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B231" t="n">
+        <v>253.9972934738065</v>
+      </c>
+      <c r="C231" t="n">
+        <v>258.0473261663437</v>
+      </c>
+      <c r="D231" t="n">
+        <v>253.2211227437212</v>
+      </c>
+      <c r="E231" t="n">
+        <v>256.3258056640625</v>
+      </c>
+      <c r="F231" t="n">
+        <v>6472600</v>
+      </c>
+      <c r="G231" t="n">
+        <v>0</v>
+      </c>
+      <c r="H231" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B232" t="n">
+        <v>260.425593365904</v>
+      </c>
+      <c r="C232" t="n">
+        <v>260.8236242062839</v>
+      </c>
+      <c r="D232" t="n">
+        <v>254.0271572625725</v>
+      </c>
+      <c r="E232" t="n">
+        <v>255.7188262939453</v>
+      </c>
+      <c r="F232" t="n">
+        <v>6931800</v>
+      </c>
+      <c r="G232" t="n">
+        <v>0</v>
+      </c>
+      <c r="H232" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B233" t="n">
+        <v>254.6341623817563</v>
+      </c>
+      <c r="C233" t="n">
+        <v>258.3259614136433</v>
+      </c>
+      <c r="D233" t="n">
+        <v>253.8679370762885</v>
+      </c>
+      <c r="E233" t="n">
+        <v>257.9677124023438</v>
+      </c>
+      <c r="F233" t="n">
+        <v>6532100</v>
+      </c>
+      <c r="G233" t="n">
+        <v>0</v>
+      </c>
+      <c r="H233" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B234" t="n">
+        <v>257.7886121067854</v>
+      </c>
+      <c r="C234" t="n">
+        <v>260.7141859356404</v>
+      </c>
+      <c r="D234" t="n">
+        <v>257.281105309594</v>
+      </c>
+      <c r="E234" t="n">
+        <v>260.5251159667969</v>
+      </c>
+      <c r="F234" t="n">
+        <v>8985100</v>
+      </c>
+      <c r="G234" t="n">
+        <v>0</v>
+      </c>
+      <c r="H234" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B235" t="n">
+        <v>259.9479684253454</v>
+      </c>
+      <c r="C235" t="n">
+        <v>262.853620890259</v>
+      </c>
+      <c r="D235" t="n">
+        <v>257.0920280597301</v>
+      </c>
+      <c r="E235" t="n">
+        <v>258.5249633789062</v>
+      </c>
+      <c r="F235" t="n">
+        <v>5945900</v>
+      </c>
+      <c r="G235" t="n">
+        <v>0</v>
+      </c>
+      <c r="H235" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B236" t="n">
+        <v>254.7436088096904</v>
+      </c>
+      <c r="C236" t="n">
+        <v>260.1270613743755</v>
+      </c>
+      <c r="D236" t="n">
+        <v>254.00723509927</v>
+      </c>
+      <c r="E236" t="n">
+        <v>259.5797424316406</v>
+      </c>
+      <c r="F236" t="n">
+        <v>4629300</v>
+      </c>
+      <c r="G236" t="n">
+        <v>0</v>
+      </c>
+      <c r="H236" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B237" t="n">
+        <v>260.4455042155265</v>
+      </c>
+      <c r="C237" t="n">
+        <v>261.3311205223152</v>
+      </c>
+      <c r="D237" t="n">
+        <v>258.3756953399613</v>
+      </c>
+      <c r="E237" t="n">
+        <v>260.7937622070312</v>
+      </c>
+      <c r="F237" t="n">
+        <v>4852700</v>
+      </c>
+      <c r="G237" t="n">
+        <v>0</v>
+      </c>
+      <c r="H237" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B238" t="n">
+        <v>259.3707811439639</v>
+      </c>
+      <c r="C238" t="n">
+        <v>260.4255764680427</v>
+      </c>
+      <c r="D238" t="n">
+        <v>257.8881034534354</v>
+      </c>
+      <c r="E238" t="n">
+        <v>259.072265625</v>
+      </c>
+      <c r="F238" t="n">
+        <v>4998100</v>
+      </c>
+      <c r="G238" t="n">
+        <v>0</v>
+      </c>
+      <c r="H238" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B239" t="n">
+        <v>257.5995438259766</v>
+      </c>
+      <c r="C239" t="n">
+        <v>262.9829969172681</v>
+      </c>
+      <c r="D239" t="n">
+        <v>256.7437790079673</v>
+      </c>
+      <c r="E239" t="n">
+        <v>261.0823669433594</v>
+      </c>
+      <c r="F239" t="n">
+        <v>5515500</v>
+      </c>
+      <c r="G239" t="n">
+        <v>0</v>
+      </c>
+      <c r="H239" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B240" t="n">
+        <v>266.3563600087168</v>
+      </c>
+      <c r="C240" t="n">
+        <v>270.3964321763198</v>
+      </c>
+      <c r="D240" t="n">
+        <v>265.0229096495755</v>
+      </c>
+      <c r="E240" t="n">
+        <v>269.7794494628906</v>
+      </c>
+      <c r="F240" t="n">
+        <v>7838200</v>
+      </c>
+      <c r="G240" t="n">
+        <v>0</v>
+      </c>
+      <c r="H240" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B241" t="n">
+        <v>271.6601848020655</v>
+      </c>
+      <c r="C241" t="n">
+        <v>275.1131561312948</v>
+      </c>
+      <c r="D241" t="n">
+        <v>269.2321572777068</v>
+      </c>
+      <c r="E241" t="n">
+        <v>272.0681762695312</v>
+      </c>
+      <c r="F241" t="n">
+        <v>7728500</v>
+      </c>
+      <c r="G241" t="n">
+        <v>0</v>
+      </c>
+      <c r="H241" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B242" t="n">
+        <v>272.0582363321417</v>
+      </c>
+      <c r="C242" t="n">
+        <v>272.0582363321417</v>
+      </c>
+      <c r="D242" t="n">
+        <v>266.0578308105469</v>
+      </c>
+      <c r="E242" t="n">
+        <v>266.0578308105469</v>
+      </c>
+      <c r="F242" t="n">
+        <v>6475900</v>
+      </c>
+      <c r="G242" t="n">
+        <v>0</v>
+      </c>
+      <c r="H242" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B243" t="n">
+        <v>266.5155507786093</v>
+      </c>
+      <c r="C243" t="n">
+        <v>271.3218634751246</v>
+      </c>
+      <c r="D243" t="n">
+        <v>265.6896375517999</v>
+      </c>
+      <c r="E243" t="n">
+        <v>268.9137268066406</v>
+      </c>
+      <c r="F243" t="n">
+        <v>6186800</v>
+      </c>
+      <c r="G243" t="n">
+        <v>0</v>
+      </c>
+      <c r="H243" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B244" t="n">
+        <v>268.4161893708204</v>
+      </c>
+      <c r="C244" t="n">
+        <v>272.635401405727</v>
+      </c>
+      <c r="D244" t="n">
+        <v>267.2519483767422</v>
+      </c>
+      <c r="E244" t="n">
+        <v>271.7000122070312</v>
+      </c>
+      <c r="F244" t="n">
+        <v>5436100</v>
+      </c>
+      <c r="G244" t="n">
+        <v>0</v>
+      </c>
+      <c r="H244" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B245" t="n">
+        <v>271</v>
+      </c>
+      <c r="C245" t="n">
+        <v>273.7999877929688</v>
+      </c>
+      <c r="D245" t="n">
+        <v>270.1799926757812</v>
+      </c>
+      <c r="E245" t="n">
+        <v>273.1400146484375</v>
+      </c>
+      <c r="F245" t="n">
+        <v>4687000</v>
+      </c>
+      <c r="G245" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="H245" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B246" t="n">
+        <v>271.9700012207031</v>
+      </c>
+      <c r="C246" t="n">
+        <v>272.9100036621094</v>
+      </c>
+      <c r="D246" t="n">
+        <v>269.5499877929688</v>
+      </c>
+      <c r="E246" t="n">
+        <v>270</v>
+      </c>
+      <c r="F246" t="n">
+        <v>7214100</v>
+      </c>
+      <c r="G246" t="n">
+        <v>0</v>
+      </c>
+      <c r="H246" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B247" t="n">
+        <v>268.4500122070312</v>
+      </c>
+      <c r="C247" t="n">
+        <v>268.4500122070312</v>
+      </c>
+      <c r="D247" t="n">
+        <v>263.8299865722656</v>
+      </c>
+      <c r="E247" t="n">
+        <v>265.7699890136719</v>
+      </c>
+      <c r="F247" t="n">
+        <v>7306200</v>
+      </c>
+      <c r="G247" t="n">
+        <v>0</v>
+      </c>
+      <c r="H247" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B248" t="n">
+        <v>265.7799987792969</v>
+      </c>
+      <c r="C248" t="n">
+        <v>268.3800048828125</v>
+      </c>
+      <c r="D248" t="n">
+        <v>264.2699890136719</v>
+      </c>
+      <c r="E248" t="n">
+        <v>268.0400085449219</v>
+      </c>
+      <c r="F248" t="n">
+        <v>5765600</v>
+      </c>
+      <c r="G248" t="n">
+        <v>0</v>
+      </c>
+      <c r="H248" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B249" t="n">
+        <v>267.1300048828125</v>
+      </c>
+      <c r="C249" t="n">
+        <v>267.7699890136719</v>
+      </c>
+      <c r="D249" t="n">
+        <v>265.1700134277344</v>
+      </c>
+      <c r="E249" t="n">
+        <v>265.8500061035156</v>
+      </c>
+      <c r="F249" t="n">
+        <v>7900100</v>
+      </c>
+      <c r="G249" t="n">
+        <v>0</v>
+      </c>
+      <c r="H249" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B250" t="n">
+        <v>270.8299865722656</v>
+      </c>
+      <c r="C250" t="n">
+        <v>271.9100036621094</v>
+      </c>
+      <c r="D250" t="n">
+        <v>267.0199890136719</v>
+      </c>
+      <c r="E250" t="n">
+        <v>271.1900024414062</v>
+      </c>
+      <c r="F250" t="n">
+        <v>6033600</v>
+      </c>
+      <c r="G250" t="n">
+        <v>0</v>
+      </c>
+      <c r="H250" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B251" t="n">
+        <v>274.739990234375</v>
+      </c>
+      <c r="C251" t="n">
+        <v>281.0700073242188</v>
+      </c>
+      <c r="D251" t="n">
+        <v>273.5299987792969</v>
+      </c>
+      <c r="E251" t="n">
+        <v>275.2099914550781</v>
+      </c>
+      <c r="F251" t="n">
+        <v>7910600</v>
+      </c>
+      <c r="G251" t="n">
+        <v>0</v>
+      </c>
+      <c r="H251" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B252" t="n">
+        <v>277.3200073242188</v>
+      </c>
+      <c r="C252" t="n">
+        <v>278.8900146484375</v>
+      </c>
+      <c r="D252" t="n">
+        <v>273.1600036621094</v>
+      </c>
+      <c r="E252" t="n">
+        <v>278.4299926757812</v>
+      </c>
+      <c r="F252" t="n">
+        <v>5940300</v>
+      </c>
+      <c r="G252" t="n">
+        <v>0</v>
+      </c>
+      <c r="H252" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="n">
         <v>46269</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B253" t="n">
         <v>275.1300048828125</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C253" t="n">
         <v>277.7999877929688</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D253" t="n">
         <v>274.75</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E253" t="n">
         <v>275.2300109863281</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F253" t="n">
         <v>4320100</v>
       </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
+      <c r="G253" t="n">
+        <v>0</v>
+      </c>
+      <c r="H253" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5148,7 +11102,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-06 22:59:39</t>
+          <t>2026-09-07 03:08:29</t>
         </is>
       </c>
     </row>

--- a/data/JNJ_data.xlsx
+++ b/data/JNJ_data.xlsx
@@ -472,16 +472,16 @@
         <v>45905</v>
       </c>
       <c r="B2" t="n">
-        <v>174.0770425638393</v>
+        <v>174.0770273418219</v>
       </c>
       <c r="C2" t="n">
-        <v>175.5537581707923</v>
+        <v>175.5537428196448</v>
       </c>
       <c r="D2" t="n">
-        <v>172.6687764611162</v>
+        <v>172.6687613622434</v>
       </c>
       <c r="E2" t="n">
-        <v>174.49755859375</v>
+        <v>174.4975433349609</v>
       </c>
       <c r="F2" t="n">
         <v>9733800</v>
@@ -498,16 +498,16 @@
         <v>45908</v>
       </c>
       <c r="B3" t="n">
-        <v>173.4511589867753</v>
+        <v>173.4511437939455</v>
       </c>
       <c r="C3" t="n">
-        <v>175.4950938415212</v>
+        <v>175.4950784696603</v>
       </c>
       <c r="D3" t="n">
-        <v>172.8057011623818</v>
+        <v>172.8056860260886</v>
       </c>
       <c r="E3" t="n">
-        <v>174.2041931152344</v>
+        <v>174.2041778564453</v>
       </c>
       <c r="F3" t="n">
         <v>8382500</v>
@@ -524,16 +524,16 @@
         <v>45909</v>
       </c>
       <c r="B4" t="n">
-        <v>174.0770398088306</v>
+        <v>174.0770551572955</v>
       </c>
       <c r="C4" t="n">
-        <v>174.165052708233</v>
+        <v>174.1650680644581</v>
       </c>
       <c r="D4" t="n">
-        <v>172.561197432737</v>
+        <v>172.5612126475493</v>
       </c>
       <c r="E4" t="n">
-        <v>173.0599670410156</v>
+        <v>173.0599822998047</v>
       </c>
       <c r="F4" t="n">
         <v>6005700</v>
@@ -576,16 +576,16 @@
         <v>45911</v>
       </c>
       <c r="B6" t="n">
-        <v>171.8766472653515</v>
+        <v>171.8766172179321</v>
       </c>
       <c r="C6" t="n">
-        <v>174.9083323610806</v>
+        <v>174.908301783663</v>
       </c>
       <c r="D6" t="n">
-        <v>171.759296719517</v>
+        <v>171.7592666926129</v>
       </c>
       <c r="E6" t="n">
-        <v>174.5660400390625</v>
+        <v>174.5660095214844</v>
       </c>
       <c r="F6" t="n">
         <v>5792500</v>
@@ -602,16 +602,16 @@
         <v>45912</v>
       </c>
       <c r="B7" t="n">
-        <v>173.7934495446803</v>
+        <v>173.7934343158836</v>
       </c>
       <c r="C7" t="n">
-        <v>174.8594234144472</v>
+        <v>174.8594080922437</v>
       </c>
       <c r="D7" t="n">
-        <v>172.8252628178507</v>
+        <v>172.8252476738922</v>
       </c>
       <c r="E7" t="n">
-        <v>174.1357269287109</v>
+        <v>174.1357116699219</v>
       </c>
       <c r="F7" t="n">
         <v>7220200</v>
@@ -628,16 +628,16 @@
         <v>45915</v>
       </c>
       <c r="B8" t="n">
-        <v>173.8423161383384</v>
+        <v>173.8423314280924</v>
       </c>
       <c r="C8" t="n">
-        <v>175.0452187336727</v>
+        <v>175.0452341292242</v>
       </c>
       <c r="D8" t="n">
-        <v>173.0306068383358</v>
+        <v>173.0306220566984</v>
       </c>
       <c r="E8" t="n">
-        <v>173.4902496337891</v>
+        <v>173.4902648925781</v>
       </c>
       <c r="F8" t="n">
         <v>4768100</v>
@@ -706,16 +706,16 @@
         <v>45918</v>
       </c>
       <c r="B11" t="n">
-        <v>172.7078974682877</v>
+        <v>172.7079129408542</v>
       </c>
       <c r="C11" t="n">
-        <v>173.1186392474049</v>
+        <v>173.118654756769</v>
       </c>
       <c r="D11" t="n">
-        <v>170.0380535202773</v>
+        <v>170.0380687536577</v>
       </c>
       <c r="E11" t="n">
-        <v>170.3216705322266</v>
+        <v>170.3216857910156</v>
       </c>
       <c r="F11" t="n">
         <v>8200900</v>
@@ -784,16 +784,16 @@
         <v>45923</v>
       </c>
       <c r="B14" t="n">
-        <v>171.0355980210813</v>
+        <v>171.0355829083302</v>
       </c>
       <c r="C14" t="n">
-        <v>173.0697586837889</v>
+        <v>173.0697433912989</v>
       </c>
       <c r="D14" t="n">
-        <v>170.9769227489119</v>
+        <v>170.9769076413454</v>
       </c>
       <c r="E14" t="n">
-        <v>172.6883544921875</v>
+        <v>172.6883392333984</v>
       </c>
       <c r="F14" t="n">
         <v>8350400</v>
@@ -810,16 +810,16 @@
         <v>45924</v>
       </c>
       <c r="B15" t="n">
-        <v>172.2580322171388</v>
+        <v>172.2580474284301</v>
       </c>
       <c r="C15" t="n">
-        <v>173.0501781580241</v>
+        <v>173.0501934392661</v>
       </c>
       <c r="D15" t="n">
-        <v>171.8668538263927</v>
+        <v>171.8668690031409</v>
       </c>
       <c r="E15" t="n">
-        <v>172.7959136962891</v>
+        <v>172.7959289550781</v>
       </c>
       <c r="F15" t="n">
         <v>6676800</v>
@@ -1018,16 +1018,16 @@
         <v>45936</v>
       </c>
       <c r="B23" t="n">
-        <v>183.8566604823808</v>
+        <v>183.8566452365672</v>
       </c>
       <c r="C23" t="n">
-        <v>185.7343437349051</v>
+        <v>185.7343283333897</v>
       </c>
       <c r="D23" t="n">
-        <v>183.2405403023728</v>
+        <v>183.2405251076493</v>
       </c>
       <c r="E23" t="n">
-        <v>184.0131378173828</v>
+        <v>184.0131225585938</v>
       </c>
       <c r="F23" t="n">
         <v>5806100</v>
@@ -1044,16 +1044,16 @@
         <v>45937</v>
       </c>
       <c r="B24" t="n">
-        <v>179.7198952882722</v>
+        <v>179.7198804430833</v>
       </c>
       <c r="C24" t="n">
-        <v>185.0595539364086</v>
+        <v>185.0595386501542</v>
       </c>
       <c r="D24" t="n">
-        <v>178.908185875973</v>
+        <v>178.9081710978327</v>
       </c>
       <c r="E24" t="n">
-        <v>184.72705078125</v>
+        <v>184.7270355224609</v>
       </c>
       <c r="F24" t="n">
         <v>8776800</v>
@@ -1070,16 +1070,16 @@
         <v>45938</v>
       </c>
       <c r="B25" t="n">
-        <v>184.7074643396089</v>
+        <v>184.707479532436</v>
       </c>
       <c r="C25" t="n">
-        <v>186.0277174802343</v>
+        <v>186.0277327816568</v>
       </c>
       <c r="D25" t="n">
-        <v>184.1206967723854</v>
+        <v>184.1207119169489</v>
       </c>
       <c r="E25" t="n">
-        <v>185.5093994140625</v>
+        <v>185.5094146728516</v>
       </c>
       <c r="F25" t="n">
         <v>5751200</v>
@@ -1148,16 +1148,16 @@
         <v>45943</v>
       </c>
       <c r="B28" t="n">
-        <v>185.646323339356</v>
+        <v>185.6463081660922</v>
       </c>
       <c r="C28" t="n">
-        <v>187.0839270863694</v>
+        <v>187.0839117956073</v>
       </c>
       <c r="D28" t="n">
-        <v>185.1084418485517</v>
+        <v>185.1084267192501</v>
       </c>
       <c r="E28" t="n">
-        <v>186.6927337646484</v>
+        <v>186.6927185058594</v>
       </c>
       <c r="F28" t="n">
         <v>7979500</v>
@@ -1226,16 +1226,16 @@
         <v>45946</v>
       </c>
       <c r="B31" t="n">
-        <v>187.1230558646578</v>
+        <v>187.1230406678187</v>
       </c>
       <c r="C31" t="n">
-        <v>188.7953757558051</v>
+        <v>188.7953604231518</v>
       </c>
       <c r="D31" t="n">
-        <v>186.2331077651437</v>
+        <v>186.2330926405801</v>
       </c>
       <c r="E31" t="n">
-        <v>187.8858642578125</v>
+        <v>187.8858489990234</v>
       </c>
       <c r="F31" t="n">
         <v>10611800</v>
@@ -1278,16 +1278,16 @@
         <v>45950</v>
       </c>
       <c r="B33" t="n">
-        <v>189.2354242017374</v>
+        <v>189.2354394431975</v>
       </c>
       <c r="C33" t="n">
-        <v>190.1938216550539</v>
+        <v>190.1938369737056</v>
       </c>
       <c r="D33" t="n">
-        <v>188.0912117995895</v>
+        <v>188.0912269488921</v>
       </c>
       <c r="E33" t="n">
-        <v>189.4505767822266</v>
+        <v>189.4505920410156</v>
       </c>
       <c r="F33" t="n">
         <v>8034700</v>
@@ -1304,16 +1304,16 @@
         <v>45951</v>
       </c>
       <c r="B34" t="n">
-        <v>188.756223952035</v>
+        <v>188.7562393006838</v>
       </c>
       <c r="C34" t="n">
-        <v>189.2843311834856</v>
+        <v>189.2843465750772</v>
       </c>
       <c r="D34" t="n">
-        <v>187.5435620120352</v>
+        <v>187.5435772620767</v>
       </c>
       <c r="E34" t="n">
-        <v>187.6511383056641</v>
+        <v>187.6511535644531</v>
       </c>
       <c r="F34" t="n">
         <v>6716000</v>
@@ -1330,16 +1330,16 @@
         <v>45952</v>
       </c>
       <c r="B35" t="n">
-        <v>187.768489042997</v>
+        <v>187.7685194118937</v>
       </c>
       <c r="C35" t="n">
-        <v>189.186529335124</v>
+        <v>189.1865599333687</v>
       </c>
       <c r="D35" t="n">
-        <v>187.553336455502</v>
+        <v>187.5533667896008</v>
       </c>
       <c r="E35" t="n">
-        <v>188.6877746582031</v>
+        <v>188.6878051757812</v>
       </c>
       <c r="F35" t="n">
         <v>6343100</v>
@@ -1356,16 +1356,16 @@
         <v>45953</v>
       </c>
       <c r="B36" t="n">
-        <v>188.3161623201141</v>
+        <v>188.3161470541903</v>
       </c>
       <c r="C36" t="n">
-        <v>189.7244285069409</v>
+        <v>189.7244131268554</v>
       </c>
       <c r="D36" t="n">
-        <v>187.3186379506951</v>
+        <v>187.318622765636</v>
       </c>
       <c r="E36" t="n">
-        <v>188.2281494140625</v>
+        <v>188.2281341552734</v>
       </c>
       <c r="F36" t="n">
         <v>8882500</v>
@@ -1382,16 +1382,16 @@
         <v>45954</v>
       </c>
       <c r="B37" t="n">
-        <v>187.9640832263789</v>
+        <v>187.9640678233363</v>
       </c>
       <c r="C37" t="n">
-        <v>188.0716595229833</v>
+        <v>188.0716441111252</v>
       </c>
       <c r="D37" t="n">
-        <v>185.2453531003753</v>
+        <v>185.2453379201237</v>
       </c>
       <c r="E37" t="n">
-        <v>186.2037506103516</v>
+        <v>186.2037353515625</v>
       </c>
       <c r="F37" t="n">
         <v>6903400</v>
@@ -1460,16 +1460,16 @@
         <v>45959</v>
       </c>
       <c r="B40" t="n">
-        <v>182.5852901845839</v>
+        <v>182.5853054515495</v>
       </c>
       <c r="C40" t="n">
-        <v>182.9764834833836</v>
+        <v>182.9764987830591</v>
       </c>
       <c r="D40" t="n">
-        <v>180.5902565894498</v>
+        <v>180.5902716895996</v>
       </c>
       <c r="E40" t="n">
-        <v>182.4875030517578</v>
+        <v>182.4875183105469</v>
       </c>
       <c r="F40" t="n">
         <v>10551100</v>
@@ -1486,16 +1486,16 @@
         <v>45960</v>
       </c>
       <c r="B41" t="n">
-        <v>182.9569302033718</v>
+        <v>182.9569151035874</v>
       </c>
       <c r="C41" t="n">
-        <v>185.2062432977132</v>
+        <v>185.2062280122887</v>
       </c>
       <c r="D41" t="n">
-        <v>182.7906786381269</v>
+        <v>182.7906635520636</v>
       </c>
       <c r="E41" t="n">
-        <v>184.8835144042969</v>
+        <v>184.8834991455078</v>
       </c>
       <c r="F41" t="n">
         <v>7072500</v>
@@ -1538,16 +1538,16 @@
         <v>45964</v>
       </c>
       <c r="B43" t="n">
-        <v>184.8346326024117</v>
+        <v>184.834617119156</v>
       </c>
       <c r="C43" t="n">
-        <v>184.8639702391834</v>
+        <v>184.8639547534701</v>
       </c>
       <c r="D43" t="n">
-        <v>181.4313324343818</v>
+        <v>181.4313172362143</v>
       </c>
       <c r="E43" t="n">
-        <v>182.1550140380859</v>
+        <v>182.1549987792969</v>
       </c>
       <c r="F43" t="n">
         <v>7542600</v>
@@ -1668,16 +1668,16 @@
         <v>45971</v>
       </c>
       <c r="B48" t="n">
-        <v>181.9007248187872</v>
+        <v>181.9007398823969</v>
       </c>
       <c r="C48" t="n">
-        <v>184.2673883725038</v>
+        <v>184.2674036321023</v>
       </c>
       <c r="D48" t="n">
-        <v>181.0401144637998</v>
+        <v>181.0401294561404</v>
       </c>
       <c r="E48" t="n">
-        <v>184.2576141357422</v>
+        <v>184.2576293945312</v>
       </c>
       <c r="F48" t="n">
         <v>5323800</v>
@@ -1720,16 +1720,16 @@
         <v>45973</v>
       </c>
       <c r="B50" t="n">
-        <v>189.0985363418636</v>
+        <v>189.0985059859865</v>
       </c>
       <c r="C50" t="n">
-        <v>191.24027328305</v>
+        <v>191.2402425833612</v>
       </c>
       <c r="D50" t="n">
-        <v>188.8149342225856</v>
+        <v>188.814903912235</v>
       </c>
       <c r="E50" t="n">
-        <v>190.1058349609375</v>
+        <v>190.1058044433594</v>
       </c>
       <c r="F50" t="n">
         <v>8803000</v>
@@ -1772,16 +1772,16 @@
         <v>45975</v>
       </c>
       <c r="B52" t="n">
-        <v>190.7023657548931</v>
+        <v>190.7023809412554</v>
       </c>
       <c r="C52" t="n">
-        <v>192.8343132451486</v>
+        <v>192.8343286012861</v>
       </c>
       <c r="D52" t="n">
-        <v>189.2843255068563</v>
+        <v>189.2843405802947</v>
       </c>
       <c r="E52" t="n">
-        <v>191.6118621826172</v>
+        <v>191.6118774414062</v>
       </c>
       <c r="F52" t="n">
         <v>8824800</v>
@@ -1902,16 +1902,16 @@
         <v>45982</v>
       </c>
       <c r="B57" t="n">
-        <v>199.4649249339953</v>
+        <v>199.4649096707152</v>
       </c>
       <c r="C57" t="n">
-        <v>202.3792444306165</v>
+        <v>202.3792289443294</v>
       </c>
       <c r="D57" t="n">
-        <v>198.5163016043988</v>
+        <v>198.5162864137085</v>
       </c>
       <c r="E57" t="n">
-        <v>199.4062347412109</v>
+        <v>199.4062194824219</v>
       </c>
       <c r="F57" t="n">
         <v>13189100</v>
@@ -1928,16 +1928,16 @@
         <v>45985</v>
       </c>
       <c r="B58" t="n">
-        <v>199.2204251313988</v>
+        <v>199.2204100458954</v>
       </c>
       <c r="C58" t="n">
-        <v>201.5772996022027</v>
+        <v>201.5772843382305</v>
       </c>
       <c r="D58" t="n">
-        <v>198.5260663138595</v>
+        <v>198.5260512809348</v>
       </c>
       <c r="E58" t="n">
-        <v>201.5088500976562</v>
+        <v>201.5088348388672</v>
       </c>
       <c r="F58" t="n">
         <v>14803900</v>
@@ -1954,16 +1954,16 @@
         <v>45986</v>
       </c>
       <c r="B59" t="n">
-        <v>201.9320337594338</v>
+        <v>201.9320489082132</v>
       </c>
       <c r="C59" t="n">
-        <v>204.4318344688182</v>
+        <v>204.4318498051307</v>
       </c>
       <c r="D59" t="n">
-        <v>201.9320337594338</v>
+        <v>201.9320489082132</v>
       </c>
       <c r="E59" t="n">
-        <v>203.3984527587891</v>
+        <v>203.3984680175781</v>
       </c>
       <c r="F59" t="n">
         <v>10275300</v>
@@ -2110,16 +2110,16 @@
         <v>45995</v>
       </c>
       <c r="B65" t="n">
-        <v>201.3513800209524</v>
+        <v>201.35139543875</v>
       </c>
       <c r="C65" t="n">
-        <v>201.6171101829578</v>
+        <v>201.6171256211029</v>
       </c>
       <c r="D65" t="n">
-        <v>198.516980022795</v>
+        <v>198.5169952235581</v>
       </c>
       <c r="E65" t="n">
-        <v>199.2747802734375</v>
+        <v>199.2747955322266</v>
       </c>
       <c r="F65" t="n">
         <v>9049900</v>
@@ -2292,16 +2292,16 @@
         <v>46006</v>
       </c>
       <c r="B72" t="n">
-        <v>207.0202168563343</v>
+        <v>207.020201869705</v>
       </c>
       <c r="C72" t="n">
-        <v>211.7835972337083</v>
+        <v>211.7835819022478</v>
       </c>
       <c r="D72" t="n">
-        <v>205.7014173161141</v>
+        <v>205.7014024249555</v>
       </c>
       <c r="E72" t="n">
-        <v>210.7797393798828</v>
+        <v>210.7797241210938</v>
       </c>
       <c r="F72" t="n">
         <v>8467000</v>
@@ -2344,16 +2344,16 @@
         <v>46008</v>
       </c>
       <c r="B74" t="n">
-        <v>206.0753964132944</v>
+        <v>206.0753812226996</v>
       </c>
       <c r="C74" t="n">
-        <v>208.1716837329721</v>
+        <v>208.171668387852</v>
       </c>
       <c r="D74" t="n">
-        <v>205.1601253407421</v>
+        <v>205.1601102176154</v>
       </c>
       <c r="E74" t="n">
-        <v>207.0005187988281</v>
+        <v>207.0005035400391</v>
       </c>
       <c r="F74" t="n">
         <v>8457600</v>
@@ -2370,16 +2370,16 @@
         <v>46009</v>
       </c>
       <c r="B75" t="n">
-        <v>206.478915988136</v>
+        <v>206.4789006202035</v>
       </c>
       <c r="C75" t="n">
-        <v>207.7189650641044</v>
+        <v>207.7189496038768</v>
       </c>
       <c r="D75" t="n">
-        <v>204.4712003216206</v>
+        <v>204.4711851031195</v>
       </c>
       <c r="E75" t="n">
-        <v>205.0124969482422</v>
+        <v>205.0124816894531</v>
       </c>
       <c r="F75" t="n">
         <v>7499900</v>
@@ -2422,16 +2422,16 @@
         <v>46013</v>
       </c>
       <c r="B77" t="n">
-        <v>202.8670125241163</v>
+        <v>202.8669973529117</v>
       </c>
       <c r="C77" t="n">
-        <v>204.7861414522214</v>
+        <v>204.7861261374966</v>
       </c>
       <c r="D77" t="n">
-        <v>202.2469804791725</v>
+        <v>202.2469653543363</v>
       </c>
       <c r="E77" t="n">
-        <v>204.0381774902344</v>
+        <v>204.0381622314453</v>
       </c>
       <c r="F77" t="n">
         <v>8187800</v>
@@ -2448,16 +2448,16 @@
         <v>46014</v>
       </c>
       <c r="B78" t="n">
-        <v>201.7745733053134</v>
+        <v>201.7745885077481</v>
       </c>
       <c r="C78" t="n">
-        <v>203.2606648620441</v>
+        <v>203.2606801764464</v>
       </c>
       <c r="D78" t="n">
-        <v>200.062111796116</v>
+        <v>200.0621268695276</v>
       </c>
       <c r="E78" t="n">
-        <v>202.5225372314453</v>
+        <v>202.5225524902344</v>
       </c>
       <c r="F78" t="n">
         <v>7047300</v>
@@ -2474,16 +2474,16 @@
         <v>46015</v>
       </c>
       <c r="B79" t="n">
-        <v>202.739053555574</v>
+        <v>202.7390686836449</v>
       </c>
       <c r="C79" t="n">
-        <v>204.648346074342</v>
+        <v>204.6483613448813</v>
       </c>
       <c r="D79" t="n">
-        <v>202.3158675938084</v>
+        <v>202.3158826903017</v>
       </c>
       <c r="E79" t="n">
-        <v>204.4908752441406</v>
+        <v>204.4908905029297</v>
       </c>
       <c r="F79" t="n">
         <v>2376500</v>
@@ -2552,16 +2552,16 @@
         <v>46021</v>
       </c>
       <c r="B82" t="n">
-        <v>204.2251519205988</v>
+        <v>204.2251366175628</v>
       </c>
       <c r="C82" t="n">
-        <v>204.4023103648072</v>
+        <v>204.4022950484963</v>
       </c>
       <c r="D82" t="n">
-        <v>203.2508330378112</v>
+        <v>203.2508178077831</v>
       </c>
       <c r="E82" t="n">
-        <v>203.6346588134766</v>
+        <v>203.6346435546875</v>
       </c>
       <c r="F82" t="n">
         <v>3937400</v>
@@ -2578,16 +2578,16 @@
         <v>46022</v>
       </c>
       <c r="B83" t="n">
-        <v>203.6346510317296</v>
+        <v>203.6346662875698</v>
       </c>
       <c r="C83" t="n">
-        <v>204.2153078209129</v>
+        <v>204.2153231202547</v>
       </c>
       <c r="D83" t="n">
-        <v>203.103190736659</v>
+        <v>203.1032059526835</v>
       </c>
       <c r="E83" t="n">
-        <v>203.6740112304688</v>
+        <v>203.6740264892578</v>
       </c>
       <c r="F83" t="n">
         <v>4083800</v>
@@ -2604,16 +2604,16 @@
         <v>46024</v>
       </c>
       <c r="B84" t="n">
-        <v>203.546094226423</v>
+        <v>203.5460790066363</v>
       </c>
       <c r="C84" t="n">
-        <v>204.1070634486917</v>
+        <v>204.1070481869595</v>
       </c>
       <c r="D84" t="n">
-        <v>200.4557852869147</v>
+        <v>200.4557702982002</v>
       </c>
       <c r="E84" t="n">
-        <v>204.0677032470703</v>
+        <v>204.0676879882812</v>
       </c>
       <c r="F84" t="n">
         <v>6325500</v>
@@ -2656,16 +2656,16 @@
         <v>46028</v>
       </c>
       <c r="B86" t="n">
-        <v>201.3612227968269</v>
+        <v>201.3612380414601</v>
       </c>
       <c r="C86" t="n">
-        <v>203.4378224562984</v>
+        <v>203.4378378581467</v>
       </c>
       <c r="D86" t="n">
-        <v>200.8888103027919</v>
+        <v>200.8888255116597</v>
       </c>
       <c r="E86" t="n">
-        <v>201.5482025146484</v>
+        <v>201.5482177734375</v>
       </c>
       <c r="F86" t="n">
         <v>8107900</v>
@@ -2734,16 +2734,16 @@
         <v>46031</v>
       </c>
       <c r="B89" t="n">
-        <v>202.6504838830927</v>
+        <v>202.6504992553581</v>
       </c>
       <c r="C89" t="n">
-        <v>203.4279717120081</v>
+        <v>203.4279871432506</v>
       </c>
       <c r="D89" t="n">
-        <v>200.7805515444468</v>
+        <v>200.7805667748665</v>
       </c>
       <c r="E89" t="n">
-        <v>201.154541015625</v>
+        <v>201.1545562744141</v>
       </c>
       <c r="F89" t="n">
         <v>6154300</v>
@@ -2760,16 +2760,16 @@
         <v>46034</v>
       </c>
       <c r="B90" t="n">
-        <v>202.2961890410606</v>
+        <v>202.2962039964493</v>
       </c>
       <c r="C90" t="n">
-        <v>206.5773204309254</v>
+        <v>206.5773357028104</v>
       </c>
       <c r="D90" t="n">
-        <v>200.6231026927027</v>
+        <v>200.6231175244031</v>
       </c>
       <c r="E90" t="n">
-        <v>206.4001770019531</v>
+        <v>206.4001922607422</v>
       </c>
       <c r="F90" t="n">
         <v>11794300</v>
@@ -2916,16 +2916,16 @@
         <v>46043</v>
       </c>
       <c r="B96" t="n">
-        <v>207.6599020836601</v>
+        <v>207.659916851811</v>
       </c>
       <c r="C96" t="n">
-        <v>215.218321643167</v>
+        <v>215.2183369488501</v>
       </c>
       <c r="D96" t="n">
-        <v>207.1678170076325</v>
+        <v>207.1678317407877</v>
       </c>
       <c r="E96" t="n">
-        <v>214.5589294433594</v>
+        <v>214.5589447021484</v>
       </c>
       <c r="F96" t="n">
         <v>14762900</v>
@@ -2942,16 +2942,16 @@
         <v>46044</v>
       </c>
       <c r="B97" t="n">
-        <v>215.3069079934484</v>
+        <v>215.3069232717918</v>
       </c>
       <c r="C97" t="n">
-        <v>218.6530804976869</v>
+        <v>218.6530960134773</v>
       </c>
       <c r="D97" t="n">
-        <v>214.6475157947938</v>
+        <v>214.6475310263463</v>
       </c>
       <c r="E97" t="n">
-        <v>215.0313415527344</v>
+        <v>215.0313568115234</v>
       </c>
       <c r="F97" t="n">
         <v>13160000</v>
@@ -2994,16 +2994,16 @@
         <v>46048</v>
       </c>
       <c r="B99" t="n">
-        <v>216.7241347564745</v>
+        <v>216.7241195858665</v>
       </c>
       <c r="C99" t="n">
-        <v>218.5153167809881</v>
+        <v>218.515301484998</v>
       </c>
       <c r="D99" t="n">
-        <v>216.5174523988691</v>
+        <v>216.5174372427288</v>
       </c>
       <c r="E99" t="n">
-        <v>217.9838714599609</v>
+        <v>217.9838562011719</v>
       </c>
       <c r="F99" t="n">
         <v>6856700</v>
@@ -3098,16 +3098,16 @@
         <v>46052</v>
       </c>
       <c r="B103" t="n">
-        <v>224.6466859457881</v>
+        <v>224.6466706191826</v>
       </c>
       <c r="C103" t="n">
-        <v>224.8828922015737</v>
+        <v>224.8828768588529</v>
       </c>
       <c r="D103" t="n">
-        <v>221.7630744488117</v>
+        <v>221.7630593189417</v>
       </c>
       <c r="E103" t="n">
-        <v>223.6526794433594</v>
+        <v>223.6526641845703</v>
       </c>
       <c r="F103" t="n">
         <v>11045500</v>
@@ -3124,16 +3124,16 @@
         <v>46055</v>
       </c>
       <c r="B104" t="n">
-        <v>224.7057483906486</v>
+        <v>224.7057634887497</v>
       </c>
       <c r="C104" t="n">
-        <v>227.530312073188</v>
+        <v>227.530327361073</v>
       </c>
       <c r="D104" t="n">
-        <v>223.6526790631295</v>
+        <v>223.6526940904743</v>
       </c>
       <c r="E104" t="n">
-        <v>227.0972747802734</v>
+        <v>227.0972900390625</v>
       </c>
       <c r="F104" t="n">
         <v>8187500</v>
@@ -3176,16 +3176,16 @@
         <v>46057</v>
       </c>
       <c r="B106" t="n">
-        <v>231.2800013484118</v>
+        <v>231.2799860551316</v>
       </c>
       <c r="C106" t="n">
-        <v>232.0968644318395</v>
+        <v>232.0968490845446</v>
       </c>
       <c r="D106" t="n">
-        <v>229.2526131010531</v>
+        <v>229.252597941833</v>
       </c>
       <c r="E106" t="n">
-        <v>230.7583923339844</v>
+        <v>230.7583770751953</v>
       </c>
       <c r="F106" t="n">
         <v>8641400</v>
@@ -3254,16 +3254,16 @@
         <v>46062</v>
       </c>
       <c r="B109" t="n">
-        <v>236.4468956382332</v>
+        <v>236.4468802764997</v>
       </c>
       <c r="C109" t="n">
-        <v>236.9291444528193</v>
+        <v>236.9291290597546</v>
       </c>
       <c r="D109" t="n">
-        <v>233.2877026206608</v>
+        <v>233.2876874641771</v>
       </c>
       <c r="E109" t="n">
-        <v>234.8623809814453</v>
+        <v>234.8623657226562</v>
       </c>
       <c r="F109" t="n">
         <v>9378500</v>
@@ -3332,16 +3332,16 @@
         <v>46065</v>
       </c>
       <c r="B112" t="n">
-        <v>236.6732529591429</v>
+        <v>236.6732379543034</v>
       </c>
       <c r="C112" t="n">
-        <v>242.4503424271597</v>
+        <v>242.4503270560588</v>
       </c>
       <c r="D112" t="n">
-        <v>235.8859137708501</v>
+        <v>235.8858988159272</v>
       </c>
       <c r="E112" t="n">
-        <v>240.6788330078125</v>
+        <v>240.6788177490234</v>
       </c>
       <c r="F112" t="n">
         <v>10254300</v>
@@ -3358,16 +3358,16 @@
         <v>46066</v>
       </c>
       <c r="B113" t="n">
-        <v>240.7181753030812</v>
+        <v>240.7181906333224</v>
       </c>
       <c r="C113" t="n">
-        <v>241.0724771605951</v>
+        <v>241.0724925134001</v>
       </c>
       <c r="D113" t="n">
-        <v>238.7695225953774</v>
+        <v>238.7695378015177</v>
       </c>
       <c r="E113" t="n">
-        <v>239.5962219238281</v>
+        <v>239.5962371826172</v>
       </c>
       <c r="F113" t="n">
         <v>13268500</v>
@@ -3488,16 +3488,16 @@
         <v>46076</v>
       </c>
       <c r="B118" t="n">
-        <v>239.7733870753068</v>
+        <v>239.7734021969262</v>
       </c>
       <c r="C118" t="n">
-        <v>242.9030410566114</v>
+        <v>242.9030563756065</v>
       </c>
       <c r="D118" t="n">
-        <v>238.7596929857211</v>
+        <v>238.7597080434106</v>
       </c>
       <c r="E118" t="n">
-        <v>241.9483947753906</v>
+        <v>241.9484100341797</v>
       </c>
       <c r="F118" t="n">
         <v>9622700</v>
@@ -3514,16 +3514,16 @@
         <v>46077</v>
       </c>
       <c r="B119" t="n">
-        <v>242.7498156695138</v>
+        <v>242.7498308706833</v>
       </c>
       <c r="C119" t="n">
-        <v>244.6296736547229</v>
+        <v>244.6296889736104</v>
       </c>
       <c r="D119" t="n">
-        <v>241.9483872724562</v>
+        <v>241.9484024234396</v>
       </c>
       <c r="E119" t="n">
-        <v>243.6699523925781</v>
+        <v>243.6699676513672</v>
       </c>
       <c r="F119" t="n">
         <v>7246300</v>
@@ -3540,16 +3540,16 @@
         <v>46078</v>
       </c>
       <c r="B120" t="n">
-        <v>242.2650040664713</v>
+        <v>242.2650193059668</v>
       </c>
       <c r="C120" t="n">
-        <v>244.629674532896</v>
+        <v>244.6296899211394</v>
       </c>
       <c r="D120" t="n">
-        <v>241.1370862518812</v>
+        <v>241.1371014204259</v>
       </c>
       <c r="E120" t="n">
-        <v>242.5717163085938</v>
+        <v>242.5717315673828</v>
       </c>
       <c r="F120" t="n">
         <v>7698200</v>
@@ -3566,16 +3566,16 @@
         <v>46079</v>
       </c>
       <c r="B121" t="n">
-        <v>242.5123588943122</v>
+        <v>242.5123742558835</v>
       </c>
       <c r="C121" t="n">
-        <v>242.8685442682355</v>
+        <v>242.8685596523689</v>
       </c>
       <c r="D121" t="n">
-        <v>239.4551099080992</v>
+        <v>239.4551250760139</v>
       </c>
       <c r="E121" t="n">
-        <v>240.8897399902344</v>
+        <v>240.8897552490234</v>
       </c>
       <c r="F121" t="n">
         <v>7172600</v>
@@ -3670,16 +3670,16 @@
         <v>46085</v>
       </c>
       <c r="B125" t="n">
-        <v>243.145575843863</v>
+        <v>243.1455911306439</v>
       </c>
       <c r="C125" t="n">
-        <v>243.9568928450567</v>
+        <v>243.9569081828458</v>
       </c>
       <c r="D125" t="n">
-        <v>240.6028050981046</v>
+        <v>240.6028202250193</v>
       </c>
       <c r="E125" t="n">
-        <v>242.7003479003906</v>
+        <v>242.7003631591797</v>
       </c>
       <c r="F125" t="n">
         <v>5768000</v>
@@ -3696,16 +3696,16 @@
         <v>46086</v>
       </c>
       <c r="B126" t="n">
-        <v>240.0586452528019</v>
+        <v>240.0586607026203</v>
       </c>
       <c r="C126" t="n">
-        <v>240.424719212307</v>
+        <v>240.4247346856854</v>
       </c>
       <c r="D126" t="n">
-        <v>233.4296388594088</v>
+        <v>233.4296538825942</v>
       </c>
       <c r="E126" t="n">
-        <v>237.0904388427734</v>
+        <v>237.0904541015625</v>
       </c>
       <c r="F126" t="n">
         <v>9375400</v>
@@ -3722,16 +3722,16 @@
         <v>46087</v>
       </c>
       <c r="B127" t="n">
-        <v>235.596428770922</v>
+        <v>235.5964438849938</v>
       </c>
       <c r="C127" t="n">
-        <v>238.2381306285037</v>
+        <v>238.238145912047</v>
       </c>
       <c r="D127" t="n">
-        <v>232.9349346436922</v>
+        <v>232.9349495870229</v>
       </c>
       <c r="E127" t="n">
-        <v>237.8522644042969</v>
+        <v>237.8522796630859</v>
       </c>
       <c r="F127" t="n">
         <v>7179800</v>
@@ -3748,16 +3748,16 @@
         <v>46090</v>
       </c>
       <c r="B128" t="n">
-        <v>238.3173005129137</v>
+        <v>238.3172853623119</v>
       </c>
       <c r="C128" t="n">
-        <v>241.5031767703235</v>
+        <v>241.5031614171852</v>
       </c>
       <c r="D128" t="n">
-        <v>237.4960948841201</v>
+        <v>237.496079785725</v>
       </c>
       <c r="E128" t="n">
-        <v>240.0190734863281</v>
+        <v>240.0190582275391</v>
       </c>
       <c r="F128" t="n">
         <v>7844000</v>
@@ -3826,16 +3826,16 @@
         <v>46093</v>
       </c>
       <c r="B131" t="n">
-        <v>238.9010593075404</v>
+        <v>238.9010440853151</v>
       </c>
       <c r="C131" t="n">
-        <v>241.8098890629796</v>
+        <v>241.8098736554103</v>
       </c>
       <c r="D131" t="n">
-        <v>237.7533491444783</v>
+        <v>237.7533339953824</v>
       </c>
       <c r="E131" t="n">
-        <v>239.4748992919922</v>
+        <v>239.4748840332031</v>
       </c>
       <c r="F131" t="n">
         <v>7710200</v>
@@ -3852,16 +3852,16 @@
         <v>46094</v>
       </c>
       <c r="B132" t="n">
-        <v>241.6219129804633</v>
+        <v>241.6218975517249</v>
       </c>
       <c r="C132" t="n">
-        <v>242.9872777226232</v>
+        <v>242.9872622066995</v>
       </c>
       <c r="D132" t="n">
-        <v>238.940626430393</v>
+        <v>238.9406111728678</v>
       </c>
       <c r="E132" t="n">
-        <v>238.9604187011719</v>
+        <v>238.9604034423828</v>
       </c>
       <c r="F132" t="n">
         <v>6415300</v>
@@ -3878,16 +3878,16 @@
         <v>46097</v>
       </c>
       <c r="B133" t="n">
-        <v>241.3349760333344</v>
+        <v>241.3349607287423</v>
       </c>
       <c r="C133" t="n">
-        <v>242.4628939057684</v>
+        <v>242.4628785296478</v>
       </c>
       <c r="D133" t="n">
-        <v>239.1088211458664</v>
+        <v>239.1088059824489</v>
       </c>
       <c r="E133" t="n">
-        <v>240.6127166748047</v>
+        <v>240.6127014160156</v>
       </c>
       <c r="F133" t="n">
         <v>7571500</v>
@@ -3930,16 +3930,16 @@
         <v>46099</v>
       </c>
       <c r="B135" t="n">
-        <v>235.349094010365</v>
+        <v>235.349078713635</v>
       </c>
       <c r="C135" t="n">
-        <v>236.5759581604242</v>
+        <v>236.5759427839531</v>
       </c>
       <c r="D135" t="n">
-        <v>232.9250616652477</v>
+        <v>232.9250465260699</v>
       </c>
       <c r="E135" t="n">
-        <v>234.7653503417969</v>
+        <v>234.7653350830078</v>
       </c>
       <c r="F135" t="n">
         <v>6811500</v>
@@ -4242,16 +4242,16 @@
         <v>46118</v>
       </c>
       <c r="B147" t="n">
-        <v>240.0784329225297</v>
+        <v>240.0784175573595</v>
       </c>
       <c r="C147" t="n">
-        <v>240.9392230850874</v>
+        <v>240.9392076648261</v>
       </c>
       <c r="D147" t="n">
-        <v>237.9512242744999</v>
+        <v>237.9512090454724</v>
       </c>
       <c r="E147" t="n">
-        <v>238.4162445068359</v>
+        <v>238.4162292480469</v>
       </c>
       <c r="F147" t="n">
         <v>4442400</v>
@@ -4450,16 +4450,16 @@
         <v>46128</v>
       </c>
       <c r="B155" t="n">
-        <v>234.9038500080299</v>
+        <v>234.9038654541874</v>
       </c>
       <c r="C155" t="n">
-        <v>235.6162207436799</v>
+        <v>235.6162362366795</v>
       </c>
       <c r="D155" t="n">
-        <v>229.6600157416919</v>
+        <v>229.6600308430398</v>
       </c>
       <c r="E155" t="n">
-        <v>232.0543670654297</v>
+        <v>232.0543823242188</v>
       </c>
       <c r="F155" t="n">
         <v>8668900</v>
@@ -4528,16 +4528,16 @@
         <v>46133</v>
       </c>
       <c r="B158" t="n">
-        <v>226.9193941968888</v>
+        <v>226.9193787228735</v>
       </c>
       <c r="C158" t="n">
-        <v>227.2557873120845</v>
+        <v>227.2557718151299</v>
       </c>
       <c r="D158" t="n">
-        <v>222.3186650386415</v>
+        <v>222.3186498783577</v>
       </c>
       <c r="E158" t="n">
-        <v>223.7631988525391</v>
+        <v>223.76318359375</v>
       </c>
       <c r="F158" t="n">
         <v>11681200</v>
@@ -4580,16 +4580,16 @@
         <v>46135</v>
       </c>
       <c r="B160" t="n">
-        <v>224.8416356959219</v>
+        <v>224.8416507297823</v>
       </c>
       <c r="C160" t="n">
-        <v>228.9377599403605</v>
+        <v>228.937775248105</v>
       </c>
       <c r="D160" t="n">
-        <v>224.6239660179549</v>
+        <v>224.623981037261</v>
       </c>
       <c r="E160" t="n">
-        <v>228.2055969238281</v>
+        <v>228.2056121826172</v>
       </c>
       <c r="F160" t="n">
         <v>7097600</v>
@@ -4606,16 +4606,16 @@
         <v>46136</v>
       </c>
       <c r="B161" t="n">
-        <v>226.6027887018479</v>
+        <v>226.6027733404394</v>
       </c>
       <c r="C161" t="n">
-        <v>227.5526214735122</v>
+        <v>227.5526060477145</v>
       </c>
       <c r="D161" t="n">
-        <v>224.6140956793093</v>
+        <v>224.6140804527143</v>
       </c>
       <c r="E161" t="n">
-        <v>225.0890045166016</v>
+        <v>225.0889892578125</v>
       </c>
       <c r="F161" t="n">
         <v>6067500</v>
@@ -4632,16 +4632,16 @@
         <v>46139</v>
       </c>
       <c r="B162" t="n">
-        <v>223.3773245484034</v>
+        <v>223.3773398363102</v>
       </c>
       <c r="C162" t="n">
-        <v>225.4946445162854</v>
+        <v>225.4946599491012</v>
       </c>
       <c r="D162" t="n">
-        <v>221.9723753264516</v>
+        <v>221.972390518204</v>
       </c>
       <c r="E162" t="n">
-        <v>222.9518737792969</v>
+        <v>222.9518890380859</v>
       </c>
       <c r="F162" t="n">
         <v>7897800</v>
@@ -4684,16 +4684,16 @@
         <v>46141</v>
       </c>
       <c r="B164" t="n">
-        <v>223.1299896858621</v>
+        <v>223.1299745498951</v>
       </c>
       <c r="C164" t="n">
-        <v>226.2861851379911</v>
+        <v>226.2861697879244</v>
       </c>
       <c r="D164" t="n">
-        <v>222.4769806067155</v>
+        <v>222.4769655150452</v>
       </c>
       <c r="E164" t="n">
-        <v>224.9405975341797</v>
+        <v>224.9405822753906</v>
       </c>
       <c r="F164" t="n">
         <v>7071100</v>
@@ -4840,16 +4840,16 @@
         <v>46149</v>
       </c>
       <c r="B170" t="n">
-        <v>222.3978024591847</v>
+        <v>222.397817873641</v>
       </c>
       <c r="C170" t="n">
-        <v>222.3978024591847</v>
+        <v>222.397817873641</v>
       </c>
       <c r="D170" t="n">
-        <v>218.2917897898664</v>
+        <v>218.2918049197337</v>
       </c>
       <c r="E170" t="n">
-        <v>220.15185546875</v>
+        <v>220.1518707275391</v>
       </c>
       <c r="F170" t="n">
         <v>7269700</v>
@@ -4918,16 +4918,16 @@
         <v>46154</v>
       </c>
       <c r="B173" t="n">
-        <v>220.6366899653626</v>
+        <v>220.6366747923043</v>
       </c>
       <c r="C173" t="n">
-        <v>225.2374041432973</v>
+        <v>225.2373886538506</v>
       </c>
       <c r="D173" t="n">
-        <v>219.3009909603728</v>
+        <v>219.3009758791698</v>
       </c>
       <c r="E173" t="n">
-        <v>221.8833312988281</v>
+        <v>221.8833160400391</v>
       </c>
       <c r="F173" t="n">
         <v>8632500</v>
@@ -4970,16 +4970,16 @@
         <v>46156</v>
       </c>
       <c r="B175" t="n">
-        <v>228.5518965755589</v>
+        <v>228.5519118475702</v>
       </c>
       <c r="C175" t="n">
-        <v>229.3038367743656</v>
+        <v>229.3038520966222</v>
       </c>
       <c r="D175" t="n">
-        <v>226.7314002434507</v>
+        <v>226.7314153938151</v>
       </c>
       <c r="E175" t="n">
-        <v>228.3540191650391</v>
+        <v>228.3540344238281</v>
       </c>
       <c r="F175" t="n">
         <v>6974400</v>
@@ -11102,7 +11102,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-07 03:08:29</t>
+          <t>2026-09-08 08:52:20</t>
         </is>
       </c>
     </row>

--- a/data/JNJ_data.xlsx
+++ b/data/JNJ_data.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H253"/>
+  <dimension ref="A1:H252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45905</v>
+        <v>45909</v>
       </c>
       <c r="B2" t="n">
-        <v>174.0770273418219</v>
+        <v>174.0770398088306</v>
       </c>
       <c r="C2" t="n">
-        <v>175.5537428196448</v>
+        <v>174.165052708233</v>
       </c>
       <c r="D2" t="n">
-        <v>172.6687613622434</v>
+        <v>172.561197432737</v>
       </c>
       <c r="E2" t="n">
-        <v>174.4975433349609</v>
+        <v>173.0599670410156</v>
       </c>
       <c r="F2" t="n">
-        <v>9733800</v>
+        <v>6005700</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45908</v>
+        <v>45910</v>
       </c>
       <c r="B3" t="n">
-        <v>173.4511437939455</v>
+        <v>172.4145258819289</v>
       </c>
       <c r="C3" t="n">
-        <v>175.4950784696603</v>
+        <v>172.7176914018626</v>
       </c>
       <c r="D3" t="n">
-        <v>172.8056860260886</v>
+        <v>170.4879415338014</v>
       </c>
       <c r="E3" t="n">
-        <v>174.2041778564453</v>
+        <v>171.9157562255859</v>
       </c>
       <c r="F3" t="n">
-        <v>8382500</v>
+        <v>6891600</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45909</v>
+        <v>45911</v>
       </c>
       <c r="B4" t="n">
-        <v>174.0770551572955</v>
+        <v>171.8766322416418</v>
       </c>
       <c r="C4" t="n">
-        <v>174.1650680644581</v>
+        <v>174.9083170723718</v>
       </c>
       <c r="D4" t="n">
-        <v>172.5612126475493</v>
+        <v>171.7592817060649</v>
       </c>
       <c r="E4" t="n">
-        <v>173.0599822998047</v>
+        <v>174.5660247802734</v>
       </c>
       <c r="F4" t="n">
-        <v>6005700</v>
+        <v>5792500</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45910</v>
+        <v>45912</v>
       </c>
       <c r="B5" t="n">
-        <v>172.4145258819289</v>
+        <v>173.7934343158836</v>
       </c>
       <c r="C5" t="n">
-        <v>172.7176914018626</v>
+        <v>174.8594080922437</v>
       </c>
       <c r="D5" t="n">
-        <v>170.4879415338014</v>
+        <v>172.8252476738922</v>
       </c>
       <c r="E5" t="n">
-        <v>171.9157562255859</v>
+        <v>174.1357116699219</v>
       </c>
       <c r="F5" t="n">
-        <v>6891600</v>
+        <v>7220200</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45911</v>
+        <v>45915</v>
       </c>
       <c r="B6" t="n">
-        <v>171.8766172179321</v>
+        <v>173.8423161383384</v>
       </c>
       <c r="C6" t="n">
-        <v>174.908301783663</v>
+        <v>175.0452187336727</v>
       </c>
       <c r="D6" t="n">
-        <v>171.7592666926129</v>
+        <v>173.0306068383358</v>
       </c>
       <c r="E6" t="n">
-        <v>174.5660095214844</v>
+        <v>173.4902496337891</v>
       </c>
       <c r="F6" t="n">
-        <v>5792500</v>
+        <v>4768100</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45912</v>
+        <v>45916</v>
       </c>
       <c r="B7" t="n">
-        <v>173.7934343158836</v>
+        <v>173.6565364179341</v>
       </c>
       <c r="C7" t="n">
-        <v>174.8594080922437</v>
+        <v>173.7054225283811</v>
       </c>
       <c r="D7" t="n">
-        <v>172.8252476738922</v>
+        <v>171.7788382257642</v>
       </c>
       <c r="E7" t="n">
-        <v>174.1357116699219</v>
+        <v>172.5709991455078</v>
       </c>
       <c r="F7" t="n">
-        <v>7220200</v>
+        <v>7959300</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45915</v>
+        <v>45917</v>
       </c>
       <c r="B8" t="n">
-        <v>173.8423314280924</v>
+        <v>172.8154712016315</v>
       </c>
       <c r="C8" t="n">
-        <v>175.0452341292242</v>
+        <v>174.5757888224823</v>
       </c>
       <c r="D8" t="n">
-        <v>173.0306220566984</v>
+        <v>172.6981057504092</v>
       </c>
       <c r="E8" t="n">
-        <v>173.4902648925781</v>
+        <v>173.2946624755859</v>
       </c>
       <c r="F8" t="n">
-        <v>4768100</v>
+        <v>6714900</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45916</v>
+        <v>45918</v>
       </c>
       <c r="B9" t="n">
-        <v>173.6565364179341</v>
+        <v>172.7079129408542</v>
       </c>
       <c r="C9" t="n">
-        <v>173.7054225283811</v>
+        <v>173.118654756769</v>
       </c>
       <c r="D9" t="n">
-        <v>171.7788382257642</v>
+        <v>170.0380687536577</v>
       </c>
       <c r="E9" t="n">
-        <v>172.5709991455078</v>
+        <v>170.3216857910156</v>
       </c>
       <c r="F9" t="n">
-        <v>7959300</v>
+        <v>8200900</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45917</v>
+        <v>45919</v>
       </c>
       <c r="B10" t="n">
-        <v>172.8154864182272</v>
+        <v>170.8400043448543</v>
       </c>
       <c r="C10" t="n">
-        <v>174.5758041940759</v>
+        <v>173.2555691360807</v>
       </c>
       <c r="D10" t="n">
-        <v>172.6981209566707</v>
+        <v>169.5099768279138</v>
       </c>
       <c r="E10" t="n">
-        <v>173.294677734375</v>
+        <v>172.3069458007812</v>
       </c>
       <c r="F10" t="n">
-        <v>6714900</v>
+        <v>25621000</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45918</v>
+        <v>45922</v>
       </c>
       <c r="B11" t="n">
-        <v>172.7079129408542</v>
+        <v>172.2091312958323</v>
       </c>
       <c r="C11" t="n">
-        <v>173.118654756769</v>
+        <v>172.7470127753203</v>
       </c>
       <c r="D11" t="n">
-        <v>170.0380687536577</v>
+        <v>170.2825471290745</v>
       </c>
       <c r="E11" t="n">
-        <v>170.3216857910156</v>
+        <v>170.3705749511719</v>
       </c>
       <c r="F11" t="n">
-        <v>8200900</v>
+        <v>7193900</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45919</v>
+        <v>45923</v>
       </c>
       <c r="B12" t="n">
-        <v>170.8400043448543</v>
+        <v>171.0355829083302</v>
       </c>
       <c r="C12" t="n">
-        <v>173.2555691360807</v>
+        <v>173.0697433912989</v>
       </c>
       <c r="D12" t="n">
-        <v>169.5099768279138</v>
+        <v>170.9769076413454</v>
       </c>
       <c r="E12" t="n">
-        <v>172.3069458007812</v>
+        <v>172.6883392333984</v>
       </c>
       <c r="F12" t="n">
-        <v>25621000</v>
+        <v>8350400</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45922</v>
+        <v>45924</v>
       </c>
       <c r="B13" t="n">
-        <v>172.2091312958323</v>
+        <v>172.2580322171388</v>
       </c>
       <c r="C13" t="n">
-        <v>172.7470127753203</v>
+        <v>173.0501781580241</v>
       </c>
       <c r="D13" t="n">
-        <v>170.2825471290745</v>
+        <v>171.8668538263927</v>
       </c>
       <c r="E13" t="n">
-        <v>170.3705749511719</v>
+        <v>172.7959136962891</v>
       </c>
       <c r="F13" t="n">
-        <v>7193900</v>
+        <v>6676800</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45923</v>
+        <v>45925</v>
       </c>
       <c r="B14" t="n">
-        <v>171.0355829083302</v>
+        <v>173.2946854062595</v>
       </c>
       <c r="C14" t="n">
-        <v>173.0697433912989</v>
+        <v>174.4682356162792</v>
       </c>
       <c r="D14" t="n">
-        <v>170.9769076413454</v>
+        <v>172.0331222880509</v>
       </c>
       <c r="E14" t="n">
-        <v>172.6883392333984</v>
+        <v>173.8130035400391</v>
       </c>
       <c r="F14" t="n">
-        <v>8350400</v>
+        <v>8475000</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45924</v>
+        <v>45926</v>
       </c>
       <c r="B15" t="n">
-        <v>172.2580474284301</v>
+        <v>174.6638219397404</v>
       </c>
       <c r="C15" t="n">
-        <v>173.0501934392661</v>
+        <v>175.9449483254981</v>
       </c>
       <c r="D15" t="n">
-        <v>171.8668690031409</v>
+        <v>173.4120331870535</v>
       </c>
       <c r="E15" t="n">
-        <v>172.7959289550781</v>
+        <v>175.7493591308594</v>
       </c>
       <c r="F15" t="n">
-        <v>6676800</v>
+        <v>8634400</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45925</v>
+        <v>45929</v>
       </c>
       <c r="B16" t="n">
-        <v>173.2946701929729</v>
+        <v>175.8667202511636</v>
       </c>
       <c r="C16" t="n">
-        <v>174.4682202999683</v>
+        <v>177.861754032588</v>
       </c>
       <c r="D16" t="n">
-        <v>172.0331071855151</v>
+        <v>175.8373826163265</v>
       </c>
       <c r="E16" t="n">
-        <v>173.81298828125</v>
+        <v>177.6172637939453</v>
       </c>
       <c r="F16" t="n">
-        <v>8475000</v>
+        <v>8597100</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45926</v>
+        <v>45930</v>
       </c>
       <c r="B17" t="n">
-        <v>174.6638219397404</v>
+        <v>177.6954955492426</v>
       </c>
       <c r="C17" t="n">
-        <v>175.9449483254981</v>
+        <v>181.8909562377616</v>
       </c>
       <c r="D17" t="n">
-        <v>173.4120331870535</v>
+        <v>177.0793903191274</v>
       </c>
       <c r="E17" t="n">
-        <v>175.7493591308594</v>
+        <v>181.3335113525391</v>
       </c>
       <c r="F17" t="n">
-        <v>8634400</v>
+        <v>11569000</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45929</v>
+        <v>45931</v>
       </c>
       <c r="B18" t="n">
-        <v>175.8667202511636</v>
+        <v>181.9007449618727</v>
       </c>
       <c r="C18" t="n">
-        <v>177.861754032588</v>
+        <v>182.4484007311471</v>
       </c>
       <c r="D18" t="n">
-        <v>175.8373826163265</v>
+        <v>179.8568100649378</v>
       </c>
       <c r="E18" t="n">
-        <v>177.6172637939453</v>
+        <v>181.9496459960938</v>
       </c>
       <c r="F18" t="n">
-        <v>8597100</v>
+        <v>13063800</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45930</v>
+        <v>45932</v>
       </c>
       <c r="B19" t="n">
-        <v>177.6954955492426</v>
+        <v>180.1306362123439</v>
       </c>
       <c r="C19" t="n">
-        <v>181.8909562377616</v>
+        <v>182.4777366073124</v>
       </c>
       <c r="D19" t="n">
-        <v>177.0793903191274</v>
+        <v>180.032834144845</v>
       </c>
       <c r="E19" t="n">
-        <v>181.3335113525391</v>
+        <v>181.8811798095703</v>
       </c>
       <c r="F19" t="n">
-        <v>11569000</v>
+        <v>7728100</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45931</v>
+        <v>45933</v>
       </c>
       <c r="B20" t="n">
-        <v>181.9007297071846</v>
+        <v>182.9373639295453</v>
       </c>
       <c r="C20" t="n">
-        <v>182.4483854305311</v>
+        <v>185.5974187766257</v>
       </c>
       <c r="D20" t="n">
-        <v>179.8567949816596</v>
+        <v>182.7906757632537</v>
       </c>
       <c r="E20" t="n">
-        <v>181.9496307373047</v>
+        <v>184.4825439453125</v>
       </c>
       <c r="F20" t="n">
-        <v>13063800</v>
+        <v>8675100</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45932</v>
+        <v>45936</v>
       </c>
       <c r="B21" t="n">
-        <v>180.1306362123439</v>
+        <v>183.8566452365672</v>
       </c>
       <c r="C21" t="n">
-        <v>182.4777366073124</v>
+        <v>185.7343283333897</v>
       </c>
       <c r="D21" t="n">
-        <v>180.032834144845</v>
+        <v>183.2405251076493</v>
       </c>
       <c r="E21" t="n">
-        <v>181.8811798095703</v>
+        <v>184.0131225585938</v>
       </c>
       <c r="F21" t="n">
-        <v>7728100</v>
+        <v>5806100</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45933</v>
+        <v>45937</v>
       </c>
       <c r="B22" t="n">
-        <v>182.9373639295453</v>
+        <v>179.7198804430833</v>
       </c>
       <c r="C22" t="n">
-        <v>185.5974187766257</v>
+        <v>185.0595386501542</v>
       </c>
       <c r="D22" t="n">
-        <v>182.7906757632537</v>
+        <v>178.9081710978327</v>
       </c>
       <c r="E22" t="n">
-        <v>184.4825439453125</v>
+        <v>184.7270355224609</v>
       </c>
       <c r="F22" t="n">
-        <v>8675100</v>
+        <v>8776800</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45936</v>
+        <v>45938</v>
       </c>
       <c r="B23" t="n">
-        <v>183.8566452365672</v>
+        <v>184.7074643396089</v>
       </c>
       <c r="C23" t="n">
-        <v>185.7343283333897</v>
+        <v>186.0277174802343</v>
       </c>
       <c r="D23" t="n">
-        <v>183.2405251076493</v>
+        <v>184.1206967723854</v>
       </c>
       <c r="E23" t="n">
-        <v>184.0131225585938</v>
+        <v>185.5093994140625</v>
       </c>
       <c r="F23" t="n">
-        <v>5806100</v>
+        <v>5751200</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45937</v>
+        <v>45939</v>
       </c>
       <c r="B24" t="n">
-        <v>179.7198804430833</v>
+        <v>185.8125748295944</v>
       </c>
       <c r="C24" t="n">
-        <v>185.0595386501542</v>
+        <v>187.8662987309212</v>
       </c>
       <c r="D24" t="n">
-        <v>178.9081710978327</v>
+        <v>185.5485212028525</v>
       </c>
       <c r="E24" t="n">
-        <v>184.7270355224609</v>
+        <v>186.8687744140625</v>
       </c>
       <c r="F24" t="n">
-        <v>8776800</v>
+        <v>7484800</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45938</v>
+        <v>45940</v>
       </c>
       <c r="B25" t="n">
-        <v>184.707479532436</v>
+        <v>187.7782713984262</v>
       </c>
       <c r="C25" t="n">
-        <v>186.0277327816568</v>
+        <v>187.8369615886886</v>
       </c>
       <c r="D25" t="n">
-        <v>184.1207119169489</v>
+        <v>185.6658871464611</v>
       </c>
       <c r="E25" t="n">
-        <v>185.5094146728516</v>
+        <v>186.5167083740234</v>
       </c>
       <c r="F25" t="n">
-        <v>5751200</v>
+        <v>9598000</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45939</v>
+        <v>45943</v>
       </c>
       <c r="B26" t="n">
-        <v>185.8125748295944</v>
+        <v>185.646323339356</v>
       </c>
       <c r="C26" t="n">
-        <v>187.8662987309212</v>
+        <v>187.0839270863694</v>
       </c>
       <c r="D26" t="n">
-        <v>185.5485212028525</v>
+        <v>185.1084418485517</v>
       </c>
       <c r="E26" t="n">
-        <v>186.8687744140625</v>
+        <v>186.6927337646484</v>
       </c>
       <c r="F26" t="n">
-        <v>7484800</v>
+        <v>7979500</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45940</v>
+        <v>45944</v>
       </c>
       <c r="B27" t="n">
-        <v>187.7782713984262</v>
+        <v>188.6682313415227</v>
       </c>
       <c r="C27" t="n">
-        <v>187.8369615886886</v>
+        <v>190.1156094203016</v>
       </c>
       <c r="D27" t="n">
-        <v>185.6658871464611</v>
+        <v>181.7833925764523</v>
       </c>
       <c r="E27" t="n">
-        <v>186.5167083740234</v>
+        <v>186.6438598632812</v>
       </c>
       <c r="F27" t="n">
-        <v>9598000</v>
+        <v>13613300</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45943</v>
+        <v>45945</v>
       </c>
       <c r="B28" t="n">
-        <v>185.6463081660922</v>
+        <v>187.2599526066892</v>
       </c>
       <c r="C28" t="n">
-        <v>187.0839117956073</v>
+        <v>189.303902268661</v>
       </c>
       <c r="D28" t="n">
-        <v>185.1084267192501</v>
+        <v>185.1280049658996</v>
       </c>
       <c r="E28" t="n">
-        <v>186.6927185058594</v>
+        <v>186.956787109375</v>
       </c>
       <c r="F28" t="n">
-        <v>7979500</v>
+        <v>9473000</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45944</v>
+        <v>45946</v>
       </c>
       <c r="B29" t="n">
-        <v>188.6682159172342</v>
+        <v>187.1230558646578</v>
       </c>
       <c r="C29" t="n">
-        <v>190.1155938776849</v>
+        <v>188.7953757558051</v>
       </c>
       <c r="D29" t="n">
-        <v>181.7833777150234</v>
+        <v>186.2331077651437</v>
       </c>
       <c r="E29" t="n">
-        <v>186.6438446044922</v>
+        <v>187.8858642578125</v>
       </c>
       <c r="F29" t="n">
-        <v>13613300</v>
+        <v>10611800</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45945</v>
+        <v>45947</v>
       </c>
       <c r="B30" t="n">
-        <v>187.2599526066892</v>
+        <v>188.2574758352493</v>
       </c>
       <c r="C30" t="n">
-        <v>189.303902268661</v>
+        <v>189.3332388090219</v>
       </c>
       <c r="D30" t="n">
-        <v>185.1280049658996</v>
+        <v>187.4555407234371</v>
       </c>
       <c r="E30" t="n">
-        <v>186.956787109375</v>
+        <v>188.9616088867188</v>
       </c>
       <c r="F30" t="n">
-        <v>9473000</v>
+        <v>7764400</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45946</v>
+        <v>45950</v>
       </c>
       <c r="B31" t="n">
-        <v>187.1230406678187</v>
+        <v>189.2354242017374</v>
       </c>
       <c r="C31" t="n">
-        <v>188.7953604231518</v>
+        <v>190.1938216550539</v>
       </c>
       <c r="D31" t="n">
-        <v>186.2330926405801</v>
+        <v>188.0912117995895</v>
       </c>
       <c r="E31" t="n">
-        <v>187.8858489990234</v>
+        <v>189.4505767822266</v>
       </c>
       <c r="F31" t="n">
-        <v>10611800</v>
+        <v>8034700</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45947</v>
+        <v>45951</v>
       </c>
       <c r="B32" t="n">
-        <v>188.2574758352493</v>
+        <v>188.756223952035</v>
       </c>
       <c r="C32" t="n">
-        <v>189.3332388090219</v>
+        <v>189.2843311834856</v>
       </c>
       <c r="D32" t="n">
-        <v>187.4555407234371</v>
+        <v>187.5435620120352</v>
       </c>
       <c r="E32" t="n">
-        <v>188.9616088867188</v>
+        <v>187.6511383056641</v>
       </c>
       <c r="F32" t="n">
-        <v>7764400</v>
+        <v>6716000</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45950</v>
+        <v>45952</v>
       </c>
       <c r="B33" t="n">
-        <v>189.2354394431975</v>
+        <v>187.7685042274453</v>
       </c>
       <c r="C33" t="n">
-        <v>190.1938369737056</v>
+        <v>189.1865446342463</v>
       </c>
       <c r="D33" t="n">
-        <v>188.0912269488921</v>
+        <v>187.5533516225514</v>
       </c>
       <c r="E33" t="n">
-        <v>189.4505920410156</v>
+        <v>188.6877899169922</v>
       </c>
       <c r="F33" t="n">
-        <v>8034700</v>
+        <v>6343100</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45951</v>
+        <v>45953</v>
       </c>
       <c r="B34" t="n">
-        <v>188.7562393006838</v>
+        <v>188.3161623201141</v>
       </c>
       <c r="C34" t="n">
-        <v>189.2843465750772</v>
+        <v>189.7244285069409</v>
       </c>
       <c r="D34" t="n">
-        <v>187.5435772620767</v>
+        <v>187.3186379506951</v>
       </c>
       <c r="E34" t="n">
-        <v>187.6511535644531</v>
+        <v>188.2281494140625</v>
       </c>
       <c r="F34" t="n">
-        <v>6716000</v>
+        <v>8882500</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45952</v>
+        <v>45954</v>
       </c>
       <c r="B35" t="n">
-        <v>187.7685194118937</v>
+        <v>187.9640832263789</v>
       </c>
       <c r="C35" t="n">
-        <v>189.1865599333687</v>
+        <v>188.0716595229833</v>
       </c>
       <c r="D35" t="n">
-        <v>187.5533667896008</v>
+        <v>185.2453531003753</v>
       </c>
       <c r="E35" t="n">
-        <v>188.6878051757812</v>
+        <v>186.2037506103516</v>
       </c>
       <c r="F35" t="n">
-        <v>6343100</v>
+        <v>6903400</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45953</v>
+        <v>45957</v>
       </c>
       <c r="B36" t="n">
-        <v>188.3161470541903</v>
+        <v>185.8027763144259</v>
       </c>
       <c r="C36" t="n">
-        <v>189.7244131268554</v>
+        <v>186.5949221686458</v>
       </c>
       <c r="D36" t="n">
-        <v>187.318622765636</v>
+        <v>185.352907784037</v>
       </c>
       <c r="E36" t="n">
-        <v>188.2281341552734</v>
+        <v>186.1059417724609</v>
       </c>
       <c r="F36" t="n">
-        <v>8882500</v>
+        <v>7126000</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45954</v>
+        <v>45958</v>
       </c>
       <c r="B37" t="n">
-        <v>187.9640678233363</v>
+        <v>185.0888926090998</v>
       </c>
       <c r="C37" t="n">
-        <v>188.0716441111252</v>
+        <v>185.333382857939</v>
       </c>
       <c r="D37" t="n">
-        <v>185.2453379201237</v>
+        <v>182.5070761782583</v>
       </c>
       <c r="E37" t="n">
-        <v>186.2037353515625</v>
+        <v>182.8102416992188</v>
       </c>
       <c r="F37" t="n">
-        <v>6903400</v>
+        <v>8329500</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45957</v>
+        <v>45959</v>
       </c>
       <c r="B38" t="n">
-        <v>185.8027915483585</v>
+        <v>182.5852901845839</v>
       </c>
       <c r="C38" t="n">
-        <v>186.5949374675263</v>
+        <v>182.9764834833836</v>
       </c>
       <c r="D38" t="n">
-        <v>185.3529229810849</v>
+        <v>180.5902565894498</v>
       </c>
       <c r="E38" t="n">
-        <v>186.10595703125</v>
+        <v>182.4875030517578</v>
       </c>
       <c r="F38" t="n">
-        <v>7126000</v>
+        <v>10551100</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45958</v>
+        <v>45960</v>
       </c>
       <c r="B39" t="n">
-        <v>185.0888771601165</v>
+        <v>182.9569302033718</v>
       </c>
       <c r="C39" t="n">
-        <v>185.3333673885486</v>
+        <v>185.2062432977132</v>
       </c>
       <c r="D39" t="n">
-        <v>182.5070609447738</v>
+        <v>182.7906786381269</v>
       </c>
       <c r="E39" t="n">
-        <v>182.8102264404297</v>
+        <v>184.8835144042969</v>
       </c>
       <c r="F39" t="n">
-        <v>8329500</v>
+        <v>7072500</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45959</v>
+        <v>45961</v>
       </c>
       <c r="B40" t="n">
-        <v>182.5853054515495</v>
+        <v>183.3285602019948</v>
       </c>
       <c r="C40" t="n">
-        <v>182.9764987830591</v>
+        <v>185.3235939082472</v>
       </c>
       <c r="D40" t="n">
-        <v>180.5902716895996</v>
+        <v>182.6439756215902</v>
       </c>
       <c r="E40" t="n">
-        <v>182.4875183105469</v>
+        <v>184.7074737548828</v>
       </c>
       <c r="F40" t="n">
-        <v>10551100</v>
+        <v>8791700</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45960</v>
+        <v>45964</v>
       </c>
       <c r="B41" t="n">
-        <v>182.9569151035874</v>
+        <v>184.8346326024117</v>
       </c>
       <c r="C41" t="n">
-        <v>185.2062280122887</v>
+        <v>184.8639702391834</v>
       </c>
       <c r="D41" t="n">
-        <v>182.7906635520636</v>
+        <v>181.4313324343818</v>
       </c>
       <c r="E41" t="n">
-        <v>184.8834991455078</v>
+        <v>182.1550140380859</v>
       </c>
       <c r="F41" t="n">
-        <v>7072500</v>
+        <v>7542600</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45961</v>
+        <v>45965</v>
       </c>
       <c r="B42" t="n">
-        <v>183.3285602019948</v>
+        <v>182.7124378793119</v>
       </c>
       <c r="C42" t="n">
-        <v>185.3235939082472</v>
+        <v>183.680624548461</v>
       </c>
       <c r="D42" t="n">
-        <v>182.6439756215902</v>
+        <v>181.5290986170187</v>
       </c>
       <c r="E42" t="n">
-        <v>184.7074737548828</v>
+        <v>182.7417755126953</v>
       </c>
       <c r="F42" t="n">
-        <v>8791700</v>
+        <v>7209400</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45964</v>
+        <v>45966</v>
       </c>
       <c r="B43" t="n">
-        <v>184.834617119156</v>
+        <v>182.5266206937376</v>
       </c>
       <c r="C43" t="n">
-        <v>184.8639547534701</v>
+        <v>183.6903965454173</v>
       </c>
       <c r="D43" t="n">
-        <v>181.4313172362143</v>
+        <v>181.3139438128489</v>
       </c>
       <c r="E43" t="n">
-        <v>182.1549987792969</v>
+        <v>181.9007263183594</v>
       </c>
       <c r="F43" t="n">
-        <v>7542600</v>
+        <v>5049400</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45965</v>
+        <v>45967</v>
       </c>
       <c r="B44" t="n">
-        <v>182.7124378793119</v>
+        <v>182.6439716214627</v>
       </c>
       <c r="C44" t="n">
-        <v>183.680624548461</v>
+        <v>183.3872314530524</v>
       </c>
       <c r="D44" t="n">
-        <v>181.5290986170187</v>
+        <v>181.2846065725014</v>
       </c>
       <c r="E44" t="n">
-        <v>182.7417755126953</v>
+        <v>182.8493499755859</v>
       </c>
       <c r="F44" t="n">
-        <v>7209400</v>
+        <v>6767400</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45966</v>
+        <v>45968</v>
       </c>
       <c r="B45" t="n">
-        <v>182.5266206937376</v>
+        <v>183.6024034971757</v>
       </c>
       <c r="C45" t="n">
-        <v>183.6903965454173</v>
+        <v>184.1989603040272</v>
       </c>
       <c r="D45" t="n">
-        <v>181.3139438128489</v>
+        <v>181.6073547007375</v>
       </c>
       <c r="E45" t="n">
-        <v>181.9007263183594</v>
+        <v>182.4581909179688</v>
       </c>
       <c r="F45" t="n">
-        <v>5049400</v>
+        <v>6959200</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45967</v>
+        <v>45971</v>
       </c>
       <c r="B46" t="n">
-        <v>182.6439716214627</v>
+        <v>181.9007248187872</v>
       </c>
       <c r="C46" t="n">
-        <v>183.3872314530524</v>
+        <v>184.2673883725038</v>
       </c>
       <c r="D46" t="n">
-        <v>181.2846065725014</v>
+        <v>181.0401144637998</v>
       </c>
       <c r="E46" t="n">
-        <v>182.8493499755859</v>
+        <v>184.2576141357422</v>
       </c>
       <c r="F46" t="n">
-        <v>6767400</v>
+        <v>5323800</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45968</v>
+        <v>45972</v>
       </c>
       <c r="B47" t="n">
-        <v>183.6023881426973</v>
+        <v>185.2160176409071</v>
       </c>
       <c r="C47" t="n">
-        <v>184.1989448996594</v>
+        <v>189.6461794051158</v>
       </c>
       <c r="D47" t="n">
-        <v>181.607339513103</v>
+        <v>184.8835145102268</v>
       </c>
       <c r="E47" t="n">
-        <v>182.4581756591797</v>
+        <v>189.5581665039062</v>
       </c>
       <c r="F47" t="n">
-        <v>6959200</v>
+        <v>7465600</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45971</v>
+        <v>45973</v>
       </c>
       <c r="B48" t="n">
-        <v>181.9007398823969</v>
+        <v>189.098521163925</v>
       </c>
       <c r="C48" t="n">
-        <v>184.2674036321023</v>
+        <v>191.2402579332056</v>
       </c>
       <c r="D48" t="n">
-        <v>181.0401294561404</v>
+        <v>188.8149190674103</v>
       </c>
       <c r="E48" t="n">
-        <v>184.2576293945312</v>
+        <v>190.1058197021484</v>
       </c>
       <c r="F48" t="n">
-        <v>5323800</v>
+        <v>8803000</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45972</v>
+        <v>45974</v>
       </c>
       <c r="B49" t="n">
-        <v>185.2160176409071</v>
+        <v>189.9297961094911</v>
       </c>
       <c r="C49" t="n">
-        <v>189.6461794051158</v>
+        <v>191.6803395836668</v>
       </c>
       <c r="D49" t="n">
-        <v>184.8835145102268</v>
+        <v>189.1865362627468</v>
       </c>
       <c r="E49" t="n">
-        <v>189.5581665039062</v>
+        <v>190.9468688964844</v>
       </c>
       <c r="F49" t="n">
-        <v>7465600</v>
+        <v>8631600</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45973</v>
+        <v>45975</v>
       </c>
       <c r="B50" t="n">
-        <v>189.0985059859865</v>
+        <v>190.7023809412554</v>
       </c>
       <c r="C50" t="n">
-        <v>191.2402425833612</v>
+        <v>192.8343286012861</v>
       </c>
       <c r="D50" t="n">
-        <v>188.814903912235</v>
+        <v>189.2843405802947</v>
       </c>
       <c r="E50" t="n">
-        <v>190.1058044433594</v>
+        <v>191.6118774414062</v>
       </c>
       <c r="F50" t="n">
-        <v>8803000</v>
+        <v>8824800</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45974</v>
+        <v>45978</v>
       </c>
       <c r="B51" t="n">
-        <v>189.9297961094911</v>
+        <v>192.619189424801</v>
       </c>
       <c r="C51" t="n">
-        <v>191.6803395836668</v>
+        <v>195.8660119204403</v>
       </c>
       <c r="D51" t="n">
-        <v>189.1865362627468</v>
+        <v>191.5825383144018</v>
       </c>
       <c r="E51" t="n">
-        <v>190.9468688964844</v>
+        <v>195.1814422607422</v>
       </c>
       <c r="F51" t="n">
-        <v>8631600</v>
+        <v>13257000</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45975</v>
+        <v>45979</v>
       </c>
       <c r="B52" t="n">
-        <v>190.7023809412554</v>
+        <v>194.6239916898205</v>
       </c>
       <c r="C52" t="n">
-        <v>192.8343286012861</v>
+        <v>195.8855695967434</v>
       </c>
       <c r="D52" t="n">
-        <v>189.2843405802947</v>
+        <v>194.1545746400929</v>
       </c>
       <c r="E52" t="n">
-        <v>191.6118774414062</v>
+        <v>195.5921783447266</v>
       </c>
       <c r="F52" t="n">
-        <v>8824800</v>
+        <v>12468600</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45978</v>
+        <v>45980</v>
       </c>
       <c r="B53" t="n">
-        <v>192.619189424801</v>
+        <v>195.5921832139753</v>
       </c>
       <c r="C53" t="n">
-        <v>195.8660119204403</v>
+        <v>198.9954830235987</v>
       </c>
       <c r="D53" t="n">
-        <v>191.5825383144018</v>
+        <v>194.9858522212118</v>
       </c>
       <c r="E53" t="n">
-        <v>195.1814422607422</v>
+        <v>198.0468597412109</v>
       </c>
       <c r="F53" t="n">
-        <v>13257000</v>
+        <v>14690800</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45979</v>
+        <v>45981</v>
       </c>
       <c r="B54" t="n">
-        <v>194.6239916898205</v>
+        <v>197.5480876884036</v>
       </c>
       <c r="C54" t="n">
-        <v>195.8855695967434</v>
+        <v>200.0027639999573</v>
       </c>
       <c r="D54" t="n">
-        <v>194.1545746400929</v>
+        <v>197.1275716942422</v>
       </c>
       <c r="E54" t="n">
-        <v>195.5921783447266</v>
+        <v>198.5945129394531</v>
       </c>
       <c r="F54" t="n">
-        <v>12468600</v>
+        <v>10612600</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45980</v>
+        <v>45982</v>
       </c>
       <c r="B55" t="n">
-        <v>195.5921832139753</v>
+        <v>199.4649249339953</v>
       </c>
       <c r="C55" t="n">
-        <v>198.9954830235987</v>
+        <v>202.3792444306165</v>
       </c>
       <c r="D55" t="n">
-        <v>194.9858522212118</v>
+        <v>198.5163016043988</v>
       </c>
       <c r="E55" t="n">
-        <v>198.0468597412109</v>
+        <v>199.4062347412109</v>
       </c>
       <c r="F55" t="n">
-        <v>14690800</v>
+        <v>13189100</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45981</v>
+        <v>45985</v>
       </c>
       <c r="B56" t="n">
-        <v>197.5480876884036</v>
+        <v>199.2204251313988</v>
       </c>
       <c r="C56" t="n">
-        <v>200.0027639999573</v>
+        <v>201.5772996022027</v>
       </c>
       <c r="D56" t="n">
-        <v>197.1275716942422</v>
+        <v>198.5260663138595</v>
       </c>
       <c r="E56" t="n">
-        <v>198.5945129394531</v>
+        <v>201.5088500976562</v>
       </c>
       <c r="F56" t="n">
-        <v>10612600</v>
+        <v>14803900</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,25 +1899,25 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45982</v>
+        <v>45986</v>
       </c>
       <c r="B57" t="n">
-        <v>199.4649096707152</v>
+        <v>201.9320337594338</v>
       </c>
       <c r="C57" t="n">
-        <v>202.3792289443294</v>
+        <v>204.4318344688182</v>
       </c>
       <c r="D57" t="n">
-        <v>198.5162864137085</v>
+        <v>201.9320337594338</v>
       </c>
       <c r="E57" t="n">
-        <v>199.4062194824219</v>
+        <v>203.3984527587891</v>
       </c>
       <c r="F57" t="n">
-        <v>13189100</v>
+        <v>10275300</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45985</v>
+        <v>45987</v>
       </c>
       <c r="B58" t="n">
-        <v>199.2204100458954</v>
+        <v>203.2213139605992</v>
       </c>
       <c r="C58" t="n">
-        <v>201.5772843382305</v>
+        <v>204.5204108409229</v>
       </c>
       <c r="D58" t="n">
-        <v>198.5260512809348</v>
+        <v>202.6800173366119</v>
       </c>
       <c r="E58" t="n">
-        <v>201.5088348388672</v>
+        <v>204.2743682861328</v>
       </c>
       <c r="F58" t="n">
-        <v>14803900</v>
+        <v>6729000</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,25 +1951,25 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45986</v>
+        <v>45989</v>
       </c>
       <c r="B59" t="n">
-        <v>201.9320489082132</v>
+        <v>203.723236152328</v>
       </c>
       <c r="C59" t="n">
-        <v>204.4318498051307</v>
+        <v>204.1759610624769</v>
       </c>
       <c r="D59" t="n">
-        <v>201.9320489082132</v>
+        <v>201.390757529436</v>
       </c>
       <c r="E59" t="n">
-        <v>203.3984680175781</v>
+        <v>203.6445007324219</v>
       </c>
       <c r="F59" t="n">
-        <v>10275300</v>
+        <v>5638300</v>
       </c>
       <c r="G59" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45987</v>
+        <v>45992</v>
       </c>
       <c r="B60" t="n">
-        <v>203.2213139605992</v>
+        <v>203.2311491085565</v>
       </c>
       <c r="C60" t="n">
-        <v>204.5204108409229</v>
+        <v>204.4121503614282</v>
       </c>
       <c r="D60" t="n">
-        <v>202.6800173366119</v>
+        <v>202.0895080566406</v>
       </c>
       <c r="E60" t="n">
-        <v>204.2743682861328</v>
+        <v>202.0895080566406</v>
       </c>
       <c r="F60" t="n">
-        <v>6729000</v>
+        <v>8473700</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45989</v>
+        <v>45993</v>
       </c>
       <c r="B61" t="n">
-        <v>203.723236152328</v>
+        <v>201.9910999780921</v>
       </c>
       <c r="C61" t="n">
-        <v>204.1759610624769</v>
+        <v>202.3552381514841</v>
       </c>
       <c r="D61" t="n">
-        <v>201.390757529436</v>
+        <v>199.8849763223805</v>
       </c>
       <c r="E61" t="n">
-        <v>203.6445007324219</v>
+        <v>202.1682434082031</v>
       </c>
       <c r="F61" t="n">
-        <v>5638300</v>
+        <v>8393600</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45992</v>
+        <v>45994</v>
       </c>
       <c r="B62" t="n">
-        <v>203.2311491085565</v>
+        <v>202.6406353348706</v>
       </c>
       <c r="C62" t="n">
-        <v>204.4121503614282</v>
+        <v>203.7429161551587</v>
       </c>
       <c r="D62" t="n">
-        <v>202.0895080566406</v>
+        <v>201.7450518785209</v>
       </c>
       <c r="E62" t="n">
-        <v>202.0895080566406</v>
+        <v>202.0796661376953</v>
       </c>
       <c r="F62" t="n">
-        <v>8473700</v>
+        <v>8363300</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45993</v>
+        <v>45995</v>
       </c>
       <c r="B63" t="n">
-        <v>201.9910999780921</v>
+        <v>201.3513800209524</v>
       </c>
       <c r="C63" t="n">
-        <v>202.3552381514841</v>
+        <v>201.6171101829578</v>
       </c>
       <c r="D63" t="n">
-        <v>199.8849763223805</v>
+        <v>198.516980022795</v>
       </c>
       <c r="E63" t="n">
-        <v>202.1682434082031</v>
+        <v>199.2747802734375</v>
       </c>
       <c r="F63" t="n">
-        <v>8393600</v>
+        <v>9049900</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>45994</v>
+        <v>45996</v>
       </c>
       <c r="B64" t="n">
-        <v>202.6406353348706</v>
+        <v>199.7668717489871</v>
       </c>
       <c r="C64" t="n">
-        <v>203.7429161551587</v>
+        <v>200.2294329646455</v>
       </c>
       <c r="D64" t="n">
-        <v>201.7450518785209</v>
+        <v>197.6312241234294</v>
       </c>
       <c r="E64" t="n">
-        <v>202.0796661376953</v>
+        <v>198.7334899902344</v>
       </c>
       <c r="F64" t="n">
-        <v>8363300</v>
+        <v>7785300</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>45995</v>
+        <v>45999</v>
       </c>
       <c r="B65" t="n">
-        <v>201.35139543875</v>
+        <v>199.4519359184436</v>
       </c>
       <c r="C65" t="n">
-        <v>201.6171256211029</v>
+        <v>200.0424290268597</v>
       </c>
       <c r="D65" t="n">
-        <v>198.5169952235581</v>
+        <v>197.8083734899551</v>
       </c>
       <c r="E65" t="n">
-        <v>199.2747955322266</v>
+        <v>198.4283905029297</v>
       </c>
       <c r="F65" t="n">
-        <v>9049900</v>
+        <v>7785700</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>45996</v>
+        <v>46000</v>
       </c>
       <c r="B66" t="n">
-        <v>199.7668717489871</v>
+        <v>199.7078130861464</v>
       </c>
       <c r="C66" t="n">
-        <v>200.2294329646455</v>
+        <v>202.2863341775681</v>
       </c>
       <c r="D66" t="n">
-        <v>197.6312241234294</v>
+        <v>196.7454662214423</v>
       </c>
       <c r="E66" t="n">
-        <v>198.7334899902344</v>
+        <v>196.794677734375</v>
       </c>
       <c r="F66" t="n">
-        <v>7785300</v>
+        <v>7509400</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>45999</v>
+        <v>46001</v>
       </c>
       <c r="B67" t="n">
-        <v>199.4519359184436</v>
+        <v>197.4146980881505</v>
       </c>
       <c r="C67" t="n">
-        <v>200.0424290268597</v>
+        <v>203.5264016771889</v>
       </c>
       <c r="D67" t="n">
-        <v>197.8083734899551</v>
+        <v>197.011184699407</v>
       </c>
       <c r="E67" t="n">
-        <v>198.4283905029297</v>
+        <v>203.2705078125</v>
       </c>
       <c r="F67" t="n">
-        <v>7785700</v>
+        <v>11599800</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="B68" t="n">
-        <v>199.7078130861464</v>
+        <v>204.608977678963</v>
       </c>
       <c r="C68" t="n">
-        <v>202.2863341775681</v>
+        <v>207.8961175457048</v>
       </c>
       <c r="D68" t="n">
-        <v>196.7454662214423</v>
+        <v>204.5400935742317</v>
       </c>
       <c r="E68" t="n">
-        <v>196.794677734375</v>
+        <v>206.6855773925781</v>
       </c>
       <c r="F68" t="n">
-        <v>7509400</v>
+        <v>9009000</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46001</v>
+        <v>46003</v>
       </c>
       <c r="B69" t="n">
-        <v>197.4146980881505</v>
+        <v>206.951319079071</v>
       </c>
       <c r="C69" t="n">
-        <v>203.5264016771889</v>
+        <v>208.9098232838249</v>
       </c>
       <c r="D69" t="n">
-        <v>197.011184699407</v>
+        <v>205.6522221573458</v>
       </c>
       <c r="E69" t="n">
-        <v>203.2705078125</v>
+        <v>208.2307434082031</v>
       </c>
       <c r="F69" t="n">
-        <v>11599800</v>
+        <v>6922700</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46002</v>
+        <v>46006</v>
       </c>
       <c r="B70" t="n">
-        <v>204.608977678963</v>
+        <v>207.0202168563343</v>
       </c>
       <c r="C70" t="n">
-        <v>207.8961175457048</v>
+        <v>211.7835972337083</v>
       </c>
       <c r="D70" t="n">
-        <v>204.5400935742317</v>
+        <v>205.7014173161141</v>
       </c>
       <c r="E70" t="n">
-        <v>206.6855773925781</v>
+        <v>210.7797393798828</v>
       </c>
       <c r="F70" t="n">
-        <v>9009000</v>
+        <v>8467000</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46003</v>
+        <v>46007</v>
       </c>
       <c r="B71" t="n">
-        <v>206.951319079071</v>
+        <v>210.612413130432</v>
       </c>
       <c r="C71" t="n">
-        <v>208.9098232838249</v>
+        <v>211.3308531386185</v>
       </c>
       <c r="D71" t="n">
-        <v>205.6522221573458</v>
+        <v>205.5045676241825</v>
       </c>
       <c r="E71" t="n">
-        <v>208.2307434082031</v>
+        <v>205.98681640625</v>
       </c>
       <c r="F71" t="n">
-        <v>6922700</v>
+        <v>9949800</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46006</v>
+        <v>46008</v>
       </c>
       <c r="B72" t="n">
-        <v>207.020201869705</v>
+        <v>206.0753964132944</v>
       </c>
       <c r="C72" t="n">
-        <v>211.7835819022478</v>
+        <v>208.1716837329721</v>
       </c>
       <c r="D72" t="n">
-        <v>205.7014024249555</v>
+        <v>205.1601253407421</v>
       </c>
       <c r="E72" t="n">
-        <v>210.7797241210938</v>
+        <v>207.0005187988281</v>
       </c>
       <c r="F72" t="n">
-        <v>8467000</v>
+        <v>8457600</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46007</v>
+        <v>46009</v>
       </c>
       <c r="B73" t="n">
-        <v>210.612413130432</v>
+        <v>206.478915988136</v>
       </c>
       <c r="C73" t="n">
-        <v>211.3308531386185</v>
+        <v>207.7189650641044</v>
       </c>
       <c r="D73" t="n">
-        <v>205.5045676241825</v>
+        <v>204.4712003216206</v>
       </c>
       <c r="E73" t="n">
-        <v>205.98681640625</v>
+        <v>205.0124969482422</v>
       </c>
       <c r="F73" t="n">
-        <v>9949800</v>
+        <v>7499900</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46008</v>
+        <v>46010</v>
       </c>
       <c r="B74" t="n">
-        <v>206.0753812226996</v>
+        <v>204.2743754538735</v>
       </c>
       <c r="C74" t="n">
-        <v>208.171668387852</v>
+        <v>205.9277892890467</v>
       </c>
       <c r="D74" t="n">
-        <v>205.1601102176154</v>
+        <v>202.768596167102</v>
       </c>
       <c r="E74" t="n">
-        <v>207.0005035400391</v>
+        <v>203.1032104492188</v>
       </c>
       <c r="F74" t="n">
-        <v>8457600</v>
+        <v>24803900</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46009</v>
+        <v>46013</v>
       </c>
       <c r="B75" t="n">
-        <v>206.4789006202035</v>
+        <v>202.8670125241163</v>
       </c>
       <c r="C75" t="n">
-        <v>207.7189496038768</v>
+        <v>204.7861414522214</v>
       </c>
       <c r="D75" t="n">
-        <v>204.4711851031195</v>
+        <v>202.2469804791725</v>
       </c>
       <c r="E75" t="n">
-        <v>205.0124816894531</v>
+        <v>204.0381774902344</v>
       </c>
       <c r="F75" t="n">
-        <v>7499900</v>
+        <v>8187800</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46010</v>
+        <v>46014</v>
       </c>
       <c r="B76" t="n">
-        <v>204.2743754538735</v>
+        <v>201.7745733053134</v>
       </c>
       <c r="C76" t="n">
-        <v>205.9277892890467</v>
+        <v>203.2606648620441</v>
       </c>
       <c r="D76" t="n">
-        <v>202.768596167102</v>
+        <v>200.062111796116</v>
       </c>
       <c r="E76" t="n">
-        <v>203.1032104492188</v>
+        <v>202.5225372314453</v>
       </c>
       <c r="F76" t="n">
-        <v>24803900</v>
+        <v>7047300</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46013</v>
+        <v>46015</v>
       </c>
       <c r="B77" t="n">
-        <v>202.8669973529117</v>
+        <v>202.739053555574</v>
       </c>
       <c r="C77" t="n">
-        <v>204.7861261374966</v>
+        <v>204.648346074342</v>
       </c>
       <c r="D77" t="n">
-        <v>202.2469653543363</v>
+        <v>202.3158675938084</v>
       </c>
       <c r="E77" t="n">
-        <v>204.0381622314453</v>
+        <v>204.4908752441406</v>
       </c>
       <c r="F77" t="n">
-        <v>8187800</v>
+        <v>2376500</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46014</v>
+        <v>46017</v>
       </c>
       <c r="B78" t="n">
-        <v>201.7745885077481</v>
+        <v>204.2448386926768</v>
       </c>
       <c r="C78" t="n">
-        <v>203.2606801764464</v>
+        <v>204.7467600842614</v>
       </c>
       <c r="D78" t="n">
-        <v>200.0621268695276</v>
+        <v>203.4378269444086</v>
       </c>
       <c r="E78" t="n">
-        <v>202.5225524902344</v>
+        <v>204.34326171875</v>
       </c>
       <c r="F78" t="n">
-        <v>7047300</v>
+        <v>2316700</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46015</v>
+        <v>46020</v>
       </c>
       <c r="B79" t="n">
-        <v>202.7390686836449</v>
+        <v>204.7074055853226</v>
       </c>
       <c r="C79" t="n">
-        <v>204.6483613448813</v>
+        <v>206.1541370088678</v>
       </c>
       <c r="D79" t="n">
-        <v>202.3158826903017</v>
+        <v>204.097224854962</v>
       </c>
       <c r="E79" t="n">
-        <v>204.4908905029297</v>
+        <v>204.2743682861328</v>
       </c>
       <c r="F79" t="n">
-        <v>2376500</v>
+        <v>4348900</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46017</v>
+        <v>46021</v>
       </c>
       <c r="B80" t="n">
-        <v>204.2448386926768</v>
+        <v>204.2251519205988</v>
       </c>
       <c r="C80" t="n">
-        <v>204.7467600842614</v>
+        <v>204.4023103648072</v>
       </c>
       <c r="D80" t="n">
-        <v>203.4378269444086</v>
+        <v>203.2508330378112</v>
       </c>
       <c r="E80" t="n">
-        <v>204.34326171875</v>
+        <v>203.6346588134766</v>
       </c>
       <c r="F80" t="n">
-        <v>2316700</v>
+        <v>3937400</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46020</v>
+        <v>46022</v>
       </c>
       <c r="B81" t="n">
-        <v>204.7074055853226</v>
+        <v>203.6346510317296</v>
       </c>
       <c r="C81" t="n">
-        <v>206.1541370088678</v>
+        <v>204.2153078209129</v>
       </c>
       <c r="D81" t="n">
-        <v>204.097224854962</v>
+        <v>203.103190736659</v>
       </c>
       <c r="E81" t="n">
-        <v>204.2743682861328</v>
+        <v>203.6740112304688</v>
       </c>
       <c r="F81" t="n">
-        <v>4348900</v>
+        <v>4083800</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46021</v>
+        <v>46024</v>
       </c>
       <c r="B82" t="n">
-        <v>204.2251366175628</v>
+        <v>203.546094226423</v>
       </c>
       <c r="C82" t="n">
-        <v>204.4022950484963</v>
+        <v>204.1070634486917</v>
       </c>
       <c r="D82" t="n">
-        <v>203.2508178077831</v>
+        <v>200.4557852869147</v>
       </c>
       <c r="E82" t="n">
-        <v>203.6346435546875</v>
+        <v>204.0677032470703</v>
       </c>
       <c r="F82" t="n">
-        <v>3937400</v>
+        <v>6325500</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46022</v>
+        <v>46027</v>
       </c>
       <c r="B83" t="n">
-        <v>203.6346662875698</v>
+        <v>202.6111087313451</v>
       </c>
       <c r="C83" t="n">
-        <v>204.2153231202547</v>
+        <v>202.68000785174</v>
       </c>
       <c r="D83" t="n">
-        <v>203.1032059526835</v>
+        <v>197.7296330824079</v>
       </c>
       <c r="E83" t="n">
-        <v>203.6740264892578</v>
+        <v>201.0758056640625</v>
       </c>
       <c r="F83" t="n">
-        <v>4083800</v>
+        <v>9477000</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46024</v>
+        <v>46028</v>
       </c>
       <c r="B84" t="n">
-        <v>203.5460790066363</v>
+        <v>201.3612227968269</v>
       </c>
       <c r="C84" t="n">
-        <v>204.1070481869595</v>
+        <v>203.4378224562984</v>
       </c>
       <c r="D84" t="n">
-        <v>200.4557702982002</v>
+        <v>200.8888103027919</v>
       </c>
       <c r="E84" t="n">
-        <v>204.0676879882812</v>
+        <v>201.5482025146484</v>
       </c>
       <c r="F84" t="n">
-        <v>6325500</v>
+        <v>8107900</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46027</v>
+        <v>46029</v>
       </c>
       <c r="B85" t="n">
-        <v>202.6111087313451</v>
+        <v>202.0107645526058</v>
       </c>
       <c r="C85" t="n">
-        <v>202.68000785174</v>
+        <v>204.9632750752426</v>
       </c>
       <c r="D85" t="n">
-        <v>197.7296330824079</v>
+        <v>201.7844096173656</v>
       </c>
       <c r="E85" t="n">
-        <v>201.0758056640625</v>
+        <v>204.2054748535156</v>
       </c>
       <c r="F85" t="n">
-        <v>9477000</v>
+        <v>7545900</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46028</v>
+        <v>46030</v>
       </c>
       <c r="B86" t="n">
-        <v>201.3612380414601</v>
+        <v>203.6543250611801</v>
       </c>
       <c r="C86" t="n">
-        <v>203.4378378581467</v>
+        <v>205.6718769031367</v>
       </c>
       <c r="D86" t="n">
-        <v>200.8888255116597</v>
+        <v>201.7253599471909</v>
       </c>
       <c r="E86" t="n">
-        <v>201.5482177734375</v>
+        <v>202.4930114746094</v>
       </c>
       <c r="F86" t="n">
-        <v>8107900</v>
+        <v>6557800</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46029</v>
+        <v>46031</v>
       </c>
       <c r="B87" t="n">
-        <v>202.0107645526058</v>
+        <v>202.6504838830927</v>
       </c>
       <c r="C87" t="n">
-        <v>204.9632750752426</v>
+        <v>203.4279717120081</v>
       </c>
       <c r="D87" t="n">
-        <v>201.7844096173656</v>
+        <v>200.7805515444468</v>
       </c>
       <c r="E87" t="n">
-        <v>204.2054748535156</v>
+        <v>201.154541015625</v>
       </c>
       <c r="F87" t="n">
-        <v>7545900</v>
+        <v>6154300</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46030</v>
+        <v>46034</v>
       </c>
       <c r="B88" t="n">
-        <v>203.6543250611801</v>
+        <v>202.2961890410606</v>
       </c>
       <c r="C88" t="n">
-        <v>205.6718769031367</v>
+        <v>206.5773204309254</v>
       </c>
       <c r="D88" t="n">
-        <v>201.7253599471909</v>
+        <v>200.6231026927027</v>
       </c>
       <c r="E88" t="n">
-        <v>202.4930114746094</v>
+        <v>206.4001770019531</v>
       </c>
       <c r="F88" t="n">
-        <v>6557800</v>
+        <v>11794300</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46031</v>
+        <v>46035</v>
       </c>
       <c r="B89" t="n">
-        <v>202.6504992553581</v>
+        <v>206.5871726162479</v>
       </c>
       <c r="C89" t="n">
-        <v>203.4279871432506</v>
+        <v>210.9962509571494</v>
       </c>
       <c r="D89" t="n">
-        <v>200.7805667748665</v>
+        <v>205.5537908911432</v>
       </c>
       <c r="E89" t="n">
-        <v>201.1545562744141</v>
+        <v>210.2679595947266</v>
       </c>
       <c r="F89" t="n">
-        <v>6154300</v>
+        <v>11379600</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46034</v>
+        <v>46036</v>
       </c>
       <c r="B90" t="n">
-        <v>202.2962039964493</v>
+        <v>211.3308558190507</v>
       </c>
       <c r="C90" t="n">
-        <v>206.5773357028104</v>
+        <v>215.3954834155094</v>
       </c>
       <c r="D90" t="n">
-        <v>200.6231175244031</v>
+        <v>210.7600353199485</v>
       </c>
       <c r="E90" t="n">
-        <v>206.4001922607422</v>
+        <v>215.0903930664062</v>
       </c>
       <c r="F90" t="n">
-        <v>11794300</v>
+        <v>11858800</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46035</v>
+        <v>46037</v>
       </c>
       <c r="B91" t="n">
-        <v>206.5871726162479</v>
+        <v>214.7754540862871</v>
       </c>
       <c r="C91" t="n">
-        <v>210.9962509571494</v>
+        <v>216.2713969640869</v>
       </c>
       <c r="D91" t="n">
-        <v>205.5537908911432</v>
+        <v>212.4921870786144</v>
       </c>
       <c r="E91" t="n">
-        <v>210.2679595947266</v>
+        <v>216.0942535400391</v>
       </c>
       <c r="F91" t="n">
-        <v>11379600</v>
+        <v>8492100</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46036</v>
+        <v>46038</v>
       </c>
       <c r="B92" t="n">
-        <v>211.3308558190507</v>
+        <v>215.5726286297608</v>
       </c>
       <c r="C92" t="n">
-        <v>215.3954834155094</v>
+        <v>216.6256979258031</v>
       </c>
       <c r="D92" t="n">
-        <v>210.7600353199485</v>
+        <v>214.686881478726</v>
       </c>
       <c r="E92" t="n">
-        <v>215.0903930664062</v>
+        <v>215.1986541748047</v>
       </c>
       <c r="F92" t="n">
-        <v>11858800</v>
+        <v>10021500</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46037</v>
+        <v>46042</v>
       </c>
       <c r="B93" t="n">
-        <v>214.7754540862871</v>
+        <v>213.6535022600511</v>
       </c>
       <c r="C93" t="n">
-        <v>216.2713969640869</v>
+        <v>215.2675407658023</v>
       </c>
       <c r="D93" t="n">
-        <v>212.4921870786144</v>
+        <v>211.1045050802375</v>
       </c>
       <c r="E93" t="n">
-        <v>216.0942535400391</v>
+        <v>214.7557830810547</v>
       </c>
       <c r="F93" t="n">
-        <v>8492100</v>
+        <v>14057100</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46038</v>
+        <v>46043</v>
       </c>
       <c r="B94" t="n">
-        <v>215.5726286297608</v>
+        <v>207.6599020836601</v>
       </c>
       <c r="C94" t="n">
-        <v>216.6256979258031</v>
+        <v>215.218321643167</v>
       </c>
       <c r="D94" t="n">
-        <v>214.686881478726</v>
+        <v>207.1678170076325</v>
       </c>
       <c r="E94" t="n">
-        <v>215.1986541748047</v>
+        <v>214.5589294433594</v>
       </c>
       <c r="F94" t="n">
-        <v>10021500</v>
+        <v>14762900</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46042</v>
+        <v>46044</v>
       </c>
       <c r="B95" t="n">
-        <v>213.6535022600511</v>
+        <v>215.3069079934484</v>
       </c>
       <c r="C95" t="n">
-        <v>215.2675407658023</v>
+        <v>218.6530804976869</v>
       </c>
       <c r="D95" t="n">
-        <v>211.1045050802375</v>
+        <v>214.6475157947938</v>
       </c>
       <c r="E95" t="n">
-        <v>214.7557830810547</v>
+        <v>215.0313415527344</v>
       </c>
       <c r="F95" t="n">
-        <v>14057100</v>
+        <v>13160000</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46043</v>
+        <v>46045</v>
       </c>
       <c r="B96" t="n">
-        <v>207.659916851811</v>
+        <v>216.3206133966017</v>
       </c>
       <c r="C96" t="n">
-        <v>215.2183369488501</v>
+        <v>217.7082969855193</v>
       </c>
       <c r="D96" t="n">
-        <v>207.1678317407877</v>
+        <v>214.3916331931512</v>
       </c>
       <c r="E96" t="n">
-        <v>214.5589447021484</v>
+        <v>216.6552276611328</v>
       </c>
       <c r="F96" t="n">
-        <v>14762900</v>
+        <v>6950600</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="B97" t="n">
-        <v>215.3069232717918</v>
+        <v>216.7241347564745</v>
       </c>
       <c r="C97" t="n">
-        <v>218.6530960134773</v>
+        <v>218.5153167809881</v>
       </c>
       <c r="D97" t="n">
-        <v>214.6475310263463</v>
+        <v>216.5174523988691</v>
       </c>
       <c r="E97" t="n">
-        <v>215.0313568115234</v>
+        <v>217.9838714599609</v>
       </c>
       <c r="F97" t="n">
-        <v>13160000</v>
+        <v>6856700</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46045</v>
+        <v>46049</v>
       </c>
       <c r="B98" t="n">
-        <v>216.3206133966017</v>
+        <v>218.4857835732108</v>
       </c>
       <c r="C98" t="n">
-        <v>217.7082969855193</v>
+        <v>221.9303792601758</v>
       </c>
       <c r="D98" t="n">
-        <v>214.3916331931512</v>
+        <v>217.2063593146032</v>
       </c>
       <c r="E98" t="n">
-        <v>216.6552276611328</v>
+        <v>220.8871612548828</v>
       </c>
       <c r="F98" t="n">
-        <v>6950600</v>
+        <v>8154100</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="B99" t="n">
-        <v>216.7241195858665</v>
+        <v>222.8161377007139</v>
       </c>
       <c r="C99" t="n">
-        <v>218.515301484998</v>
+        <v>224.9518003498371</v>
       </c>
       <c r="D99" t="n">
-        <v>216.5174372427288</v>
+        <v>222.5012110309432</v>
       </c>
       <c r="E99" t="n">
-        <v>217.9838562011719</v>
+        <v>224.1152496337891</v>
       </c>
       <c r="F99" t="n">
-        <v>6856700</v>
+        <v>9026500</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46049</v>
+        <v>46051</v>
       </c>
       <c r="B100" t="n">
-        <v>218.4857835732108</v>
+        <v>225.1879747271155</v>
       </c>
       <c r="C100" t="n">
-        <v>221.9303792601758</v>
+        <v>226.3591396349424</v>
       </c>
       <c r="D100" t="n">
-        <v>217.2063593146032</v>
+        <v>223.4853645338204</v>
       </c>
       <c r="E100" t="n">
-        <v>220.8871612548828</v>
+        <v>223.6920318603516</v>
       </c>
       <c r="F100" t="n">
-        <v>8154100</v>
+        <v>9645300</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46050</v>
+        <v>46052</v>
       </c>
       <c r="B101" t="n">
-        <v>222.8161377007139</v>
+        <v>224.6466859457881</v>
       </c>
       <c r="C101" t="n">
-        <v>224.9518003498371</v>
+        <v>224.8828922015737</v>
       </c>
       <c r="D101" t="n">
-        <v>222.5012110309432</v>
+        <v>221.7630744488117</v>
       </c>
       <c r="E101" t="n">
-        <v>224.1152496337891</v>
+        <v>223.6526794433594</v>
       </c>
       <c r="F101" t="n">
-        <v>9026500</v>
+        <v>11045500</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46051</v>
+        <v>46055</v>
       </c>
       <c r="B102" t="n">
-        <v>225.1879747271155</v>
+        <v>224.7057483906486</v>
       </c>
       <c r="C102" t="n">
-        <v>226.3591396349424</v>
+        <v>227.530312073188</v>
       </c>
       <c r="D102" t="n">
-        <v>223.4853645338204</v>
+        <v>223.6526790631295</v>
       </c>
       <c r="E102" t="n">
-        <v>223.6920318603516</v>
+        <v>227.0972747802734</v>
       </c>
       <c r="F102" t="n">
-        <v>9645300</v>
+        <v>8187500</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46052</v>
+        <v>46056</v>
       </c>
       <c r="B103" t="n">
-        <v>224.6466706191826</v>
+        <v>227.8354016268972</v>
       </c>
       <c r="C103" t="n">
-        <v>224.8828768588529</v>
+        <v>231.4768283686728</v>
       </c>
       <c r="D103" t="n">
-        <v>221.7630593189417</v>
+        <v>226.8315438166281</v>
       </c>
       <c r="E103" t="n">
-        <v>223.6526641845703</v>
+        <v>229.4100799560547</v>
       </c>
       <c r="F103" t="n">
-        <v>11045500</v>
+        <v>9346600</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B104" t="n">
-        <v>224.7057634887497</v>
+        <v>231.2800013484118</v>
       </c>
       <c r="C104" t="n">
-        <v>227.530327361073</v>
+        <v>232.0968644318395</v>
       </c>
       <c r="D104" t="n">
-        <v>223.6526940904743</v>
+        <v>229.2526131010531</v>
       </c>
       <c r="E104" t="n">
-        <v>227.0972900390625</v>
+        <v>230.7583923339844</v>
       </c>
       <c r="F104" t="n">
-        <v>8187500</v>
+        <v>8641400</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46056</v>
+        <v>46058</v>
       </c>
       <c r="B105" t="n">
-        <v>227.8354016268972</v>
+        <v>231.2799897072634</v>
       </c>
       <c r="C105" t="n">
-        <v>231.4768283686728</v>
+        <v>235.787490883202</v>
       </c>
       <c r="D105" t="n">
-        <v>226.8315438166281</v>
+        <v>231.2701534117819</v>
       </c>
       <c r="E105" t="n">
-        <v>229.4100799560547</v>
+        <v>234.0258178710938</v>
       </c>
       <c r="F105" t="n">
-        <v>9346600</v>
+        <v>10267500</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46057</v>
+        <v>46059</v>
       </c>
       <c r="B106" t="n">
-        <v>231.2799860551316</v>
+        <v>235.1773154262319</v>
       </c>
       <c r="C106" t="n">
-        <v>232.0968490845446</v>
+        <v>237.125968199395</v>
       </c>
       <c r="D106" t="n">
-        <v>229.252597941833</v>
+        <v>234.2128178267284</v>
       </c>
       <c r="E106" t="n">
-        <v>230.7583770751953</v>
+        <v>236.1910095214844</v>
       </c>
       <c r="F106" t="n">
-        <v>8641400</v>
+        <v>8274000</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46058</v>
+        <v>46062</v>
       </c>
       <c r="B107" t="n">
-        <v>231.2799897072634</v>
+        <v>236.4468956382332</v>
       </c>
       <c r="C107" t="n">
-        <v>235.787490883202</v>
+        <v>236.9291444528193</v>
       </c>
       <c r="D107" t="n">
-        <v>231.2701534117819</v>
+        <v>233.2877026206608</v>
       </c>
       <c r="E107" t="n">
-        <v>234.0258178710938</v>
+        <v>234.8623809814453</v>
       </c>
       <c r="F107" t="n">
-        <v>10267500</v>
+        <v>9378500</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46059</v>
+        <v>46063</v>
       </c>
       <c r="B108" t="n">
-        <v>235.1773154262319</v>
+        <v>236.1811678557945</v>
       </c>
       <c r="C108" t="n">
-        <v>237.125968199395</v>
+        <v>236.6929405807981</v>
       </c>
       <c r="D108" t="n">
-        <v>234.2128178267284</v>
+        <v>234.1144193808212</v>
       </c>
       <c r="E108" t="n">
-        <v>236.1910095214844</v>
+        <v>234.5769805908203</v>
       </c>
       <c r="F108" t="n">
-        <v>8274000</v>
+        <v>6723300</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46062</v>
+        <v>46064</v>
       </c>
       <c r="B109" t="n">
-        <v>236.4468802764997</v>
+        <v>235.5512982627408</v>
       </c>
       <c r="C109" t="n">
-        <v>236.9291290597546</v>
+        <v>237.4409032943991</v>
       </c>
       <c r="D109" t="n">
-        <v>233.2876874641771</v>
+        <v>233.6420056217357</v>
       </c>
       <c r="E109" t="n">
-        <v>234.8623657226562</v>
+        <v>237.0472412109375</v>
       </c>
       <c r="F109" t="n">
-        <v>9378500</v>
+        <v>6803900</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B110" t="n">
-        <v>236.1811678557945</v>
+        <v>236.6732529591429</v>
       </c>
       <c r="C110" t="n">
-        <v>236.6929405807981</v>
+        <v>242.4503424271597</v>
       </c>
       <c r="D110" t="n">
-        <v>234.1144193808212</v>
+        <v>235.8859137708501</v>
       </c>
       <c r="E110" t="n">
-        <v>234.5769805908203</v>
+        <v>240.6788330078125</v>
       </c>
       <c r="F110" t="n">
-        <v>6723300</v>
+        <v>10254300</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46064</v>
+        <v>46066</v>
       </c>
       <c r="B111" t="n">
-        <v>235.5512982627408</v>
+        <v>240.7181753030812</v>
       </c>
       <c r="C111" t="n">
-        <v>237.4409032943991</v>
+        <v>241.0724771605951</v>
       </c>
       <c r="D111" t="n">
-        <v>233.6420056217357</v>
+        <v>238.7695225953774</v>
       </c>
       <c r="E111" t="n">
-        <v>237.0472412109375</v>
+        <v>239.5962219238281</v>
       </c>
       <c r="F111" t="n">
-        <v>6803900</v>
+        <v>13268500</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46065</v>
+        <v>46070</v>
       </c>
       <c r="B112" t="n">
-        <v>236.6732379543034</v>
+        <v>240.2654733107899</v>
       </c>
       <c r="C112" t="n">
-        <v>242.4503270560588</v>
+        <v>240.6197751799101</v>
       </c>
       <c r="D112" t="n">
-        <v>235.8858988159272</v>
+        <v>238.0412390701625</v>
       </c>
       <c r="E112" t="n">
-        <v>240.6788177490234</v>
+        <v>239.4781341552734</v>
       </c>
       <c r="F112" t="n">
-        <v>10254300</v>
+        <v>12703000</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46066</v>
+        <v>46071</v>
       </c>
       <c r="B113" t="n">
-        <v>240.7181906333224</v>
+        <v>239.389564336343</v>
       </c>
       <c r="C113" t="n">
-        <v>241.0724925134001</v>
+        <v>241.1905976005163</v>
       </c>
       <c r="D113" t="n">
-        <v>238.7695378015177</v>
+        <v>238.9762146553066</v>
       </c>
       <c r="E113" t="n">
-        <v>239.5962371826172</v>
+        <v>241.1118621826172</v>
       </c>
       <c r="F113" t="n">
-        <v>13268500</v>
+        <v>8129700</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46070</v>
+        <v>46072</v>
       </c>
       <c r="B114" t="n">
-        <v>240.2654733107899</v>
+        <v>240.7477067024548</v>
       </c>
       <c r="C114" t="n">
-        <v>240.6197751799101</v>
+        <v>243.0506763566235</v>
       </c>
       <c r="D114" t="n">
-        <v>238.0412390701625</v>
+        <v>240.4032561468311</v>
       </c>
       <c r="E114" t="n">
-        <v>239.4781341552734</v>
+        <v>243.00146484375</v>
       </c>
       <c r="F114" t="n">
-        <v>12703000</v>
+        <v>7553900</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B115" t="n">
-        <v>239.389564336343</v>
+        <v>242.568421266413</v>
       </c>
       <c r="C115" t="n">
-        <v>241.1905976005163</v>
+        <v>242.9719346373659</v>
       </c>
       <c r="D115" t="n">
-        <v>238.9762146553066</v>
+        <v>236.4764055549244</v>
       </c>
       <c r="E115" t="n">
-        <v>241.1118621826172</v>
+        <v>238.6514282226562</v>
       </c>
       <c r="F115" t="n">
-        <v>8129700</v>
+        <v>13565800</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46072</v>
+        <v>46076</v>
       </c>
       <c r="B116" t="n">
-        <v>240.7477067024548</v>
+        <v>239.7733870753068</v>
       </c>
       <c r="C116" t="n">
-        <v>243.0506763566235</v>
+        <v>242.9030410566114</v>
       </c>
       <c r="D116" t="n">
-        <v>240.4032561468311</v>
+        <v>238.7596929857211</v>
       </c>
       <c r="E116" t="n">
-        <v>243.00146484375</v>
+        <v>241.9483947753906</v>
       </c>
       <c r="F116" t="n">
-        <v>7553900</v>
+        <v>9622700</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,25 +3459,25 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46073</v>
+        <v>46077</v>
       </c>
       <c r="B117" t="n">
-        <v>242.568421266413</v>
+        <v>242.7498156695138</v>
       </c>
       <c r="C117" t="n">
-        <v>242.9719346373659</v>
+        <v>244.6296736547229</v>
       </c>
       <c r="D117" t="n">
-        <v>236.4764055549244</v>
+        <v>241.9483872724562</v>
       </c>
       <c r="E117" t="n">
-        <v>238.6514282226562</v>
+        <v>243.6699523925781</v>
       </c>
       <c r="F117" t="n">
-        <v>13565800</v>
+        <v>7246300</v>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46076</v>
+        <v>46078</v>
       </c>
       <c r="B118" t="n">
-        <v>239.7734021969262</v>
+        <v>242.2650040664713</v>
       </c>
       <c r="C118" t="n">
-        <v>242.9030563756065</v>
+        <v>244.629674532896</v>
       </c>
       <c r="D118" t="n">
-        <v>238.7597080434106</v>
+        <v>241.1370862518812</v>
       </c>
       <c r="E118" t="n">
-        <v>241.9484100341797</v>
+        <v>242.5717163085938</v>
       </c>
       <c r="F118" t="n">
-        <v>9622700</v>
+        <v>7698200</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,25 +3511,25 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="B119" t="n">
-        <v>242.7498308706833</v>
+        <v>242.5123588943122</v>
       </c>
       <c r="C119" t="n">
-        <v>244.6296889736104</v>
+        <v>242.8685442682355</v>
       </c>
       <c r="D119" t="n">
-        <v>241.9484024234396</v>
+        <v>239.4551099080992</v>
       </c>
       <c r="E119" t="n">
-        <v>243.6699676513672</v>
+        <v>240.8897399902344</v>
       </c>
       <c r="F119" t="n">
-        <v>7246300</v>
+        <v>7172600</v>
       </c>
       <c r="G119" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="B120" t="n">
-        <v>242.2650193059668</v>
+        <v>241.4438165545137</v>
       </c>
       <c r="C120" t="n">
-        <v>244.6296899211394</v>
+        <v>246.3017849576054</v>
       </c>
       <c r="D120" t="n">
-        <v>241.1371014204259</v>
+        <v>239.9300324032001</v>
       </c>
       <c r="E120" t="n">
-        <v>242.5717315673828</v>
+        <v>245.7971801757812</v>
       </c>
       <c r="F120" t="n">
-        <v>7698200</v>
+        <v>16428600</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46079</v>
+        <v>46083</v>
       </c>
       <c r="B121" t="n">
-        <v>242.5123742558835</v>
+        <v>246.549124695673</v>
       </c>
       <c r="C121" t="n">
-        <v>242.8685596523689</v>
+        <v>249.0424223461303</v>
       </c>
       <c r="D121" t="n">
-        <v>239.4551250760139</v>
+        <v>244.2537044562187</v>
       </c>
       <c r="E121" t="n">
-        <v>240.8897552490234</v>
+        <v>245.9257965087891</v>
       </c>
       <c r="F121" t="n">
-        <v>7172600</v>
+        <v>9042400</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46080</v>
+        <v>46084</v>
       </c>
       <c r="B122" t="n">
-        <v>241.4438165545137</v>
+        <v>243.8480592687475</v>
       </c>
       <c r="C122" t="n">
-        <v>246.3017849576054</v>
+        <v>245.2530085028214</v>
       </c>
       <c r="D122" t="n">
-        <v>239.9300324032001</v>
+        <v>241.7703087256774</v>
       </c>
       <c r="E122" t="n">
-        <v>245.7971801757812</v>
+        <v>244.1349792480469</v>
       </c>
       <c r="F122" t="n">
-        <v>16428600</v>
+        <v>6178700</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="B123" t="n">
-        <v>246.549124695673</v>
+        <v>243.145575843863</v>
       </c>
       <c r="C123" t="n">
-        <v>249.0424223461303</v>
+        <v>243.9568928450567</v>
       </c>
       <c r="D123" t="n">
-        <v>244.2537044562187</v>
+        <v>240.6028050981046</v>
       </c>
       <c r="E123" t="n">
-        <v>245.9257965087891</v>
+        <v>242.7003479003906</v>
       </c>
       <c r="F123" t="n">
-        <v>9042400</v>
+        <v>5768000</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46084</v>
+        <v>46086</v>
       </c>
       <c r="B124" t="n">
-        <v>243.8480592687475</v>
+        <v>240.0586452528019</v>
       </c>
       <c r="C124" t="n">
-        <v>245.2530085028214</v>
+        <v>240.424719212307</v>
       </c>
       <c r="D124" t="n">
-        <v>241.7703087256774</v>
+        <v>233.4296388594088</v>
       </c>
       <c r="E124" t="n">
-        <v>244.1349792480469</v>
+        <v>237.0904388427734</v>
       </c>
       <c r="F124" t="n">
-        <v>6178700</v>
+        <v>9375400</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46085</v>
+        <v>46087</v>
       </c>
       <c r="B125" t="n">
-        <v>243.1455911306439</v>
+        <v>235.596428770922</v>
       </c>
       <c r="C125" t="n">
-        <v>243.9569081828458</v>
+        <v>238.2381306285037</v>
       </c>
       <c r="D125" t="n">
-        <v>240.6028202250193</v>
+        <v>232.9349346436922</v>
       </c>
       <c r="E125" t="n">
-        <v>242.7003631591797</v>
+        <v>237.8522644042969</v>
       </c>
       <c r="F125" t="n">
-        <v>5768000</v>
+        <v>7179800</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="B126" t="n">
-        <v>240.0586607026203</v>
+        <v>238.3173005129137</v>
       </c>
       <c r="C126" t="n">
-        <v>240.4247346856854</v>
+        <v>241.5031767703235</v>
       </c>
       <c r="D126" t="n">
-        <v>233.4296538825942</v>
+        <v>237.4960948841201</v>
       </c>
       <c r="E126" t="n">
-        <v>237.0904541015625</v>
+        <v>240.0190734863281</v>
       </c>
       <c r="F126" t="n">
-        <v>9375400</v>
+        <v>7844000</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46087</v>
+        <v>46091</v>
       </c>
       <c r="B127" t="n">
-        <v>235.5964438849938</v>
+        <v>239.732151823879</v>
       </c>
       <c r="C127" t="n">
-        <v>238.238145912047</v>
+        <v>242.4035346970428</v>
       </c>
       <c r="D127" t="n">
-        <v>232.9349495870229</v>
+        <v>238.2678408210546</v>
       </c>
       <c r="E127" t="n">
-        <v>237.8522796630859</v>
+        <v>241.1272125244141</v>
       </c>
       <c r="F127" t="n">
-        <v>7179800</v>
+        <v>7214100</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46090</v>
+        <v>46092</v>
       </c>
       <c r="B128" t="n">
-        <v>238.3172853623119</v>
+        <v>240.2960869196001</v>
       </c>
       <c r="C128" t="n">
-        <v>241.5031614171852</v>
+        <v>241.1074039007698</v>
       </c>
       <c r="D128" t="n">
-        <v>237.496079785725</v>
+        <v>238.802095160397</v>
       </c>
       <c r="E128" t="n">
-        <v>240.0190582275391</v>
+        <v>240.4148254394531</v>
       </c>
       <c r="F128" t="n">
-        <v>7844000</v>
+        <v>6933200</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46091</v>
+        <v>46093</v>
       </c>
       <c r="B129" t="n">
-        <v>239.732151823879</v>
+        <v>238.9010593075404</v>
       </c>
       <c r="C129" t="n">
-        <v>242.4035346970428</v>
+        <v>241.8098890629796</v>
       </c>
       <c r="D129" t="n">
-        <v>238.2678408210546</v>
+        <v>237.7533491444783</v>
       </c>
       <c r="E129" t="n">
-        <v>241.1272125244141</v>
+        <v>239.4748992919922</v>
       </c>
       <c r="F129" t="n">
-        <v>7214100</v>
+        <v>7710200</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46092</v>
+        <v>46094</v>
       </c>
       <c r="B130" t="n">
-        <v>240.2960869196001</v>
+        <v>241.6219129804633</v>
       </c>
       <c r="C130" t="n">
-        <v>241.1074039007698</v>
+        <v>242.9872777226232</v>
       </c>
       <c r="D130" t="n">
-        <v>238.802095160397</v>
+        <v>238.940626430393</v>
       </c>
       <c r="E130" t="n">
-        <v>240.4148254394531</v>
+        <v>238.9604187011719</v>
       </c>
       <c r="F130" t="n">
-        <v>6933200</v>
+        <v>6415300</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46093</v>
+        <v>46097</v>
       </c>
       <c r="B131" t="n">
-        <v>238.9010440853151</v>
+        <v>241.3349760333344</v>
       </c>
       <c r="C131" t="n">
-        <v>241.8098736554103</v>
+        <v>242.4628939057684</v>
       </c>
       <c r="D131" t="n">
-        <v>237.7533339953824</v>
+        <v>239.1088211458664</v>
       </c>
       <c r="E131" t="n">
-        <v>239.4748840332031</v>
+        <v>240.6127166748047</v>
       </c>
       <c r="F131" t="n">
-        <v>7710200</v>
+        <v>7571500</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46094</v>
+        <v>46098</v>
       </c>
       <c r="B132" t="n">
-        <v>241.6218975517249</v>
+        <v>240.99857884995</v>
       </c>
       <c r="C132" t="n">
-        <v>242.9872622066995</v>
+        <v>241.5526416415011</v>
       </c>
       <c r="D132" t="n">
-        <v>238.9406111728678</v>
+        <v>234.7059805370448</v>
       </c>
       <c r="E132" t="n">
-        <v>238.9604034423828</v>
+        <v>235.5865478515625</v>
       </c>
       <c r="F132" t="n">
-        <v>6415300</v>
+        <v>7281800</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="B133" t="n">
-        <v>241.3349607287423</v>
+        <v>235.349094010365</v>
       </c>
       <c r="C133" t="n">
-        <v>242.4628785296478</v>
+        <v>236.5759581604242</v>
       </c>
       <c r="D133" t="n">
-        <v>239.1088059824489</v>
+        <v>232.9250616652477</v>
       </c>
       <c r="E133" t="n">
-        <v>240.6127014160156</v>
+        <v>234.7653503417969</v>
       </c>
       <c r="F133" t="n">
-        <v>7571500</v>
+        <v>6811500</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46098</v>
+        <v>46100</v>
       </c>
       <c r="B134" t="n">
-        <v>240.99857884995</v>
+        <v>235.814102878936</v>
       </c>
       <c r="C134" t="n">
-        <v>241.5526416415011</v>
+        <v>236.7243510378414</v>
       </c>
       <c r="D134" t="n">
-        <v>234.7059805370448</v>
+        <v>233.80561773863</v>
       </c>
       <c r="E134" t="n">
-        <v>235.5865478515625</v>
+        <v>235.0819549560547</v>
       </c>
       <c r="F134" t="n">
-        <v>7281800</v>
+        <v>7511500</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46099</v>
+        <v>46101</v>
       </c>
       <c r="B135" t="n">
-        <v>235.349078713635</v>
+        <v>234.3201136195421</v>
       </c>
       <c r="C135" t="n">
-        <v>236.5759427839531</v>
+        <v>235.764632308021</v>
       </c>
       <c r="D135" t="n">
-        <v>232.9250465260699</v>
+        <v>232.0148047922595</v>
       </c>
       <c r="E135" t="n">
-        <v>234.7653350830078</v>
+        <v>232.8755798339844</v>
       </c>
       <c r="F135" t="n">
-        <v>6811500</v>
+        <v>17156600</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46100</v>
+        <v>46104</v>
       </c>
       <c r="B136" t="n">
-        <v>235.814102878936</v>
+        <v>234.884060828395</v>
       </c>
       <c r="C136" t="n">
-        <v>236.7243510378414</v>
+        <v>235.7844203946137</v>
       </c>
       <c r="D136" t="n">
-        <v>233.80561773863</v>
+        <v>231.7674501417346</v>
       </c>
       <c r="E136" t="n">
-        <v>235.0819549560547</v>
+        <v>232.925048828125</v>
       </c>
       <c r="F136" t="n">
-        <v>7511500</v>
+        <v>7313700</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46101</v>
+        <v>46105</v>
       </c>
       <c r="B137" t="n">
-        <v>234.3201136195421</v>
+        <v>231.6586126149741</v>
       </c>
       <c r="C137" t="n">
-        <v>235.764632308021</v>
+        <v>233.4989011687466</v>
       </c>
       <c r="D137" t="n">
-        <v>232.0148047922595</v>
+        <v>229.7787546189723</v>
       </c>
       <c r="E137" t="n">
-        <v>232.8755798339844</v>
+        <v>232.7766418457031</v>
       </c>
       <c r="F137" t="n">
-        <v>17156600</v>
+        <v>9046200</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="B138" t="n">
-        <v>234.884060828395</v>
+        <v>234.2904343153693</v>
       </c>
       <c r="C138" t="n">
-        <v>235.7844203946137</v>
+        <v>238.9010520004889</v>
       </c>
       <c r="D138" t="n">
-        <v>231.7674501417346</v>
+        <v>233.2317667584392</v>
       </c>
       <c r="E138" t="n">
-        <v>232.925048828125</v>
+        <v>237.3872528076172</v>
       </c>
       <c r="F138" t="n">
-        <v>7313700</v>
+        <v>6456400</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B139" t="n">
-        <v>231.6586126149741</v>
+        <v>237.4565300874115</v>
       </c>
       <c r="C139" t="n">
-        <v>233.4989011687466</v>
+        <v>239.0890376929306</v>
       </c>
       <c r="D139" t="n">
-        <v>229.7787546189723</v>
+        <v>236.3978624775069</v>
       </c>
       <c r="E139" t="n">
-        <v>232.7766418457031</v>
+        <v>236.70458984375</v>
       </c>
       <c r="F139" t="n">
-        <v>9046200</v>
+        <v>5171400</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="B140" t="n">
-        <v>234.2904343153693</v>
+        <v>238.6339116976677</v>
       </c>
       <c r="C140" t="n">
-        <v>238.9010520004889</v>
+        <v>240.1081112682183</v>
       </c>
       <c r="D140" t="n">
-        <v>233.2317667584392</v>
+        <v>236.5957456438558</v>
       </c>
       <c r="E140" t="n">
-        <v>237.3872528076172</v>
+        <v>237.9017486572266</v>
       </c>
       <c r="F140" t="n">
-        <v>6456400</v>
+        <v>7617600</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="B141" t="n">
-        <v>237.4565300874115</v>
+        <v>240.9095376592209</v>
       </c>
       <c r="C141" t="n">
-        <v>239.0890376929306</v>
+        <v>241.6219084230326</v>
       </c>
       <c r="D141" t="n">
-        <v>236.3978624775069</v>
+        <v>237.9611083490254</v>
       </c>
       <c r="E141" t="n">
-        <v>236.70458984375</v>
+        <v>239.9201354980469</v>
       </c>
       <c r="F141" t="n">
-        <v>5171400</v>
+        <v>7241300</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="B142" t="n">
-        <v>238.6339116976677</v>
+        <v>240.4346190736229</v>
       </c>
       <c r="C142" t="n">
-        <v>240.1081112682183</v>
+        <v>242.7300393849503</v>
       </c>
       <c r="D142" t="n">
-        <v>236.5957456438558</v>
+        <v>240.0784336838334</v>
       </c>
       <c r="E142" t="n">
-        <v>237.9017486572266</v>
+        <v>241.8494720458984</v>
       </c>
       <c r="F142" t="n">
-        <v>7617600</v>
+        <v>7554200</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="B143" t="n">
-        <v>240.9095376592209</v>
+        <v>242.9971782498834</v>
       </c>
       <c r="C143" t="n">
-        <v>241.6219084230326</v>
+        <v>244.580212658809</v>
       </c>
       <c r="D143" t="n">
-        <v>237.9611083490254</v>
+        <v>241.1568896154117</v>
       </c>
       <c r="E143" t="n">
-        <v>239.9201354980469</v>
+        <v>241.5328521728516</v>
       </c>
       <c r="F143" t="n">
-        <v>7241300</v>
+        <v>6314600</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="B144" t="n">
-        <v>240.4346190736229</v>
+        <v>242.5123641523277</v>
       </c>
       <c r="C144" t="n">
-        <v>242.7300393849503</v>
+        <v>244.5901147281089</v>
       </c>
       <c r="D144" t="n">
-        <v>240.0784336838334</v>
+        <v>239.3066957175141</v>
       </c>
       <c r="E144" t="n">
-        <v>241.8494720458984</v>
+        <v>240.4642944335938</v>
       </c>
       <c r="F144" t="n">
-        <v>7554200</v>
+        <v>6878700</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B145" t="n">
-        <v>242.9971782498834</v>
+        <v>240.0784329225297</v>
       </c>
       <c r="C145" t="n">
-        <v>244.580212658809</v>
+        <v>240.9392230850874</v>
       </c>
       <c r="D145" t="n">
-        <v>241.1568896154117</v>
+        <v>237.9512242744999</v>
       </c>
       <c r="E145" t="n">
-        <v>241.5328521728516</v>
+        <v>238.4162445068359</v>
       </c>
       <c r="F145" t="n">
-        <v>6314600</v>
+        <v>4442400</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46114</v>
+        <v>46119</v>
       </c>
       <c r="B146" t="n">
-        <v>242.5123641523277</v>
+        <v>238.2282554079276</v>
       </c>
       <c r="C146" t="n">
-        <v>244.5901147281089</v>
+        <v>238.2282554079276</v>
       </c>
       <c r="D146" t="n">
-        <v>239.3066957175141</v>
+        <v>233.5088027877857</v>
       </c>
       <c r="E146" t="n">
-        <v>240.4642944335938</v>
+        <v>235.8833770751953</v>
       </c>
       <c r="F146" t="n">
-        <v>6878700</v>
+        <v>6241100</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46118</v>
+        <v>46120</v>
       </c>
       <c r="B147" t="n">
-        <v>240.0784175573595</v>
+        <v>234.1321342347395</v>
       </c>
       <c r="C147" t="n">
-        <v>240.9392076648261</v>
+        <v>238.7724329332046</v>
       </c>
       <c r="D147" t="n">
-        <v>237.9512090454724</v>
+        <v>231.4211667922781</v>
       </c>
       <c r="E147" t="n">
-        <v>238.4162292480469</v>
+        <v>238.7427520751953</v>
       </c>
       <c r="F147" t="n">
-        <v>4442400</v>
+        <v>8771100</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="B148" t="n">
-        <v>238.2282554079276</v>
+        <v>238.7427511835681</v>
       </c>
       <c r="C148" t="n">
-        <v>238.2282554079276</v>
+        <v>241.612011492337</v>
       </c>
       <c r="D148" t="n">
-        <v>233.5088027877857</v>
+        <v>237.9907958579282</v>
       </c>
       <c r="E148" t="n">
-        <v>235.8833770751953</v>
+        <v>238.7526397705078</v>
       </c>
       <c r="F148" t="n">
-        <v>6241100</v>
+        <v>6216500</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="B149" t="n">
-        <v>234.1321342347395</v>
+        <v>239.4353230782619</v>
       </c>
       <c r="C149" t="n">
-        <v>238.7724329332046</v>
+        <v>239.6925622052984</v>
       </c>
       <c r="D149" t="n">
-        <v>231.4211667922781</v>
+        <v>235.3886718611059</v>
       </c>
       <c r="E149" t="n">
-        <v>238.7427520751953</v>
+        <v>235.9328460693359</v>
       </c>
       <c r="F149" t="n">
-        <v>8771100</v>
+        <v>7354500</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46121</v>
+        <v>46125</v>
       </c>
       <c r="B150" t="n">
-        <v>238.7427511835681</v>
+        <v>235.1907903330984</v>
       </c>
       <c r="C150" t="n">
-        <v>241.612011492337</v>
+        <v>235.8635765445355</v>
       </c>
       <c r="D150" t="n">
-        <v>237.9907958579282</v>
+        <v>232.6875890190388</v>
       </c>
       <c r="E150" t="n">
-        <v>238.7526397705078</v>
+        <v>235.4381408691406</v>
       </c>
       <c r="F150" t="n">
-        <v>6216500</v>
+        <v>7663600</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="B151" t="n">
-        <v>239.4353230782619</v>
+        <v>232.5193972079424</v>
       </c>
       <c r="C151" t="n">
-        <v>239.6925622052984</v>
+        <v>239.6233125984258</v>
       </c>
       <c r="D151" t="n">
-        <v>235.3886718611059</v>
+        <v>230.7780548336423</v>
       </c>
       <c r="E151" t="n">
-        <v>235.9328460693359</v>
+        <v>237.5554656982422</v>
       </c>
       <c r="F151" t="n">
-        <v>7354500</v>
+        <v>10318700</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="B152" t="n">
-        <v>235.1907903330984</v>
+        <v>237.3971547010872</v>
       </c>
       <c r="C152" t="n">
-        <v>235.8635765445355</v>
+        <v>237.8720635067345</v>
       </c>
       <c r="D152" t="n">
-        <v>232.6875890190388</v>
+        <v>234.2409594215431</v>
       </c>
       <c r="E152" t="n">
-        <v>235.4381408691406</v>
+        <v>236.1406097412109</v>
       </c>
       <c r="F152" t="n">
-        <v>7663600</v>
+        <v>6463500</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="B153" t="n">
-        <v>232.5193972079424</v>
+        <v>234.9038500080299</v>
       </c>
       <c r="C153" t="n">
-        <v>239.6233125984258</v>
+        <v>235.6162207436799</v>
       </c>
       <c r="D153" t="n">
-        <v>230.7780548336423</v>
+        <v>229.6600157416919</v>
       </c>
       <c r="E153" t="n">
-        <v>237.5554656982422</v>
+        <v>232.0543670654297</v>
       </c>
       <c r="F153" t="n">
-        <v>10318700</v>
+        <v>8668900</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46127</v>
+        <v>46129</v>
       </c>
       <c r="B154" t="n">
-        <v>237.3971547010872</v>
+        <v>231.8762966548944</v>
       </c>
       <c r="C154" t="n">
-        <v>237.8720635067345</v>
+        <v>233.0437839864675</v>
       </c>
       <c r="D154" t="n">
-        <v>234.2409594215431</v>
+        <v>229.5808763393496</v>
       </c>
       <c r="E154" t="n">
-        <v>236.1406097412109</v>
+        <v>231.6981964111328</v>
       </c>
       <c r="F154" t="n">
-        <v>6463500</v>
+        <v>8946300</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="B155" t="n">
-        <v>234.9038654541874</v>
+        <v>232.321525670587</v>
       </c>
       <c r="C155" t="n">
-        <v>235.6162362366795</v>
+        <v>232.7667536363879</v>
       </c>
       <c r="D155" t="n">
-        <v>229.6600308430398</v>
+        <v>227.0974833184763</v>
       </c>
       <c r="E155" t="n">
-        <v>232.0543823242188</v>
+        <v>228.2451934814453</v>
       </c>
       <c r="F155" t="n">
-        <v>8668900</v>
+        <v>7810500</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="B156" t="n">
-        <v>231.8762966548944</v>
+        <v>226.9193941968888</v>
       </c>
       <c r="C156" t="n">
-        <v>233.0437839864675</v>
+        <v>227.2557873120845</v>
       </c>
       <c r="D156" t="n">
-        <v>229.5808763393496</v>
+        <v>222.3186650386415</v>
       </c>
       <c r="E156" t="n">
-        <v>231.6981964111328</v>
+        <v>223.7631988525391</v>
       </c>
       <c r="F156" t="n">
-        <v>8946300</v>
+        <v>11681200</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="B157" t="n">
-        <v>232.321525670587</v>
+        <v>223.7829810531976</v>
       </c>
       <c r="C157" t="n">
-        <v>232.7667536363879</v>
+        <v>225.0692069251634</v>
       </c>
       <c r="D157" t="n">
-        <v>227.0974833184763</v>
+        <v>221.4084218257834</v>
       </c>
       <c r="E157" t="n">
-        <v>228.2451934814453</v>
+        <v>223.7038421630859</v>
       </c>
       <c r="F157" t="n">
-        <v>7810500</v>
+        <v>9003400</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B158" t="n">
-        <v>226.9193787228735</v>
+        <v>224.8416356959219</v>
       </c>
       <c r="C158" t="n">
-        <v>227.2557718151299</v>
+        <v>228.9377599403605</v>
       </c>
       <c r="D158" t="n">
-        <v>222.3186498783577</v>
+        <v>224.6239660179549</v>
       </c>
       <c r="E158" t="n">
-        <v>223.76318359375</v>
+        <v>228.2055969238281</v>
       </c>
       <c r="F158" t="n">
-        <v>11681200</v>
+        <v>7097600</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="B159" t="n">
-        <v>223.7829810531976</v>
+        <v>226.6027887018479</v>
       </c>
       <c r="C159" t="n">
-        <v>225.0692069251634</v>
+        <v>227.5526214735122</v>
       </c>
       <c r="D159" t="n">
-        <v>221.4084218257834</v>
+        <v>224.6140956793093</v>
       </c>
       <c r="E159" t="n">
-        <v>223.7038421630859</v>
+        <v>225.0890045166016</v>
       </c>
       <c r="F159" t="n">
-        <v>9003400</v>
+        <v>6067500</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46135</v>
+        <v>46139</v>
       </c>
       <c r="B160" t="n">
-        <v>224.8416507297823</v>
+        <v>223.3773245484034</v>
       </c>
       <c r="C160" t="n">
-        <v>228.937775248105</v>
+        <v>225.4946445162854</v>
       </c>
       <c r="D160" t="n">
-        <v>224.623981037261</v>
+        <v>221.9723753264516</v>
       </c>
       <c r="E160" t="n">
-        <v>228.2056121826172</v>
+        <v>222.9518737792969</v>
       </c>
       <c r="F160" t="n">
-        <v>7097600</v>
+        <v>7897800</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="B161" t="n">
-        <v>226.6027733404394</v>
+        <v>225.316553812185</v>
       </c>
       <c r="C161" t="n">
-        <v>227.5526060477145</v>
+        <v>228.5815840196301</v>
       </c>
       <c r="D161" t="n">
-        <v>224.6140804527143</v>
+        <v>223.9709662459624</v>
       </c>
       <c r="E161" t="n">
-        <v>225.0889892578125</v>
+        <v>225.3759155273438</v>
       </c>
       <c r="F161" t="n">
-        <v>6067500</v>
+        <v>7179800</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46139</v>
+        <v>46141</v>
       </c>
       <c r="B162" t="n">
-        <v>223.3773398363102</v>
+        <v>223.1299896858621</v>
       </c>
       <c r="C162" t="n">
-        <v>225.4946599491012</v>
+        <v>226.2861851379911</v>
       </c>
       <c r="D162" t="n">
-        <v>221.972390518204</v>
+        <v>222.4769806067155</v>
       </c>
       <c r="E162" t="n">
-        <v>222.9518890380859</v>
+        <v>224.9405975341797</v>
       </c>
       <c r="F162" t="n">
-        <v>7897800</v>
+        <v>7071100</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="B163" t="n">
-        <v>225.316553812185</v>
+        <v>225.534219851175</v>
       </c>
       <c r="C163" t="n">
-        <v>228.5815840196301</v>
+        <v>228.7102074345108</v>
       </c>
       <c r="D163" t="n">
-        <v>223.9709662459624</v>
+        <v>225.3957041523519</v>
       </c>
       <c r="E163" t="n">
-        <v>225.3759155273438</v>
+        <v>227.4140930175781</v>
       </c>
       <c r="F163" t="n">
-        <v>7179800</v>
+        <v>8157200</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46141</v>
+        <v>46143</v>
       </c>
       <c r="B164" t="n">
-        <v>223.1299745498951</v>
+        <v>226.6324494909732</v>
       </c>
       <c r="C164" t="n">
-        <v>226.2861697879244</v>
+        <v>227.3349316460146</v>
       </c>
       <c r="D164" t="n">
-        <v>222.4769655150452</v>
+        <v>224.6140757884101</v>
       </c>
       <c r="E164" t="n">
-        <v>224.9405822753906</v>
+        <v>224.7822723388672</v>
       </c>
       <c r="F164" t="n">
-        <v>7071100</v>
+        <v>6863600</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="B165" t="n">
-        <v>225.534219851175</v>
+        <v>223.12007375354</v>
       </c>
       <c r="C165" t="n">
-        <v>228.7102074345108</v>
+        <v>224.6635537914519</v>
       </c>
       <c r="D165" t="n">
-        <v>225.3957041523519</v>
+        <v>221.2105348477109</v>
       </c>
       <c r="E165" t="n">
-        <v>227.4140930175781</v>
+        <v>221.8239593505859</v>
       </c>
       <c r="F165" t="n">
-        <v>8157200</v>
+        <v>8215200</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46143</v>
+        <v>46147</v>
       </c>
       <c r="B166" t="n">
-        <v>226.6324494909732</v>
+        <v>223.0013599943453</v>
       </c>
       <c r="C166" t="n">
-        <v>227.3349316460146</v>
+        <v>224.1292778920903</v>
       </c>
       <c r="D166" t="n">
-        <v>224.6140757884101</v>
+        <v>222.5165474841354</v>
       </c>
       <c r="E166" t="n">
-        <v>224.7822723388672</v>
+        <v>223.15966796875</v>
       </c>
       <c r="F166" t="n">
-        <v>6863600</v>
+        <v>5556700</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46146</v>
+        <v>46148</v>
       </c>
       <c r="B167" t="n">
-        <v>223.12007375354</v>
+        <v>222.86284542864</v>
       </c>
       <c r="C167" t="n">
-        <v>224.6635537914519</v>
+        <v>223.9412902027537</v>
       </c>
       <c r="D167" t="n">
-        <v>221.2105348477109</v>
+        <v>220.5872173504634</v>
       </c>
       <c r="E167" t="n">
-        <v>221.8239593505859</v>
+        <v>222.2395172119141</v>
       </c>
       <c r="F167" t="n">
-        <v>8215200</v>
+        <v>7982300</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="B168" t="n">
-        <v>223.0013599943453</v>
+        <v>222.3978024591847</v>
       </c>
       <c r="C168" t="n">
-        <v>224.1292778920903</v>
+        <v>222.3978024591847</v>
       </c>
       <c r="D168" t="n">
-        <v>222.5165474841354</v>
+        <v>218.2917897898664</v>
       </c>
       <c r="E168" t="n">
-        <v>223.15966796875</v>
+        <v>220.15185546875</v>
       </c>
       <c r="F168" t="n">
-        <v>5556700</v>
+        <v>7269700</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="B169" t="n">
-        <v>222.86284542864</v>
+        <v>220.5773139289545</v>
       </c>
       <c r="C169" t="n">
-        <v>223.9412902027537</v>
+        <v>221.0027495995129</v>
       </c>
       <c r="D169" t="n">
-        <v>220.5872173504634</v>
+        <v>218.578717393272</v>
       </c>
       <c r="E169" t="n">
-        <v>222.2395172119141</v>
+        <v>218.9744873046875</v>
       </c>
       <c r="F169" t="n">
-        <v>7982300</v>
+        <v>5550600</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="B170" t="n">
-        <v>222.397817873641</v>
+        <v>218.9744932439037</v>
       </c>
       <c r="C170" t="n">
-        <v>222.397817873641</v>
+        <v>220.9137130226623</v>
       </c>
       <c r="D170" t="n">
-        <v>218.2918049197337</v>
+        <v>218.034549114472</v>
       </c>
       <c r="E170" t="n">
-        <v>220.1518707275391</v>
+        <v>219.0833129882812</v>
       </c>
       <c r="F170" t="n">
-        <v>7269700</v>
+        <v>6223200</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="B171" t="n">
-        <v>220.5773139289545</v>
+        <v>220.6366899653626</v>
       </c>
       <c r="C171" t="n">
-        <v>221.0027495995129</v>
+        <v>225.2374041432973</v>
       </c>
       <c r="D171" t="n">
-        <v>218.578717393272</v>
+        <v>219.3009909603728</v>
       </c>
       <c r="E171" t="n">
-        <v>218.9744873046875</v>
+        <v>221.8833312988281</v>
       </c>
       <c r="F171" t="n">
-        <v>5550600</v>
+        <v>8632500</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B172" t="n">
-        <v>218.9744932439037</v>
+        <v>223.4268017505994</v>
       </c>
       <c r="C172" t="n">
-        <v>220.9137130226623</v>
+        <v>228.3540202522719</v>
       </c>
       <c r="D172" t="n">
-        <v>218.034549114472</v>
+        <v>223.0508241008666</v>
       </c>
       <c r="E172" t="n">
-        <v>219.0833129882812</v>
+        <v>227.9780426025391</v>
       </c>
       <c r="F172" t="n">
-        <v>6223200</v>
+        <v>7464500</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="B173" t="n">
-        <v>220.6366747923043</v>
+        <v>228.5518965755589</v>
       </c>
       <c r="C173" t="n">
-        <v>225.2373886538506</v>
+        <v>229.3038367743656</v>
       </c>
       <c r="D173" t="n">
-        <v>219.3009758791698</v>
+        <v>226.7314002434507</v>
       </c>
       <c r="E173" t="n">
-        <v>221.8833160400391</v>
+        <v>228.3540191650391</v>
       </c>
       <c r="F173" t="n">
-        <v>8632500</v>
+        <v>6974400</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="B174" t="n">
-        <v>223.4268017505994</v>
+        <v>228.324343449484</v>
       </c>
       <c r="C174" t="n">
-        <v>228.3540202522719</v>
+        <v>229.6798195939985</v>
       </c>
       <c r="D174" t="n">
-        <v>223.0508241008666</v>
+        <v>224.0402302332647</v>
       </c>
       <c r="E174" t="n">
-        <v>227.9780426025391</v>
+        <v>224.307373046875</v>
       </c>
       <c r="F174" t="n">
-        <v>7464500</v>
+        <v>12167000</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46156</v>
+        <v>46160</v>
       </c>
       <c r="B175" t="n">
-        <v>228.5519118475702</v>
+        <v>224.3073719260098</v>
       </c>
       <c r="C175" t="n">
-        <v>229.3038520966222</v>
+        <v>227.2656747432453</v>
       </c>
       <c r="D175" t="n">
-        <v>226.7314153938151</v>
+        <v>223.466374045218</v>
       </c>
       <c r="E175" t="n">
-        <v>228.3540344238281</v>
+        <v>226.4939422607422</v>
       </c>
       <c r="F175" t="n">
-        <v>6974400</v>
+        <v>10141600</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="B176" t="n">
-        <v>228.324343449484</v>
+        <v>226.5137209227187</v>
       </c>
       <c r="C176" t="n">
-        <v>229.6798195939985</v>
+        <v>228.4034825714771</v>
       </c>
       <c r="D176" t="n">
-        <v>224.0402302332647</v>
+        <v>225.6232499676584</v>
       </c>
       <c r="E176" t="n">
-        <v>224.307373046875</v>
+        <v>227.5624847412109</v>
       </c>
       <c r="F176" t="n">
-        <v>12167000</v>
+        <v>9677900</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="B177" t="n">
-        <v>224.3073719260098</v>
+        <v>229.2345877493695</v>
       </c>
       <c r="C177" t="n">
-        <v>227.2656747432453</v>
+        <v>229.5413000019429</v>
       </c>
       <c r="D177" t="n">
-        <v>223.466374045218</v>
+        <v>226.7412900911319</v>
       </c>
       <c r="E177" t="n">
-        <v>226.4939422607422</v>
+        <v>226.8897094726562</v>
       </c>
       <c r="F177" t="n">
-        <v>10141600</v>
+        <v>7353800</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46161</v>
+        <v>46163</v>
       </c>
       <c r="B178" t="n">
-        <v>226.5137209227187</v>
+        <v>226.8897069691897</v>
       </c>
       <c r="C178" t="n">
-        <v>228.4034825714771</v>
+        <v>229.432462629467</v>
       </c>
       <c r="D178" t="n">
-        <v>225.6232499676584</v>
+        <v>224.9405835372236</v>
       </c>
       <c r="E178" t="n">
-        <v>227.5624847412109</v>
+        <v>229.2741546630859</v>
       </c>
       <c r="F178" t="n">
-        <v>9677900</v>
+        <v>5239000</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="B179" t="n">
-        <v>229.2345877493695</v>
+        <v>230.5307110319731</v>
       </c>
       <c r="C179" t="n">
-        <v>229.5413000019429</v>
+        <v>233.0042165151488</v>
       </c>
       <c r="D179" t="n">
-        <v>226.7412900911319</v>
+        <v>230.2536796256238</v>
       </c>
       <c r="E179" t="n">
-        <v>226.8897094726562</v>
+        <v>231.8565063476562</v>
       </c>
       <c r="F179" t="n">
-        <v>7353800</v>
+        <v>5462300</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,25 +5097,25 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46163</v>
+        <v>46168</v>
       </c>
       <c r="B180" t="n">
-        <v>226.8897069691897</v>
+        <v>231.856506324529</v>
       </c>
       <c r="C180" t="n">
-        <v>229.432462629467</v>
+        <v>232.0953339431715</v>
       </c>
       <c r="D180" t="n">
-        <v>224.9405835372236</v>
+        <v>227.9557463234551</v>
       </c>
       <c r="E180" t="n">
-        <v>229.2741546630859</v>
+        <v>229.0503387451172</v>
       </c>
       <c r="F180" t="n">
-        <v>5239000</v>
+        <v>6619600</v>
       </c>
       <c r="G180" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46164</v>
+        <v>46169</v>
       </c>
       <c r="B181" t="n">
-        <v>230.5307110319731</v>
+        <v>228.8513234809034</v>
       </c>
       <c r="C181" t="n">
-        <v>233.0042165151488</v>
+        <v>231.7470457253588</v>
       </c>
       <c r="D181" t="n">
-        <v>230.2536796256238</v>
+        <v>227.896043373475</v>
       </c>
       <c r="E181" t="n">
-        <v>231.8565063476562</v>
+        <v>230.1548919677734</v>
       </c>
       <c r="F181" t="n">
-        <v>5462300</v>
+        <v>5835500</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,25 +5149,25 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="B182" t="n">
-        <v>231.856506324529</v>
+        <v>228.9010720691913</v>
       </c>
       <c r="C182" t="n">
-        <v>232.0953339431715</v>
+        <v>230.7320381891827</v>
       </c>
       <c r="D182" t="n">
-        <v>227.9557463234551</v>
+        <v>228.6025413534768</v>
       </c>
       <c r="E182" t="n">
-        <v>229.0503387451172</v>
+        <v>229.6672973632812</v>
       </c>
       <c r="F182" t="n">
-        <v>6619600</v>
+        <v>7193400</v>
       </c>
       <c r="G182" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="B183" t="n">
-        <v>228.8513234809034</v>
+        <v>230.0951744973679</v>
       </c>
       <c r="C183" t="n">
-        <v>231.7470457253588</v>
+        <v>230.36385365377</v>
       </c>
       <c r="D183" t="n">
-        <v>227.896043373475</v>
+        <v>223.4877626284344</v>
       </c>
       <c r="E183" t="n">
-        <v>230.1548919677734</v>
+        <v>224.2241363525391</v>
       </c>
       <c r="F183" t="n">
-        <v>5835500</v>
+        <v>13897700</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46170</v>
+        <v>46174</v>
       </c>
       <c r="B184" t="n">
-        <v>228.9010720691913</v>
+        <v>222.1045945004449</v>
       </c>
       <c r="C184" t="n">
-        <v>230.7320381891827</v>
+        <v>223.3385143974124</v>
       </c>
       <c r="D184" t="n">
-        <v>228.6025413534768</v>
+        <v>219.7561761055088</v>
       </c>
       <c r="E184" t="n">
-        <v>229.6672973632812</v>
+        <v>222.4130706787109</v>
       </c>
       <c r="F184" t="n">
-        <v>7193400</v>
+        <v>8041000</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46171</v>
+        <v>46175</v>
       </c>
       <c r="B185" t="n">
-        <v>230.0951744973679</v>
+        <v>221.4876358909895</v>
       </c>
       <c r="C185" t="n">
-        <v>230.36385365377</v>
+        <v>224.3933034528787</v>
       </c>
       <c r="D185" t="n">
-        <v>223.4877626284344</v>
+        <v>220.0845521676131</v>
       </c>
       <c r="E185" t="n">
-        <v>224.2241363525391</v>
+        <v>221.7961120605469</v>
       </c>
       <c r="F185" t="n">
-        <v>13897700</v>
+        <v>5669000</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="B186" t="n">
-        <v>222.1045945004449</v>
+        <v>221.3582777644383</v>
       </c>
       <c r="C186" t="n">
-        <v>223.3385143974124</v>
+        <v>223.8261024020756</v>
       </c>
       <c r="D186" t="n">
-        <v>219.7561761055088</v>
+        <v>220.9104892689172</v>
       </c>
       <c r="E186" t="n">
-        <v>222.4130706787109</v>
+        <v>222.1444091796875</v>
       </c>
       <c r="F186" t="n">
-        <v>8041000</v>
+        <v>6507200</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="B187" t="n">
-        <v>221.4876358909895</v>
+        <v>225.9754999423843</v>
       </c>
       <c r="C187" t="n">
-        <v>224.3933034528787</v>
+        <v>227.5477475509985</v>
       </c>
       <c r="D187" t="n">
-        <v>220.0845521676131</v>
+        <v>224.7913377117005</v>
       </c>
       <c r="E187" t="n">
-        <v>221.7961120605469</v>
+        <v>227.0502014160156</v>
       </c>
       <c r="F187" t="n">
-        <v>5669000</v>
+        <v>7274800</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="B188" t="n">
-        <v>221.3582777644383</v>
+        <v>228.8712298379233</v>
       </c>
       <c r="C188" t="n">
-        <v>223.8261024020756</v>
+        <v>234.0656128776528</v>
       </c>
       <c r="D188" t="n">
-        <v>220.9104892689172</v>
+        <v>227.8761375342802</v>
       </c>
       <c r="E188" t="n">
-        <v>222.1444091796875</v>
+        <v>231.6276397705078</v>
       </c>
       <c r="F188" t="n">
-        <v>6507200</v>
+        <v>8034900</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46177</v>
+        <v>46181</v>
       </c>
       <c r="B189" t="n">
-        <v>225.9754999423843</v>
+        <v>231.6276367875738</v>
       </c>
       <c r="C189" t="n">
-        <v>227.5477475509985</v>
+        <v>233.7969306933057</v>
       </c>
       <c r="D189" t="n">
-        <v>224.7913377117005</v>
+        <v>229.428476143926</v>
       </c>
       <c r="E189" t="n">
-        <v>227.0502014160156</v>
+        <v>231.0206298828125</v>
       </c>
       <c r="F189" t="n">
-        <v>7274800</v>
+        <v>7559800</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="B190" t="n">
-        <v>228.8712298379233</v>
+        <v>231.2395468518091</v>
       </c>
       <c r="C190" t="n">
-        <v>234.0656128776528</v>
+        <v>236.5433904796373</v>
       </c>
       <c r="D190" t="n">
-        <v>227.8761375342802</v>
+        <v>229.2792138627353</v>
       </c>
       <c r="E190" t="n">
-        <v>231.6276397705078</v>
+        <v>235.8368682861328</v>
       </c>
       <c r="F190" t="n">
-        <v>8034900</v>
+        <v>8354500</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="B191" t="n">
-        <v>231.6276367875738</v>
+        <v>237.6777986497502</v>
       </c>
       <c r="C191" t="n">
-        <v>233.7969306933057</v>
+        <v>239.7475772433621</v>
       </c>
       <c r="D191" t="n">
-        <v>229.428476143926</v>
+        <v>235.886629497679</v>
       </c>
       <c r="E191" t="n">
-        <v>231.0206298828125</v>
+        <v>237.3195648193359</v>
       </c>
       <c r="F191" t="n">
-        <v>7559800</v>
+        <v>8350800</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="B192" t="n">
-        <v>231.2395468518091</v>
+        <v>238.822141602048</v>
       </c>
       <c r="C192" t="n">
-        <v>236.5433904796373</v>
+        <v>240.4142952862894</v>
       </c>
       <c r="D192" t="n">
-        <v>229.2792138627353</v>
+        <v>236.971269397276</v>
       </c>
       <c r="E192" t="n">
-        <v>235.8368682861328</v>
+        <v>237.1603393554688</v>
       </c>
       <c r="F192" t="n">
-        <v>8354500</v>
+        <v>7399000</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46183</v>
+        <v>46185</v>
       </c>
       <c r="B193" t="n">
-        <v>237.6777986497502</v>
+        <v>238.8221408093525</v>
       </c>
       <c r="C193" t="n">
-        <v>239.7475772433621</v>
+        <v>239.7276784040579</v>
       </c>
       <c r="D193" t="n">
-        <v>235.886629497679</v>
+        <v>236.354316272482</v>
       </c>
       <c r="E193" t="n">
-        <v>237.3195648193359</v>
+        <v>239.6878662109375</v>
       </c>
       <c r="F193" t="n">
-        <v>8350800</v>
+        <v>6459400</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="B194" t="n">
-        <v>238.822141602048</v>
+        <v>237.8270530309927</v>
       </c>
       <c r="C194" t="n">
-        <v>240.4142952862894</v>
+        <v>238.3245991670408</v>
       </c>
       <c r="D194" t="n">
-        <v>236.971269397276</v>
+        <v>232.4336547382997</v>
       </c>
       <c r="E194" t="n">
-        <v>237.1603393554688</v>
+        <v>234.5034484863281</v>
       </c>
       <c r="F194" t="n">
-        <v>7399000</v>
+        <v>7732000</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="B195" t="n">
-        <v>238.8221408093525</v>
+        <v>235.2099495568312</v>
       </c>
       <c r="C195" t="n">
-        <v>239.7276784040579</v>
+        <v>235.2099495568312</v>
       </c>
       <c r="D195" t="n">
-        <v>236.354316272482</v>
+        <v>229.8862151458974</v>
       </c>
       <c r="E195" t="n">
-        <v>239.6878662109375</v>
+        <v>234.0257873535156</v>
       </c>
       <c r="F195" t="n">
-        <v>6459400</v>
+        <v>7718100</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="B196" t="n">
-        <v>237.8270530309927</v>
+        <v>232.8814495345484</v>
       </c>
       <c r="C196" t="n">
-        <v>238.3245991670408</v>
+        <v>234.2745726796724</v>
       </c>
       <c r="D196" t="n">
-        <v>232.4336547382997</v>
+        <v>229.5677903566066</v>
       </c>
       <c r="E196" t="n">
-        <v>234.5034484863281</v>
+        <v>233.0506134033203</v>
       </c>
       <c r="F196" t="n">
-        <v>7732000</v>
+        <v>8548000</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="B197" t="n">
-        <v>235.2099495568312</v>
+        <v>230.6424813960874</v>
       </c>
       <c r="C197" t="n">
-        <v>235.2099495568312</v>
+        <v>231.6077220970904</v>
       </c>
       <c r="D197" t="n">
-        <v>229.8862151458974</v>
+        <v>226.4830030630252</v>
       </c>
       <c r="E197" t="n">
-        <v>234.0257873535156</v>
+        <v>227.2691192626953</v>
       </c>
       <c r="F197" t="n">
-        <v>7718100</v>
+        <v>18989800</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46190</v>
+        <v>46195</v>
       </c>
       <c r="B198" t="n">
-        <v>232.8814495345484</v>
+        <v>227.8263796240252</v>
       </c>
       <c r="C198" t="n">
-        <v>234.2745726796724</v>
+        <v>230.3141103803127</v>
       </c>
       <c r="D198" t="n">
-        <v>229.5677903566066</v>
+        <v>226.3834988221592</v>
       </c>
       <c r="E198" t="n">
-        <v>233.0506134033203</v>
+        <v>230.1548919677734</v>
       </c>
       <c r="F198" t="n">
-        <v>8548000</v>
+        <v>8518300</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46191</v>
+        <v>46196</v>
       </c>
       <c r="B199" t="n">
-        <v>230.6424813960874</v>
+        <v>234.4835421454308</v>
       </c>
       <c r="C199" t="n">
-        <v>231.6077220970904</v>
+        <v>238.6231296371808</v>
       </c>
       <c r="D199" t="n">
-        <v>226.4830030630252</v>
+        <v>233.1998797966796</v>
       </c>
       <c r="E199" t="n">
-        <v>227.2691192626953</v>
+        <v>237.9066619873047</v>
       </c>
       <c r="F199" t="n">
-        <v>18989800</v>
+        <v>11802000</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="B200" t="n">
-        <v>227.8263796240252</v>
+        <v>238.7126772290818</v>
       </c>
       <c r="C200" t="n">
-        <v>230.3141103803127</v>
+        <v>241.8472117165478</v>
       </c>
       <c r="D200" t="n">
-        <v>226.3834988221592</v>
+        <v>237.5782726810186</v>
       </c>
       <c r="E200" t="n">
-        <v>230.1548919677734</v>
+        <v>239.8172302246094</v>
       </c>
       <c r="F200" t="n">
-        <v>8518300</v>
+        <v>8139200</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46196</v>
+        <v>46198</v>
       </c>
       <c r="B201" t="n">
-        <v>234.4835421454308</v>
+        <v>240.0859235854152</v>
       </c>
       <c r="C201" t="n">
-        <v>238.6231296371808</v>
+        <v>246.9719604825856</v>
       </c>
       <c r="D201" t="n">
-        <v>233.1998797966796</v>
+        <v>239.7077836523882</v>
       </c>
       <c r="E201" t="n">
-        <v>237.9066619873047</v>
+        <v>243.6782073974609</v>
       </c>
       <c r="F201" t="n">
-        <v>11802000</v>
+        <v>10130400</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46197</v>
+        <v>46199</v>
       </c>
       <c r="B202" t="n">
-        <v>238.7126772290818</v>
+        <v>247.0515630057391</v>
       </c>
       <c r="C202" t="n">
-        <v>241.8472117165478</v>
+        <v>253.857990512684</v>
       </c>
       <c r="D202" t="n">
-        <v>237.5782726810186</v>
+        <v>246.6535169859773</v>
       </c>
       <c r="E202" t="n">
-        <v>239.8172302246094</v>
+        <v>253.4102020263672</v>
       </c>
       <c r="F202" t="n">
-        <v>8139200</v>
+        <v>16316800</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="B203" t="n">
-        <v>240.0859235854152</v>
+        <v>251.9474045302274</v>
       </c>
       <c r="C203" t="n">
-        <v>246.9719604825856</v>
+        <v>257.3109358669097</v>
       </c>
       <c r="D203" t="n">
-        <v>239.7077836523882</v>
+        <v>250.7930938975173</v>
       </c>
       <c r="E203" t="n">
-        <v>243.6782073974609</v>
+        <v>257.2413024902344</v>
       </c>
       <c r="F203" t="n">
-        <v>10130400</v>
+        <v>8608400</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46199</v>
+        <v>46203</v>
       </c>
       <c r="B204" t="n">
-        <v>247.0515630057391</v>
+        <v>257.7288999793201</v>
       </c>
       <c r="C204" t="n">
-        <v>253.857990512684</v>
+        <v>258.62447695588</v>
       </c>
       <c r="D204" t="n">
-        <v>246.6535169859773</v>
+        <v>251.9275101770222</v>
       </c>
       <c r="E204" t="n">
-        <v>253.4102020263672</v>
+        <v>252.7235870361328</v>
       </c>
       <c r="F204" t="n">
-        <v>16316800</v>
+        <v>8469500</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46202</v>
+        <v>46204</v>
       </c>
       <c r="B205" t="n">
-        <v>251.9474045302274</v>
+        <v>252.0071226458085</v>
       </c>
       <c r="C205" t="n">
-        <v>257.3109358669097</v>
+        <v>252.9524572852904</v>
       </c>
       <c r="D205" t="n">
-        <v>250.7930938975173</v>
+        <v>249.8477741968348</v>
       </c>
       <c r="E205" t="n">
-        <v>257.2413024902344</v>
+        <v>252.7335357666016</v>
       </c>
       <c r="F205" t="n">
-        <v>8608400</v>
+        <v>6516500</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46203</v>
+        <v>46205</v>
       </c>
       <c r="B206" t="n">
-        <v>257.7288999793201</v>
+        <v>254.5247047293354</v>
       </c>
       <c r="C206" t="n">
-        <v>258.62447695588</v>
+        <v>261.8087875806335</v>
       </c>
       <c r="D206" t="n">
-        <v>251.9275101770222</v>
+        <v>252.753441667793</v>
       </c>
       <c r="E206" t="n">
-        <v>252.7235870361328</v>
+        <v>261.7490844726562</v>
       </c>
       <c r="F206" t="n">
-        <v>8469500</v>
+        <v>7998700</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="B207" t="n">
-        <v>252.0071226458085</v>
+        <v>258.9528582650781</v>
       </c>
       <c r="C207" t="n">
-        <v>252.9524572852904</v>
+        <v>260.0972082397536</v>
       </c>
       <c r="D207" t="n">
-        <v>249.8477741968348</v>
+        <v>254.673943516207</v>
       </c>
       <c r="E207" t="n">
-        <v>252.7335357666016</v>
+        <v>258.0572509765625</v>
       </c>
       <c r="F207" t="n">
-        <v>6516500</v>
+        <v>6803700</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46205</v>
+        <v>46210</v>
       </c>
       <c r="B208" t="n">
-        <v>254.5247047293354</v>
+        <v>263.5899938466549</v>
       </c>
       <c r="C208" t="n">
-        <v>261.8087875806335</v>
+        <v>268.1076906797339</v>
       </c>
       <c r="D208" t="n">
-        <v>252.753441667793</v>
+        <v>262.7540896546532</v>
       </c>
       <c r="E208" t="n">
-        <v>261.7490844726562</v>
+        <v>265.9284362792969</v>
       </c>
       <c r="F208" t="n">
-        <v>7998700</v>
+        <v>9089700</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="B209" t="n">
-        <v>258.9528582650781</v>
+        <v>267.2817917945089</v>
       </c>
       <c r="C209" t="n">
-        <v>260.0972082397536</v>
+        <v>267.2817917945089</v>
       </c>
       <c r="D209" t="n">
-        <v>254.673943516207</v>
+        <v>261.8386358221884</v>
       </c>
       <c r="E209" t="n">
-        <v>258.0572509765625</v>
+        <v>262.1072998046875</v>
       </c>
       <c r="F209" t="n">
-        <v>6803700</v>
+        <v>6769400</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46210</v>
+        <v>46212</v>
       </c>
       <c r="B210" t="n">
-        <v>263.5899938466549</v>
+        <v>259.3508895364454</v>
       </c>
       <c r="C210" t="n">
-        <v>268.1076906797339</v>
+        <v>262.1570568783993</v>
       </c>
       <c r="D210" t="n">
-        <v>262.7540896546532</v>
+        <v>256.8631589924022</v>
       </c>
       <c r="E210" t="n">
-        <v>265.9284362792969</v>
+        <v>257.8283996582031</v>
       </c>
       <c r="F210" t="n">
-        <v>9089700</v>
+        <v>6426100</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="B211" t="n">
-        <v>267.2817917945089</v>
+        <v>258.9130640253377</v>
       </c>
       <c r="C211" t="n">
-        <v>267.2817917945089</v>
+        <v>260.0176018849775</v>
       </c>
       <c r="D211" t="n">
-        <v>261.8386358221884</v>
+        <v>254.2659848771424</v>
       </c>
       <c r="E211" t="n">
-        <v>262.1072998046875</v>
+        <v>255.7188262939453</v>
       </c>
       <c r="F211" t="n">
-        <v>6769400</v>
+        <v>6534700</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="B212" t="n">
-        <v>259.3508895364454</v>
+        <v>256.6840530111044</v>
       </c>
       <c r="C212" t="n">
-        <v>262.1570568783993</v>
+        <v>258.2562853735001</v>
       </c>
       <c r="D212" t="n">
-        <v>256.8631589924022</v>
+        <v>254.892868775476</v>
       </c>
       <c r="E212" t="n">
-        <v>257.8283996582031</v>
+        <v>256.5049133300781</v>
       </c>
       <c r="F212" t="n">
-        <v>6426100</v>
+        <v>5272200</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="B213" t="n">
-        <v>258.9130640253377</v>
+        <v>254.2759347913044</v>
       </c>
       <c r="C213" t="n">
-        <v>260.0176018849775</v>
+        <v>255.1317299625397</v>
       </c>
       <c r="D213" t="n">
-        <v>254.2659848771424</v>
+        <v>250.9025724938729</v>
       </c>
       <c r="E213" t="n">
-        <v>255.7188262939453</v>
+        <v>252.6041870117188</v>
       </c>
       <c r="F213" t="n">
-        <v>6534700</v>
+        <v>8770600</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="B214" t="n">
-        <v>256.6840530111044</v>
+        <v>248.8626188136353</v>
       </c>
       <c r="C214" t="n">
-        <v>258.2562853735001</v>
+        <v>255.5695309055475</v>
       </c>
       <c r="D214" t="n">
-        <v>254.892868775476</v>
+        <v>244.842452777813</v>
       </c>
       <c r="E214" t="n">
-        <v>256.5049133300781</v>
+        <v>245.8076934814453</v>
       </c>
       <c r="F214" t="n">
-        <v>5272200</v>
+        <v>10547300</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="B215" t="n">
-        <v>254.2759347913044</v>
+        <v>247.6784538478382</v>
       </c>
       <c r="C215" t="n">
-        <v>255.1317299625397</v>
+        <v>252.3056419000621</v>
       </c>
       <c r="D215" t="n">
-        <v>250.9025724938729</v>
+        <v>245.091223119708</v>
       </c>
       <c r="E215" t="n">
-        <v>252.6041870117188</v>
+        <v>248.7432098388672</v>
       </c>
       <c r="F215" t="n">
-        <v>8770600</v>
+        <v>11097600</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B216" t="n">
-        <v>248.8626188136353</v>
+        <v>251.350352994489</v>
       </c>
       <c r="C216" t="n">
-        <v>255.5695309055475</v>
+        <v>254.4052935535989</v>
       </c>
       <c r="D216" t="n">
-        <v>244.842452777813</v>
+        <v>250.7134945486414</v>
       </c>
       <c r="E216" t="n">
-        <v>245.8076934814453</v>
+        <v>251.7981414794922</v>
       </c>
       <c r="F216" t="n">
-        <v>10547300</v>
+        <v>10167700</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="B217" t="n">
-        <v>247.6784538478382</v>
+        <v>250.7731932271148</v>
       </c>
       <c r="C217" t="n">
-        <v>252.3056419000621</v>
+        <v>252.9325415941838</v>
       </c>
       <c r="D217" t="n">
-        <v>245.091223119708</v>
+        <v>247.4097917368304</v>
       </c>
       <c r="E217" t="n">
-        <v>248.7432098388672</v>
+        <v>247.5988616943359</v>
       </c>
       <c r="F217" t="n">
-        <v>11097600</v>
+        <v>8114700</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="B218" t="n">
-        <v>251.350352994489</v>
+        <v>246.2355858738711</v>
       </c>
       <c r="C218" t="n">
-        <v>254.4052935535989</v>
+        <v>250.1064943021279</v>
       </c>
       <c r="D218" t="n">
-        <v>250.7134945486414</v>
+        <v>244.2852134745944</v>
       </c>
       <c r="E218" t="n">
-        <v>251.7981414794922</v>
+        <v>249.3800811767578</v>
       </c>
       <c r="F218" t="n">
-        <v>10167700</v>
+        <v>7793100</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B219" t="n">
-        <v>250.7731932271148</v>
+        <v>251.5195173574522</v>
       </c>
       <c r="C219" t="n">
-        <v>252.9325415941838</v>
+        <v>255.0322070489389</v>
       </c>
       <c r="D219" t="n">
-        <v>247.4097917368304</v>
+        <v>249.9771364820368</v>
       </c>
       <c r="E219" t="n">
-        <v>247.5988616943359</v>
+        <v>254.3754425048828</v>
       </c>
       <c r="F219" t="n">
-        <v>8114700</v>
+        <v>9100200</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="B220" t="n">
-        <v>246.2355858738711</v>
+        <v>253.9873531958193</v>
       </c>
       <c r="C220" t="n">
-        <v>250.1064943021279</v>
+        <v>258.9230174724852</v>
       </c>
       <c r="D220" t="n">
-        <v>244.2852134745944</v>
+        <v>253.1713702566359</v>
       </c>
       <c r="E220" t="n">
-        <v>249.3800811767578</v>
+        <v>257.99755859375</v>
       </c>
       <c r="F220" t="n">
-        <v>7793100</v>
+        <v>8063300</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="B221" t="n">
-        <v>251.5195173574522</v>
+        <v>260.1469668034143</v>
       </c>
       <c r="C221" t="n">
-        <v>255.0322070489389</v>
+        <v>262.41577598127</v>
       </c>
       <c r="D221" t="n">
-        <v>249.9771364820368</v>
+        <v>258.3358915701962</v>
       </c>
       <c r="E221" t="n">
-        <v>254.3754425048828</v>
+        <v>262.1072998046875</v>
       </c>
       <c r="F221" t="n">
-        <v>9100200</v>
+        <v>6351800</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="B222" t="n">
-        <v>253.9873531958193</v>
+        <v>261.2614678377304</v>
       </c>
       <c r="C222" t="n">
-        <v>258.9230174724852</v>
+        <v>267.4807946322661</v>
       </c>
       <c r="D222" t="n">
-        <v>253.1713702566359</v>
+        <v>260.0673753138636</v>
       </c>
       <c r="E222" t="n">
-        <v>257.99755859375</v>
+        <v>264.6448059082031</v>
       </c>
       <c r="F222" t="n">
-        <v>8063300</v>
+        <v>9647900</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="B223" t="n">
-        <v>260.1469668034143</v>
+        <v>268.6749001082239</v>
       </c>
       <c r="C223" t="n">
-        <v>262.41577598127</v>
+        <v>273.5508459255159</v>
       </c>
       <c r="D223" t="n">
-        <v>258.3358915701962</v>
+        <v>264.8736405295307</v>
       </c>
       <c r="E223" t="n">
-        <v>262.1072998046875</v>
+        <v>265.4209594726562</v>
       </c>
       <c r="F223" t="n">
-        <v>6351800</v>
+        <v>10491000</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="B224" t="n">
-        <v>261.2614678377304</v>
+        <v>267.1822622796963</v>
       </c>
       <c r="C224" t="n">
-        <v>267.4807946322661</v>
+        <v>268.0181361041443</v>
       </c>
       <c r="D224" t="n">
-        <v>260.0673753138636</v>
+        <v>263.4904786297666</v>
       </c>
       <c r="E224" t="n">
-        <v>264.6448059082031</v>
+        <v>264.2268371582031</v>
       </c>
       <c r="F224" t="n">
-        <v>9647900</v>
+        <v>6105600</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46231</v>
+        <v>46233</v>
       </c>
       <c r="B225" t="n">
-        <v>268.6749001082239</v>
+        <v>257.7587518734895</v>
       </c>
       <c r="C225" t="n">
-        <v>273.5508459255159</v>
+        <v>259.2414296518399</v>
       </c>
       <c r="D225" t="n">
-        <v>264.8736405295307</v>
+        <v>253.310688170632</v>
       </c>
       <c r="E225" t="n">
-        <v>265.4209594726562</v>
+        <v>254.5645141601562</v>
       </c>
       <c r="F225" t="n">
-        <v>10491000</v>
+        <v>8216500</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="B226" t="n">
-        <v>267.1822622796963</v>
+        <v>254.7535759665547</v>
       </c>
       <c r="C226" t="n">
-        <v>268.0181361041443</v>
+        <v>257.2114550322676</v>
       </c>
       <c r="D226" t="n">
-        <v>263.4904786297666</v>
+        <v>252.046908655097</v>
       </c>
       <c r="E226" t="n">
-        <v>264.2268371582031</v>
+        <v>255.0919036865234</v>
       </c>
       <c r="F226" t="n">
-        <v>6105600</v>
+        <v>6782100</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="B227" t="n">
-        <v>257.7587518734895</v>
+        <v>253.7186719595458</v>
       </c>
       <c r="C227" t="n">
-        <v>259.2414296518399</v>
+        <v>256.4850271972422</v>
       </c>
       <c r="D227" t="n">
-        <v>253.310688170632</v>
+        <v>249.6785998577546</v>
       </c>
       <c r="E227" t="n">
-        <v>254.5645141601562</v>
+        <v>253.1614227294922</v>
       </c>
       <c r="F227" t="n">
-        <v>8216500</v>
+        <v>8136300</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="B228" t="n">
-        <v>254.7535759665547</v>
+        <v>253.1614264806184</v>
       </c>
       <c r="C228" t="n">
-        <v>257.2114550322676</v>
+        <v>254.2659795008061</v>
       </c>
       <c r="D228" t="n">
-        <v>252.046908655097</v>
+        <v>249.2109089785714</v>
       </c>
       <c r="E228" t="n">
-        <v>255.0919036865234</v>
+        <v>253.6788635253906</v>
       </c>
       <c r="F228" t="n">
-        <v>6782100</v>
+        <v>7362400</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="B229" t="n">
-        <v>253.7186719595458</v>
+        <v>253.9972934738065</v>
       </c>
       <c r="C229" t="n">
-        <v>256.4850271972422</v>
+        <v>258.0473261663437</v>
       </c>
       <c r="D229" t="n">
-        <v>249.6785998577546</v>
+        <v>253.2211227437212</v>
       </c>
       <c r="E229" t="n">
-        <v>253.1614227294922</v>
+        <v>256.3258056640625</v>
       </c>
       <c r="F229" t="n">
-        <v>8136300</v>
+        <v>6472600</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="B230" t="n">
-        <v>253.1614264806184</v>
+        <v>260.425593365904</v>
       </c>
       <c r="C230" t="n">
-        <v>254.2659795008061</v>
+        <v>260.8236242062839</v>
       </c>
       <c r="D230" t="n">
-        <v>249.2109089785714</v>
+        <v>254.0271572625725</v>
       </c>
       <c r="E230" t="n">
-        <v>253.6788635253906</v>
+        <v>255.7188262939453</v>
       </c>
       <c r="F230" t="n">
-        <v>7362400</v>
+        <v>6931800</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="B231" t="n">
-        <v>253.9972934738065</v>
+        <v>254.6341623817563</v>
       </c>
       <c r="C231" t="n">
-        <v>258.0473261663437</v>
+        <v>258.3259614136433</v>
       </c>
       <c r="D231" t="n">
-        <v>253.2211227437212</v>
+        <v>253.8679370762885</v>
       </c>
       <c r="E231" t="n">
-        <v>256.3258056640625</v>
+        <v>257.9677124023438</v>
       </c>
       <c r="F231" t="n">
-        <v>6472600</v>
+        <v>6532100</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="B232" t="n">
-        <v>260.425593365904</v>
+        <v>257.7886121067854</v>
       </c>
       <c r="C232" t="n">
-        <v>260.8236242062839</v>
+        <v>260.7141859356404</v>
       </c>
       <c r="D232" t="n">
-        <v>254.0271572625725</v>
+        <v>257.281105309594</v>
       </c>
       <c r="E232" t="n">
-        <v>255.7188262939453</v>
+        <v>260.5251159667969</v>
       </c>
       <c r="F232" t="n">
-        <v>6931800</v>
+        <v>8985100</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="B233" t="n">
-        <v>254.6341623817563</v>
+        <v>259.9479684253454</v>
       </c>
       <c r="C233" t="n">
-        <v>258.3259614136433</v>
+        <v>262.853620890259</v>
       </c>
       <c r="D233" t="n">
-        <v>253.8679370762885</v>
+        <v>257.0920280597301</v>
       </c>
       <c r="E233" t="n">
-        <v>257.9677124023438</v>
+        <v>258.5249633789062</v>
       </c>
       <c r="F233" t="n">
-        <v>6532100</v>
+        <v>5945900</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B234" t="n">
-        <v>257.7886121067854</v>
+        <v>254.7436088096904</v>
       </c>
       <c r="C234" t="n">
-        <v>260.7141859356404</v>
+        <v>260.1270613743755</v>
       </c>
       <c r="D234" t="n">
-        <v>257.281105309594</v>
+        <v>254.00723509927</v>
       </c>
       <c r="E234" t="n">
-        <v>260.5251159667969</v>
+        <v>259.5797424316406</v>
       </c>
       <c r="F234" t="n">
-        <v>8985100</v>
+        <v>4629300</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="B235" t="n">
-        <v>259.9479684253454</v>
+        <v>260.4455042155265</v>
       </c>
       <c r="C235" t="n">
-        <v>262.853620890259</v>
+        <v>261.3311205223152</v>
       </c>
       <c r="D235" t="n">
-        <v>257.0920280597301</v>
+        <v>258.3756953399613</v>
       </c>
       <c r="E235" t="n">
-        <v>258.5249633789062</v>
+        <v>260.7937622070312</v>
       </c>
       <c r="F235" t="n">
-        <v>5945900</v>
+        <v>4852700</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="B236" t="n">
-        <v>254.7436088096904</v>
+        <v>259.3707811439639</v>
       </c>
       <c r="C236" t="n">
-        <v>260.1270613743755</v>
+        <v>260.4255764680427</v>
       </c>
       <c r="D236" t="n">
-        <v>254.00723509927</v>
+        <v>257.8881034534354</v>
       </c>
       <c r="E236" t="n">
-        <v>259.5797424316406</v>
+        <v>259.072265625</v>
       </c>
       <c r="F236" t="n">
-        <v>4629300</v>
+        <v>4998100</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="B237" t="n">
-        <v>260.4455042155265</v>
+        <v>257.5995438259766</v>
       </c>
       <c r="C237" t="n">
-        <v>261.3311205223152</v>
+        <v>262.9829969172681</v>
       </c>
       <c r="D237" t="n">
-        <v>258.3756953399613</v>
+        <v>256.7437790079673</v>
       </c>
       <c r="E237" t="n">
-        <v>260.7937622070312</v>
+        <v>261.0823669433594</v>
       </c>
       <c r="F237" t="n">
-        <v>4852700</v>
+        <v>5515500</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="B238" t="n">
-        <v>259.3707811439639</v>
+        <v>266.3563600087168</v>
       </c>
       <c r="C238" t="n">
-        <v>260.4255764680427</v>
+        <v>270.3964321763198</v>
       </c>
       <c r="D238" t="n">
-        <v>257.8881034534354</v>
+        <v>265.0229096495755</v>
       </c>
       <c r="E238" t="n">
-        <v>259.072265625</v>
+        <v>269.7794494628906</v>
       </c>
       <c r="F238" t="n">
-        <v>4998100</v>
+        <v>7838200</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="B239" t="n">
-        <v>257.5995438259766</v>
+        <v>271.6601848020655</v>
       </c>
       <c r="C239" t="n">
-        <v>262.9829969172681</v>
+        <v>275.1131561312948</v>
       </c>
       <c r="D239" t="n">
-        <v>256.7437790079673</v>
+        <v>269.2321572777068</v>
       </c>
       <c r="E239" t="n">
-        <v>261.0823669433594</v>
+        <v>272.0681762695312</v>
       </c>
       <c r="F239" t="n">
-        <v>5515500</v>
+        <v>7728500</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B240" t="n">
-        <v>266.3563600087168</v>
+        <v>272.0582363321417</v>
       </c>
       <c r="C240" t="n">
-        <v>270.3964321763198</v>
+        <v>272.0582363321417</v>
       </c>
       <c r="D240" t="n">
-        <v>265.0229096495755</v>
+        <v>266.0578308105469</v>
       </c>
       <c r="E240" t="n">
-        <v>269.7794494628906</v>
+        <v>266.0578308105469</v>
       </c>
       <c r="F240" t="n">
-        <v>7838200</v>
+        <v>6475900</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="B241" t="n">
-        <v>271.6601848020655</v>
+        <v>266.5155507786093</v>
       </c>
       <c r="C241" t="n">
-        <v>275.1131561312948</v>
+        <v>271.3218634751246</v>
       </c>
       <c r="D241" t="n">
-        <v>269.2321572777068</v>
+        <v>265.6896375517999</v>
       </c>
       <c r="E241" t="n">
-        <v>272.0681762695312</v>
+        <v>268.9137268066406</v>
       </c>
       <c r="F241" t="n">
-        <v>7728500</v>
+        <v>6186800</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="B242" t="n">
-        <v>272.0582363321417</v>
+        <v>268.4161893708204</v>
       </c>
       <c r="C242" t="n">
-        <v>272.0582363321417</v>
+        <v>272.635401405727</v>
       </c>
       <c r="D242" t="n">
-        <v>266.0578308105469</v>
+        <v>267.2519483767422</v>
       </c>
       <c r="E242" t="n">
-        <v>266.0578308105469</v>
+        <v>271.7000122070312</v>
       </c>
       <c r="F242" t="n">
-        <v>6475900</v>
+        <v>5436100</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,25 +6735,25 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="B243" t="n">
-        <v>266.5155507786093</v>
+        <v>271</v>
       </c>
       <c r="C243" t="n">
-        <v>271.3218634751246</v>
+        <v>273.7999877929688</v>
       </c>
       <c r="D243" t="n">
-        <v>265.6896375517999</v>
+        <v>270.1799926757812</v>
       </c>
       <c r="E243" t="n">
-        <v>268.9137268066406</v>
+        <v>273.1400146484375</v>
       </c>
       <c r="F243" t="n">
-        <v>6186800</v>
+        <v>4687000</v>
       </c>
       <c r="G243" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B244" t="n">
-        <v>268.4161893708204</v>
+        <v>271.9700012207031</v>
       </c>
       <c r="C244" t="n">
-        <v>272.635401405727</v>
+        <v>272.9100036621094</v>
       </c>
       <c r="D244" t="n">
-        <v>267.2519483767422</v>
+        <v>269.5499877929688</v>
       </c>
       <c r="E244" t="n">
-        <v>271.7000122070312</v>
+        <v>270</v>
       </c>
       <c r="F244" t="n">
-        <v>5436100</v>
+        <v>7214100</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,25 +6787,25 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="B245" t="n">
-        <v>271</v>
+        <v>268.4500122070312</v>
       </c>
       <c r="C245" t="n">
-        <v>273.7999877929688</v>
+        <v>268.4500122070312</v>
       </c>
       <c r="D245" t="n">
-        <v>270.1799926757812</v>
+        <v>263.8299865722656</v>
       </c>
       <c r="E245" t="n">
-        <v>273.1400146484375</v>
+        <v>265.7699890136719</v>
       </c>
       <c r="F245" t="n">
-        <v>4687000</v>
+        <v>7306200</v>
       </c>
       <c r="G245" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="H245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="B246" t="n">
-        <v>271.9700012207031</v>
+        <v>265.7799987792969</v>
       </c>
       <c r="C246" t="n">
-        <v>272.9100036621094</v>
+        <v>268.3800048828125</v>
       </c>
       <c r="D246" t="n">
-        <v>269.5499877929688</v>
+        <v>264.2699890136719</v>
       </c>
       <c r="E246" t="n">
-        <v>270</v>
+        <v>268.0400085449219</v>
       </c>
       <c r="F246" t="n">
-        <v>7214100</v>
+        <v>5765600</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="B247" t="n">
-        <v>268.4500122070312</v>
+        <v>267.1300048828125</v>
       </c>
       <c r="C247" t="n">
-        <v>268.4500122070312</v>
+        <v>267.7699890136719</v>
       </c>
       <c r="D247" t="n">
-        <v>263.8299865722656</v>
+        <v>265.1700134277344</v>
       </c>
       <c r="E247" t="n">
-        <v>265.7699890136719</v>
+        <v>265.8500061035156</v>
       </c>
       <c r="F247" t="n">
-        <v>7306200</v>
+        <v>7900100</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="B248" t="n">
-        <v>265.7799987792969</v>
+        <v>270.8299865722656</v>
       </c>
       <c r="C248" t="n">
-        <v>268.3800048828125</v>
+        <v>271.9100036621094</v>
       </c>
       <c r="D248" t="n">
-        <v>264.2699890136719</v>
+        <v>267.0199890136719</v>
       </c>
       <c r="E248" t="n">
-        <v>268.0400085449219</v>
+        <v>271.1900024414062</v>
       </c>
       <c r="F248" t="n">
-        <v>5765600</v>
+        <v>6033600</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="B249" t="n">
-        <v>267.1300048828125</v>
+        <v>274.739990234375</v>
       </c>
       <c r="C249" t="n">
-        <v>267.7699890136719</v>
+        <v>281.0700073242188</v>
       </c>
       <c r="D249" t="n">
-        <v>265.1700134277344</v>
+        <v>273.5299987792969</v>
       </c>
       <c r="E249" t="n">
-        <v>265.8500061035156</v>
+        <v>275.2099914550781</v>
       </c>
       <c r="F249" t="n">
-        <v>7900100</v>
+        <v>7910600</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B250" t="n">
-        <v>270.8299865722656</v>
+        <v>277.3200073242188</v>
       </c>
       <c r="C250" t="n">
-        <v>271.9100036621094</v>
+        <v>278.8900146484375</v>
       </c>
       <c r="D250" t="n">
-        <v>267.0199890136719</v>
+        <v>273.1600036621094</v>
       </c>
       <c r="E250" t="n">
-        <v>271.1900024414062</v>
+        <v>278.4299926757812</v>
       </c>
       <c r="F250" t="n">
-        <v>6033600</v>
+        <v>5940300</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="B251" t="n">
-        <v>274.739990234375</v>
+        <v>275.1300048828125</v>
       </c>
       <c r="C251" t="n">
-        <v>281.0700073242188</v>
+        <v>277.7999877929688</v>
       </c>
       <c r="D251" t="n">
-        <v>273.5299987792969</v>
+        <v>274.75</v>
       </c>
       <c r="E251" t="n">
-        <v>275.2099914550781</v>
+        <v>275.2300109863281</v>
       </c>
       <c r="F251" t="n">
-        <v>7910600</v>
+        <v>4320100</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,53 +6969,19 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46268</v>
-      </c>
-      <c r="B252" t="n">
-        <v>277.3200073242188</v>
-      </c>
-      <c r="C252" t="n">
-        <v>278.8900146484375</v>
-      </c>
-      <c r="D252" t="n">
-        <v>273.1600036621094</v>
-      </c>
-      <c r="E252" t="n">
-        <v>278.4299926757812</v>
-      </c>
+        <v>46273</v>
+      </c>
+      <c r="B252" t="inlineStr"/>
+      <c r="C252" t="inlineStr"/>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr"/>
       <c r="F252" t="n">
-        <v>5940300</v>
+        <v>7768078</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
       </c>
       <c r="H252" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="1" t="n">
-        <v>46269</v>
-      </c>
-      <c r="B253" t="n">
-        <v>275.1300048828125</v>
-      </c>
-      <c r="C253" t="n">
-        <v>277.7999877929688</v>
-      </c>
-      <c r="D253" t="n">
-        <v>274.75</v>
-      </c>
-      <c r="E253" t="n">
-        <v>275.2300109863281</v>
-      </c>
-      <c r="F253" t="n">
-        <v>4320100</v>
-      </c>
-      <c r="G253" t="n">
-        <v>0</v>
-      </c>
-      <c r="H253" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10997,34 +10963,34 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>269.12</v>
+      </c>
+      <c r="D2" t="n">
         <v>275.23</v>
       </c>
-      <c r="D2" t="n">
-        <v>278.43</v>
-      </c>
       <c r="E2" t="n">
-        <v>275.13</v>
+        <v>271.28</v>
       </c>
       <c r="F2" t="n">
-        <v>277.8</v>
+        <v>271.99</v>
       </c>
       <c r="G2" t="n">
-        <v>274.75</v>
+        <v>266.8828</v>
       </c>
       <c r="H2" t="n">
-        <v>3878977</v>
+        <v>7768078</v>
       </c>
       <c r="I2" t="n">
-        <v>7791449</v>
+        <v>7795185</v>
       </c>
       <c r="J2" t="n">
-        <v>663276421120</v>
+        <v>648551858176</v>
       </c>
       <c r="K2" t="n">
-        <v>31.96632</v>
+        <v>31.25668</v>
       </c>
       <c r="L2" t="n">
-        <v>22.362787</v>
+        <v>21.86634</v>
       </c>
       <c r="M2" t="n">
         <v>8.609999999999999</v>
@@ -11063,7 +11029,7 @@
         <v>35.284</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.80042</v>
+        <v>7.627253</v>
       </c>
       <c r="Z2" t="n">
         <v>-0.008999999999999999</v>
@@ -11075,7 +11041,7 @@
         <v>97929003008</v>
       </c>
       <c r="AC2" t="n">
-        <v>691554418688</v>
+        <v>676829921280</v>
       </c>
       <c r="AD2" t="n">
         <v>34872000512</v>
@@ -11102,7 +11068,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-08 08:52:20</t>
+          <t>2026-09-09 09:15:17</t>
         </is>
       </c>
     </row>

--- a/data/JNJ_data.xlsx
+++ b/data/JNJ_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45909</v>
+        <v>45910</v>
       </c>
       <c r="B2" t="n">
-        <v>174.0770398088306</v>
+        <v>172.4145258819289</v>
       </c>
       <c r="C2" t="n">
-        <v>174.165052708233</v>
+        <v>172.7176914018626</v>
       </c>
       <c r="D2" t="n">
-        <v>172.561197432737</v>
+        <v>170.4879415338014</v>
       </c>
       <c r="E2" t="n">
-        <v>173.0599670410156</v>
+        <v>171.9157562255859</v>
       </c>
       <c r="F2" t="n">
-        <v>6005700</v>
+        <v>6891600</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45910</v>
+        <v>45911</v>
       </c>
       <c r="B3" t="n">
-        <v>172.4145258819289</v>
+        <v>171.8766472653515</v>
       </c>
       <c r="C3" t="n">
-        <v>172.7176914018626</v>
+        <v>174.9083323610806</v>
       </c>
       <c r="D3" t="n">
-        <v>170.4879415338014</v>
+        <v>171.759296719517</v>
       </c>
       <c r="E3" t="n">
-        <v>171.9157562255859</v>
+        <v>174.5660400390625</v>
       </c>
       <c r="F3" t="n">
-        <v>6891600</v>
+        <v>5792500</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="B4" t="n">
-        <v>171.8766322416418</v>
+        <v>173.7934343158836</v>
       </c>
       <c r="C4" t="n">
-        <v>174.9083170723718</v>
+        <v>174.8594080922437</v>
       </c>
       <c r="D4" t="n">
-        <v>171.7592817060649</v>
+        <v>172.8252476738922</v>
       </c>
       <c r="E4" t="n">
-        <v>174.5660247802734</v>
+        <v>174.1357116699219</v>
       </c>
       <c r="F4" t="n">
-        <v>5792500</v>
+        <v>7220200</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="B5" t="n">
-        <v>173.7934343158836</v>
+        <v>173.8423314280924</v>
       </c>
       <c r="C5" t="n">
-        <v>174.8594080922437</v>
+        <v>175.0452341292242</v>
       </c>
       <c r="D5" t="n">
-        <v>172.8252476738922</v>
+        <v>173.0306220566984</v>
       </c>
       <c r="E5" t="n">
-        <v>174.1357116699219</v>
+        <v>173.4902648925781</v>
       </c>
       <c r="F5" t="n">
-        <v>7220200</v>
+        <v>4768100</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="B6" t="n">
-        <v>173.8423161383384</v>
+        <v>173.6565364179341</v>
       </c>
       <c r="C6" t="n">
-        <v>175.0452187336727</v>
+        <v>173.7054225283811</v>
       </c>
       <c r="D6" t="n">
-        <v>173.0306068383358</v>
+        <v>171.7788382257642</v>
       </c>
       <c r="E6" t="n">
-        <v>173.4902496337891</v>
+        <v>172.5709991455078</v>
       </c>
       <c r="F6" t="n">
-        <v>4768100</v>
+        <v>7959300</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="B7" t="n">
-        <v>173.6565364179341</v>
+        <v>172.8154864182272</v>
       </c>
       <c r="C7" t="n">
-        <v>173.7054225283811</v>
+        <v>174.5758041940759</v>
       </c>
       <c r="D7" t="n">
-        <v>171.7788382257642</v>
+        <v>172.6981209566707</v>
       </c>
       <c r="E7" t="n">
-        <v>172.5709991455078</v>
+        <v>173.294677734375</v>
       </c>
       <c r="F7" t="n">
-        <v>7959300</v>
+        <v>6714900</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B8" t="n">
-        <v>172.8154712016315</v>
+        <v>172.7078974682877</v>
       </c>
       <c r="C8" t="n">
-        <v>174.5757888224823</v>
+        <v>173.1186392474049</v>
       </c>
       <c r="D8" t="n">
-        <v>172.6981057504092</v>
+        <v>170.0380535202773</v>
       </c>
       <c r="E8" t="n">
-        <v>173.2946624755859</v>
+        <v>170.3216705322266</v>
       </c>
       <c r="F8" t="n">
-        <v>6714900</v>
+        <v>8200900</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B9" t="n">
-        <v>172.7079129408542</v>
+        <v>170.8400043448543</v>
       </c>
       <c r="C9" t="n">
-        <v>173.118654756769</v>
+        <v>173.2555691360807</v>
       </c>
       <c r="D9" t="n">
-        <v>170.0380687536577</v>
+        <v>169.5099768279138</v>
       </c>
       <c r="E9" t="n">
-        <v>170.3216857910156</v>
+        <v>172.3069458007812</v>
       </c>
       <c r="F9" t="n">
-        <v>8200900</v>
+        <v>25621000</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B10" t="n">
-        <v>170.8400043448543</v>
+        <v>172.2091467192868</v>
       </c>
       <c r="C10" t="n">
-        <v>173.2555691360807</v>
+        <v>172.7470282469487</v>
       </c>
       <c r="D10" t="n">
-        <v>169.5099768279138</v>
+        <v>170.2825623799796</v>
       </c>
       <c r="E10" t="n">
-        <v>172.3069458007812</v>
+        <v>170.3705902099609</v>
       </c>
       <c r="F10" t="n">
-        <v>25621000</v>
+        <v>7193900</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B11" t="n">
-        <v>172.2091312958323</v>
+        <v>171.0355829083302</v>
       </c>
       <c r="C11" t="n">
-        <v>172.7470127753203</v>
+        <v>173.0697433912989</v>
       </c>
       <c r="D11" t="n">
-        <v>170.2825471290745</v>
+        <v>170.9769076413454</v>
       </c>
       <c r="E11" t="n">
-        <v>170.3705749511719</v>
+        <v>172.6883392333984</v>
       </c>
       <c r="F11" t="n">
-        <v>7193900</v>
+        <v>8350400</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B12" t="n">
-        <v>171.0355829083302</v>
+        <v>172.2580322171388</v>
       </c>
       <c r="C12" t="n">
-        <v>173.0697433912989</v>
+        <v>173.0501781580241</v>
       </c>
       <c r="D12" t="n">
-        <v>170.9769076413454</v>
+        <v>171.8668538263927</v>
       </c>
       <c r="E12" t="n">
-        <v>172.6883392333984</v>
+        <v>172.7959136962891</v>
       </c>
       <c r="F12" t="n">
-        <v>8350400</v>
+        <v>6676800</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B13" t="n">
-        <v>172.2580322171388</v>
+        <v>173.2946701929729</v>
       </c>
       <c r="C13" t="n">
-        <v>173.0501781580241</v>
+        <v>174.4682202999683</v>
       </c>
       <c r="D13" t="n">
-        <v>171.8668538263927</v>
+        <v>172.0331071855151</v>
       </c>
       <c r="E13" t="n">
-        <v>172.7959136962891</v>
+        <v>173.81298828125</v>
       </c>
       <c r="F13" t="n">
-        <v>6676800</v>
+        <v>8475000</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B14" t="n">
-        <v>173.2946854062595</v>
+        <v>174.6638219397404</v>
       </c>
       <c r="C14" t="n">
-        <v>174.4682356162792</v>
+        <v>175.9449483254981</v>
       </c>
       <c r="D14" t="n">
-        <v>172.0331222880509</v>
+        <v>173.4120331870535</v>
       </c>
       <c r="E14" t="n">
-        <v>173.8130035400391</v>
+        <v>175.7493591308594</v>
       </c>
       <c r="F14" t="n">
-        <v>8475000</v>
+        <v>8634400</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B15" t="n">
-        <v>174.6638219397404</v>
+        <v>175.8667353595665</v>
       </c>
       <c r="C15" t="n">
-        <v>175.9449483254981</v>
+        <v>177.8617693123808</v>
       </c>
       <c r="D15" t="n">
-        <v>173.4120331870535</v>
+        <v>175.837397722209</v>
       </c>
       <c r="E15" t="n">
-        <v>175.7493591308594</v>
+        <v>177.6172790527344</v>
       </c>
       <c r="F15" t="n">
-        <v>8634400</v>
+        <v>8597100</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B16" t="n">
-        <v>175.8667202511636</v>
+        <v>177.6955105019011</v>
       </c>
       <c r="C16" t="n">
-        <v>177.861754032588</v>
+        <v>181.8909715434583</v>
       </c>
       <c r="D16" t="n">
-        <v>175.8373826163265</v>
+        <v>177.0794052199421</v>
       </c>
       <c r="E16" t="n">
-        <v>177.6172637939453</v>
+        <v>181.3335266113281</v>
       </c>
       <c r="F16" t="n">
-        <v>8597100</v>
+        <v>11569000</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B17" t="n">
-        <v>177.6954955492426</v>
+        <v>181.9007144524965</v>
       </c>
       <c r="C17" t="n">
-        <v>181.8909562377616</v>
+        <v>182.4483701299151</v>
       </c>
       <c r="D17" t="n">
-        <v>177.0793903191274</v>
+        <v>179.8567798983815</v>
       </c>
       <c r="E17" t="n">
-        <v>181.3335113525391</v>
+        <v>181.9496154785156</v>
       </c>
       <c r="F17" t="n">
-        <v>11569000</v>
+        <v>13063800</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B18" t="n">
-        <v>181.9007449618727</v>
+        <v>180.1306362123439</v>
       </c>
       <c r="C18" t="n">
-        <v>182.4484007311471</v>
+        <v>182.4777366073124</v>
       </c>
       <c r="D18" t="n">
-        <v>179.8568100649378</v>
+        <v>180.032834144845</v>
       </c>
       <c r="E18" t="n">
-        <v>181.9496459960938</v>
+        <v>181.8811798095703</v>
       </c>
       <c r="F18" t="n">
-        <v>13063800</v>
+        <v>7728100</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B19" t="n">
-        <v>180.1306362123439</v>
+        <v>182.9373790605305</v>
       </c>
       <c r="C19" t="n">
-        <v>182.4777366073124</v>
+        <v>185.5974341276275</v>
       </c>
       <c r="D19" t="n">
-        <v>180.032834144845</v>
+        <v>182.7906908821062</v>
       </c>
       <c r="E19" t="n">
-        <v>181.8811798095703</v>
+        <v>184.4825592041016</v>
       </c>
       <c r="F19" t="n">
-        <v>7728100</v>
+        <v>8675100</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B20" t="n">
-        <v>182.9373639295453</v>
+        <v>183.8566452365672</v>
       </c>
       <c r="C20" t="n">
-        <v>185.5974187766257</v>
+        <v>185.7343283333897</v>
       </c>
       <c r="D20" t="n">
-        <v>182.7906757632537</v>
+        <v>183.2405251076493</v>
       </c>
       <c r="E20" t="n">
-        <v>184.4825439453125</v>
+        <v>184.0131225585938</v>
       </c>
       <c r="F20" t="n">
-        <v>8675100</v>
+        <v>5806100</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B21" t="n">
-        <v>183.8566452365672</v>
+        <v>179.7198952882722</v>
       </c>
       <c r="C21" t="n">
-        <v>185.7343283333897</v>
+        <v>185.0595539364086</v>
       </c>
       <c r="D21" t="n">
-        <v>183.2405251076493</v>
+        <v>178.908185875973</v>
       </c>
       <c r="E21" t="n">
-        <v>184.0131225585938</v>
+        <v>184.72705078125</v>
       </c>
       <c r="F21" t="n">
-        <v>5806100</v>
+        <v>8776800</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B22" t="n">
-        <v>179.7198804430833</v>
+        <v>184.707479532436</v>
       </c>
       <c r="C22" t="n">
-        <v>185.0595386501542</v>
+        <v>186.0277327816568</v>
       </c>
       <c r="D22" t="n">
-        <v>178.9081710978327</v>
+        <v>184.1207119169489</v>
       </c>
       <c r="E22" t="n">
-        <v>184.7270355224609</v>
+        <v>185.5094146728516</v>
       </c>
       <c r="F22" t="n">
-        <v>8776800</v>
+        <v>5751200</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B23" t="n">
-        <v>184.7074643396089</v>
+        <v>185.8125596570494</v>
       </c>
       <c r="C23" t="n">
-        <v>186.0277174802343</v>
+        <v>187.8662833906792</v>
       </c>
       <c r="D23" t="n">
-        <v>184.1206967723854</v>
+        <v>185.5485060518688</v>
       </c>
       <c r="E23" t="n">
-        <v>185.5093994140625</v>
+        <v>186.8687591552734</v>
       </c>
       <c r="F23" t="n">
-        <v>5751200</v>
+        <v>7484800</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B24" t="n">
-        <v>185.8125748295944</v>
+        <v>187.7782560364296</v>
       </c>
       <c r="C24" t="n">
-        <v>187.8662987309212</v>
+        <v>187.8369462218906</v>
       </c>
       <c r="D24" t="n">
-        <v>185.5485212028525</v>
+        <v>185.6658719572771</v>
       </c>
       <c r="E24" t="n">
-        <v>186.8687744140625</v>
+        <v>186.5166931152344</v>
       </c>
       <c r="F24" t="n">
-        <v>7484800</v>
+        <v>9598000</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B25" t="n">
-        <v>187.7782713984262</v>
+        <v>185.646323339356</v>
       </c>
       <c r="C25" t="n">
-        <v>187.8369615886886</v>
+        <v>187.0839270863694</v>
       </c>
       <c r="D25" t="n">
-        <v>185.6658871464611</v>
+        <v>185.1084418485517</v>
       </c>
       <c r="E25" t="n">
-        <v>186.5167083740234</v>
+        <v>186.6927337646484</v>
       </c>
       <c r="F25" t="n">
-        <v>9598000</v>
+        <v>7979500</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B26" t="n">
-        <v>185.646323339356</v>
+        <v>188.6682159172342</v>
       </c>
       <c r="C26" t="n">
-        <v>187.0839270863694</v>
+        <v>190.1155938776849</v>
       </c>
       <c r="D26" t="n">
-        <v>185.1084418485517</v>
+        <v>181.7833777150234</v>
       </c>
       <c r="E26" t="n">
-        <v>186.6927337646484</v>
+        <v>186.6438446044922</v>
       </c>
       <c r="F26" t="n">
-        <v>7979500</v>
+        <v>13613300</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B27" t="n">
-        <v>188.6682313415227</v>
+        <v>187.2599526066892</v>
       </c>
       <c r="C27" t="n">
-        <v>190.1156094203016</v>
+        <v>189.303902268661</v>
       </c>
       <c r="D27" t="n">
-        <v>181.7833925764523</v>
+        <v>185.1280049658996</v>
       </c>
       <c r="E27" t="n">
-        <v>186.6438598632812</v>
+        <v>186.956787109375</v>
       </c>
       <c r="F27" t="n">
-        <v>13613300</v>
+        <v>9473000</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B28" t="n">
-        <v>187.2599526066892</v>
+        <v>187.1230406678187</v>
       </c>
       <c r="C28" t="n">
-        <v>189.303902268661</v>
+        <v>188.7953604231518</v>
       </c>
       <c r="D28" t="n">
-        <v>185.1280049658996</v>
+        <v>186.2330926405801</v>
       </c>
       <c r="E28" t="n">
-        <v>186.956787109375</v>
+        <v>187.8858489990234</v>
       </c>
       <c r="F28" t="n">
-        <v>9473000</v>
+        <v>10611800</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B29" t="n">
-        <v>187.1230558646578</v>
+        <v>188.2574758352493</v>
       </c>
       <c r="C29" t="n">
-        <v>188.7953757558051</v>
+        <v>189.3332388090219</v>
       </c>
       <c r="D29" t="n">
-        <v>186.2331077651437</v>
+        <v>187.4555407234371</v>
       </c>
       <c r="E29" t="n">
-        <v>187.8858642578125</v>
+        <v>188.9616088867188</v>
       </c>
       <c r="F29" t="n">
-        <v>10611800</v>
+        <v>7764400</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B30" t="n">
-        <v>188.2574758352493</v>
+        <v>189.2354242017374</v>
       </c>
       <c r="C30" t="n">
-        <v>189.3332388090219</v>
+        <v>190.1938216550539</v>
       </c>
       <c r="D30" t="n">
-        <v>187.4555407234371</v>
+        <v>188.0912117995895</v>
       </c>
       <c r="E30" t="n">
-        <v>188.9616088867188</v>
+        <v>189.4505767822266</v>
       </c>
       <c r="F30" t="n">
-        <v>7764400</v>
+        <v>8034700</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B31" t="n">
-        <v>189.2354242017374</v>
+        <v>188.7562393006838</v>
       </c>
       <c r="C31" t="n">
-        <v>190.1938216550539</v>
+        <v>189.2843465750772</v>
       </c>
       <c r="D31" t="n">
-        <v>188.0912117995895</v>
+        <v>187.5435772620767</v>
       </c>
       <c r="E31" t="n">
-        <v>189.4505767822266</v>
+        <v>187.6511535644531</v>
       </c>
       <c r="F31" t="n">
-        <v>8034700</v>
+        <v>6716000</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B32" t="n">
-        <v>188.756223952035</v>
+        <v>187.7685042274453</v>
       </c>
       <c r="C32" t="n">
-        <v>189.2843311834856</v>
+        <v>189.1865446342463</v>
       </c>
       <c r="D32" t="n">
-        <v>187.5435620120352</v>
+        <v>187.5533516225514</v>
       </c>
       <c r="E32" t="n">
-        <v>187.6511383056641</v>
+        <v>188.6877899169922</v>
       </c>
       <c r="F32" t="n">
-        <v>6716000</v>
+        <v>6343100</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B33" t="n">
-        <v>187.7685042274453</v>
+        <v>188.3161623201141</v>
       </c>
       <c r="C33" t="n">
-        <v>189.1865446342463</v>
+        <v>189.7244285069409</v>
       </c>
       <c r="D33" t="n">
-        <v>187.5533516225514</v>
+        <v>187.3186379506951</v>
       </c>
       <c r="E33" t="n">
-        <v>188.6877899169922</v>
+        <v>188.2281494140625</v>
       </c>
       <c r="F33" t="n">
-        <v>6343100</v>
+        <v>8882500</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B34" t="n">
-        <v>188.3161623201141</v>
+        <v>187.9640832263789</v>
       </c>
       <c r="C34" t="n">
-        <v>189.7244285069409</v>
+        <v>188.0716595229833</v>
       </c>
       <c r="D34" t="n">
-        <v>187.3186379506951</v>
+        <v>185.2453531003753</v>
       </c>
       <c r="E34" t="n">
-        <v>188.2281494140625</v>
+        <v>186.2037506103516</v>
       </c>
       <c r="F34" t="n">
-        <v>8882500</v>
+        <v>6903400</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B35" t="n">
-        <v>187.9640832263789</v>
+        <v>185.8028067822911</v>
       </c>
       <c r="C35" t="n">
-        <v>188.0716595229833</v>
+        <v>186.5949527664067</v>
       </c>
       <c r="D35" t="n">
-        <v>185.2453531003753</v>
+        <v>185.3529381781329</v>
       </c>
       <c r="E35" t="n">
-        <v>186.2037506103516</v>
+        <v>186.1059722900391</v>
       </c>
       <c r="F35" t="n">
-        <v>6903400</v>
+        <v>7126000</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B36" t="n">
-        <v>185.8027763144259</v>
+        <v>185.0888771601165</v>
       </c>
       <c r="C36" t="n">
-        <v>186.5949221686458</v>
+        <v>185.3333673885486</v>
       </c>
       <c r="D36" t="n">
-        <v>185.352907784037</v>
+        <v>182.5070609447738</v>
       </c>
       <c r="E36" t="n">
-        <v>186.1059417724609</v>
+        <v>182.8102264404297</v>
       </c>
       <c r="F36" t="n">
-        <v>7126000</v>
+        <v>8329500</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B37" t="n">
-        <v>185.0888926090998</v>
+        <v>182.5853054515495</v>
       </c>
       <c r="C37" t="n">
-        <v>185.333382857939</v>
+        <v>182.9764987830591</v>
       </c>
       <c r="D37" t="n">
-        <v>182.5070761782583</v>
+        <v>180.5902716895996</v>
       </c>
       <c r="E37" t="n">
-        <v>182.8102416992188</v>
+        <v>182.4875183105469</v>
       </c>
       <c r="F37" t="n">
-        <v>8329500</v>
+        <v>10551100</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B38" t="n">
-        <v>182.5852901845839</v>
+        <v>182.9569302033718</v>
       </c>
       <c r="C38" t="n">
-        <v>182.9764834833836</v>
+        <v>185.2062432977132</v>
       </c>
       <c r="D38" t="n">
-        <v>180.5902565894498</v>
+        <v>182.7906786381269</v>
       </c>
       <c r="E38" t="n">
-        <v>182.4875030517578</v>
+        <v>184.8835144042969</v>
       </c>
       <c r="F38" t="n">
-        <v>10551100</v>
+        <v>7072500</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B39" t="n">
-        <v>182.9569302033718</v>
+        <v>183.3285602019948</v>
       </c>
       <c r="C39" t="n">
-        <v>185.2062432977132</v>
+        <v>185.3235939082472</v>
       </c>
       <c r="D39" t="n">
-        <v>182.7906786381269</v>
+        <v>182.6439756215902</v>
       </c>
       <c r="E39" t="n">
-        <v>184.8835144042969</v>
+        <v>184.7074737548828</v>
       </c>
       <c r="F39" t="n">
-        <v>7072500</v>
+        <v>8791700</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B40" t="n">
-        <v>183.3285602019948</v>
+        <v>184.834617119156</v>
       </c>
       <c r="C40" t="n">
-        <v>185.3235939082472</v>
+        <v>184.8639547534701</v>
       </c>
       <c r="D40" t="n">
-        <v>182.6439756215902</v>
+        <v>181.4313172362143</v>
       </c>
       <c r="E40" t="n">
-        <v>184.7074737548828</v>
+        <v>182.1549987792969</v>
       </c>
       <c r="F40" t="n">
-        <v>8791700</v>
+        <v>7542600</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B41" t="n">
-        <v>184.8346326024117</v>
+        <v>182.7124378793119</v>
       </c>
       <c r="C41" t="n">
-        <v>184.8639702391834</v>
+        <v>183.680624548461</v>
       </c>
       <c r="D41" t="n">
-        <v>181.4313324343818</v>
+        <v>181.5290986170187</v>
       </c>
       <c r="E41" t="n">
-        <v>182.1550140380859</v>
+        <v>182.7417755126953</v>
       </c>
       <c r="F41" t="n">
-        <v>7542600</v>
+        <v>7209400</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B42" t="n">
-        <v>182.7124378793119</v>
+        <v>182.5266206937376</v>
       </c>
       <c r="C42" t="n">
-        <v>183.680624548461</v>
+        <v>183.6903965454173</v>
       </c>
       <c r="D42" t="n">
-        <v>181.5290986170187</v>
+        <v>181.3139438128489</v>
       </c>
       <c r="E42" t="n">
-        <v>182.7417755126953</v>
+        <v>181.9007263183594</v>
       </c>
       <c r="F42" t="n">
-        <v>7209400</v>
+        <v>5049400</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B43" t="n">
-        <v>182.5266206937376</v>
+        <v>182.643986863113</v>
       </c>
       <c r="C43" t="n">
-        <v>183.6903965454173</v>
+        <v>183.3872467567277</v>
       </c>
       <c r="D43" t="n">
-        <v>181.3139438128489</v>
+        <v>181.2846217007125</v>
       </c>
       <c r="E43" t="n">
-        <v>181.9007263183594</v>
+        <v>182.849365234375</v>
       </c>
       <c r="F43" t="n">
-        <v>5049400</v>
+        <v>6767400</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B44" t="n">
-        <v>182.6439716214627</v>
+        <v>183.6023727882189</v>
       </c>
       <c r="C44" t="n">
-        <v>183.3872314530524</v>
+        <v>184.1989294952916</v>
       </c>
       <c r="D44" t="n">
-        <v>181.2846065725014</v>
+        <v>181.6073243254685</v>
       </c>
       <c r="E44" t="n">
-        <v>182.8493499755859</v>
+        <v>182.4581604003906</v>
       </c>
       <c r="F44" t="n">
-        <v>6767400</v>
+        <v>6959200</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B45" t="n">
-        <v>183.6024034971757</v>
+        <v>181.9007248187872</v>
       </c>
       <c r="C45" t="n">
-        <v>184.1989603040272</v>
+        <v>184.2673883725038</v>
       </c>
       <c r="D45" t="n">
-        <v>181.6073547007375</v>
+        <v>181.0401144637998</v>
       </c>
       <c r="E45" t="n">
-        <v>182.4581909179688</v>
+        <v>184.2576141357422</v>
       </c>
       <c r="F45" t="n">
-        <v>6959200</v>
+        <v>5323800</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B46" t="n">
-        <v>181.9007248187872</v>
+        <v>185.2160027316463</v>
       </c>
       <c r="C46" t="n">
-        <v>184.2673883725038</v>
+        <v>189.646164139242</v>
       </c>
       <c r="D46" t="n">
-        <v>181.0401144637998</v>
+        <v>184.8834996277314</v>
       </c>
       <c r="E46" t="n">
-        <v>184.2576141357422</v>
+        <v>189.5581512451172</v>
       </c>
       <c r="F46" t="n">
-        <v>5323800</v>
+        <v>7465600</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B47" t="n">
-        <v>185.2160176409071</v>
+        <v>189.0985059859865</v>
       </c>
       <c r="C47" t="n">
-        <v>189.6461794051158</v>
+        <v>191.2402425833612</v>
       </c>
       <c r="D47" t="n">
-        <v>184.8835145102268</v>
+        <v>188.814903912235</v>
       </c>
       <c r="E47" t="n">
-        <v>189.5581665039062</v>
+        <v>190.1058044433594</v>
       </c>
       <c r="F47" t="n">
-        <v>7465600</v>
+        <v>8803000</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B48" t="n">
-        <v>189.098521163925</v>
+        <v>189.9297961094911</v>
       </c>
       <c r="C48" t="n">
-        <v>191.2402579332056</v>
+        <v>191.6803395836668</v>
       </c>
       <c r="D48" t="n">
-        <v>188.8149190674103</v>
+        <v>189.1865362627468</v>
       </c>
       <c r="E48" t="n">
-        <v>190.1058197021484</v>
+        <v>190.9468688964844</v>
       </c>
       <c r="F48" t="n">
-        <v>8803000</v>
+        <v>8631600</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B49" t="n">
-        <v>189.9297961094911</v>
+        <v>190.7023809412554</v>
       </c>
       <c r="C49" t="n">
-        <v>191.6803395836668</v>
+        <v>192.8343286012861</v>
       </c>
       <c r="D49" t="n">
-        <v>189.1865362627468</v>
+        <v>189.2843405802947</v>
       </c>
       <c r="E49" t="n">
-        <v>190.9468688964844</v>
+        <v>191.6118774414062</v>
       </c>
       <c r="F49" t="n">
-        <v>8631600</v>
+        <v>8824800</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B50" t="n">
-        <v>190.7023809412554</v>
+        <v>192.6192044832797</v>
       </c>
       <c r="C50" t="n">
-        <v>192.8343286012861</v>
+        <v>195.8660272327473</v>
       </c>
       <c r="D50" t="n">
-        <v>189.2843405802947</v>
+        <v>191.5825532918377</v>
       </c>
       <c r="E50" t="n">
-        <v>191.6118774414062</v>
+        <v>195.1814575195312</v>
       </c>
       <c r="F50" t="n">
-        <v>8824800</v>
+        <v>13257000</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B51" t="n">
-        <v>192.619189424801</v>
+        <v>194.6239916898205</v>
       </c>
       <c r="C51" t="n">
-        <v>195.8660119204403</v>
+        <v>195.8855695967434</v>
       </c>
       <c r="D51" t="n">
-        <v>191.5825383144018</v>
+        <v>194.1545746400929</v>
       </c>
       <c r="E51" t="n">
-        <v>195.1814422607422</v>
+        <v>195.5921783447266</v>
       </c>
       <c r="F51" t="n">
-        <v>13257000</v>
+        <v>12468600</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B52" t="n">
-        <v>194.6239916898205</v>
+        <v>195.5921681443101</v>
       </c>
       <c r="C52" t="n">
-        <v>195.8855695967434</v>
+        <v>198.9954676917216</v>
       </c>
       <c r="D52" t="n">
-        <v>194.1545746400929</v>
+        <v>194.9858371982622</v>
       </c>
       <c r="E52" t="n">
-        <v>195.5921783447266</v>
+        <v>198.0468444824219</v>
       </c>
       <c r="F52" t="n">
-        <v>12468600</v>
+        <v>14690800</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B53" t="n">
-        <v>195.5921832139753</v>
+        <v>197.5481028667918</v>
       </c>
       <c r="C53" t="n">
-        <v>198.9954830235987</v>
+        <v>200.0027793669477</v>
       </c>
       <c r="D53" t="n">
-        <v>194.9858522212118</v>
+        <v>197.1275868403205</v>
       </c>
       <c r="E53" t="n">
-        <v>198.0468597412109</v>
+        <v>198.5945281982422</v>
       </c>
       <c r="F53" t="n">
-        <v>14690800</v>
+        <v>10612600</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B54" t="n">
-        <v>197.5480876884036</v>
+        <v>199.4649096707152</v>
       </c>
       <c r="C54" t="n">
-        <v>200.0027639999573</v>
+        <v>202.3792289443294</v>
       </c>
       <c r="D54" t="n">
-        <v>197.1275716942422</v>
+        <v>198.5162864137085</v>
       </c>
       <c r="E54" t="n">
-        <v>198.5945129394531</v>
+        <v>199.4062194824219</v>
       </c>
       <c r="F54" t="n">
-        <v>10612600</v>
+        <v>13189100</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B55" t="n">
-        <v>199.4649249339953</v>
+        <v>199.2204100458954</v>
       </c>
       <c r="C55" t="n">
-        <v>202.3792444306165</v>
+        <v>201.5772843382305</v>
       </c>
       <c r="D55" t="n">
-        <v>198.5163016043988</v>
+        <v>198.5260512809348</v>
       </c>
       <c r="E55" t="n">
-        <v>199.4062347412109</v>
+        <v>201.5088348388672</v>
       </c>
       <c r="F55" t="n">
-        <v>13189100</v>
+        <v>14803900</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,25 +1873,25 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B56" t="n">
-        <v>199.2204251313988</v>
+        <v>201.9320489082132</v>
       </c>
       <c r="C56" t="n">
-        <v>201.5772996022027</v>
+        <v>204.4318498051307</v>
       </c>
       <c r="D56" t="n">
-        <v>198.5260663138595</v>
+        <v>201.9320489082132</v>
       </c>
       <c r="E56" t="n">
-        <v>201.5088500976562</v>
+        <v>203.3984680175781</v>
       </c>
       <c r="F56" t="n">
-        <v>14803900</v>
+        <v>10275300</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -1899,25 +1899,25 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B57" t="n">
-        <v>201.9320337594338</v>
+        <v>203.2213139605992</v>
       </c>
       <c r="C57" t="n">
-        <v>204.4318344688182</v>
+        <v>204.5204108409229</v>
       </c>
       <c r="D57" t="n">
-        <v>201.9320337594338</v>
+        <v>202.6800173366119</v>
       </c>
       <c r="E57" t="n">
-        <v>203.3984527587891</v>
+        <v>204.2743682861328</v>
       </c>
       <c r="F57" t="n">
-        <v>10275300</v>
+        <v>6729000</v>
       </c>
       <c r="G57" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B58" t="n">
-        <v>203.2213139605992</v>
+        <v>203.723236152328</v>
       </c>
       <c r="C58" t="n">
-        <v>204.5204108409229</v>
+        <v>204.1759610624769</v>
       </c>
       <c r="D58" t="n">
-        <v>202.6800173366119</v>
+        <v>201.390757529436</v>
       </c>
       <c r="E58" t="n">
-        <v>204.2743682861328</v>
+        <v>203.6445007324219</v>
       </c>
       <c r="F58" t="n">
-        <v>6729000</v>
+        <v>5638300</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B59" t="n">
-        <v>203.723236152328</v>
+        <v>203.2311491085565</v>
       </c>
       <c r="C59" t="n">
-        <v>204.1759610624769</v>
+        <v>204.4121503614282</v>
       </c>
       <c r="D59" t="n">
-        <v>201.390757529436</v>
+        <v>202.0895080566406</v>
       </c>
       <c r="E59" t="n">
-        <v>203.6445007324219</v>
+        <v>202.0895080566406</v>
       </c>
       <c r="F59" t="n">
-        <v>5638300</v>
+        <v>8473700</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B60" t="n">
-        <v>203.2311491085565</v>
+        <v>201.9910999780921</v>
       </c>
       <c r="C60" t="n">
-        <v>204.4121503614282</v>
+        <v>202.3552381514841</v>
       </c>
       <c r="D60" t="n">
-        <v>202.0895080566406</v>
+        <v>199.8849763223805</v>
       </c>
       <c r="E60" t="n">
-        <v>202.0895080566406</v>
+        <v>202.1682434082031</v>
       </c>
       <c r="F60" t="n">
-        <v>8473700</v>
+        <v>8393600</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B61" t="n">
-        <v>201.9910999780921</v>
+        <v>202.6406353348706</v>
       </c>
       <c r="C61" t="n">
-        <v>202.3552381514841</v>
+        <v>203.7429161551587</v>
       </c>
       <c r="D61" t="n">
-        <v>199.8849763223805</v>
+        <v>201.7450518785209</v>
       </c>
       <c r="E61" t="n">
-        <v>202.1682434082031</v>
+        <v>202.0796661376953</v>
       </c>
       <c r="F61" t="n">
-        <v>8393600</v>
+        <v>8363300</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B62" t="n">
-        <v>202.6406353348706</v>
+        <v>201.35139543875</v>
       </c>
       <c r="C62" t="n">
-        <v>203.7429161551587</v>
+        <v>201.6171256211029</v>
       </c>
       <c r="D62" t="n">
-        <v>201.7450518785209</v>
+        <v>198.5169952235581</v>
       </c>
       <c r="E62" t="n">
-        <v>202.0796661376953</v>
+        <v>199.2747955322266</v>
       </c>
       <c r="F62" t="n">
-        <v>8363300</v>
+        <v>9049900</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B63" t="n">
-        <v>201.3513800209524</v>
+        <v>199.7668717489871</v>
       </c>
       <c r="C63" t="n">
-        <v>201.6171101829578</v>
+        <v>200.2294329646455</v>
       </c>
       <c r="D63" t="n">
-        <v>198.516980022795</v>
+        <v>197.6312241234294</v>
       </c>
       <c r="E63" t="n">
-        <v>199.2747802734375</v>
+        <v>198.7334899902344</v>
       </c>
       <c r="F63" t="n">
-        <v>9049900</v>
+        <v>7785300</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B64" t="n">
-        <v>199.7668717489871</v>
+        <v>199.4519359184436</v>
       </c>
       <c r="C64" t="n">
-        <v>200.2294329646455</v>
+        <v>200.0424290268597</v>
       </c>
       <c r="D64" t="n">
-        <v>197.6312241234294</v>
+        <v>197.8083734899551</v>
       </c>
       <c r="E64" t="n">
-        <v>198.7334899902344</v>
+        <v>198.4283905029297</v>
       </c>
       <c r="F64" t="n">
-        <v>7785300</v>
+        <v>7785700</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B65" t="n">
-        <v>199.4519359184436</v>
+        <v>199.7078130861464</v>
       </c>
       <c r="C65" t="n">
-        <v>200.0424290268597</v>
+        <v>202.2863341775681</v>
       </c>
       <c r="D65" t="n">
-        <v>197.8083734899551</v>
+        <v>196.7454662214423</v>
       </c>
       <c r="E65" t="n">
-        <v>198.4283905029297</v>
+        <v>196.794677734375</v>
       </c>
       <c r="F65" t="n">
-        <v>7785700</v>
+        <v>7509400</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B66" t="n">
-        <v>199.7078130861464</v>
+        <v>197.4146980881505</v>
       </c>
       <c r="C66" t="n">
-        <v>202.2863341775681</v>
+        <v>203.5264016771889</v>
       </c>
       <c r="D66" t="n">
-        <v>196.7454662214423</v>
+        <v>197.011184699407</v>
       </c>
       <c r="E66" t="n">
-        <v>196.794677734375</v>
+        <v>203.2705078125</v>
       </c>
       <c r="F66" t="n">
-        <v>7509400</v>
+        <v>11599800</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B67" t="n">
-        <v>197.4146980881505</v>
+        <v>204.608977678963</v>
       </c>
       <c r="C67" t="n">
-        <v>203.5264016771889</v>
+        <v>207.8961175457048</v>
       </c>
       <c r="D67" t="n">
-        <v>197.011184699407</v>
+        <v>204.5400935742317</v>
       </c>
       <c r="E67" t="n">
-        <v>203.2705078125</v>
+        <v>206.6855773925781</v>
       </c>
       <c r="F67" t="n">
-        <v>11599800</v>
+        <v>9009000</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B68" t="n">
-        <v>204.608977678963</v>
+        <v>206.951319079071</v>
       </c>
       <c r="C68" t="n">
-        <v>207.8961175457048</v>
+        <v>208.9098232838249</v>
       </c>
       <c r="D68" t="n">
-        <v>204.5400935742317</v>
+        <v>205.6522221573458</v>
       </c>
       <c r="E68" t="n">
-        <v>206.6855773925781</v>
+        <v>208.2307434082031</v>
       </c>
       <c r="F68" t="n">
-        <v>9009000</v>
+        <v>6922700</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B69" t="n">
-        <v>206.951319079071</v>
+        <v>207.020201869705</v>
       </c>
       <c r="C69" t="n">
-        <v>208.9098232838249</v>
+        <v>211.7835819022478</v>
       </c>
       <c r="D69" t="n">
-        <v>205.6522221573458</v>
+        <v>205.7014024249555</v>
       </c>
       <c r="E69" t="n">
-        <v>208.2307434082031</v>
+        <v>210.7797241210938</v>
       </c>
       <c r="F69" t="n">
-        <v>6922700</v>
+        <v>8467000</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B70" t="n">
-        <v>207.0202168563343</v>
+        <v>210.612413130432</v>
       </c>
       <c r="C70" t="n">
-        <v>211.7835972337083</v>
+        <v>211.3308531386185</v>
       </c>
       <c r="D70" t="n">
-        <v>205.7014173161141</v>
+        <v>205.5045676241825</v>
       </c>
       <c r="E70" t="n">
-        <v>210.7797393798828</v>
+        <v>205.98681640625</v>
       </c>
       <c r="F70" t="n">
-        <v>8467000</v>
+        <v>9949800</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B71" t="n">
-        <v>210.612413130432</v>
+        <v>206.0753812226996</v>
       </c>
       <c r="C71" t="n">
-        <v>211.3308531386185</v>
+        <v>208.171668387852</v>
       </c>
       <c r="D71" t="n">
-        <v>205.5045676241825</v>
+        <v>205.1601102176154</v>
       </c>
       <c r="E71" t="n">
-        <v>205.98681640625</v>
+        <v>207.0005035400391</v>
       </c>
       <c r="F71" t="n">
-        <v>9949800</v>
+        <v>8457600</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B72" t="n">
-        <v>206.0753964132944</v>
+        <v>206.4789006202035</v>
       </c>
       <c r="C72" t="n">
-        <v>208.1716837329721</v>
+        <v>207.7189496038768</v>
       </c>
       <c r="D72" t="n">
-        <v>205.1601253407421</v>
+        <v>204.4711851031195</v>
       </c>
       <c r="E72" t="n">
-        <v>207.0005187988281</v>
+        <v>205.0124816894531</v>
       </c>
       <c r="F72" t="n">
-        <v>8457600</v>
+        <v>7499900</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B73" t="n">
-        <v>206.478915988136</v>
+        <v>204.2743754538735</v>
       </c>
       <c r="C73" t="n">
-        <v>207.7189650641044</v>
+        <v>205.9277892890467</v>
       </c>
       <c r="D73" t="n">
-        <v>204.4712003216206</v>
+        <v>202.768596167102</v>
       </c>
       <c r="E73" t="n">
-        <v>205.0124969482422</v>
+        <v>203.1032104492188</v>
       </c>
       <c r="F73" t="n">
-        <v>7499900</v>
+        <v>24803900</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B74" t="n">
-        <v>204.2743754538735</v>
+        <v>202.8669973529117</v>
       </c>
       <c r="C74" t="n">
-        <v>205.9277892890467</v>
+        <v>204.7861261374966</v>
       </c>
       <c r="D74" t="n">
-        <v>202.768596167102</v>
+        <v>202.2469653543363</v>
       </c>
       <c r="E74" t="n">
-        <v>203.1032104492188</v>
+        <v>204.0381622314453</v>
       </c>
       <c r="F74" t="n">
-        <v>24803900</v>
+        <v>8187800</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B75" t="n">
-        <v>202.8670125241163</v>
+        <v>201.7745885077481</v>
       </c>
       <c r="C75" t="n">
-        <v>204.7861414522214</v>
+        <v>203.2606801764464</v>
       </c>
       <c r="D75" t="n">
-        <v>202.2469804791725</v>
+        <v>200.0621268695276</v>
       </c>
       <c r="E75" t="n">
-        <v>204.0381774902344</v>
+        <v>202.5225524902344</v>
       </c>
       <c r="F75" t="n">
-        <v>8187800</v>
+        <v>7047300</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B76" t="n">
-        <v>201.7745733053134</v>
+        <v>202.7390686836449</v>
       </c>
       <c r="C76" t="n">
-        <v>203.2606648620441</v>
+        <v>204.6483613448813</v>
       </c>
       <c r="D76" t="n">
-        <v>200.062111796116</v>
+        <v>202.3158826903017</v>
       </c>
       <c r="E76" t="n">
-        <v>202.5225372314453</v>
+        <v>204.4908905029297</v>
       </c>
       <c r="F76" t="n">
-        <v>7047300</v>
+        <v>2376500</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B77" t="n">
-        <v>202.739053555574</v>
+        <v>204.2448386926768</v>
       </c>
       <c r="C77" t="n">
-        <v>204.648346074342</v>
+        <v>204.7467600842614</v>
       </c>
       <c r="D77" t="n">
-        <v>202.3158675938084</v>
+        <v>203.4378269444086</v>
       </c>
       <c r="E77" t="n">
-        <v>204.4908752441406</v>
+        <v>204.34326171875</v>
       </c>
       <c r="F77" t="n">
-        <v>2376500</v>
+        <v>2316700</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B78" t="n">
-        <v>204.2448386926768</v>
+        <v>204.7074055853226</v>
       </c>
       <c r="C78" t="n">
-        <v>204.7467600842614</v>
+        <v>206.1541370088678</v>
       </c>
       <c r="D78" t="n">
-        <v>203.4378269444086</v>
+        <v>204.097224854962</v>
       </c>
       <c r="E78" t="n">
-        <v>204.34326171875</v>
+        <v>204.2743682861328</v>
       </c>
       <c r="F78" t="n">
-        <v>2316700</v>
+        <v>4348900</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B79" t="n">
-        <v>204.7074055853226</v>
+        <v>204.2251366175628</v>
       </c>
       <c r="C79" t="n">
-        <v>206.1541370088678</v>
+        <v>204.4022950484963</v>
       </c>
       <c r="D79" t="n">
-        <v>204.097224854962</v>
+        <v>203.2508178077831</v>
       </c>
       <c r="E79" t="n">
-        <v>204.2743682861328</v>
+        <v>203.6346435546875</v>
       </c>
       <c r="F79" t="n">
-        <v>4348900</v>
+        <v>3937400</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B80" t="n">
-        <v>204.2251519205988</v>
+        <v>203.6346662875698</v>
       </c>
       <c r="C80" t="n">
-        <v>204.4023103648072</v>
+        <v>204.2153231202547</v>
       </c>
       <c r="D80" t="n">
-        <v>203.2508330378112</v>
+        <v>203.1032059526835</v>
       </c>
       <c r="E80" t="n">
-        <v>203.6346588134766</v>
+        <v>203.6740264892578</v>
       </c>
       <c r="F80" t="n">
-        <v>3937400</v>
+        <v>4083800</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B81" t="n">
-        <v>203.6346510317296</v>
+        <v>203.5460790066363</v>
       </c>
       <c r="C81" t="n">
-        <v>204.2153078209129</v>
+        <v>204.1070481869595</v>
       </c>
       <c r="D81" t="n">
-        <v>203.103190736659</v>
+        <v>200.4557702982002</v>
       </c>
       <c r="E81" t="n">
-        <v>203.6740112304688</v>
+        <v>204.0676879882812</v>
       </c>
       <c r="F81" t="n">
-        <v>4083800</v>
+        <v>6325500</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B82" t="n">
-        <v>203.546094226423</v>
+        <v>202.6111087313451</v>
       </c>
       <c r="C82" t="n">
-        <v>204.1070634486917</v>
+        <v>202.68000785174</v>
       </c>
       <c r="D82" t="n">
-        <v>200.4557852869147</v>
+        <v>197.7296330824079</v>
       </c>
       <c r="E82" t="n">
-        <v>204.0677032470703</v>
+        <v>201.0758056640625</v>
       </c>
       <c r="F82" t="n">
-        <v>6325500</v>
+        <v>9477000</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B83" t="n">
-        <v>202.6111087313451</v>
+        <v>201.3612380414601</v>
       </c>
       <c r="C83" t="n">
-        <v>202.68000785174</v>
+        <v>203.4378378581467</v>
       </c>
       <c r="D83" t="n">
-        <v>197.7296330824079</v>
+        <v>200.8888255116597</v>
       </c>
       <c r="E83" t="n">
-        <v>201.0758056640625</v>
+        <v>201.5482177734375</v>
       </c>
       <c r="F83" t="n">
-        <v>9477000</v>
+        <v>8107900</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B84" t="n">
-        <v>201.3612227968269</v>
+        <v>202.0107645526058</v>
       </c>
       <c r="C84" t="n">
-        <v>203.4378224562984</v>
+        <v>204.9632750752426</v>
       </c>
       <c r="D84" t="n">
-        <v>200.8888103027919</v>
+        <v>201.7844096173656</v>
       </c>
       <c r="E84" t="n">
-        <v>201.5482025146484</v>
+        <v>204.2054748535156</v>
       </c>
       <c r="F84" t="n">
-        <v>8107900</v>
+        <v>7545900</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B85" t="n">
-        <v>202.0107645526058</v>
+        <v>203.6543250611801</v>
       </c>
       <c r="C85" t="n">
-        <v>204.9632750752426</v>
+        <v>205.6718769031367</v>
       </c>
       <c r="D85" t="n">
-        <v>201.7844096173656</v>
+        <v>201.7253599471909</v>
       </c>
       <c r="E85" t="n">
-        <v>204.2054748535156</v>
+        <v>202.4930114746094</v>
       </c>
       <c r="F85" t="n">
-        <v>7545900</v>
+        <v>6557800</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B86" t="n">
-        <v>203.6543250611801</v>
+        <v>202.6504992553581</v>
       </c>
       <c r="C86" t="n">
-        <v>205.6718769031367</v>
+        <v>203.4279871432506</v>
       </c>
       <c r="D86" t="n">
-        <v>201.7253599471909</v>
+        <v>200.7805667748665</v>
       </c>
       <c r="E86" t="n">
-        <v>202.4930114746094</v>
+        <v>201.1545562744141</v>
       </c>
       <c r="F86" t="n">
-        <v>6557800</v>
+        <v>6154300</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B87" t="n">
-        <v>202.6504838830927</v>
+        <v>202.2962039964493</v>
       </c>
       <c r="C87" t="n">
-        <v>203.4279717120081</v>
+        <v>206.5773357028104</v>
       </c>
       <c r="D87" t="n">
-        <v>200.7805515444468</v>
+        <v>200.6231175244031</v>
       </c>
       <c r="E87" t="n">
-        <v>201.154541015625</v>
+        <v>206.4001922607422</v>
       </c>
       <c r="F87" t="n">
-        <v>6154300</v>
+        <v>11794300</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B88" t="n">
-        <v>202.2961890410606</v>
+        <v>206.5871726162479</v>
       </c>
       <c r="C88" t="n">
-        <v>206.5773204309254</v>
+        <v>210.9962509571494</v>
       </c>
       <c r="D88" t="n">
-        <v>200.6231026927027</v>
+        <v>205.5537908911432</v>
       </c>
       <c r="E88" t="n">
-        <v>206.4001770019531</v>
+        <v>210.2679595947266</v>
       </c>
       <c r="F88" t="n">
-        <v>11794300</v>
+        <v>11379600</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B89" t="n">
-        <v>206.5871726162479</v>
+        <v>211.3308558190507</v>
       </c>
       <c r="C89" t="n">
-        <v>210.9962509571494</v>
+        <v>215.3954834155094</v>
       </c>
       <c r="D89" t="n">
-        <v>205.5537908911432</v>
+        <v>210.7600353199485</v>
       </c>
       <c r="E89" t="n">
-        <v>210.2679595947266</v>
+        <v>215.0903930664062</v>
       </c>
       <c r="F89" t="n">
-        <v>11379600</v>
+        <v>11858800</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B90" t="n">
-        <v>211.3308558190507</v>
+        <v>214.7754540862871</v>
       </c>
       <c r="C90" t="n">
-        <v>215.3954834155094</v>
+        <v>216.2713969640869</v>
       </c>
       <c r="D90" t="n">
-        <v>210.7600353199485</v>
+        <v>212.4921870786144</v>
       </c>
       <c r="E90" t="n">
-        <v>215.0903930664062</v>
+        <v>216.0942535400391</v>
       </c>
       <c r="F90" t="n">
-        <v>11858800</v>
+        <v>8492100</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B91" t="n">
-        <v>214.7754540862871</v>
+        <v>215.5726286297608</v>
       </c>
       <c r="C91" t="n">
-        <v>216.2713969640869</v>
+        <v>216.6256979258031</v>
       </c>
       <c r="D91" t="n">
-        <v>212.4921870786144</v>
+        <v>214.686881478726</v>
       </c>
       <c r="E91" t="n">
-        <v>216.0942535400391</v>
+        <v>215.1986541748047</v>
       </c>
       <c r="F91" t="n">
-        <v>8492100</v>
+        <v>10021500</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B92" t="n">
-        <v>215.5726286297608</v>
+        <v>213.6535022600511</v>
       </c>
       <c r="C92" t="n">
-        <v>216.6256979258031</v>
+        <v>215.2675407658023</v>
       </c>
       <c r="D92" t="n">
-        <v>214.686881478726</v>
+        <v>211.1045050802375</v>
       </c>
       <c r="E92" t="n">
-        <v>215.1986541748047</v>
+        <v>214.7557830810547</v>
       </c>
       <c r="F92" t="n">
-        <v>10021500</v>
+        <v>14057100</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B93" t="n">
-        <v>213.6535022600511</v>
+        <v>207.659916851811</v>
       </c>
       <c r="C93" t="n">
-        <v>215.2675407658023</v>
+        <v>215.2183369488501</v>
       </c>
       <c r="D93" t="n">
-        <v>211.1045050802375</v>
+        <v>207.1678317407877</v>
       </c>
       <c r="E93" t="n">
-        <v>214.7557830810547</v>
+        <v>214.5589447021484</v>
       </c>
       <c r="F93" t="n">
-        <v>14057100</v>
+        <v>14762900</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B94" t="n">
-        <v>207.6599020836601</v>
+        <v>215.3069232717918</v>
       </c>
       <c r="C94" t="n">
-        <v>215.218321643167</v>
+        <v>218.6530960134773</v>
       </c>
       <c r="D94" t="n">
-        <v>207.1678170076325</v>
+        <v>214.6475310263463</v>
       </c>
       <c r="E94" t="n">
-        <v>214.5589294433594</v>
+        <v>215.0313568115234</v>
       </c>
       <c r="F94" t="n">
-        <v>14762900</v>
+        <v>13160000</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B95" t="n">
-        <v>215.3069079934484</v>
+        <v>216.3206133966017</v>
       </c>
       <c r="C95" t="n">
-        <v>218.6530804976869</v>
+        <v>217.7082969855193</v>
       </c>
       <c r="D95" t="n">
-        <v>214.6475157947938</v>
+        <v>214.3916331931512</v>
       </c>
       <c r="E95" t="n">
-        <v>215.0313415527344</v>
+        <v>216.6552276611328</v>
       </c>
       <c r="F95" t="n">
-        <v>13160000</v>
+        <v>6950600</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B96" t="n">
-        <v>216.3206133966017</v>
+        <v>216.7241195858665</v>
       </c>
       <c r="C96" t="n">
-        <v>217.7082969855193</v>
+        <v>218.515301484998</v>
       </c>
       <c r="D96" t="n">
-        <v>214.3916331931512</v>
+        <v>216.5174372427288</v>
       </c>
       <c r="E96" t="n">
-        <v>216.6552276611328</v>
+        <v>217.9838562011719</v>
       </c>
       <c r="F96" t="n">
-        <v>6950600</v>
+        <v>6856700</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B97" t="n">
-        <v>216.7241347564745</v>
+        <v>218.4857835732108</v>
       </c>
       <c r="C97" t="n">
-        <v>218.5153167809881</v>
+        <v>221.9303792601758</v>
       </c>
       <c r="D97" t="n">
-        <v>216.5174523988691</v>
+        <v>217.2063593146032</v>
       </c>
       <c r="E97" t="n">
-        <v>217.9838714599609</v>
+        <v>220.8871612548828</v>
       </c>
       <c r="F97" t="n">
-        <v>6856700</v>
+        <v>8154100</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B98" t="n">
-        <v>218.4857835732108</v>
+        <v>222.8161377007139</v>
       </c>
       <c r="C98" t="n">
-        <v>221.9303792601758</v>
+        <v>224.9518003498371</v>
       </c>
       <c r="D98" t="n">
-        <v>217.2063593146032</v>
+        <v>222.5012110309432</v>
       </c>
       <c r="E98" t="n">
-        <v>220.8871612548828</v>
+        <v>224.1152496337891</v>
       </c>
       <c r="F98" t="n">
-        <v>8154100</v>
+        <v>9026500</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B99" t="n">
-        <v>222.8161377007139</v>
+        <v>225.1879747271155</v>
       </c>
       <c r="C99" t="n">
-        <v>224.9518003498371</v>
+        <v>226.3591396349424</v>
       </c>
       <c r="D99" t="n">
-        <v>222.5012110309432</v>
+        <v>223.4853645338204</v>
       </c>
       <c r="E99" t="n">
-        <v>224.1152496337891</v>
+        <v>223.6920318603516</v>
       </c>
       <c r="F99" t="n">
-        <v>9026500</v>
+        <v>9645300</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B100" t="n">
-        <v>225.1879747271155</v>
+        <v>224.6466706191826</v>
       </c>
       <c r="C100" t="n">
-        <v>226.3591396349424</v>
+        <v>224.8828768588529</v>
       </c>
       <c r="D100" t="n">
-        <v>223.4853645338204</v>
+        <v>221.7630593189417</v>
       </c>
       <c r="E100" t="n">
-        <v>223.6920318603516</v>
+        <v>223.6526641845703</v>
       </c>
       <c r="F100" t="n">
-        <v>9645300</v>
+        <v>11045500</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B101" t="n">
-        <v>224.6466859457881</v>
+        <v>224.7057634887497</v>
       </c>
       <c r="C101" t="n">
-        <v>224.8828922015737</v>
+        <v>227.530327361073</v>
       </c>
       <c r="D101" t="n">
-        <v>221.7630744488117</v>
+        <v>223.6526940904743</v>
       </c>
       <c r="E101" t="n">
-        <v>223.6526794433594</v>
+        <v>227.0972900390625</v>
       </c>
       <c r="F101" t="n">
-        <v>11045500</v>
+        <v>8187500</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B102" t="n">
-        <v>224.7057483906486</v>
+        <v>227.8354016268972</v>
       </c>
       <c r="C102" t="n">
-        <v>227.530312073188</v>
+        <v>231.4768283686728</v>
       </c>
       <c r="D102" t="n">
-        <v>223.6526790631295</v>
+        <v>226.8315438166281</v>
       </c>
       <c r="E102" t="n">
-        <v>227.0972747802734</v>
+        <v>229.4100799560547</v>
       </c>
       <c r="F102" t="n">
-        <v>8187500</v>
+        <v>9346600</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B103" t="n">
-        <v>227.8354016268972</v>
+        <v>231.2799860551316</v>
       </c>
       <c r="C103" t="n">
-        <v>231.4768283686728</v>
+        <v>232.0968490845446</v>
       </c>
       <c r="D103" t="n">
-        <v>226.8315438166281</v>
+        <v>229.252597941833</v>
       </c>
       <c r="E103" t="n">
-        <v>229.4100799560547</v>
+        <v>230.7583770751953</v>
       </c>
       <c r="F103" t="n">
-        <v>9346600</v>
+        <v>8641400</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B104" t="n">
-        <v>231.2800013484118</v>
+        <v>231.2799897072634</v>
       </c>
       <c r="C104" t="n">
-        <v>232.0968644318395</v>
+        <v>235.787490883202</v>
       </c>
       <c r="D104" t="n">
-        <v>229.2526131010531</v>
+        <v>231.2701534117819</v>
       </c>
       <c r="E104" t="n">
-        <v>230.7583923339844</v>
+        <v>234.0258178710938</v>
       </c>
       <c r="F104" t="n">
-        <v>8641400</v>
+        <v>10267500</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B105" t="n">
-        <v>231.2799897072634</v>
+        <v>235.1773154262319</v>
       </c>
       <c r="C105" t="n">
-        <v>235.787490883202</v>
+        <v>237.125968199395</v>
       </c>
       <c r="D105" t="n">
-        <v>231.2701534117819</v>
+        <v>234.2128178267284</v>
       </c>
       <c r="E105" t="n">
-        <v>234.0258178710938</v>
+        <v>236.1910095214844</v>
       </c>
       <c r="F105" t="n">
-        <v>10267500</v>
+        <v>8274000</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B106" t="n">
-        <v>235.1773154262319</v>
+        <v>236.4468802764997</v>
       </c>
       <c r="C106" t="n">
-        <v>237.125968199395</v>
+        <v>236.9291290597546</v>
       </c>
       <c r="D106" t="n">
-        <v>234.2128178267284</v>
+        <v>233.2876874641771</v>
       </c>
       <c r="E106" t="n">
-        <v>236.1910095214844</v>
+        <v>234.8623657226562</v>
       </c>
       <c r="F106" t="n">
-        <v>8274000</v>
+        <v>9378500</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B107" t="n">
-        <v>236.4468956382332</v>
+        <v>236.1811678557945</v>
       </c>
       <c r="C107" t="n">
-        <v>236.9291444528193</v>
+        <v>236.6929405807981</v>
       </c>
       <c r="D107" t="n">
-        <v>233.2877026206608</v>
+        <v>234.1144193808212</v>
       </c>
       <c r="E107" t="n">
-        <v>234.8623809814453</v>
+        <v>234.5769805908203</v>
       </c>
       <c r="F107" t="n">
-        <v>9378500</v>
+        <v>6723300</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B108" t="n">
-        <v>236.1811678557945</v>
+        <v>235.5512982627408</v>
       </c>
       <c r="C108" t="n">
-        <v>236.6929405807981</v>
+        <v>237.4409032943991</v>
       </c>
       <c r="D108" t="n">
-        <v>234.1144193808212</v>
+        <v>233.6420056217357</v>
       </c>
       <c r="E108" t="n">
-        <v>234.5769805908203</v>
+        <v>237.0472412109375</v>
       </c>
       <c r="F108" t="n">
-        <v>6723300</v>
+        <v>6803900</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B109" t="n">
-        <v>235.5512982627408</v>
+        <v>236.6732379543034</v>
       </c>
       <c r="C109" t="n">
-        <v>237.4409032943991</v>
+        <v>242.4503270560588</v>
       </c>
       <c r="D109" t="n">
-        <v>233.6420056217357</v>
+        <v>235.8858988159272</v>
       </c>
       <c r="E109" t="n">
-        <v>237.0472412109375</v>
+        <v>240.6788177490234</v>
       </c>
       <c r="F109" t="n">
-        <v>6803900</v>
+        <v>10254300</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B110" t="n">
-        <v>236.6732529591429</v>
+        <v>240.7181906333224</v>
       </c>
       <c r="C110" t="n">
-        <v>242.4503424271597</v>
+        <v>241.0724925134001</v>
       </c>
       <c r="D110" t="n">
-        <v>235.8859137708501</v>
+        <v>238.7695378015177</v>
       </c>
       <c r="E110" t="n">
-        <v>240.6788330078125</v>
+        <v>239.5962371826172</v>
       </c>
       <c r="F110" t="n">
-        <v>10254300</v>
+        <v>13268500</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B111" t="n">
-        <v>240.7181753030812</v>
+        <v>240.2654733107899</v>
       </c>
       <c r="C111" t="n">
-        <v>241.0724771605951</v>
+        <v>240.6197751799101</v>
       </c>
       <c r="D111" t="n">
-        <v>238.7695225953774</v>
+        <v>238.0412390701625</v>
       </c>
       <c r="E111" t="n">
-        <v>239.5962219238281</v>
+        <v>239.4781341552734</v>
       </c>
       <c r="F111" t="n">
-        <v>13268500</v>
+        <v>12703000</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B112" t="n">
-        <v>240.2654733107899</v>
+        <v>239.389564336343</v>
       </c>
       <c r="C112" t="n">
-        <v>240.6197751799101</v>
+        <v>241.1905976005163</v>
       </c>
       <c r="D112" t="n">
-        <v>238.0412390701625</v>
+        <v>238.9762146553066</v>
       </c>
       <c r="E112" t="n">
-        <v>239.4781341552734</v>
+        <v>241.1118621826172</v>
       </c>
       <c r="F112" t="n">
-        <v>12703000</v>
+        <v>8129700</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B113" t="n">
-        <v>239.389564336343</v>
+        <v>240.7477067024548</v>
       </c>
       <c r="C113" t="n">
-        <v>241.1905976005163</v>
+        <v>243.0506763566235</v>
       </c>
       <c r="D113" t="n">
-        <v>238.9762146553066</v>
+        <v>240.4032561468311</v>
       </c>
       <c r="E113" t="n">
-        <v>241.1118621826172</v>
+        <v>243.00146484375</v>
       </c>
       <c r="F113" t="n">
-        <v>8129700</v>
+        <v>7553900</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B114" t="n">
-        <v>240.7477067024548</v>
+        <v>242.568421266413</v>
       </c>
       <c r="C114" t="n">
-        <v>243.0506763566235</v>
+        <v>242.9719346373659</v>
       </c>
       <c r="D114" t="n">
-        <v>240.4032561468311</v>
+        <v>236.4764055549244</v>
       </c>
       <c r="E114" t="n">
-        <v>243.00146484375</v>
+        <v>238.6514282226562</v>
       </c>
       <c r="F114" t="n">
-        <v>7553900</v>
+        <v>13565800</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B115" t="n">
-        <v>242.568421266413</v>
+        <v>239.7734021969262</v>
       </c>
       <c r="C115" t="n">
-        <v>242.9719346373659</v>
+        <v>242.9030563756065</v>
       </c>
       <c r="D115" t="n">
-        <v>236.4764055549244</v>
+        <v>238.7597080434106</v>
       </c>
       <c r="E115" t="n">
-        <v>238.6514282226562</v>
+        <v>241.9484100341797</v>
       </c>
       <c r="F115" t="n">
-        <v>13565800</v>
+        <v>9622700</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,25 +3433,25 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B116" t="n">
-        <v>239.7733870753068</v>
+        <v>242.7498308706833</v>
       </c>
       <c r="C116" t="n">
-        <v>242.9030410566114</v>
+        <v>244.6296889736104</v>
       </c>
       <c r="D116" t="n">
-        <v>238.7596929857211</v>
+        <v>241.9484024234396</v>
       </c>
       <c r="E116" t="n">
-        <v>241.9483947753906</v>
+        <v>243.6699676513672</v>
       </c>
       <c r="F116" t="n">
-        <v>9622700</v>
+        <v>7246300</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -3459,25 +3459,25 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B117" t="n">
-        <v>242.7498156695138</v>
+        <v>242.2650193059668</v>
       </c>
       <c r="C117" t="n">
-        <v>244.6296736547229</v>
+        <v>244.6296899211394</v>
       </c>
       <c r="D117" t="n">
-        <v>241.9483872724562</v>
+        <v>241.1371014204259</v>
       </c>
       <c r="E117" t="n">
-        <v>243.6699523925781</v>
+        <v>242.5717315673828</v>
       </c>
       <c r="F117" t="n">
-        <v>7246300</v>
+        <v>7698200</v>
       </c>
       <c r="G117" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B118" t="n">
-        <v>242.2650040664713</v>
+        <v>242.5123742558835</v>
       </c>
       <c r="C118" t="n">
-        <v>244.629674532896</v>
+        <v>242.8685596523689</v>
       </c>
       <c r="D118" t="n">
-        <v>241.1370862518812</v>
+        <v>239.4551250760139</v>
       </c>
       <c r="E118" t="n">
-        <v>242.5717163085938</v>
+        <v>240.8897552490234</v>
       </c>
       <c r="F118" t="n">
-        <v>7698200</v>
+        <v>7172600</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B119" t="n">
-        <v>242.5123588943122</v>
+        <v>241.4438165545137</v>
       </c>
       <c r="C119" t="n">
-        <v>242.8685442682355</v>
+        <v>246.3017849576054</v>
       </c>
       <c r="D119" t="n">
-        <v>239.4551099080992</v>
+        <v>239.9300324032001</v>
       </c>
       <c r="E119" t="n">
-        <v>240.8897399902344</v>
+        <v>245.7971801757812</v>
       </c>
       <c r="F119" t="n">
-        <v>7172600</v>
+        <v>16428600</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B120" t="n">
-        <v>241.4438165545137</v>
+        <v>246.549124695673</v>
       </c>
       <c r="C120" t="n">
-        <v>246.3017849576054</v>
+        <v>249.0424223461303</v>
       </c>
       <c r="D120" t="n">
-        <v>239.9300324032001</v>
+        <v>244.2537044562187</v>
       </c>
       <c r="E120" t="n">
-        <v>245.7971801757812</v>
+        <v>245.9257965087891</v>
       </c>
       <c r="F120" t="n">
-        <v>16428600</v>
+        <v>9042400</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B121" t="n">
-        <v>246.549124695673</v>
+        <v>243.8480592687475</v>
       </c>
       <c r="C121" t="n">
-        <v>249.0424223461303</v>
+        <v>245.2530085028214</v>
       </c>
       <c r="D121" t="n">
-        <v>244.2537044562187</v>
+        <v>241.7703087256774</v>
       </c>
       <c r="E121" t="n">
-        <v>245.9257965087891</v>
+        <v>244.1349792480469</v>
       </c>
       <c r="F121" t="n">
-        <v>9042400</v>
+        <v>6178700</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B122" t="n">
-        <v>243.8480592687475</v>
+        <v>243.1455911306439</v>
       </c>
       <c r="C122" t="n">
-        <v>245.2530085028214</v>
+        <v>243.9569081828458</v>
       </c>
       <c r="D122" t="n">
-        <v>241.7703087256774</v>
+        <v>240.6028202250193</v>
       </c>
       <c r="E122" t="n">
-        <v>244.1349792480469</v>
+        <v>242.7003631591797</v>
       </c>
       <c r="F122" t="n">
-        <v>6178700</v>
+        <v>5768000</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B123" t="n">
-        <v>243.145575843863</v>
+        <v>240.0586607026203</v>
       </c>
       <c r="C123" t="n">
-        <v>243.9568928450567</v>
+        <v>240.4247346856854</v>
       </c>
       <c r="D123" t="n">
-        <v>240.6028050981046</v>
+        <v>233.4296538825942</v>
       </c>
       <c r="E123" t="n">
-        <v>242.7003479003906</v>
+        <v>237.0904541015625</v>
       </c>
       <c r="F123" t="n">
-        <v>5768000</v>
+        <v>9375400</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B124" t="n">
-        <v>240.0586452528019</v>
+        <v>235.5964438849938</v>
       </c>
       <c r="C124" t="n">
-        <v>240.424719212307</v>
+        <v>238.238145912047</v>
       </c>
       <c r="D124" t="n">
-        <v>233.4296388594088</v>
+        <v>232.9349495870229</v>
       </c>
       <c r="E124" t="n">
-        <v>237.0904388427734</v>
+        <v>237.8522796630859</v>
       </c>
       <c r="F124" t="n">
-        <v>9375400</v>
+        <v>7179800</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B125" t="n">
-        <v>235.596428770922</v>
+        <v>238.3172853623119</v>
       </c>
       <c r="C125" t="n">
-        <v>238.2381306285037</v>
+        <v>241.5031614171852</v>
       </c>
       <c r="D125" t="n">
-        <v>232.9349346436922</v>
+        <v>237.496079785725</v>
       </c>
       <c r="E125" t="n">
-        <v>237.8522644042969</v>
+        <v>240.0190582275391</v>
       </c>
       <c r="F125" t="n">
-        <v>7179800</v>
+        <v>7844000</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B126" t="n">
-        <v>238.3173005129137</v>
+        <v>239.732151823879</v>
       </c>
       <c r="C126" t="n">
-        <v>241.5031767703235</v>
+        <v>242.4035346970428</v>
       </c>
       <c r="D126" t="n">
-        <v>237.4960948841201</v>
+        <v>238.2678408210546</v>
       </c>
       <c r="E126" t="n">
-        <v>240.0190734863281</v>
+        <v>241.1272125244141</v>
       </c>
       <c r="F126" t="n">
-        <v>7844000</v>
+        <v>7214100</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B127" t="n">
-        <v>239.732151823879</v>
+        <v>240.2960869196001</v>
       </c>
       <c r="C127" t="n">
-        <v>242.4035346970428</v>
+        <v>241.1074039007698</v>
       </c>
       <c r="D127" t="n">
-        <v>238.2678408210546</v>
+        <v>238.802095160397</v>
       </c>
       <c r="E127" t="n">
-        <v>241.1272125244141</v>
+        <v>240.4148254394531</v>
       </c>
       <c r="F127" t="n">
-        <v>7214100</v>
+        <v>6933200</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B128" t="n">
-        <v>240.2960869196001</v>
+        <v>238.9010440853151</v>
       </c>
       <c r="C128" t="n">
-        <v>241.1074039007698</v>
+        <v>241.8098736554103</v>
       </c>
       <c r="D128" t="n">
-        <v>238.802095160397</v>
+        <v>237.7533339953824</v>
       </c>
       <c r="E128" t="n">
-        <v>240.4148254394531</v>
+        <v>239.4748840332031</v>
       </c>
       <c r="F128" t="n">
-        <v>6933200</v>
+        <v>7710200</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B129" t="n">
-        <v>238.9010593075404</v>
+        <v>241.6218975517249</v>
       </c>
       <c r="C129" t="n">
-        <v>241.8098890629796</v>
+        <v>242.9872622066995</v>
       </c>
       <c r="D129" t="n">
-        <v>237.7533491444783</v>
+        <v>238.9406111728678</v>
       </c>
       <c r="E129" t="n">
-        <v>239.4748992919922</v>
+        <v>238.9604034423828</v>
       </c>
       <c r="F129" t="n">
-        <v>7710200</v>
+        <v>6415300</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B130" t="n">
-        <v>241.6219129804633</v>
+        <v>241.3349607287423</v>
       </c>
       <c r="C130" t="n">
-        <v>242.9872777226232</v>
+        <v>242.4628785296478</v>
       </c>
       <c r="D130" t="n">
-        <v>238.940626430393</v>
+        <v>239.1088059824489</v>
       </c>
       <c r="E130" t="n">
-        <v>238.9604187011719</v>
+        <v>240.6127014160156</v>
       </c>
       <c r="F130" t="n">
-        <v>6415300</v>
+        <v>7571500</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B131" t="n">
-        <v>241.3349760333344</v>
+        <v>240.99857884995</v>
       </c>
       <c r="C131" t="n">
-        <v>242.4628939057684</v>
+        <v>241.5526416415011</v>
       </c>
       <c r="D131" t="n">
-        <v>239.1088211458664</v>
+        <v>234.7059805370448</v>
       </c>
       <c r="E131" t="n">
-        <v>240.6127166748047</v>
+        <v>235.5865478515625</v>
       </c>
       <c r="F131" t="n">
-        <v>7571500</v>
+        <v>7281800</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B132" t="n">
-        <v>240.99857884995</v>
+        <v>235.349078713635</v>
       </c>
       <c r="C132" t="n">
-        <v>241.5526416415011</v>
+        <v>236.5759427839531</v>
       </c>
       <c r="D132" t="n">
-        <v>234.7059805370448</v>
+        <v>232.9250465260699</v>
       </c>
       <c r="E132" t="n">
-        <v>235.5865478515625</v>
+        <v>234.7653350830078</v>
       </c>
       <c r="F132" t="n">
-        <v>7281800</v>
+        <v>6811500</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B133" t="n">
-        <v>235.349094010365</v>
+        <v>235.814102878936</v>
       </c>
       <c r="C133" t="n">
-        <v>236.5759581604242</v>
+        <v>236.7243510378414</v>
       </c>
       <c r="D133" t="n">
-        <v>232.9250616652477</v>
+        <v>233.80561773863</v>
       </c>
       <c r="E133" t="n">
-        <v>234.7653503417969</v>
+        <v>235.0819549560547</v>
       </c>
       <c r="F133" t="n">
-        <v>6811500</v>
+        <v>7511500</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B134" t="n">
-        <v>235.814102878936</v>
+        <v>234.3201136195421</v>
       </c>
       <c r="C134" t="n">
-        <v>236.7243510378414</v>
+        <v>235.764632308021</v>
       </c>
       <c r="D134" t="n">
-        <v>233.80561773863</v>
+        <v>232.0148047922595</v>
       </c>
       <c r="E134" t="n">
-        <v>235.0819549560547</v>
+        <v>232.8755798339844</v>
       </c>
       <c r="F134" t="n">
-        <v>7511500</v>
+        <v>17156600</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B135" t="n">
-        <v>234.3201136195421</v>
+        <v>234.884060828395</v>
       </c>
       <c r="C135" t="n">
-        <v>235.764632308021</v>
+        <v>235.7844203946137</v>
       </c>
       <c r="D135" t="n">
-        <v>232.0148047922595</v>
+        <v>231.7674501417346</v>
       </c>
       <c r="E135" t="n">
-        <v>232.8755798339844</v>
+        <v>232.925048828125</v>
       </c>
       <c r="F135" t="n">
-        <v>17156600</v>
+        <v>7313700</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B136" t="n">
-        <v>234.884060828395</v>
+        <v>231.6586126149741</v>
       </c>
       <c r="C136" t="n">
-        <v>235.7844203946137</v>
+        <v>233.4989011687466</v>
       </c>
       <c r="D136" t="n">
-        <v>231.7674501417346</v>
+        <v>229.7787546189723</v>
       </c>
       <c r="E136" t="n">
-        <v>232.925048828125</v>
+        <v>232.7766418457031</v>
       </c>
       <c r="F136" t="n">
-        <v>7313700</v>
+        <v>9046200</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B137" t="n">
-        <v>231.6586126149741</v>
+        <v>234.2904343153693</v>
       </c>
       <c r="C137" t="n">
-        <v>233.4989011687466</v>
+        <v>238.9010520004889</v>
       </c>
       <c r="D137" t="n">
-        <v>229.7787546189723</v>
+        <v>233.2317667584392</v>
       </c>
       <c r="E137" t="n">
-        <v>232.7766418457031</v>
+        <v>237.3872528076172</v>
       </c>
       <c r="F137" t="n">
-        <v>9046200</v>
+        <v>6456400</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B138" t="n">
-        <v>234.2904343153693</v>
+        <v>237.4565300874115</v>
       </c>
       <c r="C138" t="n">
-        <v>238.9010520004889</v>
+        <v>239.0890376929306</v>
       </c>
       <c r="D138" t="n">
-        <v>233.2317667584392</v>
+        <v>236.3978624775069</v>
       </c>
       <c r="E138" t="n">
-        <v>237.3872528076172</v>
+        <v>236.70458984375</v>
       </c>
       <c r="F138" t="n">
-        <v>6456400</v>
+        <v>5171400</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B139" t="n">
-        <v>237.4565300874115</v>
+        <v>238.6339116976677</v>
       </c>
       <c r="C139" t="n">
-        <v>239.0890376929306</v>
+        <v>240.1081112682183</v>
       </c>
       <c r="D139" t="n">
-        <v>236.3978624775069</v>
+        <v>236.5957456438558</v>
       </c>
       <c r="E139" t="n">
-        <v>236.70458984375</v>
+        <v>237.9017486572266</v>
       </c>
       <c r="F139" t="n">
-        <v>5171400</v>
+        <v>7617600</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B140" t="n">
-        <v>238.6339116976677</v>
+        <v>240.9095376592209</v>
       </c>
       <c r="C140" t="n">
-        <v>240.1081112682183</v>
+        <v>241.6219084230326</v>
       </c>
       <c r="D140" t="n">
-        <v>236.5957456438558</v>
+        <v>237.9611083490254</v>
       </c>
       <c r="E140" t="n">
-        <v>237.9017486572266</v>
+        <v>239.9201354980469</v>
       </c>
       <c r="F140" t="n">
-        <v>7617600</v>
+        <v>7241300</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B141" t="n">
-        <v>240.9095376592209</v>
+        <v>240.4346190736229</v>
       </c>
       <c r="C141" t="n">
-        <v>241.6219084230326</v>
+        <v>242.7300393849503</v>
       </c>
       <c r="D141" t="n">
-        <v>237.9611083490254</v>
+        <v>240.0784336838334</v>
       </c>
       <c r="E141" t="n">
-        <v>239.9201354980469</v>
+        <v>241.8494720458984</v>
       </c>
       <c r="F141" t="n">
-        <v>7241300</v>
+        <v>7554200</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B142" t="n">
-        <v>240.4346190736229</v>
+        <v>242.9971782498834</v>
       </c>
       <c r="C142" t="n">
-        <v>242.7300393849503</v>
+        <v>244.580212658809</v>
       </c>
       <c r="D142" t="n">
-        <v>240.0784336838334</v>
+        <v>241.1568896154117</v>
       </c>
       <c r="E142" t="n">
-        <v>241.8494720458984</v>
+        <v>241.5328521728516</v>
       </c>
       <c r="F142" t="n">
-        <v>7554200</v>
+        <v>6314600</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B143" t="n">
-        <v>242.9971782498834</v>
+        <v>242.5123641523277</v>
       </c>
       <c r="C143" t="n">
-        <v>244.580212658809</v>
+        <v>244.5901147281089</v>
       </c>
       <c r="D143" t="n">
-        <v>241.1568896154117</v>
+        <v>239.3066957175141</v>
       </c>
       <c r="E143" t="n">
-        <v>241.5328521728516</v>
+        <v>240.4642944335938</v>
       </c>
       <c r="F143" t="n">
-        <v>6314600</v>
+        <v>6878700</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B144" t="n">
-        <v>242.5123641523277</v>
+        <v>240.0784175573595</v>
       </c>
       <c r="C144" t="n">
-        <v>244.5901147281089</v>
+        <v>240.9392076648261</v>
       </c>
       <c r="D144" t="n">
-        <v>239.3066957175141</v>
+        <v>237.9512090454724</v>
       </c>
       <c r="E144" t="n">
-        <v>240.4642944335938</v>
+        <v>238.4162292480469</v>
       </c>
       <c r="F144" t="n">
-        <v>6878700</v>
+        <v>4442400</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B145" t="n">
-        <v>240.0784329225297</v>
+        <v>238.2282554079276</v>
       </c>
       <c r="C145" t="n">
-        <v>240.9392230850874</v>
+        <v>238.2282554079276</v>
       </c>
       <c r="D145" t="n">
-        <v>237.9512242744999</v>
+        <v>233.5088027877857</v>
       </c>
       <c r="E145" t="n">
-        <v>238.4162445068359</v>
+        <v>235.8833770751953</v>
       </c>
       <c r="F145" t="n">
-        <v>4442400</v>
+        <v>6241100</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B146" t="n">
-        <v>238.2282554079276</v>
+        <v>234.1321342347395</v>
       </c>
       <c r="C146" t="n">
-        <v>238.2282554079276</v>
+        <v>238.7724329332046</v>
       </c>
       <c r="D146" t="n">
-        <v>233.5088027877857</v>
+        <v>231.4211667922781</v>
       </c>
       <c r="E146" t="n">
-        <v>235.8833770751953</v>
+        <v>238.7427520751953</v>
       </c>
       <c r="F146" t="n">
-        <v>6241100</v>
+        <v>8771100</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B147" t="n">
-        <v>234.1321342347395</v>
+        <v>238.7427511835681</v>
       </c>
       <c r="C147" t="n">
-        <v>238.7724329332046</v>
+        <v>241.612011492337</v>
       </c>
       <c r="D147" t="n">
-        <v>231.4211667922781</v>
+        <v>237.9907958579282</v>
       </c>
       <c r="E147" t="n">
-        <v>238.7427520751953</v>
+        <v>238.7526397705078</v>
       </c>
       <c r="F147" t="n">
-        <v>8771100</v>
+        <v>6216500</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B148" t="n">
-        <v>238.7427511835681</v>
+        <v>239.4353230782619</v>
       </c>
       <c r="C148" t="n">
-        <v>241.612011492337</v>
+        <v>239.6925622052984</v>
       </c>
       <c r="D148" t="n">
-        <v>237.9907958579282</v>
+        <v>235.3886718611059</v>
       </c>
       <c r="E148" t="n">
-        <v>238.7526397705078</v>
+        <v>235.9328460693359</v>
       </c>
       <c r="F148" t="n">
-        <v>6216500</v>
+        <v>7354500</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B149" t="n">
-        <v>239.4353230782619</v>
+        <v>235.1907903330984</v>
       </c>
       <c r="C149" t="n">
-        <v>239.6925622052984</v>
+        <v>235.8635765445355</v>
       </c>
       <c r="D149" t="n">
-        <v>235.3886718611059</v>
+        <v>232.6875890190388</v>
       </c>
       <c r="E149" t="n">
-        <v>235.9328460693359</v>
+        <v>235.4381408691406</v>
       </c>
       <c r="F149" t="n">
-        <v>7354500</v>
+        <v>7663600</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B150" t="n">
-        <v>235.1907903330984</v>
+        <v>232.5193972079424</v>
       </c>
       <c r="C150" t="n">
-        <v>235.8635765445355</v>
+        <v>239.6233125984258</v>
       </c>
       <c r="D150" t="n">
-        <v>232.6875890190388</v>
+        <v>230.7780548336423</v>
       </c>
       <c r="E150" t="n">
-        <v>235.4381408691406</v>
+        <v>237.5554656982422</v>
       </c>
       <c r="F150" t="n">
-        <v>7663600</v>
+        <v>10318700</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B151" t="n">
-        <v>232.5193972079424</v>
+        <v>237.3971547010872</v>
       </c>
       <c r="C151" t="n">
-        <v>239.6233125984258</v>
+        <v>237.8720635067345</v>
       </c>
       <c r="D151" t="n">
-        <v>230.7780548336423</v>
+        <v>234.2409594215431</v>
       </c>
       <c r="E151" t="n">
-        <v>237.5554656982422</v>
+        <v>236.1406097412109</v>
       </c>
       <c r="F151" t="n">
-        <v>10318700</v>
+        <v>6463500</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B152" t="n">
-        <v>237.3971547010872</v>
+        <v>234.9038654541874</v>
       </c>
       <c r="C152" t="n">
-        <v>237.8720635067345</v>
+        <v>235.6162362366795</v>
       </c>
       <c r="D152" t="n">
-        <v>234.2409594215431</v>
+        <v>229.6600308430398</v>
       </c>
       <c r="E152" t="n">
-        <v>236.1406097412109</v>
+        <v>232.0543823242188</v>
       </c>
       <c r="F152" t="n">
-        <v>6463500</v>
+        <v>8668900</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B153" t="n">
-        <v>234.9038500080299</v>
+        <v>231.8762966548944</v>
       </c>
       <c r="C153" t="n">
-        <v>235.6162207436799</v>
+        <v>233.0437839864675</v>
       </c>
       <c r="D153" t="n">
-        <v>229.6600157416919</v>
+        <v>229.5808763393496</v>
       </c>
       <c r="E153" t="n">
-        <v>232.0543670654297</v>
+        <v>231.6981964111328</v>
       </c>
       <c r="F153" t="n">
-        <v>8668900</v>
+        <v>8946300</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B154" t="n">
-        <v>231.8762966548944</v>
+        <v>232.321525670587</v>
       </c>
       <c r="C154" t="n">
-        <v>233.0437839864675</v>
+        <v>232.7667536363879</v>
       </c>
       <c r="D154" t="n">
-        <v>229.5808763393496</v>
+        <v>227.0974833184763</v>
       </c>
       <c r="E154" t="n">
-        <v>231.6981964111328</v>
+        <v>228.2451934814453</v>
       </c>
       <c r="F154" t="n">
-        <v>8946300</v>
+        <v>7810500</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B155" t="n">
-        <v>232.321525670587</v>
+        <v>226.9193787228735</v>
       </c>
       <c r="C155" t="n">
-        <v>232.7667536363879</v>
+        <v>227.2557718151299</v>
       </c>
       <c r="D155" t="n">
-        <v>227.0974833184763</v>
+        <v>222.3186498783577</v>
       </c>
       <c r="E155" t="n">
-        <v>228.2451934814453</v>
+        <v>223.76318359375</v>
       </c>
       <c r="F155" t="n">
-        <v>7810500</v>
+        <v>11681200</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B156" t="n">
-        <v>226.9193941968888</v>
+        <v>223.7829810531976</v>
       </c>
       <c r="C156" t="n">
-        <v>227.2557873120845</v>
+        <v>225.0692069251634</v>
       </c>
       <c r="D156" t="n">
-        <v>222.3186650386415</v>
+        <v>221.4084218257834</v>
       </c>
       <c r="E156" t="n">
-        <v>223.7631988525391</v>
+        <v>223.7038421630859</v>
       </c>
       <c r="F156" t="n">
-        <v>11681200</v>
+        <v>9003400</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B157" t="n">
-        <v>223.7829810531976</v>
+        <v>224.8416507297823</v>
       </c>
       <c r="C157" t="n">
-        <v>225.0692069251634</v>
+        <v>228.937775248105</v>
       </c>
       <c r="D157" t="n">
-        <v>221.4084218257834</v>
+        <v>224.623981037261</v>
       </c>
       <c r="E157" t="n">
-        <v>223.7038421630859</v>
+        <v>228.2056121826172</v>
       </c>
       <c r="F157" t="n">
-        <v>9003400</v>
+        <v>7097600</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B158" t="n">
-        <v>224.8416356959219</v>
+        <v>226.6027733404394</v>
       </c>
       <c r="C158" t="n">
-        <v>228.9377599403605</v>
+        <v>227.5526060477145</v>
       </c>
       <c r="D158" t="n">
-        <v>224.6239660179549</v>
+        <v>224.6140804527143</v>
       </c>
       <c r="E158" t="n">
-        <v>228.2055969238281</v>
+        <v>225.0889892578125</v>
       </c>
       <c r="F158" t="n">
-        <v>7097600</v>
+        <v>6067500</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B159" t="n">
-        <v>226.6027887018479</v>
+        <v>223.3773398363102</v>
       </c>
       <c r="C159" t="n">
-        <v>227.5526214735122</v>
+        <v>225.4946599491012</v>
       </c>
       <c r="D159" t="n">
-        <v>224.6140956793093</v>
+        <v>221.972390518204</v>
       </c>
       <c r="E159" t="n">
-        <v>225.0890045166016</v>
+        <v>222.9518890380859</v>
       </c>
       <c r="F159" t="n">
-        <v>6067500</v>
+        <v>7897800</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B160" t="n">
-        <v>223.3773245484034</v>
+        <v>225.316553812185</v>
       </c>
       <c r="C160" t="n">
-        <v>225.4946445162854</v>
+        <v>228.5815840196301</v>
       </c>
       <c r="D160" t="n">
-        <v>221.9723753264516</v>
+        <v>223.9709662459624</v>
       </c>
       <c r="E160" t="n">
-        <v>222.9518737792969</v>
+        <v>225.3759155273438</v>
       </c>
       <c r="F160" t="n">
-        <v>7897800</v>
+        <v>7179800</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B161" t="n">
-        <v>225.316553812185</v>
+        <v>223.1299745498951</v>
       </c>
       <c r="C161" t="n">
-        <v>228.5815840196301</v>
+        <v>226.2861697879244</v>
       </c>
       <c r="D161" t="n">
-        <v>223.9709662459624</v>
+        <v>222.4769655150452</v>
       </c>
       <c r="E161" t="n">
-        <v>225.3759155273438</v>
+        <v>224.9405822753906</v>
       </c>
       <c r="F161" t="n">
-        <v>7179800</v>
+        <v>7071100</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B162" t="n">
-        <v>223.1299896858621</v>
+        <v>225.534219851175</v>
       </c>
       <c r="C162" t="n">
-        <v>226.2861851379911</v>
+        <v>228.7102074345108</v>
       </c>
       <c r="D162" t="n">
-        <v>222.4769806067155</v>
+        <v>225.3957041523519</v>
       </c>
       <c r="E162" t="n">
-        <v>224.9405975341797</v>
+        <v>227.4140930175781</v>
       </c>
       <c r="F162" t="n">
-        <v>7071100</v>
+        <v>8157200</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B163" t="n">
-        <v>225.534219851175</v>
+        <v>226.6324494909732</v>
       </c>
       <c r="C163" t="n">
-        <v>228.7102074345108</v>
+        <v>227.3349316460146</v>
       </c>
       <c r="D163" t="n">
-        <v>225.3957041523519</v>
+        <v>224.6140757884101</v>
       </c>
       <c r="E163" t="n">
-        <v>227.4140930175781</v>
+        <v>224.7822723388672</v>
       </c>
       <c r="F163" t="n">
-        <v>8157200</v>
+        <v>6863600</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B164" t="n">
-        <v>226.6324494909732</v>
+        <v>223.12007375354</v>
       </c>
       <c r="C164" t="n">
-        <v>227.3349316460146</v>
+        <v>224.6635537914519</v>
       </c>
       <c r="D164" t="n">
-        <v>224.6140757884101</v>
+        <v>221.2105348477109</v>
       </c>
       <c r="E164" t="n">
-        <v>224.7822723388672</v>
+        <v>221.8239593505859</v>
       </c>
       <c r="F164" t="n">
-        <v>6863600</v>
+        <v>8215200</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B165" t="n">
-        <v>223.12007375354</v>
+        <v>223.0013599943453</v>
       </c>
       <c r="C165" t="n">
-        <v>224.6635537914519</v>
+        <v>224.1292778920903</v>
       </c>
       <c r="D165" t="n">
-        <v>221.2105348477109</v>
+        <v>222.5165474841354</v>
       </c>
       <c r="E165" t="n">
-        <v>221.8239593505859</v>
+        <v>223.15966796875</v>
       </c>
       <c r="F165" t="n">
-        <v>8215200</v>
+        <v>5556700</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B166" t="n">
-        <v>223.0013599943453</v>
+        <v>222.86284542864</v>
       </c>
       <c r="C166" t="n">
-        <v>224.1292778920903</v>
+        <v>223.9412902027537</v>
       </c>
       <c r="D166" t="n">
-        <v>222.5165474841354</v>
+        <v>220.5872173504634</v>
       </c>
       <c r="E166" t="n">
-        <v>223.15966796875</v>
+        <v>222.2395172119141</v>
       </c>
       <c r="F166" t="n">
-        <v>5556700</v>
+        <v>7982300</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B167" t="n">
-        <v>222.86284542864</v>
+        <v>222.397817873641</v>
       </c>
       <c r="C167" t="n">
-        <v>223.9412902027537</v>
+        <v>222.397817873641</v>
       </c>
       <c r="D167" t="n">
-        <v>220.5872173504634</v>
+        <v>218.2918049197337</v>
       </c>
       <c r="E167" t="n">
-        <v>222.2395172119141</v>
+        <v>220.1518707275391</v>
       </c>
       <c r="F167" t="n">
-        <v>7982300</v>
+        <v>7269700</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B168" t="n">
-        <v>222.3978024591847</v>
+        <v>220.5773139289545</v>
       </c>
       <c r="C168" t="n">
-        <v>222.3978024591847</v>
+        <v>221.0027495995129</v>
       </c>
       <c r="D168" t="n">
-        <v>218.2917897898664</v>
+        <v>218.578717393272</v>
       </c>
       <c r="E168" t="n">
-        <v>220.15185546875</v>
+        <v>218.9744873046875</v>
       </c>
       <c r="F168" t="n">
-        <v>7269700</v>
+        <v>5550600</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B169" t="n">
-        <v>220.5773139289545</v>
+        <v>218.9744932439037</v>
       </c>
       <c r="C169" t="n">
-        <v>221.0027495995129</v>
+        <v>220.9137130226623</v>
       </c>
       <c r="D169" t="n">
-        <v>218.578717393272</v>
+        <v>218.034549114472</v>
       </c>
       <c r="E169" t="n">
-        <v>218.9744873046875</v>
+        <v>219.0833129882812</v>
       </c>
       <c r="F169" t="n">
-        <v>5550600</v>
+        <v>6223200</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B170" t="n">
-        <v>218.9744932439037</v>
+        <v>220.6366747923043</v>
       </c>
       <c r="C170" t="n">
-        <v>220.9137130226623</v>
+        <v>225.2373886538506</v>
       </c>
       <c r="D170" t="n">
-        <v>218.034549114472</v>
+        <v>219.3009758791698</v>
       </c>
       <c r="E170" t="n">
-        <v>219.0833129882812</v>
+        <v>221.8833160400391</v>
       </c>
       <c r="F170" t="n">
-        <v>6223200</v>
+        <v>8632500</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B171" t="n">
-        <v>220.6366899653626</v>
+        <v>223.4268017505994</v>
       </c>
       <c r="C171" t="n">
-        <v>225.2374041432973</v>
+        <v>228.3540202522719</v>
       </c>
       <c r="D171" t="n">
-        <v>219.3009909603728</v>
+        <v>223.0508241008666</v>
       </c>
       <c r="E171" t="n">
-        <v>221.8833312988281</v>
+        <v>227.9780426025391</v>
       </c>
       <c r="F171" t="n">
-        <v>8632500</v>
+        <v>7464500</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B172" t="n">
-        <v>223.4268017505994</v>
+        <v>228.5519118475702</v>
       </c>
       <c r="C172" t="n">
-        <v>228.3540202522719</v>
+        <v>229.3038520966222</v>
       </c>
       <c r="D172" t="n">
-        <v>223.0508241008666</v>
+        <v>226.7314153938151</v>
       </c>
       <c r="E172" t="n">
-        <v>227.9780426025391</v>
+        <v>228.3540344238281</v>
       </c>
       <c r="F172" t="n">
-        <v>7464500</v>
+        <v>6974400</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B173" t="n">
-        <v>228.5518965755589</v>
+        <v>228.324343449484</v>
       </c>
       <c r="C173" t="n">
-        <v>229.3038367743656</v>
+        <v>229.6798195939985</v>
       </c>
       <c r="D173" t="n">
-        <v>226.7314002434507</v>
+        <v>224.0402302332647</v>
       </c>
       <c r="E173" t="n">
-        <v>228.3540191650391</v>
+        <v>224.307373046875</v>
       </c>
       <c r="F173" t="n">
-        <v>6974400</v>
+        <v>12167000</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B174" t="n">
-        <v>228.324343449484</v>
+        <v>224.3073719260098</v>
       </c>
       <c r="C174" t="n">
-        <v>229.6798195939985</v>
+        <v>227.2656747432453</v>
       </c>
       <c r="D174" t="n">
-        <v>224.0402302332647</v>
+        <v>223.466374045218</v>
       </c>
       <c r="E174" t="n">
-        <v>224.307373046875</v>
+        <v>226.4939422607422</v>
       </c>
       <c r="F174" t="n">
-        <v>12167000</v>
+        <v>10141600</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B175" t="n">
-        <v>224.3073719260098</v>
+        <v>226.5137209227187</v>
       </c>
       <c r="C175" t="n">
-        <v>227.2656747432453</v>
+        <v>228.4034825714771</v>
       </c>
       <c r="D175" t="n">
-        <v>223.466374045218</v>
+        <v>225.6232499676584</v>
       </c>
       <c r="E175" t="n">
-        <v>226.4939422607422</v>
+        <v>227.5624847412109</v>
       </c>
       <c r="F175" t="n">
-        <v>10141600</v>
+        <v>9677900</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B176" t="n">
-        <v>226.5137209227187</v>
+        <v>229.2345877493695</v>
       </c>
       <c r="C176" t="n">
-        <v>228.4034825714771</v>
+        <v>229.5413000019429</v>
       </c>
       <c r="D176" t="n">
-        <v>225.6232499676584</v>
+        <v>226.7412900911319</v>
       </c>
       <c r="E176" t="n">
-        <v>227.5624847412109</v>
+        <v>226.8897094726562</v>
       </c>
       <c r="F176" t="n">
-        <v>9677900</v>
+        <v>7353800</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B177" t="n">
-        <v>229.2345877493695</v>
+        <v>226.8897069691897</v>
       </c>
       <c r="C177" t="n">
-        <v>229.5413000019429</v>
+        <v>229.432462629467</v>
       </c>
       <c r="D177" t="n">
-        <v>226.7412900911319</v>
+        <v>224.9405835372236</v>
       </c>
       <c r="E177" t="n">
-        <v>226.8897094726562</v>
+        <v>229.2741546630859</v>
       </c>
       <c r="F177" t="n">
-        <v>7353800</v>
+        <v>5239000</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B178" t="n">
-        <v>226.8897069691897</v>
+        <v>230.5307110319731</v>
       </c>
       <c r="C178" t="n">
-        <v>229.432462629467</v>
+        <v>233.0042165151488</v>
       </c>
       <c r="D178" t="n">
-        <v>224.9405835372236</v>
+        <v>230.2536796256238</v>
       </c>
       <c r="E178" t="n">
-        <v>229.2741546630859</v>
+        <v>231.8565063476562</v>
       </c>
       <c r="F178" t="n">
-        <v>5239000</v>
+        <v>5462300</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,25 +5071,25 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B179" t="n">
-        <v>230.5307110319731</v>
+        <v>231.856506324529</v>
       </c>
       <c r="C179" t="n">
-        <v>233.0042165151488</v>
+        <v>232.0953339431715</v>
       </c>
       <c r="D179" t="n">
-        <v>230.2536796256238</v>
+        <v>227.9557463234551</v>
       </c>
       <c r="E179" t="n">
-        <v>231.8565063476562</v>
+        <v>229.0503387451172</v>
       </c>
       <c r="F179" t="n">
-        <v>5462300</v>
+        <v>6619600</v>
       </c>
       <c r="G179" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -5097,25 +5097,25 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B180" t="n">
-        <v>231.856506324529</v>
+        <v>228.8513234809034</v>
       </c>
       <c r="C180" t="n">
-        <v>232.0953339431715</v>
+        <v>231.7470457253588</v>
       </c>
       <c r="D180" t="n">
-        <v>227.9557463234551</v>
+        <v>227.896043373475</v>
       </c>
       <c r="E180" t="n">
-        <v>229.0503387451172</v>
+        <v>230.1548919677734</v>
       </c>
       <c r="F180" t="n">
-        <v>6619600</v>
+        <v>5835500</v>
       </c>
       <c r="G180" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B181" t="n">
-        <v>228.8513234809034</v>
+        <v>228.9010720691913</v>
       </c>
       <c r="C181" t="n">
-        <v>231.7470457253588</v>
+        <v>230.7320381891827</v>
       </c>
       <c r="D181" t="n">
-        <v>227.896043373475</v>
+        <v>228.6025413534768</v>
       </c>
       <c r="E181" t="n">
-        <v>230.1548919677734</v>
+        <v>229.6672973632812</v>
       </c>
       <c r="F181" t="n">
-        <v>5835500</v>
+        <v>7193400</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B182" t="n">
-        <v>228.9010720691913</v>
+        <v>230.0951744973679</v>
       </c>
       <c r="C182" t="n">
-        <v>230.7320381891827</v>
+        <v>230.36385365377</v>
       </c>
       <c r="D182" t="n">
-        <v>228.6025413534768</v>
+        <v>223.4877626284344</v>
       </c>
       <c r="E182" t="n">
-        <v>229.6672973632812</v>
+        <v>224.2241363525391</v>
       </c>
       <c r="F182" t="n">
-        <v>7193400</v>
+        <v>13897700</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B183" t="n">
-        <v>230.0951744973679</v>
+        <v>222.1045945004449</v>
       </c>
       <c r="C183" t="n">
-        <v>230.36385365377</v>
+        <v>223.3385143974124</v>
       </c>
       <c r="D183" t="n">
-        <v>223.4877626284344</v>
+        <v>219.7561761055088</v>
       </c>
       <c r="E183" t="n">
-        <v>224.2241363525391</v>
+        <v>222.4130706787109</v>
       </c>
       <c r="F183" t="n">
-        <v>13897700</v>
+        <v>8041000</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B184" t="n">
-        <v>222.1045945004449</v>
+        <v>221.4876358909895</v>
       </c>
       <c r="C184" t="n">
-        <v>223.3385143974124</v>
+        <v>224.3933034528787</v>
       </c>
       <c r="D184" t="n">
-        <v>219.7561761055088</v>
+        <v>220.0845521676131</v>
       </c>
       <c r="E184" t="n">
-        <v>222.4130706787109</v>
+        <v>221.7961120605469</v>
       </c>
       <c r="F184" t="n">
-        <v>8041000</v>
+        <v>5669000</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B185" t="n">
-        <v>221.4876358909895</v>
+        <v>221.3582777644383</v>
       </c>
       <c r="C185" t="n">
-        <v>224.3933034528787</v>
+        <v>223.8261024020756</v>
       </c>
       <c r="D185" t="n">
-        <v>220.0845521676131</v>
+        <v>220.9104892689172</v>
       </c>
       <c r="E185" t="n">
-        <v>221.7961120605469</v>
+        <v>222.1444091796875</v>
       </c>
       <c r="F185" t="n">
-        <v>5669000</v>
+        <v>6507200</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B186" t="n">
-        <v>221.3582777644383</v>
+        <v>225.9754999423843</v>
       </c>
       <c r="C186" t="n">
-        <v>223.8261024020756</v>
+        <v>227.5477475509985</v>
       </c>
       <c r="D186" t="n">
-        <v>220.9104892689172</v>
+        <v>224.7913377117005</v>
       </c>
       <c r="E186" t="n">
-        <v>222.1444091796875</v>
+        <v>227.0502014160156</v>
       </c>
       <c r="F186" t="n">
-        <v>6507200</v>
+        <v>7274800</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B187" t="n">
-        <v>225.9754999423843</v>
+        <v>228.8712298379233</v>
       </c>
       <c r="C187" t="n">
-        <v>227.5477475509985</v>
+        <v>234.0656128776528</v>
       </c>
       <c r="D187" t="n">
-        <v>224.7913377117005</v>
+        <v>227.8761375342802</v>
       </c>
       <c r="E187" t="n">
-        <v>227.0502014160156</v>
+        <v>231.6276397705078</v>
       </c>
       <c r="F187" t="n">
-        <v>7274800</v>
+        <v>8034900</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B188" t="n">
-        <v>228.8712298379233</v>
+        <v>231.6276367875738</v>
       </c>
       <c r="C188" t="n">
-        <v>234.0656128776528</v>
+        <v>233.7969306933057</v>
       </c>
       <c r="D188" t="n">
-        <v>227.8761375342802</v>
+        <v>229.428476143926</v>
       </c>
       <c r="E188" t="n">
-        <v>231.6276397705078</v>
+        <v>231.0206298828125</v>
       </c>
       <c r="F188" t="n">
-        <v>8034900</v>
+        <v>7559800</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B189" t="n">
-        <v>231.6276367875738</v>
+        <v>231.2395468518091</v>
       </c>
       <c r="C189" t="n">
-        <v>233.7969306933057</v>
+        <v>236.5433904796373</v>
       </c>
       <c r="D189" t="n">
-        <v>229.428476143926</v>
+        <v>229.2792138627353</v>
       </c>
       <c r="E189" t="n">
-        <v>231.0206298828125</v>
+        <v>235.8368682861328</v>
       </c>
       <c r="F189" t="n">
-        <v>7559800</v>
+        <v>8354500</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B190" t="n">
-        <v>231.2395468518091</v>
+        <v>237.6777986497502</v>
       </c>
       <c r="C190" t="n">
-        <v>236.5433904796373</v>
+        <v>239.7475772433621</v>
       </c>
       <c r="D190" t="n">
-        <v>229.2792138627353</v>
+        <v>235.886629497679</v>
       </c>
       <c r="E190" t="n">
-        <v>235.8368682861328</v>
+        <v>237.3195648193359</v>
       </c>
       <c r="F190" t="n">
-        <v>8354500</v>
+        <v>8350800</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B191" t="n">
-        <v>237.6777986497502</v>
+        <v>238.822141602048</v>
       </c>
       <c r="C191" t="n">
-        <v>239.7475772433621</v>
+        <v>240.4142952862894</v>
       </c>
       <c r="D191" t="n">
-        <v>235.886629497679</v>
+        <v>236.971269397276</v>
       </c>
       <c r="E191" t="n">
-        <v>237.3195648193359</v>
+        <v>237.1603393554688</v>
       </c>
       <c r="F191" t="n">
-        <v>8350800</v>
+        <v>7399000</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B192" t="n">
-        <v>238.822141602048</v>
+        <v>238.8221408093525</v>
       </c>
       <c r="C192" t="n">
-        <v>240.4142952862894</v>
+        <v>239.7276784040579</v>
       </c>
       <c r="D192" t="n">
-        <v>236.971269397276</v>
+        <v>236.354316272482</v>
       </c>
       <c r="E192" t="n">
-        <v>237.1603393554688</v>
+        <v>239.6878662109375</v>
       </c>
       <c r="F192" t="n">
-        <v>7399000</v>
+        <v>6459400</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B193" t="n">
-        <v>238.8221408093525</v>
+        <v>237.8270530309927</v>
       </c>
       <c r="C193" t="n">
-        <v>239.7276784040579</v>
+        <v>238.3245991670408</v>
       </c>
       <c r="D193" t="n">
-        <v>236.354316272482</v>
+        <v>232.4336547382997</v>
       </c>
       <c r="E193" t="n">
-        <v>239.6878662109375</v>
+        <v>234.5034484863281</v>
       </c>
       <c r="F193" t="n">
-        <v>6459400</v>
+        <v>7732000</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B194" t="n">
-        <v>237.8270530309927</v>
+        <v>235.2099495568312</v>
       </c>
       <c r="C194" t="n">
-        <v>238.3245991670408</v>
+        <v>235.2099495568312</v>
       </c>
       <c r="D194" t="n">
-        <v>232.4336547382997</v>
+        <v>229.8862151458974</v>
       </c>
       <c r="E194" t="n">
-        <v>234.5034484863281</v>
+        <v>234.0257873535156</v>
       </c>
       <c r="F194" t="n">
-        <v>7732000</v>
+        <v>7718100</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B195" t="n">
-        <v>235.2099495568312</v>
+        <v>232.8814495345484</v>
       </c>
       <c r="C195" t="n">
-        <v>235.2099495568312</v>
+        <v>234.2745726796724</v>
       </c>
       <c r="D195" t="n">
-        <v>229.8862151458974</v>
+        <v>229.5677903566066</v>
       </c>
       <c r="E195" t="n">
-        <v>234.0257873535156</v>
+        <v>233.0506134033203</v>
       </c>
       <c r="F195" t="n">
-        <v>7718100</v>
+        <v>8548000</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B196" t="n">
-        <v>232.8814495345484</v>
+        <v>230.6424813960874</v>
       </c>
       <c r="C196" t="n">
-        <v>234.2745726796724</v>
+        <v>231.6077220970904</v>
       </c>
       <c r="D196" t="n">
-        <v>229.5677903566066</v>
+        <v>226.4830030630252</v>
       </c>
       <c r="E196" t="n">
-        <v>233.0506134033203</v>
+        <v>227.2691192626953</v>
       </c>
       <c r="F196" t="n">
-        <v>8548000</v>
+        <v>18989800</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B197" t="n">
-        <v>230.6424813960874</v>
+        <v>227.8263796240252</v>
       </c>
       <c r="C197" t="n">
-        <v>231.6077220970904</v>
+        <v>230.3141103803127</v>
       </c>
       <c r="D197" t="n">
-        <v>226.4830030630252</v>
+        <v>226.3834988221592</v>
       </c>
       <c r="E197" t="n">
-        <v>227.2691192626953</v>
+        <v>230.1548919677734</v>
       </c>
       <c r="F197" t="n">
-        <v>18989800</v>
+        <v>8518300</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B198" t="n">
-        <v>227.8263796240252</v>
+        <v>234.4835421454308</v>
       </c>
       <c r="C198" t="n">
-        <v>230.3141103803127</v>
+        <v>238.6231296371808</v>
       </c>
       <c r="D198" t="n">
-        <v>226.3834988221592</v>
+        <v>233.1998797966796</v>
       </c>
       <c r="E198" t="n">
-        <v>230.1548919677734</v>
+        <v>237.9066619873047</v>
       </c>
       <c r="F198" t="n">
-        <v>8518300</v>
+        <v>11802000</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B199" t="n">
-        <v>234.4835421454308</v>
+        <v>238.7126772290818</v>
       </c>
       <c r="C199" t="n">
-        <v>238.6231296371808</v>
+        <v>241.8472117165478</v>
       </c>
       <c r="D199" t="n">
-        <v>233.1998797966796</v>
+        <v>237.5782726810186</v>
       </c>
       <c r="E199" t="n">
-        <v>237.9066619873047</v>
+        <v>239.8172302246094</v>
       </c>
       <c r="F199" t="n">
-        <v>11802000</v>
+        <v>8139200</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B200" t="n">
-        <v>238.7126772290818</v>
+        <v>240.0859235854152</v>
       </c>
       <c r="C200" t="n">
-        <v>241.8472117165478</v>
+        <v>246.9719604825856</v>
       </c>
       <c r="D200" t="n">
-        <v>237.5782726810186</v>
+        <v>239.7077836523882</v>
       </c>
       <c r="E200" t="n">
-        <v>239.8172302246094</v>
+        <v>243.6782073974609</v>
       </c>
       <c r="F200" t="n">
-        <v>8139200</v>
+        <v>10130400</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B201" t="n">
-        <v>240.0859235854152</v>
+        <v>247.0515630057391</v>
       </c>
       <c r="C201" t="n">
-        <v>246.9719604825856</v>
+        <v>253.857990512684</v>
       </c>
       <c r="D201" t="n">
-        <v>239.7077836523882</v>
+        <v>246.6535169859773</v>
       </c>
       <c r="E201" t="n">
-        <v>243.6782073974609</v>
+        <v>253.4102020263672</v>
       </c>
       <c r="F201" t="n">
-        <v>10130400</v>
+        <v>16316800</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B202" t="n">
-        <v>247.0515630057391</v>
+        <v>251.9474045302274</v>
       </c>
       <c r="C202" t="n">
-        <v>253.857990512684</v>
+        <v>257.3109358669097</v>
       </c>
       <c r="D202" t="n">
-        <v>246.6535169859773</v>
+        <v>250.7930938975173</v>
       </c>
       <c r="E202" t="n">
-        <v>253.4102020263672</v>
+        <v>257.2413024902344</v>
       </c>
       <c r="F202" t="n">
-        <v>16316800</v>
+        <v>8608400</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B203" t="n">
-        <v>251.9474045302274</v>
+        <v>257.7288999793201</v>
       </c>
       <c r="C203" t="n">
-        <v>257.3109358669097</v>
+        <v>258.62447695588</v>
       </c>
       <c r="D203" t="n">
-        <v>250.7930938975173</v>
+        <v>251.9275101770222</v>
       </c>
       <c r="E203" t="n">
-        <v>257.2413024902344</v>
+        <v>252.7235870361328</v>
       </c>
       <c r="F203" t="n">
-        <v>8608400</v>
+        <v>8469500</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B204" t="n">
-        <v>257.7288999793201</v>
+        <v>252.0071226458085</v>
       </c>
       <c r="C204" t="n">
-        <v>258.62447695588</v>
+        <v>252.9524572852904</v>
       </c>
       <c r="D204" t="n">
-        <v>251.9275101770222</v>
+        <v>249.8477741968348</v>
       </c>
       <c r="E204" t="n">
-        <v>252.7235870361328</v>
+        <v>252.7335357666016</v>
       </c>
       <c r="F204" t="n">
-        <v>8469500</v>
+        <v>6516500</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B205" t="n">
-        <v>252.0071226458085</v>
+        <v>254.5247047293354</v>
       </c>
       <c r="C205" t="n">
-        <v>252.9524572852904</v>
+        <v>261.8087875806335</v>
       </c>
       <c r="D205" t="n">
-        <v>249.8477741968348</v>
+        <v>252.753441667793</v>
       </c>
       <c r="E205" t="n">
-        <v>252.7335357666016</v>
+        <v>261.7490844726562</v>
       </c>
       <c r="F205" t="n">
-        <v>6516500</v>
+        <v>7998700</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B206" t="n">
-        <v>254.5247047293354</v>
+        <v>258.9528582650781</v>
       </c>
       <c r="C206" t="n">
-        <v>261.8087875806335</v>
+        <v>260.0972082397536</v>
       </c>
       <c r="D206" t="n">
-        <v>252.753441667793</v>
+        <v>254.673943516207</v>
       </c>
       <c r="E206" t="n">
-        <v>261.7490844726562</v>
+        <v>258.0572509765625</v>
       </c>
       <c r="F206" t="n">
-        <v>7998700</v>
+        <v>6803700</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B207" t="n">
-        <v>258.9528582650781</v>
+        <v>263.5899938466549</v>
       </c>
       <c r="C207" t="n">
-        <v>260.0972082397536</v>
+        <v>268.1076906797339</v>
       </c>
       <c r="D207" t="n">
-        <v>254.673943516207</v>
+        <v>262.7540896546532</v>
       </c>
       <c r="E207" t="n">
-        <v>258.0572509765625</v>
+        <v>265.9284362792969</v>
       </c>
       <c r="F207" t="n">
-        <v>6803700</v>
+        <v>9089700</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B208" t="n">
-        <v>263.5899938466549</v>
+        <v>267.2817917945089</v>
       </c>
       <c r="C208" t="n">
-        <v>268.1076906797339</v>
+        <v>267.2817917945089</v>
       </c>
       <c r="D208" t="n">
-        <v>262.7540896546532</v>
+        <v>261.8386358221884</v>
       </c>
       <c r="E208" t="n">
-        <v>265.9284362792969</v>
+        <v>262.1072998046875</v>
       </c>
       <c r="F208" t="n">
-        <v>9089700</v>
+        <v>6769400</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B209" t="n">
-        <v>267.2817917945089</v>
+        <v>259.3508895364454</v>
       </c>
       <c r="C209" t="n">
-        <v>267.2817917945089</v>
+        <v>262.1570568783993</v>
       </c>
       <c r="D209" t="n">
-        <v>261.8386358221884</v>
+        <v>256.8631589924022</v>
       </c>
       <c r="E209" t="n">
-        <v>262.1072998046875</v>
+        <v>257.8283996582031</v>
       </c>
       <c r="F209" t="n">
-        <v>6769400</v>
+        <v>6426100</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B210" t="n">
-        <v>259.3508895364454</v>
+        <v>258.9130640253377</v>
       </c>
       <c r="C210" t="n">
-        <v>262.1570568783993</v>
+        <v>260.0176018849775</v>
       </c>
       <c r="D210" t="n">
-        <v>256.8631589924022</v>
+        <v>254.2659848771424</v>
       </c>
       <c r="E210" t="n">
-        <v>257.8283996582031</v>
+        <v>255.7188262939453</v>
       </c>
       <c r="F210" t="n">
-        <v>6426100</v>
+        <v>6534700</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B211" t="n">
-        <v>258.9130640253377</v>
+        <v>256.6840530111044</v>
       </c>
       <c r="C211" t="n">
-        <v>260.0176018849775</v>
+        <v>258.2562853735001</v>
       </c>
       <c r="D211" t="n">
-        <v>254.2659848771424</v>
+        <v>254.892868775476</v>
       </c>
       <c r="E211" t="n">
-        <v>255.7188262939453</v>
+        <v>256.5049133300781</v>
       </c>
       <c r="F211" t="n">
-        <v>6534700</v>
+        <v>5272200</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B212" t="n">
-        <v>256.6840530111044</v>
+        <v>254.2759347913044</v>
       </c>
       <c r="C212" t="n">
-        <v>258.2562853735001</v>
+        <v>255.1317299625397</v>
       </c>
       <c r="D212" t="n">
-        <v>254.892868775476</v>
+        <v>250.9025724938729</v>
       </c>
       <c r="E212" t="n">
-        <v>256.5049133300781</v>
+        <v>252.6041870117188</v>
       </c>
       <c r="F212" t="n">
-        <v>5272200</v>
+        <v>8770600</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B213" t="n">
-        <v>254.2759347913044</v>
+        <v>248.8626188136353</v>
       </c>
       <c r="C213" t="n">
-        <v>255.1317299625397</v>
+        <v>255.5695309055475</v>
       </c>
       <c r="D213" t="n">
-        <v>250.9025724938729</v>
+        <v>244.842452777813</v>
       </c>
       <c r="E213" t="n">
-        <v>252.6041870117188</v>
+        <v>245.8076934814453</v>
       </c>
       <c r="F213" t="n">
-        <v>8770600</v>
+        <v>10547300</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B214" t="n">
-        <v>248.8626188136353</v>
+        <v>247.6784538478382</v>
       </c>
       <c r="C214" t="n">
-        <v>255.5695309055475</v>
+        <v>252.3056419000621</v>
       </c>
       <c r="D214" t="n">
-        <v>244.842452777813</v>
+        <v>245.091223119708</v>
       </c>
       <c r="E214" t="n">
-        <v>245.8076934814453</v>
+        <v>248.7432098388672</v>
       </c>
       <c r="F214" t="n">
-        <v>10547300</v>
+        <v>11097600</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B215" t="n">
-        <v>247.6784538478382</v>
+        <v>251.350352994489</v>
       </c>
       <c r="C215" t="n">
-        <v>252.3056419000621</v>
+        <v>254.4052935535989</v>
       </c>
       <c r="D215" t="n">
-        <v>245.091223119708</v>
+        <v>250.7134945486414</v>
       </c>
       <c r="E215" t="n">
-        <v>248.7432098388672</v>
+        <v>251.7981414794922</v>
       </c>
       <c r="F215" t="n">
-        <v>11097600</v>
+        <v>10167700</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B216" t="n">
-        <v>251.350352994489</v>
+        <v>250.7731932271148</v>
       </c>
       <c r="C216" t="n">
-        <v>254.4052935535989</v>
+        <v>252.9325415941838</v>
       </c>
       <c r="D216" t="n">
-        <v>250.7134945486414</v>
+        <v>247.4097917368304</v>
       </c>
       <c r="E216" t="n">
-        <v>251.7981414794922</v>
+        <v>247.5988616943359</v>
       </c>
       <c r="F216" t="n">
-        <v>10167700</v>
+        <v>8114700</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B217" t="n">
-        <v>250.7731932271148</v>
+        <v>246.2355858738711</v>
       </c>
       <c r="C217" t="n">
-        <v>252.9325415941838</v>
+        <v>250.1064943021279</v>
       </c>
       <c r="D217" t="n">
-        <v>247.4097917368304</v>
+        <v>244.2852134745944</v>
       </c>
       <c r="E217" t="n">
-        <v>247.5988616943359</v>
+        <v>249.3800811767578</v>
       </c>
       <c r="F217" t="n">
-        <v>8114700</v>
+        <v>7793100</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B218" t="n">
-        <v>246.2355858738711</v>
+        <v>251.5195173574522</v>
       </c>
       <c r="C218" t="n">
-        <v>250.1064943021279</v>
+        <v>255.0322070489389</v>
       </c>
       <c r="D218" t="n">
-        <v>244.2852134745944</v>
+        <v>249.9771364820368</v>
       </c>
       <c r="E218" t="n">
-        <v>249.3800811767578</v>
+        <v>254.3754425048828</v>
       </c>
       <c r="F218" t="n">
-        <v>7793100</v>
+        <v>9100200</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B219" t="n">
-        <v>251.5195173574522</v>
+        <v>253.9873531958193</v>
       </c>
       <c r="C219" t="n">
-        <v>255.0322070489389</v>
+        <v>258.9230174724852</v>
       </c>
       <c r="D219" t="n">
-        <v>249.9771364820368</v>
+        <v>253.1713702566359</v>
       </c>
       <c r="E219" t="n">
-        <v>254.3754425048828</v>
+        <v>257.99755859375</v>
       </c>
       <c r="F219" t="n">
-        <v>9100200</v>
+        <v>8063300</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B220" t="n">
-        <v>253.9873531958193</v>
+        <v>260.1469668034143</v>
       </c>
       <c r="C220" t="n">
-        <v>258.9230174724852</v>
+        <v>262.41577598127</v>
       </c>
       <c r="D220" t="n">
-        <v>253.1713702566359</v>
+        <v>258.3358915701962</v>
       </c>
       <c r="E220" t="n">
-        <v>257.99755859375</v>
+        <v>262.1072998046875</v>
       </c>
       <c r="F220" t="n">
-        <v>8063300</v>
+        <v>6351800</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B221" t="n">
-        <v>260.1469668034143</v>
+        <v>261.2614678377304</v>
       </c>
       <c r="C221" t="n">
-        <v>262.41577598127</v>
+        <v>267.4807946322661</v>
       </c>
       <c r="D221" t="n">
-        <v>258.3358915701962</v>
+        <v>260.0673753138636</v>
       </c>
       <c r="E221" t="n">
-        <v>262.1072998046875</v>
+        <v>264.6448059082031</v>
       </c>
       <c r="F221" t="n">
-        <v>6351800</v>
+        <v>9647900</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B222" t="n">
-        <v>261.2614678377304</v>
+        <v>268.6749001082239</v>
       </c>
       <c r="C222" t="n">
-        <v>267.4807946322661</v>
+        <v>273.5508459255159</v>
       </c>
       <c r="D222" t="n">
-        <v>260.0673753138636</v>
+        <v>264.8736405295307</v>
       </c>
       <c r="E222" t="n">
-        <v>264.6448059082031</v>
+        <v>265.4209594726562</v>
       </c>
       <c r="F222" t="n">
-        <v>9647900</v>
+        <v>10491000</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B223" t="n">
-        <v>268.6749001082239</v>
+        <v>267.1822622796963</v>
       </c>
       <c r="C223" t="n">
-        <v>273.5508459255159</v>
+        <v>268.0181361041443</v>
       </c>
       <c r="D223" t="n">
-        <v>264.8736405295307</v>
+        <v>263.4904786297666</v>
       </c>
       <c r="E223" t="n">
-        <v>265.4209594726562</v>
+        <v>264.2268371582031</v>
       </c>
       <c r="F223" t="n">
-        <v>10491000</v>
+        <v>6105600</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B224" t="n">
-        <v>267.1822622796963</v>
+        <v>257.7587518734895</v>
       </c>
       <c r="C224" t="n">
-        <v>268.0181361041443</v>
+        <v>259.2414296518399</v>
       </c>
       <c r="D224" t="n">
-        <v>263.4904786297666</v>
+        <v>253.310688170632</v>
       </c>
       <c r="E224" t="n">
-        <v>264.2268371582031</v>
+        <v>254.5645141601562</v>
       </c>
       <c r="F224" t="n">
-        <v>6105600</v>
+        <v>8216500</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B225" t="n">
-        <v>257.7587518734895</v>
+        <v>254.7535759665547</v>
       </c>
       <c r="C225" t="n">
-        <v>259.2414296518399</v>
+        <v>257.2114550322676</v>
       </c>
       <c r="D225" t="n">
-        <v>253.310688170632</v>
+        <v>252.046908655097</v>
       </c>
       <c r="E225" t="n">
-        <v>254.5645141601562</v>
+        <v>255.0919036865234</v>
       </c>
       <c r="F225" t="n">
-        <v>8216500</v>
+        <v>6782100</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B226" t="n">
-        <v>254.7535759665547</v>
+        <v>253.7186719595458</v>
       </c>
       <c r="C226" t="n">
-        <v>257.2114550322676</v>
+        <v>256.4850271972422</v>
       </c>
       <c r="D226" t="n">
-        <v>252.046908655097</v>
+        <v>249.6785998577546</v>
       </c>
       <c r="E226" t="n">
-        <v>255.0919036865234</v>
+        <v>253.1614227294922</v>
       </c>
       <c r="F226" t="n">
-        <v>6782100</v>
+        <v>8136300</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B227" t="n">
-        <v>253.7186719595458</v>
+        <v>253.1614264806184</v>
       </c>
       <c r="C227" t="n">
-        <v>256.4850271972422</v>
+        <v>254.2659795008061</v>
       </c>
       <c r="D227" t="n">
-        <v>249.6785998577546</v>
+        <v>249.2109089785714</v>
       </c>
       <c r="E227" t="n">
-        <v>253.1614227294922</v>
+        <v>253.6788635253906</v>
       </c>
       <c r="F227" t="n">
-        <v>8136300</v>
+        <v>7362400</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B228" t="n">
-        <v>253.1614264806184</v>
+        <v>253.9972934738065</v>
       </c>
       <c r="C228" t="n">
-        <v>254.2659795008061</v>
+        <v>258.0473261663437</v>
       </c>
       <c r="D228" t="n">
-        <v>249.2109089785714</v>
+        <v>253.2211227437212</v>
       </c>
       <c r="E228" t="n">
-        <v>253.6788635253906</v>
+        <v>256.3258056640625</v>
       </c>
       <c r="F228" t="n">
-        <v>7362400</v>
+        <v>6472600</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B229" t="n">
-        <v>253.9972934738065</v>
+        <v>260.425593365904</v>
       </c>
       <c r="C229" t="n">
-        <v>258.0473261663437</v>
+        <v>260.8236242062839</v>
       </c>
       <c r="D229" t="n">
-        <v>253.2211227437212</v>
+        <v>254.0271572625725</v>
       </c>
       <c r="E229" t="n">
-        <v>256.3258056640625</v>
+        <v>255.7188262939453</v>
       </c>
       <c r="F229" t="n">
-        <v>6472600</v>
+        <v>6931800</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B230" t="n">
-        <v>260.425593365904</v>
+        <v>254.6341623817563</v>
       </c>
       <c r="C230" t="n">
-        <v>260.8236242062839</v>
+        <v>258.3259614136433</v>
       </c>
       <c r="D230" t="n">
-        <v>254.0271572625725</v>
+        <v>253.8679370762885</v>
       </c>
       <c r="E230" t="n">
-        <v>255.7188262939453</v>
+        <v>257.9677124023438</v>
       </c>
       <c r="F230" t="n">
-        <v>6931800</v>
+        <v>6532100</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B231" t="n">
-        <v>254.6341623817563</v>
+        <v>257.7886121067854</v>
       </c>
       <c r="C231" t="n">
-        <v>258.3259614136433</v>
+        <v>260.7141859356404</v>
       </c>
       <c r="D231" t="n">
-        <v>253.8679370762885</v>
+        <v>257.281105309594</v>
       </c>
       <c r="E231" t="n">
-        <v>257.9677124023438</v>
+        <v>260.5251159667969</v>
       </c>
       <c r="F231" t="n">
-        <v>6532100</v>
+        <v>8985100</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B232" t="n">
-        <v>257.7886121067854</v>
+        <v>259.9479684253454</v>
       </c>
       <c r="C232" t="n">
-        <v>260.7141859356404</v>
+        <v>262.853620890259</v>
       </c>
       <c r="D232" t="n">
-        <v>257.281105309594</v>
+        <v>257.0920280597301</v>
       </c>
       <c r="E232" t="n">
-        <v>260.5251159667969</v>
+        <v>258.5249633789062</v>
       </c>
       <c r="F232" t="n">
-        <v>8985100</v>
+        <v>5945900</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B233" t="n">
-        <v>259.9479684253454</v>
+        <v>254.7436088096904</v>
       </c>
       <c r="C233" t="n">
-        <v>262.853620890259</v>
+        <v>260.1270613743755</v>
       </c>
       <c r="D233" t="n">
-        <v>257.0920280597301</v>
+        <v>254.00723509927</v>
       </c>
       <c r="E233" t="n">
-        <v>258.5249633789062</v>
+        <v>259.5797424316406</v>
       </c>
       <c r="F233" t="n">
-        <v>5945900</v>
+        <v>4629300</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B234" t="n">
-        <v>254.7436088096904</v>
+        <v>260.4455042155265</v>
       </c>
       <c r="C234" t="n">
-        <v>260.1270613743755</v>
+        <v>261.3311205223152</v>
       </c>
       <c r="D234" t="n">
-        <v>254.00723509927</v>
+        <v>258.3756953399613</v>
       </c>
       <c r="E234" t="n">
-        <v>259.5797424316406</v>
+        <v>260.7937622070312</v>
       </c>
       <c r="F234" t="n">
-        <v>4629300</v>
+        <v>4852700</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B235" t="n">
-        <v>260.4455042155265</v>
+        <v>259.3707811439639</v>
       </c>
       <c r="C235" t="n">
-        <v>261.3311205223152</v>
+        <v>260.4255764680427</v>
       </c>
       <c r="D235" t="n">
-        <v>258.3756953399613</v>
+        <v>257.8881034534354</v>
       </c>
       <c r="E235" t="n">
-        <v>260.7937622070312</v>
+        <v>259.072265625</v>
       </c>
       <c r="F235" t="n">
-        <v>4852700</v>
+        <v>4998100</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B236" t="n">
-        <v>259.3707811439639</v>
+        <v>257.5995438259766</v>
       </c>
       <c r="C236" t="n">
-        <v>260.4255764680427</v>
+        <v>262.9829969172681</v>
       </c>
       <c r="D236" t="n">
-        <v>257.8881034534354</v>
+        <v>256.7437790079673</v>
       </c>
       <c r="E236" t="n">
-        <v>259.072265625</v>
+        <v>261.0823669433594</v>
       </c>
       <c r="F236" t="n">
-        <v>4998100</v>
+        <v>5515500</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B237" t="n">
-        <v>257.5995438259766</v>
+        <v>266.3563600087168</v>
       </c>
       <c r="C237" t="n">
-        <v>262.9829969172681</v>
+        <v>270.3964321763198</v>
       </c>
       <c r="D237" t="n">
-        <v>256.7437790079673</v>
+        <v>265.0229096495755</v>
       </c>
       <c r="E237" t="n">
-        <v>261.0823669433594</v>
+        <v>269.7794494628906</v>
       </c>
       <c r="F237" t="n">
-        <v>5515500</v>
+        <v>7838200</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B238" t="n">
-        <v>266.3563600087168</v>
+        <v>271.6601848020655</v>
       </c>
       <c r="C238" t="n">
-        <v>270.3964321763198</v>
+        <v>275.1131561312948</v>
       </c>
       <c r="D238" t="n">
-        <v>265.0229096495755</v>
+        <v>269.2321572777068</v>
       </c>
       <c r="E238" t="n">
-        <v>269.7794494628906</v>
+        <v>272.0681762695312</v>
       </c>
       <c r="F238" t="n">
-        <v>7838200</v>
+        <v>7728500</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B239" t="n">
-        <v>271.6601848020655</v>
+        <v>272.0582363321417</v>
       </c>
       <c r="C239" t="n">
-        <v>275.1131561312948</v>
+        <v>272.0582363321417</v>
       </c>
       <c r="D239" t="n">
-        <v>269.2321572777068</v>
+        <v>266.0578308105469</v>
       </c>
       <c r="E239" t="n">
-        <v>272.0681762695312</v>
+        <v>266.0578308105469</v>
       </c>
       <c r="F239" t="n">
-        <v>7728500</v>
+        <v>6475900</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B240" t="n">
-        <v>272.0582363321417</v>
+        <v>266.5155507786093</v>
       </c>
       <c r="C240" t="n">
-        <v>272.0582363321417</v>
+        <v>271.3218634751246</v>
       </c>
       <c r="D240" t="n">
-        <v>266.0578308105469</v>
+        <v>265.6896375517999</v>
       </c>
       <c r="E240" t="n">
-        <v>266.0578308105469</v>
+        <v>268.9137268066406</v>
       </c>
       <c r="F240" t="n">
-        <v>6475900</v>
+        <v>6186800</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B241" t="n">
-        <v>266.5155507786093</v>
+        <v>268.4161893708204</v>
       </c>
       <c r="C241" t="n">
-        <v>271.3218634751246</v>
+        <v>272.635401405727</v>
       </c>
       <c r="D241" t="n">
-        <v>265.6896375517999</v>
+        <v>267.2519483767422</v>
       </c>
       <c r="E241" t="n">
-        <v>268.9137268066406</v>
+        <v>271.7000122070312</v>
       </c>
       <c r="F241" t="n">
-        <v>6186800</v>
+        <v>5436100</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,25 +6709,25 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B242" t="n">
-        <v>268.4161893708204</v>
+        <v>271</v>
       </c>
       <c r="C242" t="n">
-        <v>272.635401405727</v>
+        <v>273.7999877929688</v>
       </c>
       <c r="D242" t="n">
-        <v>267.2519483767422</v>
+        <v>270.1799926757812</v>
       </c>
       <c r="E242" t="n">
-        <v>271.7000122070312</v>
+        <v>273.1400146484375</v>
       </c>
       <c r="F242" t="n">
-        <v>5436100</v>
+        <v>4687000</v>
       </c>
       <c r="G242" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -6735,25 +6735,25 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B243" t="n">
-        <v>271</v>
+        <v>271.9700012207031</v>
       </c>
       <c r="C243" t="n">
-        <v>273.7999877929688</v>
+        <v>272.9100036621094</v>
       </c>
       <c r="D243" t="n">
-        <v>270.1799926757812</v>
+        <v>269.5499877929688</v>
       </c>
       <c r="E243" t="n">
-        <v>273.1400146484375</v>
+        <v>270</v>
       </c>
       <c r="F243" t="n">
-        <v>4687000</v>
+        <v>7214100</v>
       </c>
       <c r="G243" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B244" t="n">
-        <v>271.9700012207031</v>
+        <v>268.4500122070312</v>
       </c>
       <c r="C244" t="n">
-        <v>272.9100036621094</v>
+        <v>268.4500122070312</v>
       </c>
       <c r="D244" t="n">
-        <v>269.5499877929688</v>
+        <v>263.8299865722656</v>
       </c>
       <c r="E244" t="n">
-        <v>270</v>
+        <v>265.7699890136719</v>
       </c>
       <c r="F244" t="n">
-        <v>7214100</v>
+        <v>7306200</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B245" t="n">
-        <v>268.4500122070312</v>
+        <v>265.7799987792969</v>
       </c>
       <c r="C245" t="n">
-        <v>268.4500122070312</v>
+        <v>268.3800048828125</v>
       </c>
       <c r="D245" t="n">
-        <v>263.8299865722656</v>
+        <v>264.2699890136719</v>
       </c>
       <c r="E245" t="n">
-        <v>265.7699890136719</v>
+        <v>268.0400085449219</v>
       </c>
       <c r="F245" t="n">
-        <v>7306200</v>
+        <v>5765600</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B246" t="n">
-        <v>265.7799987792969</v>
+        <v>267.1300048828125</v>
       </c>
       <c r="C246" t="n">
-        <v>268.3800048828125</v>
+        <v>267.7699890136719</v>
       </c>
       <c r="D246" t="n">
-        <v>264.2699890136719</v>
+        <v>265.1700134277344</v>
       </c>
       <c r="E246" t="n">
-        <v>268.0400085449219</v>
+        <v>265.8500061035156</v>
       </c>
       <c r="F246" t="n">
-        <v>5765600</v>
+        <v>7900100</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B247" t="n">
-        <v>267.1300048828125</v>
+        <v>270.8299865722656</v>
       </c>
       <c r="C247" t="n">
-        <v>267.7699890136719</v>
+        <v>271.9100036621094</v>
       </c>
       <c r="D247" t="n">
-        <v>265.1700134277344</v>
+        <v>267.0199890136719</v>
       </c>
       <c r="E247" t="n">
-        <v>265.8500061035156</v>
+        <v>271.1900024414062</v>
       </c>
       <c r="F247" t="n">
-        <v>7900100</v>
+        <v>6033600</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B248" t="n">
-        <v>270.8299865722656</v>
+        <v>274.739990234375</v>
       </c>
       <c r="C248" t="n">
-        <v>271.9100036621094</v>
+        <v>281.0700073242188</v>
       </c>
       <c r="D248" t="n">
-        <v>267.0199890136719</v>
+        <v>273.5299987792969</v>
       </c>
       <c r="E248" t="n">
-        <v>271.1900024414062</v>
+        <v>275.2099914550781</v>
       </c>
       <c r="F248" t="n">
-        <v>6033600</v>
+        <v>7910600</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B249" t="n">
-        <v>274.739990234375</v>
+        <v>277.3200073242188</v>
       </c>
       <c r="C249" t="n">
-        <v>281.0700073242188</v>
+        <v>278.8900146484375</v>
       </c>
       <c r="D249" t="n">
-        <v>273.5299987792969</v>
+        <v>273.1600036621094</v>
       </c>
       <c r="E249" t="n">
-        <v>275.2099914550781</v>
+        <v>278.4299926757812</v>
       </c>
       <c r="F249" t="n">
-        <v>7910600</v>
+        <v>5940300</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B250" t="n">
-        <v>277.3200073242188</v>
+        <v>275.1300048828125</v>
       </c>
       <c r="C250" t="n">
-        <v>278.8900146484375</v>
+        <v>277.7999877929688</v>
       </c>
       <c r="D250" t="n">
-        <v>273.1600036621094</v>
+        <v>274.75</v>
       </c>
       <c r="E250" t="n">
-        <v>278.4299926757812</v>
+        <v>275.2300109863281</v>
       </c>
       <c r="F250" t="n">
-        <v>5940300</v>
+        <v>4320100</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B251" t="n">
-        <v>275.1300048828125</v>
+        <v>271.2799987792969</v>
       </c>
       <c r="C251" t="n">
-        <v>277.7999877929688</v>
+        <v>271.989990234375</v>
       </c>
       <c r="D251" t="n">
-        <v>274.75</v>
+        <v>266.8800048828125</v>
       </c>
       <c r="E251" t="n">
-        <v>275.2300109863281</v>
+        <v>269.1199951171875</v>
       </c>
       <c r="F251" t="n">
-        <v>4320100</v>
+        <v>8084700</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,14 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46273</v>
-      </c>
-      <c r="B252" t="inlineStr"/>
-      <c r="C252" t="inlineStr"/>
-      <c r="D252" t="inlineStr"/>
-      <c r="E252" t="inlineStr"/>
+        <v>46274</v>
+      </c>
+      <c r="B252" t="n">
+        <v>268.510009765625</v>
+      </c>
+      <c r="C252" t="n">
+        <v>270.1000061035156</v>
+      </c>
+      <c r="D252" t="n">
+        <v>266.7300109863281</v>
+      </c>
+      <c r="E252" t="n">
+        <v>267.0799865722656</v>
+      </c>
       <c r="F252" t="n">
-        <v>7768078</v>
+        <v>6124600</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10963,37 +10971,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>267.08</v>
+      </c>
+      <c r="D2" t="n">
         <v>269.12</v>
       </c>
-      <c r="D2" t="n">
-        <v>275.23</v>
-      </c>
       <c r="E2" t="n">
-        <v>271.28</v>
+        <v>268.51</v>
       </c>
       <c r="F2" t="n">
-        <v>271.99</v>
+        <v>270.1</v>
       </c>
       <c r="G2" t="n">
-        <v>266.8828</v>
+        <v>266.73</v>
       </c>
       <c r="H2" t="n">
-        <v>7768078</v>
+        <v>5967693</v>
       </c>
       <c r="I2" t="n">
-        <v>7795185</v>
+        <v>7781654</v>
       </c>
       <c r="J2" t="n">
-        <v>648551858176</v>
+        <v>643635675136</v>
       </c>
       <c r="K2" t="n">
-        <v>31.25668</v>
+        <v>30.947855</v>
       </c>
       <c r="L2" t="n">
-        <v>21.86634</v>
+        <v>21.700588</v>
       </c>
       <c r="M2" t="n">
-        <v>8.609999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="N2" t="n">
         <v>281.07</v>
@@ -11005,7 +11013,7 @@
         <v>0.235</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="R2" t="n">
         <v>0.21482</v>
@@ -11029,7 +11037,7 @@
         <v>35.284</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.627253</v>
+        <v>7.569436</v>
       </c>
       <c r="Z2" t="n">
         <v>-0.008999999999999999</v>
@@ -11041,7 +11049,7 @@
         <v>97929003008</v>
       </c>
       <c r="AC2" t="n">
-        <v>676829921280</v>
+        <v>671913738240</v>
       </c>
       <c r="AD2" t="n">
         <v>34872000512</v>
@@ -11068,7 +11076,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-09 09:15:17</t>
+          <t>2026-09-10 18:59:34</t>
         </is>
       </c>
     </row>

--- a/data/JNJ_data.xlsx
+++ b/data/JNJ_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45910</v>
+        <v>45911</v>
       </c>
       <c r="B2" t="n">
-        <v>172.4145258819289</v>
+        <v>171.8766472653515</v>
       </c>
       <c r="C2" t="n">
-        <v>172.7176914018626</v>
+        <v>174.9083323610806</v>
       </c>
       <c r="D2" t="n">
-        <v>170.4879415338014</v>
+        <v>171.759296719517</v>
       </c>
       <c r="E2" t="n">
-        <v>171.9157562255859</v>
+        <v>174.5660400390625</v>
       </c>
       <c r="F2" t="n">
-        <v>6891600</v>
+        <v>5792500</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="B3" t="n">
-        <v>171.8766472653515</v>
+        <v>173.7934495446803</v>
       </c>
       <c r="C3" t="n">
-        <v>174.9083323610806</v>
+        <v>174.8594234144472</v>
       </c>
       <c r="D3" t="n">
-        <v>171.759296719517</v>
+        <v>172.8252628178507</v>
       </c>
       <c r="E3" t="n">
-        <v>174.5660400390625</v>
+        <v>174.1357269287109</v>
       </c>
       <c r="F3" t="n">
-        <v>5792500</v>
+        <v>7220200</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="B4" t="n">
-        <v>173.7934343158836</v>
+        <v>173.8423314280924</v>
       </c>
       <c r="C4" t="n">
-        <v>174.8594080922437</v>
+        <v>175.0452341292242</v>
       </c>
       <c r="D4" t="n">
-        <v>172.8252476738922</v>
+        <v>173.0306220566984</v>
       </c>
       <c r="E4" t="n">
-        <v>174.1357116699219</v>
+        <v>173.4902648925781</v>
       </c>
       <c r="F4" t="n">
-        <v>7220200</v>
+        <v>4768100</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="B5" t="n">
-        <v>173.8423314280924</v>
+        <v>173.6565364179341</v>
       </c>
       <c r="C5" t="n">
-        <v>175.0452341292242</v>
+        <v>173.7054225283811</v>
       </c>
       <c r="D5" t="n">
-        <v>173.0306220566984</v>
+        <v>171.7788382257642</v>
       </c>
       <c r="E5" t="n">
-        <v>173.4902648925781</v>
+        <v>172.5709991455078</v>
       </c>
       <c r="F5" t="n">
-        <v>4768100</v>
+        <v>7959300</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="B6" t="n">
-        <v>173.6565364179341</v>
+        <v>172.815501634823</v>
       </c>
       <c r="C6" t="n">
-        <v>173.7054225283811</v>
+        <v>174.5758195656696</v>
       </c>
       <c r="D6" t="n">
-        <v>171.7788382257642</v>
+        <v>172.6981361629323</v>
       </c>
       <c r="E6" t="n">
-        <v>172.5709991455078</v>
+        <v>173.2946929931641</v>
       </c>
       <c r="F6" t="n">
-        <v>7959300</v>
+        <v>6714900</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B7" t="n">
-        <v>172.8154864182272</v>
+        <v>172.7078819957212</v>
       </c>
       <c r="C7" t="n">
-        <v>174.5758041940759</v>
+        <v>173.1186237380408</v>
       </c>
       <c r="D7" t="n">
-        <v>172.6981209566707</v>
+        <v>170.038038286897</v>
       </c>
       <c r="E7" t="n">
-        <v>173.294677734375</v>
+        <v>170.3216552734375</v>
       </c>
       <c r="F7" t="n">
-        <v>6714900</v>
+        <v>8200900</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B8" t="n">
-        <v>172.7078974682877</v>
+        <v>170.8400043448543</v>
       </c>
       <c r="C8" t="n">
-        <v>173.1186392474049</v>
+        <v>173.2555691360807</v>
       </c>
       <c r="D8" t="n">
-        <v>170.0380535202773</v>
+        <v>169.5099768279138</v>
       </c>
       <c r="E8" t="n">
-        <v>170.3216705322266</v>
+        <v>172.3069458007812</v>
       </c>
       <c r="F8" t="n">
-        <v>8200900</v>
+        <v>25621000</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B9" t="n">
-        <v>170.8400043448543</v>
+        <v>172.2091312958323</v>
       </c>
       <c r="C9" t="n">
-        <v>173.2555691360807</v>
+        <v>172.7470127753203</v>
       </c>
       <c r="D9" t="n">
-        <v>169.5099768279138</v>
+        <v>170.2825471290745</v>
       </c>
       <c r="E9" t="n">
-        <v>172.3069458007812</v>
+        <v>170.3705749511719</v>
       </c>
       <c r="F9" t="n">
-        <v>25621000</v>
+        <v>7193900</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B10" t="n">
-        <v>172.2091467192868</v>
+        <v>171.0355980210813</v>
       </c>
       <c r="C10" t="n">
-        <v>172.7470282469487</v>
+        <v>173.0697586837889</v>
       </c>
       <c r="D10" t="n">
-        <v>170.2825623799796</v>
+        <v>170.9769227489119</v>
       </c>
       <c r="E10" t="n">
-        <v>170.3705902099609</v>
+        <v>172.6883544921875</v>
       </c>
       <c r="F10" t="n">
-        <v>7193900</v>
+        <v>8350400</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B11" t="n">
-        <v>171.0355829083302</v>
+        <v>172.2580322171388</v>
       </c>
       <c r="C11" t="n">
-        <v>173.0697433912989</v>
+        <v>173.0501781580241</v>
       </c>
       <c r="D11" t="n">
-        <v>170.9769076413454</v>
+        <v>171.8668538263927</v>
       </c>
       <c r="E11" t="n">
-        <v>172.6883392333984</v>
+        <v>172.7959136962891</v>
       </c>
       <c r="F11" t="n">
-        <v>8350400</v>
+        <v>6676800</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B12" t="n">
-        <v>172.2580322171388</v>
+        <v>173.2946549796862</v>
       </c>
       <c r="C12" t="n">
-        <v>173.0501781580241</v>
+        <v>174.4682049836574</v>
       </c>
       <c r="D12" t="n">
-        <v>171.8668538263927</v>
+        <v>172.0330920829792</v>
       </c>
       <c r="E12" t="n">
-        <v>172.7959136962891</v>
+        <v>173.8129730224609</v>
       </c>
       <c r="F12" t="n">
-        <v>6676800</v>
+        <v>8475000</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B13" t="n">
-        <v>173.2946701929729</v>
+        <v>174.6638219397404</v>
       </c>
       <c r="C13" t="n">
-        <v>174.4682202999683</v>
+        <v>175.9449483254981</v>
       </c>
       <c r="D13" t="n">
-        <v>172.0331071855151</v>
+        <v>173.4120331870535</v>
       </c>
       <c r="E13" t="n">
-        <v>173.81298828125</v>
+        <v>175.7493591308594</v>
       </c>
       <c r="F13" t="n">
-        <v>8475000</v>
+        <v>8634400</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B14" t="n">
-        <v>174.6638219397404</v>
+        <v>175.8667202511636</v>
       </c>
       <c r="C14" t="n">
-        <v>175.9449483254981</v>
+        <v>177.861754032588</v>
       </c>
       <c r="D14" t="n">
-        <v>173.4120331870535</v>
+        <v>175.8373826163265</v>
       </c>
       <c r="E14" t="n">
-        <v>175.7493591308594</v>
+        <v>177.6172637939453</v>
       </c>
       <c r="F14" t="n">
-        <v>8634400</v>
+        <v>8597100</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B15" t="n">
-        <v>175.8667353595665</v>
+        <v>177.6954955492426</v>
       </c>
       <c r="C15" t="n">
-        <v>177.8617693123808</v>
+        <v>181.8909562377616</v>
       </c>
       <c r="D15" t="n">
-        <v>175.837397722209</v>
+        <v>177.0793903191274</v>
       </c>
       <c r="E15" t="n">
-        <v>177.6172790527344</v>
+        <v>181.3335113525391</v>
       </c>
       <c r="F15" t="n">
-        <v>8597100</v>
+        <v>11569000</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B16" t="n">
-        <v>177.6955105019011</v>
+        <v>181.9007144524965</v>
       </c>
       <c r="C16" t="n">
-        <v>181.8909715434583</v>
+        <v>182.4483701299151</v>
       </c>
       <c r="D16" t="n">
-        <v>177.0794052199421</v>
+        <v>179.8567798983815</v>
       </c>
       <c r="E16" t="n">
-        <v>181.3335266113281</v>
+        <v>181.9496154785156</v>
       </c>
       <c r="F16" t="n">
-        <v>11569000</v>
+        <v>13063800</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B17" t="n">
-        <v>181.9007144524965</v>
+        <v>180.1306211004154</v>
       </c>
       <c r="C17" t="n">
-        <v>182.4483701299151</v>
+        <v>182.4777212984756</v>
       </c>
       <c r="D17" t="n">
-        <v>179.8567798983815</v>
+        <v>180.0328190411216</v>
       </c>
       <c r="E17" t="n">
-        <v>181.9496154785156</v>
+        <v>181.8811645507812</v>
       </c>
       <c r="F17" t="n">
-        <v>13063800</v>
+        <v>7728100</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B18" t="n">
-        <v>180.1306362123439</v>
+        <v>182.9373790605305</v>
       </c>
       <c r="C18" t="n">
-        <v>182.4777366073124</v>
+        <v>185.5974341276275</v>
       </c>
       <c r="D18" t="n">
-        <v>180.032834144845</v>
+        <v>182.7906908821062</v>
       </c>
       <c r="E18" t="n">
-        <v>181.8811798095703</v>
+        <v>184.4825592041016</v>
       </c>
       <c r="F18" t="n">
-        <v>7728100</v>
+        <v>8675100</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B19" t="n">
-        <v>182.9373790605305</v>
+        <v>183.8566604823808</v>
       </c>
       <c r="C19" t="n">
-        <v>185.5974341276275</v>
+        <v>185.7343437349051</v>
       </c>
       <c r="D19" t="n">
-        <v>182.7906908821062</v>
+        <v>183.2405403023728</v>
       </c>
       <c r="E19" t="n">
-        <v>184.4825592041016</v>
+        <v>184.0131378173828</v>
       </c>
       <c r="F19" t="n">
-        <v>8675100</v>
+        <v>5806100</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B20" t="n">
-        <v>183.8566452365672</v>
+        <v>179.7198952882722</v>
       </c>
       <c r="C20" t="n">
-        <v>185.7343283333897</v>
+        <v>185.0595539364086</v>
       </c>
       <c r="D20" t="n">
-        <v>183.2405251076493</v>
+        <v>178.908185875973</v>
       </c>
       <c r="E20" t="n">
-        <v>184.0131225585938</v>
+        <v>184.72705078125</v>
       </c>
       <c r="F20" t="n">
-        <v>5806100</v>
+        <v>8776800</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B21" t="n">
-        <v>179.7198952882722</v>
+        <v>184.707479532436</v>
       </c>
       <c r="C21" t="n">
-        <v>185.0595539364086</v>
+        <v>186.0277327816568</v>
       </c>
       <c r="D21" t="n">
-        <v>178.908185875973</v>
+        <v>184.1207119169489</v>
       </c>
       <c r="E21" t="n">
-        <v>184.72705078125</v>
+        <v>185.5094146728516</v>
       </c>
       <c r="F21" t="n">
-        <v>8776800</v>
+        <v>5751200</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B22" t="n">
-        <v>184.707479532436</v>
+        <v>185.8125748295944</v>
       </c>
       <c r="C22" t="n">
-        <v>186.0277327816568</v>
+        <v>187.8662987309212</v>
       </c>
       <c r="D22" t="n">
-        <v>184.1207119169489</v>
+        <v>185.5485212028525</v>
       </c>
       <c r="E22" t="n">
-        <v>185.5094146728516</v>
+        <v>186.8687744140625</v>
       </c>
       <c r="F22" t="n">
-        <v>5751200</v>
+        <v>7484800</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B23" t="n">
-        <v>185.8125596570494</v>
+        <v>187.7782713984262</v>
       </c>
       <c r="C23" t="n">
-        <v>187.8662833906792</v>
+        <v>187.8369615886886</v>
       </c>
       <c r="D23" t="n">
-        <v>185.5485060518688</v>
+        <v>185.6658871464611</v>
       </c>
       <c r="E23" t="n">
-        <v>186.8687591552734</v>
+        <v>186.5167083740234</v>
       </c>
       <c r="F23" t="n">
-        <v>7484800</v>
+        <v>9598000</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B24" t="n">
-        <v>187.7782560364296</v>
+        <v>185.646323339356</v>
       </c>
       <c r="C24" t="n">
-        <v>187.8369462218906</v>
+        <v>187.0839270863694</v>
       </c>
       <c r="D24" t="n">
-        <v>185.6658719572771</v>
+        <v>185.1084418485517</v>
       </c>
       <c r="E24" t="n">
-        <v>186.5166931152344</v>
+        <v>186.6927337646484</v>
       </c>
       <c r="F24" t="n">
-        <v>9598000</v>
+        <v>7979500</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B25" t="n">
-        <v>185.646323339356</v>
+        <v>188.6682159172342</v>
       </c>
       <c r="C25" t="n">
-        <v>187.0839270863694</v>
+        <v>190.1155938776849</v>
       </c>
       <c r="D25" t="n">
-        <v>185.1084418485517</v>
+        <v>181.7833777150234</v>
       </c>
       <c r="E25" t="n">
-        <v>186.6927337646484</v>
+        <v>186.6438446044922</v>
       </c>
       <c r="F25" t="n">
-        <v>7979500</v>
+        <v>13613300</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B26" t="n">
-        <v>188.6682159172342</v>
+        <v>187.2599526066892</v>
       </c>
       <c r="C26" t="n">
-        <v>190.1155938776849</v>
+        <v>189.303902268661</v>
       </c>
       <c r="D26" t="n">
-        <v>181.7833777150234</v>
+        <v>185.1280049658996</v>
       </c>
       <c r="E26" t="n">
-        <v>186.6438446044922</v>
+        <v>186.956787109375</v>
       </c>
       <c r="F26" t="n">
-        <v>13613300</v>
+        <v>9473000</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B27" t="n">
-        <v>187.2599526066892</v>
+        <v>187.1230406678187</v>
       </c>
       <c r="C27" t="n">
-        <v>189.303902268661</v>
+        <v>188.7953604231518</v>
       </c>
       <c r="D27" t="n">
-        <v>185.1280049658996</v>
+        <v>186.2330926405801</v>
       </c>
       <c r="E27" t="n">
-        <v>186.956787109375</v>
+        <v>187.8858489990234</v>
       </c>
       <c r="F27" t="n">
-        <v>9473000</v>
+        <v>10611800</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B28" t="n">
-        <v>187.1230406678187</v>
+        <v>188.2574758352493</v>
       </c>
       <c r="C28" t="n">
-        <v>188.7953604231518</v>
+        <v>189.3332388090219</v>
       </c>
       <c r="D28" t="n">
-        <v>186.2330926405801</v>
+        <v>187.4555407234371</v>
       </c>
       <c r="E28" t="n">
-        <v>187.8858489990234</v>
+        <v>188.9616088867188</v>
       </c>
       <c r="F28" t="n">
-        <v>10611800</v>
+        <v>7764400</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B29" t="n">
-        <v>188.2574758352493</v>
+        <v>189.2354242017374</v>
       </c>
       <c r="C29" t="n">
-        <v>189.3332388090219</v>
+        <v>190.1938216550539</v>
       </c>
       <c r="D29" t="n">
-        <v>187.4555407234371</v>
+        <v>188.0912117995895</v>
       </c>
       <c r="E29" t="n">
-        <v>188.9616088867188</v>
+        <v>189.4505767822266</v>
       </c>
       <c r="F29" t="n">
-        <v>7764400</v>
+        <v>8034700</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B30" t="n">
-        <v>189.2354242017374</v>
+        <v>188.756223952035</v>
       </c>
       <c r="C30" t="n">
-        <v>190.1938216550539</v>
+        <v>189.2843311834856</v>
       </c>
       <c r="D30" t="n">
-        <v>188.0912117995895</v>
+        <v>187.5435620120352</v>
       </c>
       <c r="E30" t="n">
-        <v>189.4505767822266</v>
+        <v>187.6511383056641</v>
       </c>
       <c r="F30" t="n">
-        <v>8034700</v>
+        <v>6716000</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B31" t="n">
-        <v>188.7562393006838</v>
+        <v>187.768489042997</v>
       </c>
       <c r="C31" t="n">
-        <v>189.2843465750772</v>
+        <v>189.186529335124</v>
       </c>
       <c r="D31" t="n">
-        <v>187.5435772620767</v>
+        <v>187.553336455502</v>
       </c>
       <c r="E31" t="n">
-        <v>187.6511535644531</v>
+        <v>188.6877746582031</v>
       </c>
       <c r="F31" t="n">
-        <v>6716000</v>
+        <v>6343100</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B32" t="n">
-        <v>187.7685042274453</v>
+        <v>188.3161470541903</v>
       </c>
       <c r="C32" t="n">
-        <v>189.1865446342463</v>
+        <v>189.7244131268554</v>
       </c>
       <c r="D32" t="n">
-        <v>187.5533516225514</v>
+        <v>187.318622765636</v>
       </c>
       <c r="E32" t="n">
-        <v>188.6877899169922</v>
+        <v>188.2281341552734</v>
       </c>
       <c r="F32" t="n">
-        <v>6343100</v>
+        <v>8882500</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B33" t="n">
-        <v>188.3161623201141</v>
+        <v>187.9640678233363</v>
       </c>
       <c r="C33" t="n">
-        <v>189.7244285069409</v>
+        <v>188.0716441111252</v>
       </c>
       <c r="D33" t="n">
-        <v>187.3186379506951</v>
+        <v>185.2453379201237</v>
       </c>
       <c r="E33" t="n">
-        <v>188.2281494140625</v>
+        <v>186.2037353515625</v>
       </c>
       <c r="F33" t="n">
-        <v>8882500</v>
+        <v>6903400</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B34" t="n">
-        <v>187.9640832263789</v>
+        <v>185.8028067822911</v>
       </c>
       <c r="C34" t="n">
-        <v>188.0716595229833</v>
+        <v>186.5949527664067</v>
       </c>
       <c r="D34" t="n">
-        <v>185.2453531003753</v>
+        <v>185.3529381781329</v>
       </c>
       <c r="E34" t="n">
-        <v>186.2037506103516</v>
+        <v>186.1059722900391</v>
       </c>
       <c r="F34" t="n">
-        <v>6903400</v>
+        <v>7126000</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B35" t="n">
-        <v>185.8028067822911</v>
+        <v>185.0888617111332</v>
       </c>
       <c r="C35" t="n">
-        <v>186.5949527664067</v>
+        <v>185.3333519191582</v>
       </c>
       <c r="D35" t="n">
-        <v>185.3529381781329</v>
+        <v>182.5070457112893</v>
       </c>
       <c r="E35" t="n">
-        <v>186.1059722900391</v>
+        <v>182.8102111816406</v>
       </c>
       <c r="F35" t="n">
-        <v>7126000</v>
+        <v>8329500</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B36" t="n">
-        <v>185.0888771601165</v>
+        <v>182.5853054515495</v>
       </c>
       <c r="C36" t="n">
-        <v>185.3333673885486</v>
+        <v>182.9764987830591</v>
       </c>
       <c r="D36" t="n">
-        <v>182.5070609447738</v>
+        <v>180.5902716895996</v>
       </c>
       <c r="E36" t="n">
-        <v>182.8102264404297</v>
+        <v>182.4875183105469</v>
       </c>
       <c r="F36" t="n">
-        <v>8329500</v>
+        <v>10551100</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B37" t="n">
-        <v>182.5853054515495</v>
+        <v>182.9569302033718</v>
       </c>
       <c r="C37" t="n">
-        <v>182.9764987830591</v>
+        <v>185.2062432977132</v>
       </c>
       <c r="D37" t="n">
-        <v>180.5902716895996</v>
+        <v>182.7906786381269</v>
       </c>
       <c r="E37" t="n">
-        <v>182.4875183105469</v>
+        <v>184.8835144042969</v>
       </c>
       <c r="F37" t="n">
-        <v>10551100</v>
+        <v>7072500</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B38" t="n">
-        <v>182.9569302033718</v>
+        <v>183.3285450571186</v>
       </c>
       <c r="C38" t="n">
-        <v>185.2062432977132</v>
+        <v>185.3235785985601</v>
       </c>
       <c r="D38" t="n">
-        <v>182.7906786381269</v>
+        <v>182.6439605332679</v>
       </c>
       <c r="E38" t="n">
-        <v>184.8835144042969</v>
+        <v>184.7074584960938</v>
       </c>
       <c r="F38" t="n">
-        <v>7072500</v>
+        <v>8791700</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B39" t="n">
-        <v>183.3285602019948</v>
+        <v>184.8346326024117</v>
       </c>
       <c r="C39" t="n">
-        <v>185.3235939082472</v>
+        <v>184.8639702391834</v>
       </c>
       <c r="D39" t="n">
-        <v>182.6439756215902</v>
+        <v>181.4313324343818</v>
       </c>
       <c r="E39" t="n">
-        <v>184.7074737548828</v>
+        <v>182.1550140380859</v>
       </c>
       <c r="F39" t="n">
-        <v>8791700</v>
+        <v>7542600</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B40" t="n">
-        <v>184.834617119156</v>
+        <v>182.7124378793119</v>
       </c>
       <c r="C40" t="n">
-        <v>184.8639547534701</v>
+        <v>183.680624548461</v>
       </c>
       <c r="D40" t="n">
-        <v>181.4313172362143</v>
+        <v>181.5290986170187</v>
       </c>
       <c r="E40" t="n">
-        <v>182.1549987792969</v>
+        <v>182.7417755126953</v>
       </c>
       <c r="F40" t="n">
-        <v>7542600</v>
+        <v>7209400</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B41" t="n">
-        <v>182.7124378793119</v>
+        <v>182.5266206937376</v>
       </c>
       <c r="C41" t="n">
-        <v>183.680624548461</v>
+        <v>183.6903965454173</v>
       </c>
       <c r="D41" t="n">
-        <v>181.5290986170187</v>
+        <v>181.3139438128489</v>
       </c>
       <c r="E41" t="n">
-        <v>182.7417755126953</v>
+        <v>181.9007263183594</v>
       </c>
       <c r="F41" t="n">
-        <v>7209400</v>
+        <v>5049400</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B42" t="n">
-        <v>182.5266206937376</v>
+        <v>182.6439716214627</v>
       </c>
       <c r="C42" t="n">
-        <v>183.6903965454173</v>
+        <v>183.3872314530524</v>
       </c>
       <c r="D42" t="n">
-        <v>181.3139438128489</v>
+        <v>181.2846065725014</v>
       </c>
       <c r="E42" t="n">
-        <v>181.9007263183594</v>
+        <v>182.8493499755859</v>
       </c>
       <c r="F42" t="n">
-        <v>5049400</v>
+        <v>6767400</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B43" t="n">
-        <v>182.643986863113</v>
+        <v>183.6023881426973</v>
       </c>
       <c r="C43" t="n">
-        <v>183.3872467567277</v>
+        <v>184.1989448996594</v>
       </c>
       <c r="D43" t="n">
-        <v>181.2846217007125</v>
+        <v>181.607339513103</v>
       </c>
       <c r="E43" t="n">
-        <v>182.849365234375</v>
+        <v>182.4581756591797</v>
       </c>
       <c r="F43" t="n">
-        <v>6767400</v>
+        <v>6959200</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B44" t="n">
-        <v>183.6023727882189</v>
+        <v>181.9007248187872</v>
       </c>
       <c r="C44" t="n">
-        <v>184.1989294952916</v>
+        <v>184.2673883725038</v>
       </c>
       <c r="D44" t="n">
-        <v>181.6073243254685</v>
+        <v>181.0401144637998</v>
       </c>
       <c r="E44" t="n">
-        <v>182.4581604003906</v>
+        <v>184.2576141357422</v>
       </c>
       <c r="F44" t="n">
-        <v>6959200</v>
+        <v>5323800</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B45" t="n">
-        <v>181.9007248187872</v>
+        <v>185.2160176409071</v>
       </c>
       <c r="C45" t="n">
-        <v>184.2673883725038</v>
+        <v>189.6461794051158</v>
       </c>
       <c r="D45" t="n">
-        <v>181.0401144637998</v>
+        <v>184.8835145102268</v>
       </c>
       <c r="E45" t="n">
-        <v>184.2576141357422</v>
+        <v>189.5581665039062</v>
       </c>
       <c r="F45" t="n">
-        <v>5323800</v>
+        <v>7465600</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B46" t="n">
-        <v>185.2160027316463</v>
+        <v>189.0985363418636</v>
       </c>
       <c r="C46" t="n">
-        <v>189.646164139242</v>
+        <v>191.24027328305</v>
       </c>
       <c r="D46" t="n">
-        <v>184.8834996277314</v>
+        <v>188.8149342225856</v>
       </c>
       <c r="E46" t="n">
-        <v>189.5581512451172</v>
+        <v>190.1058349609375</v>
       </c>
       <c r="F46" t="n">
-        <v>7465600</v>
+        <v>8803000</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B47" t="n">
-        <v>189.0985059859865</v>
+        <v>189.9297961094911</v>
       </c>
       <c r="C47" t="n">
-        <v>191.2402425833612</v>
+        <v>191.6803395836668</v>
       </c>
       <c r="D47" t="n">
-        <v>188.814903912235</v>
+        <v>189.1865362627468</v>
       </c>
       <c r="E47" t="n">
-        <v>190.1058044433594</v>
+        <v>190.9468688964844</v>
       </c>
       <c r="F47" t="n">
-        <v>8803000</v>
+        <v>8631600</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B48" t="n">
-        <v>189.9297961094911</v>
+        <v>190.7023657548931</v>
       </c>
       <c r="C48" t="n">
-        <v>191.6803395836668</v>
+        <v>192.8343132451486</v>
       </c>
       <c r="D48" t="n">
-        <v>189.1865362627468</v>
+        <v>189.2843255068563</v>
       </c>
       <c r="E48" t="n">
-        <v>190.9468688964844</v>
+        <v>191.6118621826172</v>
       </c>
       <c r="F48" t="n">
-        <v>8631600</v>
+        <v>8824800</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B49" t="n">
-        <v>190.7023809412554</v>
+        <v>192.619189424801</v>
       </c>
       <c r="C49" t="n">
-        <v>192.8343286012861</v>
+        <v>195.8660119204403</v>
       </c>
       <c r="D49" t="n">
-        <v>189.2843405802947</v>
+        <v>191.5825383144018</v>
       </c>
       <c r="E49" t="n">
-        <v>191.6118774414062</v>
+        <v>195.1814422607422</v>
       </c>
       <c r="F49" t="n">
-        <v>8824800</v>
+        <v>13257000</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B50" t="n">
-        <v>192.6192044832797</v>
+        <v>194.6239916898205</v>
       </c>
       <c r="C50" t="n">
-        <v>195.8660272327473</v>
+        <v>195.8855695967434</v>
       </c>
       <c r="D50" t="n">
-        <v>191.5825532918377</v>
+        <v>194.1545746400929</v>
       </c>
       <c r="E50" t="n">
-        <v>195.1814575195312</v>
+        <v>195.5921783447266</v>
       </c>
       <c r="F50" t="n">
-        <v>13257000</v>
+        <v>12468600</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B51" t="n">
-        <v>194.6239916898205</v>
+        <v>195.5921832139753</v>
       </c>
       <c r="C51" t="n">
-        <v>195.8855695967434</v>
+        <v>198.9954830235987</v>
       </c>
       <c r="D51" t="n">
-        <v>194.1545746400929</v>
+        <v>194.9858522212118</v>
       </c>
       <c r="E51" t="n">
-        <v>195.5921783447266</v>
+        <v>198.0468597412109</v>
       </c>
       <c r="F51" t="n">
-        <v>12468600</v>
+        <v>14690800</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B52" t="n">
-        <v>195.5921681443101</v>
+        <v>197.5481028667918</v>
       </c>
       <c r="C52" t="n">
-        <v>198.9954676917216</v>
+        <v>200.0027793669477</v>
       </c>
       <c r="D52" t="n">
-        <v>194.9858371982622</v>
+        <v>197.1275868403205</v>
       </c>
       <c r="E52" t="n">
-        <v>198.0468444824219</v>
+        <v>198.5945281982422</v>
       </c>
       <c r="F52" t="n">
-        <v>14690800</v>
+        <v>10612600</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B53" t="n">
-        <v>197.5481028667918</v>
+        <v>199.4649096707152</v>
       </c>
       <c r="C53" t="n">
-        <v>200.0027793669477</v>
+        <v>202.3792289443294</v>
       </c>
       <c r="D53" t="n">
-        <v>197.1275868403205</v>
+        <v>198.5162864137085</v>
       </c>
       <c r="E53" t="n">
-        <v>198.5945281982422</v>
+        <v>199.4062194824219</v>
       </c>
       <c r="F53" t="n">
-        <v>10612600</v>
+        <v>13189100</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B54" t="n">
-        <v>199.4649096707152</v>
+        <v>199.2204251313988</v>
       </c>
       <c r="C54" t="n">
-        <v>202.3792289443294</v>
+        <v>201.5772996022027</v>
       </c>
       <c r="D54" t="n">
-        <v>198.5162864137085</v>
+        <v>198.5260663138595</v>
       </c>
       <c r="E54" t="n">
-        <v>199.4062194824219</v>
+        <v>201.5088500976562</v>
       </c>
       <c r="F54" t="n">
-        <v>13189100</v>
+        <v>14803900</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,25 +1847,25 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B55" t="n">
-        <v>199.2204100458954</v>
+        <v>201.9320337594338</v>
       </c>
       <c r="C55" t="n">
-        <v>201.5772843382305</v>
+        <v>204.4318344688182</v>
       </c>
       <c r="D55" t="n">
-        <v>198.5260512809348</v>
+        <v>201.9320337594338</v>
       </c>
       <c r="E55" t="n">
-        <v>201.5088348388672</v>
+        <v>203.3984527587891</v>
       </c>
       <c r="F55" t="n">
-        <v>14803900</v>
+        <v>10275300</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -1873,25 +1873,25 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B56" t="n">
-        <v>201.9320489082132</v>
+        <v>203.2212987804707</v>
       </c>
       <c r="C56" t="n">
-        <v>204.4318498051307</v>
+        <v>204.520395563755</v>
       </c>
       <c r="D56" t="n">
-        <v>201.9320489082132</v>
+        <v>202.6800021969169</v>
       </c>
       <c r="E56" t="n">
-        <v>203.3984680175781</v>
+        <v>204.2743530273438</v>
       </c>
       <c r="F56" t="n">
-        <v>10275300</v>
+        <v>6729000</v>
       </c>
       <c r="G56" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B57" t="n">
-        <v>203.2213139605992</v>
+        <v>203.723236152328</v>
       </c>
       <c r="C57" t="n">
-        <v>204.5204108409229</v>
+        <v>204.1759610624769</v>
       </c>
       <c r="D57" t="n">
-        <v>202.6800173366119</v>
+        <v>201.390757529436</v>
       </c>
       <c r="E57" t="n">
-        <v>204.2743682861328</v>
+        <v>203.6445007324219</v>
       </c>
       <c r="F57" t="n">
-        <v>6729000</v>
+        <v>5638300</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B58" t="n">
-        <v>203.723236152328</v>
+        <v>203.2311491085565</v>
       </c>
       <c r="C58" t="n">
-        <v>204.1759610624769</v>
+        <v>204.4121503614282</v>
       </c>
       <c r="D58" t="n">
-        <v>201.390757529436</v>
+        <v>202.0895080566406</v>
       </c>
       <c r="E58" t="n">
-        <v>203.6445007324219</v>
+        <v>202.0895080566406</v>
       </c>
       <c r="F58" t="n">
-        <v>5638300</v>
+        <v>8473700</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B59" t="n">
-        <v>203.2311491085565</v>
+        <v>201.9910847326731</v>
       </c>
       <c r="C59" t="n">
-        <v>204.4121503614282</v>
+        <v>202.3552228785814</v>
       </c>
       <c r="D59" t="n">
-        <v>202.0895080566406</v>
+        <v>199.8849612359226</v>
       </c>
       <c r="E59" t="n">
-        <v>202.0895080566406</v>
+        <v>202.1682281494141</v>
       </c>
       <c r="F59" t="n">
-        <v>8473700</v>
+        <v>8393600</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B60" t="n">
-        <v>201.9910999780921</v>
+        <v>202.6406353348706</v>
       </c>
       <c r="C60" t="n">
-        <v>202.3552381514841</v>
+        <v>203.7429161551587</v>
       </c>
       <c r="D60" t="n">
-        <v>199.8849763223805</v>
+        <v>201.7450518785209</v>
       </c>
       <c r="E60" t="n">
-        <v>202.1682434082031</v>
+        <v>202.0796661376953</v>
       </c>
       <c r="F60" t="n">
-        <v>8393600</v>
+        <v>8363300</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B61" t="n">
-        <v>202.6406353348706</v>
+        <v>201.3513800209524</v>
       </c>
       <c r="C61" t="n">
-        <v>203.7429161551587</v>
+        <v>201.6171101829578</v>
       </c>
       <c r="D61" t="n">
-        <v>201.7450518785209</v>
+        <v>198.516980022795</v>
       </c>
       <c r="E61" t="n">
-        <v>202.0796661376953</v>
+        <v>199.2747802734375</v>
       </c>
       <c r="F61" t="n">
-        <v>8363300</v>
+        <v>9049900</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B62" t="n">
-        <v>201.35139543875</v>
+        <v>199.7668717489871</v>
       </c>
       <c r="C62" t="n">
-        <v>201.6171256211029</v>
+        <v>200.2294329646455</v>
       </c>
       <c r="D62" t="n">
-        <v>198.5169952235581</v>
+        <v>197.6312241234294</v>
       </c>
       <c r="E62" t="n">
-        <v>199.2747955322266</v>
+        <v>198.7334899902344</v>
       </c>
       <c r="F62" t="n">
-        <v>9049900</v>
+        <v>7785300</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B63" t="n">
-        <v>199.7668717489871</v>
+        <v>199.4519359184436</v>
       </c>
       <c r="C63" t="n">
-        <v>200.2294329646455</v>
+        <v>200.0424290268597</v>
       </c>
       <c r="D63" t="n">
-        <v>197.6312241234294</v>
+        <v>197.8083734899551</v>
       </c>
       <c r="E63" t="n">
-        <v>198.7334899902344</v>
+        <v>198.4283905029297</v>
       </c>
       <c r="F63" t="n">
-        <v>7785300</v>
+        <v>7785700</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B64" t="n">
-        <v>199.4519359184436</v>
+        <v>199.7078130861464</v>
       </c>
       <c r="C64" t="n">
-        <v>200.0424290268597</v>
+        <v>202.2863341775681</v>
       </c>
       <c r="D64" t="n">
-        <v>197.8083734899551</v>
+        <v>196.7454662214423</v>
       </c>
       <c r="E64" t="n">
-        <v>198.4283905029297</v>
+        <v>196.794677734375</v>
       </c>
       <c r="F64" t="n">
-        <v>7785700</v>
+        <v>7509400</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B65" t="n">
-        <v>199.7078130861464</v>
+        <v>197.4146980881505</v>
       </c>
       <c r="C65" t="n">
-        <v>202.2863341775681</v>
+        <v>203.5264016771889</v>
       </c>
       <c r="D65" t="n">
-        <v>196.7454662214423</v>
+        <v>197.011184699407</v>
       </c>
       <c r="E65" t="n">
-        <v>196.794677734375</v>
+        <v>203.2705078125</v>
       </c>
       <c r="F65" t="n">
-        <v>7509400</v>
+        <v>11599800</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B66" t="n">
-        <v>197.4146980881505</v>
+        <v>204.608977678963</v>
       </c>
       <c r="C66" t="n">
-        <v>203.5264016771889</v>
+        <v>207.8961175457048</v>
       </c>
       <c r="D66" t="n">
-        <v>197.011184699407</v>
+        <v>204.5400935742317</v>
       </c>
       <c r="E66" t="n">
-        <v>203.2705078125</v>
+        <v>206.6855773925781</v>
       </c>
       <c r="F66" t="n">
-        <v>11599800</v>
+        <v>9009000</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B67" t="n">
-        <v>204.608977678963</v>
+        <v>206.951303914036</v>
       </c>
       <c r="C67" t="n">
-        <v>207.8961175457048</v>
+        <v>208.9098079752741</v>
       </c>
       <c r="D67" t="n">
-        <v>204.5400935742317</v>
+        <v>205.6522070875063</v>
       </c>
       <c r="E67" t="n">
-        <v>206.6855773925781</v>
+        <v>208.2307281494141</v>
       </c>
       <c r="F67" t="n">
-        <v>9009000</v>
+        <v>6922700</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B68" t="n">
-        <v>206.951319079071</v>
+        <v>207.0202168563343</v>
       </c>
       <c r="C68" t="n">
-        <v>208.9098232838249</v>
+        <v>211.7835972337083</v>
       </c>
       <c r="D68" t="n">
-        <v>205.6522221573458</v>
+        <v>205.7014173161141</v>
       </c>
       <c r="E68" t="n">
-        <v>208.2307434082031</v>
+        <v>210.7797393798828</v>
       </c>
       <c r="F68" t="n">
-        <v>6922700</v>
+        <v>8467000</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B69" t="n">
-        <v>207.020201869705</v>
+        <v>210.6124287318692</v>
       </c>
       <c r="C69" t="n">
-        <v>211.7835819022478</v>
+        <v>211.3308687932753</v>
       </c>
       <c r="D69" t="n">
-        <v>205.7014024249555</v>
+        <v>205.5045828472482</v>
       </c>
       <c r="E69" t="n">
-        <v>210.7797241210938</v>
+        <v>205.9868316650391</v>
       </c>
       <c r="F69" t="n">
-        <v>8467000</v>
+        <v>9949800</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B70" t="n">
-        <v>210.612413130432</v>
+        <v>206.0753964132944</v>
       </c>
       <c r="C70" t="n">
-        <v>211.3308531386185</v>
+        <v>208.1716837329721</v>
       </c>
       <c r="D70" t="n">
-        <v>205.5045676241825</v>
+        <v>205.1601253407421</v>
       </c>
       <c r="E70" t="n">
-        <v>205.98681640625</v>
+        <v>207.0005187988281</v>
       </c>
       <c r="F70" t="n">
-        <v>9949800</v>
+        <v>8457600</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B71" t="n">
-        <v>206.0753812226996</v>
+        <v>206.478915988136</v>
       </c>
       <c r="C71" t="n">
-        <v>208.171668387852</v>
+        <v>207.7189650641044</v>
       </c>
       <c r="D71" t="n">
-        <v>205.1601102176154</v>
+        <v>204.4712003216206</v>
       </c>
       <c r="E71" t="n">
-        <v>207.0005035400391</v>
+        <v>205.0124969482422</v>
       </c>
       <c r="F71" t="n">
-        <v>8457600</v>
+        <v>7499900</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B72" t="n">
-        <v>206.4789006202035</v>
+        <v>204.2743601070968</v>
       </c>
       <c r="C72" t="n">
-        <v>207.7189496038768</v>
+        <v>205.927773818052</v>
       </c>
       <c r="D72" t="n">
-        <v>204.4711851031195</v>
+        <v>202.768580933452</v>
       </c>
       <c r="E72" t="n">
-        <v>205.0124816894531</v>
+        <v>203.1031951904297</v>
       </c>
       <c r="F72" t="n">
-        <v>7499900</v>
+        <v>24803900</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B73" t="n">
-        <v>204.2743754538735</v>
+        <v>202.8670125241163</v>
       </c>
       <c r="C73" t="n">
-        <v>205.9277892890467</v>
+        <v>204.7861414522214</v>
       </c>
       <c r="D73" t="n">
-        <v>202.768596167102</v>
+        <v>202.2469804791725</v>
       </c>
       <c r="E73" t="n">
-        <v>203.1032104492188</v>
+        <v>204.0381774902344</v>
       </c>
       <c r="F73" t="n">
-        <v>24803900</v>
+        <v>8187800</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B74" t="n">
-        <v>202.8669973529117</v>
+        <v>201.7745733053134</v>
       </c>
       <c r="C74" t="n">
-        <v>204.7861261374966</v>
+        <v>203.2606648620441</v>
       </c>
       <c r="D74" t="n">
-        <v>202.2469653543363</v>
+        <v>200.062111796116</v>
       </c>
       <c r="E74" t="n">
-        <v>204.0381622314453</v>
+        <v>202.5225372314453</v>
       </c>
       <c r="F74" t="n">
-        <v>8187800</v>
+        <v>7047300</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B75" t="n">
-        <v>201.7745885077481</v>
+        <v>202.739053555574</v>
       </c>
       <c r="C75" t="n">
-        <v>203.2606801764464</v>
+        <v>204.648346074342</v>
       </c>
       <c r="D75" t="n">
-        <v>200.0621268695276</v>
+        <v>202.3158675938084</v>
       </c>
       <c r="E75" t="n">
-        <v>202.5225524902344</v>
+        <v>204.4908752441406</v>
       </c>
       <c r="F75" t="n">
-        <v>7047300</v>
+        <v>2376500</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B76" t="n">
-        <v>202.7390686836449</v>
+        <v>204.2448234412372</v>
       </c>
       <c r="C76" t="n">
-        <v>204.6483613448813</v>
+        <v>204.7467447953422</v>
       </c>
       <c r="D76" t="n">
-        <v>202.3158826903017</v>
+        <v>203.4378117532305</v>
       </c>
       <c r="E76" t="n">
-        <v>204.4908905029297</v>
+        <v>204.3432464599609</v>
       </c>
       <c r="F76" t="n">
-        <v>2376500</v>
+        <v>2316700</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B77" t="n">
-        <v>204.2448386926768</v>
+        <v>204.7073902941868</v>
       </c>
       <c r="C77" t="n">
-        <v>204.7467600842614</v>
+        <v>206.1541216096647</v>
       </c>
       <c r="D77" t="n">
-        <v>203.4378269444086</v>
+        <v>204.0972096094051</v>
       </c>
       <c r="E77" t="n">
-        <v>204.34326171875</v>
+        <v>204.2743530273438</v>
       </c>
       <c r="F77" t="n">
-        <v>2316700</v>
+        <v>4348900</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B78" t="n">
-        <v>204.7074055853226</v>
+        <v>204.2251519205988</v>
       </c>
       <c r="C78" t="n">
-        <v>206.1541370088678</v>
+        <v>204.4023103648072</v>
       </c>
       <c r="D78" t="n">
-        <v>204.097224854962</v>
+        <v>203.2508330378112</v>
       </c>
       <c r="E78" t="n">
-        <v>204.2743682861328</v>
+        <v>203.6346588134766</v>
       </c>
       <c r="F78" t="n">
-        <v>4348900</v>
+        <v>3937400</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B79" t="n">
-        <v>204.2251366175628</v>
+        <v>203.6346662875698</v>
       </c>
       <c r="C79" t="n">
-        <v>204.4022950484963</v>
+        <v>204.2153231202547</v>
       </c>
       <c r="D79" t="n">
-        <v>203.2508178077831</v>
+        <v>203.1032059526835</v>
       </c>
       <c r="E79" t="n">
-        <v>203.6346435546875</v>
+        <v>203.6740264892578</v>
       </c>
       <c r="F79" t="n">
-        <v>3937400</v>
+        <v>4083800</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B80" t="n">
-        <v>203.6346662875698</v>
+        <v>203.5460790066363</v>
       </c>
       <c r="C80" t="n">
-        <v>204.2153231202547</v>
+        <v>204.1070481869595</v>
       </c>
       <c r="D80" t="n">
-        <v>203.1032059526835</v>
+        <v>200.4557702982002</v>
       </c>
       <c r="E80" t="n">
-        <v>203.6740264892578</v>
+        <v>204.0676879882812</v>
       </c>
       <c r="F80" t="n">
-        <v>4083800</v>
+        <v>6325500</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B81" t="n">
-        <v>203.5460790066363</v>
+        <v>202.6111087313451</v>
       </c>
       <c r="C81" t="n">
-        <v>204.1070481869595</v>
+        <v>202.68000785174</v>
       </c>
       <c r="D81" t="n">
-        <v>200.4557702982002</v>
+        <v>197.7296330824079</v>
       </c>
       <c r="E81" t="n">
-        <v>204.0676879882812</v>
+        <v>201.0758056640625</v>
       </c>
       <c r="F81" t="n">
-        <v>6325500</v>
+        <v>9477000</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B82" t="n">
-        <v>202.6111087313451</v>
+        <v>201.3612227968269</v>
       </c>
       <c r="C82" t="n">
-        <v>202.68000785174</v>
+        <v>203.4378224562984</v>
       </c>
       <c r="D82" t="n">
-        <v>197.7296330824079</v>
+        <v>200.8888103027919</v>
       </c>
       <c r="E82" t="n">
-        <v>201.0758056640625</v>
+        <v>201.5482025146484</v>
       </c>
       <c r="F82" t="n">
-        <v>9477000</v>
+        <v>8107900</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B83" t="n">
-        <v>201.3612380414601</v>
+        <v>202.0107645526058</v>
       </c>
       <c r="C83" t="n">
-        <v>203.4378378581467</v>
+        <v>204.9632750752426</v>
       </c>
       <c r="D83" t="n">
-        <v>200.8888255116597</v>
+        <v>201.7844096173656</v>
       </c>
       <c r="E83" t="n">
-        <v>201.5482177734375</v>
+        <v>204.2054748535156</v>
       </c>
       <c r="F83" t="n">
-        <v>8107900</v>
+        <v>7545900</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B84" t="n">
-        <v>202.0107645526058</v>
+        <v>203.6543250611801</v>
       </c>
       <c r="C84" t="n">
-        <v>204.9632750752426</v>
+        <v>205.6718769031367</v>
       </c>
       <c r="D84" t="n">
-        <v>201.7844096173656</v>
+        <v>201.7253599471909</v>
       </c>
       <c r="E84" t="n">
-        <v>204.2054748535156</v>
+        <v>202.4930114746094</v>
       </c>
       <c r="F84" t="n">
-        <v>7545900</v>
+        <v>6557800</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B85" t="n">
-        <v>203.6543250611801</v>
+        <v>202.6504838830927</v>
       </c>
       <c r="C85" t="n">
-        <v>205.6718769031367</v>
+        <v>203.4279717120081</v>
       </c>
       <c r="D85" t="n">
-        <v>201.7253599471909</v>
+        <v>200.7805515444468</v>
       </c>
       <c r="E85" t="n">
-        <v>202.4930114746094</v>
+        <v>201.154541015625</v>
       </c>
       <c r="F85" t="n">
-        <v>6557800</v>
+        <v>6154300</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B86" t="n">
-        <v>202.6504992553581</v>
+        <v>202.2961890410606</v>
       </c>
       <c r="C86" t="n">
-        <v>203.4279871432506</v>
+        <v>206.5773204309254</v>
       </c>
       <c r="D86" t="n">
-        <v>200.7805667748665</v>
+        <v>200.6231026927027</v>
       </c>
       <c r="E86" t="n">
-        <v>201.1545562744141</v>
+        <v>206.4001770019531</v>
       </c>
       <c r="F86" t="n">
-        <v>6154300</v>
+        <v>11794300</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B87" t="n">
-        <v>202.2962039964493</v>
+        <v>206.5871576245673</v>
       </c>
       <c r="C87" t="n">
-        <v>206.5773357028104</v>
+        <v>210.9962356455094</v>
       </c>
       <c r="D87" t="n">
-        <v>200.6231175244031</v>
+        <v>205.5537759744533</v>
       </c>
       <c r="E87" t="n">
-        <v>206.4001922607422</v>
+        <v>210.2679443359375</v>
       </c>
       <c r="F87" t="n">
-        <v>11794300</v>
+        <v>11379600</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B88" t="n">
-        <v>206.5871726162479</v>
+        <v>211.3308558190507</v>
       </c>
       <c r="C88" t="n">
-        <v>210.9962509571494</v>
+        <v>215.3954834155094</v>
       </c>
       <c r="D88" t="n">
-        <v>205.5537908911432</v>
+        <v>210.7600353199485</v>
       </c>
       <c r="E88" t="n">
-        <v>210.2679595947266</v>
+        <v>215.0903930664062</v>
       </c>
       <c r="F88" t="n">
-        <v>11379600</v>
+        <v>11858800</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B89" t="n">
-        <v>211.3308558190507</v>
+        <v>214.7754540862871</v>
       </c>
       <c r="C89" t="n">
-        <v>215.3954834155094</v>
+        <v>216.2713969640869</v>
       </c>
       <c r="D89" t="n">
-        <v>210.7600353199485</v>
+        <v>212.4921870786144</v>
       </c>
       <c r="E89" t="n">
-        <v>215.0903930664062</v>
+        <v>216.0942535400391</v>
       </c>
       <c r="F89" t="n">
-        <v>11858800</v>
+        <v>8492100</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B90" t="n">
-        <v>214.7754540862871</v>
+        <v>215.5726286297608</v>
       </c>
       <c r="C90" t="n">
-        <v>216.2713969640869</v>
+        <v>216.6256979258031</v>
       </c>
       <c r="D90" t="n">
-        <v>212.4921870786144</v>
+        <v>214.686881478726</v>
       </c>
       <c r="E90" t="n">
-        <v>216.0942535400391</v>
+        <v>215.1986541748047</v>
       </c>
       <c r="F90" t="n">
-        <v>8492100</v>
+        <v>10021500</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B91" t="n">
-        <v>215.5726286297608</v>
+        <v>213.6535174405211</v>
       </c>
       <c r="C91" t="n">
-        <v>216.6256979258031</v>
+        <v>215.2675560609527</v>
       </c>
       <c r="D91" t="n">
-        <v>214.686881478726</v>
+        <v>211.1045200795966</v>
       </c>
       <c r="E91" t="n">
-        <v>215.1986541748047</v>
+        <v>214.7557983398438</v>
       </c>
       <c r="F91" t="n">
-        <v>10021500</v>
+        <v>14057100</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B92" t="n">
-        <v>213.6535022600511</v>
+        <v>207.659916851811</v>
       </c>
       <c r="C92" t="n">
-        <v>215.2675407658023</v>
+        <v>215.2183369488501</v>
       </c>
       <c r="D92" t="n">
-        <v>211.1045050802375</v>
+        <v>207.1678317407877</v>
       </c>
       <c r="E92" t="n">
-        <v>214.7557830810547</v>
+        <v>214.5589447021484</v>
       </c>
       <c r="F92" t="n">
-        <v>14057100</v>
+        <v>14762900</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B93" t="n">
-        <v>207.659916851811</v>
+        <v>215.3069232717918</v>
       </c>
       <c r="C93" t="n">
-        <v>215.2183369488501</v>
+        <v>218.6530960134773</v>
       </c>
       <c r="D93" t="n">
-        <v>207.1678317407877</v>
+        <v>214.6475310263463</v>
       </c>
       <c r="E93" t="n">
-        <v>214.5589447021484</v>
+        <v>215.0313568115234</v>
       </c>
       <c r="F93" t="n">
-        <v>14762900</v>
+        <v>13160000</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B94" t="n">
-        <v>215.3069232717918</v>
+        <v>216.3206133966017</v>
       </c>
       <c r="C94" t="n">
-        <v>218.6530960134773</v>
+        <v>217.7082969855193</v>
       </c>
       <c r="D94" t="n">
-        <v>214.6475310263463</v>
+        <v>214.3916331931512</v>
       </c>
       <c r="E94" t="n">
-        <v>215.0313568115234</v>
+        <v>216.6552276611328</v>
       </c>
       <c r="F94" t="n">
-        <v>13160000</v>
+        <v>6950600</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B95" t="n">
-        <v>216.3206133966017</v>
+        <v>216.7241347564745</v>
       </c>
       <c r="C95" t="n">
-        <v>217.7082969855193</v>
+        <v>218.5153167809881</v>
       </c>
       <c r="D95" t="n">
-        <v>214.3916331931512</v>
+        <v>216.5174523988691</v>
       </c>
       <c r="E95" t="n">
-        <v>216.6552276611328</v>
+        <v>217.9838714599609</v>
       </c>
       <c r="F95" t="n">
-        <v>6950600</v>
+        <v>6856700</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B96" t="n">
-        <v>216.7241195858665</v>
+        <v>218.4857986661137</v>
       </c>
       <c r="C96" t="n">
-        <v>218.515301484998</v>
+        <v>221.9303945910299</v>
       </c>
       <c r="D96" t="n">
-        <v>216.5174372427288</v>
+        <v>217.2063743191241</v>
       </c>
       <c r="E96" t="n">
-        <v>217.9838562011719</v>
+        <v>220.8871765136719</v>
       </c>
       <c r="F96" t="n">
-        <v>6856700</v>
+        <v>8154100</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B97" t="n">
-        <v>218.4857835732108</v>
+        <v>222.8161377007139</v>
       </c>
       <c r="C97" t="n">
-        <v>221.9303792601758</v>
+        <v>224.9518003498371</v>
       </c>
       <c r="D97" t="n">
-        <v>217.2063593146032</v>
+        <v>222.5012110309432</v>
       </c>
       <c r="E97" t="n">
-        <v>220.8871612548828</v>
+        <v>224.1152496337891</v>
       </c>
       <c r="F97" t="n">
-        <v>8154100</v>
+        <v>9026500</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B98" t="n">
-        <v>222.8161377007139</v>
+        <v>225.1879747271155</v>
       </c>
       <c r="C98" t="n">
-        <v>224.9518003498371</v>
+        <v>226.3591396349424</v>
       </c>
       <c r="D98" t="n">
-        <v>222.5012110309432</v>
+        <v>223.4853645338204</v>
       </c>
       <c r="E98" t="n">
-        <v>224.1152496337891</v>
+        <v>223.6920318603516</v>
       </c>
       <c r="F98" t="n">
-        <v>9026500</v>
+        <v>9645300</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B99" t="n">
-        <v>225.1879747271155</v>
+        <v>224.6466859457881</v>
       </c>
       <c r="C99" t="n">
-        <v>226.3591396349424</v>
+        <v>224.8828922015737</v>
       </c>
       <c r="D99" t="n">
-        <v>223.4853645338204</v>
+        <v>221.7630744488117</v>
       </c>
       <c r="E99" t="n">
-        <v>223.6920318603516</v>
+        <v>223.6526794433594</v>
       </c>
       <c r="F99" t="n">
-        <v>9645300</v>
+        <v>11045500</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B100" t="n">
-        <v>224.6466706191826</v>
+        <v>224.7057483906486</v>
       </c>
       <c r="C100" t="n">
-        <v>224.8828768588529</v>
+        <v>227.530312073188</v>
       </c>
       <c r="D100" t="n">
-        <v>221.7630593189417</v>
+        <v>223.6526790631295</v>
       </c>
       <c r="E100" t="n">
-        <v>223.6526641845703</v>
+        <v>227.0972747802734</v>
       </c>
       <c r="F100" t="n">
-        <v>11045500</v>
+        <v>8187500</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B101" t="n">
-        <v>224.7057634887497</v>
+        <v>227.8353864728449</v>
       </c>
       <c r="C101" t="n">
-        <v>227.530327361073</v>
+        <v>231.4768129724177</v>
       </c>
       <c r="D101" t="n">
-        <v>223.6526940904743</v>
+        <v>226.8315287293456</v>
       </c>
       <c r="E101" t="n">
-        <v>227.0972900390625</v>
+        <v>229.4100646972656</v>
       </c>
       <c r="F101" t="n">
-        <v>8187500</v>
+        <v>9346600</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B102" t="n">
-        <v>227.8354016268972</v>
+        <v>231.2800013484118</v>
       </c>
       <c r="C102" t="n">
-        <v>231.4768283686728</v>
+        <v>232.0968644318395</v>
       </c>
       <c r="D102" t="n">
-        <v>226.8315438166281</v>
+        <v>229.2526131010531</v>
       </c>
       <c r="E102" t="n">
-        <v>229.4100799560547</v>
+        <v>230.7583923339844</v>
       </c>
       <c r="F102" t="n">
-        <v>9346600</v>
+        <v>8641400</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B103" t="n">
-        <v>231.2799860551316</v>
+        <v>231.2799897072634</v>
       </c>
       <c r="C103" t="n">
-        <v>232.0968490845446</v>
+        <v>235.787490883202</v>
       </c>
       <c r="D103" t="n">
-        <v>229.252597941833</v>
+        <v>231.2701534117819</v>
       </c>
       <c r="E103" t="n">
-        <v>230.7583770751953</v>
+        <v>234.0258178710938</v>
       </c>
       <c r="F103" t="n">
-        <v>8641400</v>
+        <v>10267500</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B104" t="n">
-        <v>231.2799897072634</v>
+        <v>235.1773154262319</v>
       </c>
       <c r="C104" t="n">
-        <v>235.787490883202</v>
+        <v>237.125968199395</v>
       </c>
       <c r="D104" t="n">
-        <v>231.2701534117819</v>
+        <v>234.2128178267284</v>
       </c>
       <c r="E104" t="n">
-        <v>234.0258178710938</v>
+        <v>236.1910095214844</v>
       </c>
       <c r="F104" t="n">
-        <v>10267500</v>
+        <v>8274000</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B105" t="n">
-        <v>235.1773154262319</v>
+        <v>236.4468956382332</v>
       </c>
       <c r="C105" t="n">
-        <v>237.125968199395</v>
+        <v>236.9291444528193</v>
       </c>
       <c r="D105" t="n">
-        <v>234.2128178267284</v>
+        <v>233.2877026206608</v>
       </c>
       <c r="E105" t="n">
-        <v>236.1910095214844</v>
+        <v>234.8623809814453</v>
       </c>
       <c r="F105" t="n">
-        <v>8274000</v>
+        <v>9378500</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B106" t="n">
-        <v>236.4468802764997</v>
+        <v>236.1811678557945</v>
       </c>
       <c r="C106" t="n">
-        <v>236.9291290597546</v>
+        <v>236.6929405807981</v>
       </c>
       <c r="D106" t="n">
-        <v>233.2876874641771</v>
+        <v>234.1144193808212</v>
       </c>
       <c r="E106" t="n">
-        <v>234.8623657226562</v>
+        <v>234.5769805908203</v>
       </c>
       <c r="F106" t="n">
-        <v>9378500</v>
+        <v>6723300</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B107" t="n">
-        <v>236.1811678557945</v>
+        <v>235.5512982627408</v>
       </c>
       <c r="C107" t="n">
-        <v>236.6929405807981</v>
+        <v>237.4409032943991</v>
       </c>
       <c r="D107" t="n">
-        <v>234.1144193808212</v>
+        <v>233.6420056217357</v>
       </c>
       <c r="E107" t="n">
-        <v>234.5769805908203</v>
+        <v>237.0472412109375</v>
       </c>
       <c r="F107" t="n">
-        <v>6723300</v>
+        <v>6803900</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B108" t="n">
-        <v>235.5512982627408</v>
+        <v>236.6732529591429</v>
       </c>
       <c r="C108" t="n">
-        <v>237.4409032943991</v>
+        <v>242.4503424271597</v>
       </c>
       <c r="D108" t="n">
-        <v>233.6420056217357</v>
+        <v>235.8859137708501</v>
       </c>
       <c r="E108" t="n">
-        <v>237.0472412109375</v>
+        <v>240.6788330078125</v>
       </c>
       <c r="F108" t="n">
-        <v>6803900</v>
+        <v>10254300</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B109" t="n">
-        <v>236.6732379543034</v>
+        <v>240.7181753030812</v>
       </c>
       <c r="C109" t="n">
-        <v>242.4503270560588</v>
+        <v>241.0724771605951</v>
       </c>
       <c r="D109" t="n">
-        <v>235.8858988159272</v>
+        <v>238.7695225953774</v>
       </c>
       <c r="E109" t="n">
-        <v>240.6788177490234</v>
+        <v>239.5962219238281</v>
       </c>
       <c r="F109" t="n">
-        <v>10254300</v>
+        <v>13268500</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B110" t="n">
-        <v>240.7181906333224</v>
+        <v>240.2654886197458</v>
       </c>
       <c r="C110" t="n">
-        <v>241.0724925134001</v>
+        <v>240.6197905114409</v>
       </c>
       <c r="D110" t="n">
-        <v>238.7695378015177</v>
+        <v>238.0412542373971</v>
       </c>
       <c r="E110" t="n">
-        <v>239.5962371826172</v>
+        <v>239.4781494140625</v>
       </c>
       <c r="F110" t="n">
-        <v>13268500</v>
+        <v>12703000</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B111" t="n">
-        <v>240.2654733107899</v>
+        <v>239.389564336343</v>
       </c>
       <c r="C111" t="n">
-        <v>240.6197751799101</v>
+        <v>241.1905976005163</v>
       </c>
       <c r="D111" t="n">
-        <v>238.0412390701625</v>
+        <v>238.9762146553066</v>
       </c>
       <c r="E111" t="n">
-        <v>239.4781341552734</v>
+        <v>241.1118621826172</v>
       </c>
       <c r="F111" t="n">
-        <v>12703000</v>
+        <v>8129700</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B112" t="n">
-        <v>239.389564336343</v>
+        <v>240.7477218197236</v>
       </c>
       <c r="C112" t="n">
-        <v>241.1905976005163</v>
+        <v>243.0506916185027</v>
       </c>
       <c r="D112" t="n">
-        <v>238.9762146553066</v>
+        <v>240.4032712424708</v>
       </c>
       <c r="E112" t="n">
-        <v>241.1118621826172</v>
+        <v>243.0014801025391</v>
       </c>
       <c r="F112" t="n">
-        <v>8129700</v>
+        <v>7553900</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B113" t="n">
-        <v>240.7477067024548</v>
+        <v>242.5684367756451</v>
       </c>
       <c r="C113" t="n">
-        <v>243.0506763566235</v>
+        <v>242.9719501723976</v>
       </c>
       <c r="D113" t="n">
-        <v>240.4032561468311</v>
+        <v>236.4764206746478</v>
       </c>
       <c r="E113" t="n">
-        <v>243.00146484375</v>
+        <v>238.6514434814453</v>
       </c>
       <c r="F113" t="n">
-        <v>7553900</v>
+        <v>13565800</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B114" t="n">
-        <v>242.568421266413</v>
+        <v>239.7734021969262</v>
       </c>
       <c r="C114" t="n">
-        <v>242.9719346373659</v>
+        <v>242.9030563756065</v>
       </c>
       <c r="D114" t="n">
-        <v>236.4764055549244</v>
+        <v>238.7597080434106</v>
       </c>
       <c r="E114" t="n">
-        <v>238.6514282226562</v>
+        <v>241.9484100341797</v>
       </c>
       <c r="F114" t="n">
-        <v>13565800</v>
+        <v>9622700</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,25 +3407,25 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B115" t="n">
-        <v>239.7734021969262</v>
+        <v>242.7498156695138</v>
       </c>
       <c r="C115" t="n">
-        <v>242.9030563756065</v>
+        <v>244.6296736547229</v>
       </c>
       <c r="D115" t="n">
-        <v>238.7597080434106</v>
+        <v>241.9483872724562</v>
       </c>
       <c r="E115" t="n">
-        <v>241.9484100341797</v>
+        <v>243.6699523925781</v>
       </c>
       <c r="F115" t="n">
-        <v>9622700</v>
+        <v>7246300</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -3433,25 +3433,25 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B116" t="n">
-        <v>242.7498308706833</v>
+        <v>242.2650040664713</v>
       </c>
       <c r="C116" t="n">
-        <v>244.6296889736104</v>
+        <v>244.629674532896</v>
       </c>
       <c r="D116" t="n">
-        <v>241.9484024234396</v>
+        <v>241.1370862518812</v>
       </c>
       <c r="E116" t="n">
-        <v>243.6699676513672</v>
+        <v>242.5717163085938</v>
       </c>
       <c r="F116" t="n">
-        <v>7246300</v>
+        <v>7698200</v>
       </c>
       <c r="G116" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B117" t="n">
-        <v>242.2650193059668</v>
+        <v>242.5123588943122</v>
       </c>
       <c r="C117" t="n">
-        <v>244.6296899211394</v>
+        <v>242.8685442682355</v>
       </c>
       <c r="D117" t="n">
-        <v>241.1371014204259</v>
+        <v>239.4551099080992</v>
       </c>
       <c r="E117" t="n">
-        <v>242.5717315673828</v>
+        <v>240.8897399902344</v>
       </c>
       <c r="F117" t="n">
-        <v>7698200</v>
+        <v>7172600</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B118" t="n">
-        <v>242.5123742558835</v>
+        <v>241.4438165545137</v>
       </c>
       <c r="C118" t="n">
-        <v>242.8685596523689</v>
+        <v>246.3017849576054</v>
       </c>
       <c r="D118" t="n">
-        <v>239.4551250760139</v>
+        <v>239.9300324032001</v>
       </c>
       <c r="E118" t="n">
-        <v>240.8897552490234</v>
+        <v>245.7971801757812</v>
       </c>
       <c r="F118" t="n">
-        <v>7172600</v>
+        <v>16428600</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B119" t="n">
-        <v>241.4438165545137</v>
+        <v>246.549124695673</v>
       </c>
       <c r="C119" t="n">
-        <v>246.3017849576054</v>
+        <v>249.0424223461303</v>
       </c>
       <c r="D119" t="n">
-        <v>239.9300324032001</v>
+        <v>244.2537044562187</v>
       </c>
       <c r="E119" t="n">
-        <v>245.7971801757812</v>
+        <v>245.9257965087891</v>
       </c>
       <c r="F119" t="n">
-        <v>16428600</v>
+        <v>9042400</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B120" t="n">
-        <v>246.549124695673</v>
+        <v>243.8480592687475</v>
       </c>
       <c r="C120" t="n">
-        <v>249.0424223461303</v>
+        <v>245.2530085028214</v>
       </c>
       <c r="D120" t="n">
-        <v>244.2537044562187</v>
+        <v>241.7703087256774</v>
       </c>
       <c r="E120" t="n">
-        <v>245.9257965087891</v>
+        <v>244.1349792480469</v>
       </c>
       <c r="F120" t="n">
-        <v>9042400</v>
+        <v>6178700</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B121" t="n">
-        <v>243.8480592687475</v>
+        <v>243.145575843863</v>
       </c>
       <c r="C121" t="n">
-        <v>245.2530085028214</v>
+        <v>243.9568928450567</v>
       </c>
       <c r="D121" t="n">
-        <v>241.7703087256774</v>
+        <v>240.6028050981046</v>
       </c>
       <c r="E121" t="n">
-        <v>244.1349792480469</v>
+        <v>242.7003479003906</v>
       </c>
       <c r="F121" t="n">
-        <v>6178700</v>
+        <v>5768000</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B122" t="n">
-        <v>243.1455911306439</v>
+        <v>240.0586452528019</v>
       </c>
       <c r="C122" t="n">
-        <v>243.9569081828458</v>
+        <v>240.424719212307</v>
       </c>
       <c r="D122" t="n">
-        <v>240.6028202250193</v>
+        <v>233.4296388594088</v>
       </c>
       <c r="E122" t="n">
-        <v>242.7003631591797</v>
+        <v>237.0904388427734</v>
       </c>
       <c r="F122" t="n">
-        <v>5768000</v>
+        <v>9375400</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B123" t="n">
-        <v>240.0586607026203</v>
+        <v>235.596428770922</v>
       </c>
       <c r="C123" t="n">
-        <v>240.4247346856854</v>
+        <v>238.2381306285037</v>
       </c>
       <c r="D123" t="n">
-        <v>233.4296538825942</v>
+        <v>232.9349346436922</v>
       </c>
       <c r="E123" t="n">
-        <v>237.0904541015625</v>
+        <v>237.8522644042969</v>
       </c>
       <c r="F123" t="n">
-        <v>9375400</v>
+        <v>7179800</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B124" t="n">
-        <v>235.5964438849938</v>
+        <v>238.3173005129137</v>
       </c>
       <c r="C124" t="n">
-        <v>238.238145912047</v>
+        <v>241.5031767703235</v>
       </c>
       <c r="D124" t="n">
-        <v>232.9349495870229</v>
+        <v>237.4960948841201</v>
       </c>
       <c r="E124" t="n">
-        <v>237.8522796630859</v>
+        <v>240.0190734863281</v>
       </c>
       <c r="F124" t="n">
-        <v>7179800</v>
+        <v>7844000</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B125" t="n">
-        <v>238.3172853623119</v>
+        <v>239.732151823879</v>
       </c>
       <c r="C125" t="n">
-        <v>241.5031614171852</v>
+        <v>242.4035346970428</v>
       </c>
       <c r="D125" t="n">
-        <v>237.496079785725</v>
+        <v>238.2678408210546</v>
       </c>
       <c r="E125" t="n">
-        <v>240.0190582275391</v>
+        <v>241.1272125244141</v>
       </c>
       <c r="F125" t="n">
-        <v>7844000</v>
+        <v>7214100</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B126" t="n">
-        <v>239.732151823879</v>
+        <v>240.2960869196001</v>
       </c>
       <c r="C126" t="n">
-        <v>242.4035346970428</v>
+        <v>241.1074039007698</v>
       </c>
       <c r="D126" t="n">
-        <v>238.2678408210546</v>
+        <v>238.802095160397</v>
       </c>
       <c r="E126" t="n">
-        <v>241.1272125244141</v>
+        <v>240.4148254394531</v>
       </c>
       <c r="F126" t="n">
-        <v>7214100</v>
+        <v>6933200</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B127" t="n">
-        <v>240.2960869196001</v>
+        <v>238.9010593075404</v>
       </c>
       <c r="C127" t="n">
-        <v>241.1074039007698</v>
+        <v>241.8098890629796</v>
       </c>
       <c r="D127" t="n">
-        <v>238.802095160397</v>
+        <v>237.7533491444783</v>
       </c>
       <c r="E127" t="n">
-        <v>240.4148254394531</v>
+        <v>239.4748992919922</v>
       </c>
       <c r="F127" t="n">
-        <v>6933200</v>
+        <v>7710200</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B128" t="n">
-        <v>238.9010440853151</v>
+        <v>241.6219129804633</v>
       </c>
       <c r="C128" t="n">
-        <v>241.8098736554103</v>
+        <v>242.9872777226232</v>
       </c>
       <c r="D128" t="n">
-        <v>237.7533339953824</v>
+        <v>238.940626430393</v>
       </c>
       <c r="E128" t="n">
-        <v>239.4748840332031</v>
+        <v>238.9604187011719</v>
       </c>
       <c r="F128" t="n">
-        <v>7710200</v>
+        <v>6415300</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B129" t="n">
-        <v>241.6218975517249</v>
+        <v>241.3349760333344</v>
       </c>
       <c r="C129" t="n">
-        <v>242.9872622066995</v>
+        <v>242.4628939057684</v>
       </c>
       <c r="D129" t="n">
-        <v>238.9406111728678</v>
+        <v>239.1088211458664</v>
       </c>
       <c r="E129" t="n">
-        <v>238.9604034423828</v>
+        <v>240.6127166748047</v>
       </c>
       <c r="F129" t="n">
-        <v>6415300</v>
+        <v>7571500</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B130" t="n">
-        <v>241.3349607287423</v>
+        <v>240.99857884995</v>
       </c>
       <c r="C130" t="n">
-        <v>242.4628785296478</v>
+        <v>241.5526416415011</v>
       </c>
       <c r="D130" t="n">
-        <v>239.1088059824489</v>
+        <v>234.7059805370448</v>
       </c>
       <c r="E130" t="n">
-        <v>240.6127014160156</v>
+        <v>235.5865478515625</v>
       </c>
       <c r="F130" t="n">
-        <v>7571500</v>
+        <v>7281800</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B131" t="n">
-        <v>240.99857884995</v>
+        <v>235.349094010365</v>
       </c>
       <c r="C131" t="n">
-        <v>241.5526416415011</v>
+        <v>236.5759581604242</v>
       </c>
       <c r="D131" t="n">
-        <v>234.7059805370448</v>
+        <v>232.9250616652477</v>
       </c>
       <c r="E131" t="n">
-        <v>235.5865478515625</v>
+        <v>234.7653503417969</v>
       </c>
       <c r="F131" t="n">
-        <v>7281800</v>
+        <v>6811500</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B132" t="n">
-        <v>235.349078713635</v>
+        <v>235.814102878936</v>
       </c>
       <c r="C132" t="n">
-        <v>236.5759427839531</v>
+        <v>236.7243510378414</v>
       </c>
       <c r="D132" t="n">
-        <v>232.9250465260699</v>
+        <v>233.80561773863</v>
       </c>
       <c r="E132" t="n">
-        <v>234.7653350830078</v>
+        <v>235.0819549560547</v>
       </c>
       <c r="F132" t="n">
-        <v>6811500</v>
+        <v>7511500</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B133" t="n">
-        <v>235.814102878936</v>
+        <v>234.3201136195421</v>
       </c>
       <c r="C133" t="n">
-        <v>236.7243510378414</v>
+        <v>235.764632308021</v>
       </c>
       <c r="D133" t="n">
-        <v>233.80561773863</v>
+        <v>232.0148047922595</v>
       </c>
       <c r="E133" t="n">
-        <v>235.0819549560547</v>
+        <v>232.8755798339844</v>
       </c>
       <c r="F133" t="n">
-        <v>7511500</v>
+        <v>17156600</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B134" t="n">
-        <v>234.3201136195421</v>
+        <v>234.884060828395</v>
       </c>
       <c r="C134" t="n">
-        <v>235.764632308021</v>
+        <v>235.7844203946137</v>
       </c>
       <c r="D134" t="n">
-        <v>232.0148047922595</v>
+        <v>231.7674501417346</v>
       </c>
       <c r="E134" t="n">
-        <v>232.8755798339844</v>
+        <v>232.925048828125</v>
       </c>
       <c r="F134" t="n">
-        <v>17156600</v>
+        <v>7313700</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B135" t="n">
-        <v>234.884060828395</v>
+        <v>231.6586126149741</v>
       </c>
       <c r="C135" t="n">
-        <v>235.7844203946137</v>
+        <v>233.4989011687466</v>
       </c>
       <c r="D135" t="n">
-        <v>231.7674501417346</v>
+        <v>229.7787546189723</v>
       </c>
       <c r="E135" t="n">
-        <v>232.925048828125</v>
+        <v>232.7766418457031</v>
       </c>
       <c r="F135" t="n">
-        <v>7313700</v>
+        <v>9046200</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B136" t="n">
-        <v>231.6586126149741</v>
+        <v>234.2904343153693</v>
       </c>
       <c r="C136" t="n">
-        <v>233.4989011687466</v>
+        <v>238.9010520004889</v>
       </c>
       <c r="D136" t="n">
-        <v>229.7787546189723</v>
+        <v>233.2317667584392</v>
       </c>
       <c r="E136" t="n">
-        <v>232.7766418457031</v>
+        <v>237.3872528076172</v>
       </c>
       <c r="F136" t="n">
-        <v>9046200</v>
+        <v>6456400</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B137" t="n">
-        <v>234.2904343153693</v>
+        <v>237.4565300874115</v>
       </c>
       <c r="C137" t="n">
-        <v>238.9010520004889</v>
+        <v>239.0890376929306</v>
       </c>
       <c r="D137" t="n">
-        <v>233.2317667584392</v>
+        <v>236.3978624775069</v>
       </c>
       <c r="E137" t="n">
-        <v>237.3872528076172</v>
+        <v>236.70458984375</v>
       </c>
       <c r="F137" t="n">
-        <v>6456400</v>
+        <v>5171400</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B138" t="n">
-        <v>237.4565300874115</v>
+        <v>238.6339116976677</v>
       </c>
       <c r="C138" t="n">
-        <v>239.0890376929306</v>
+        <v>240.1081112682183</v>
       </c>
       <c r="D138" t="n">
-        <v>236.3978624775069</v>
+        <v>236.5957456438558</v>
       </c>
       <c r="E138" t="n">
-        <v>236.70458984375</v>
+        <v>237.9017486572266</v>
       </c>
       <c r="F138" t="n">
-        <v>5171400</v>
+        <v>7617600</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B139" t="n">
-        <v>238.6339116976677</v>
+        <v>240.9095376592209</v>
       </c>
       <c r="C139" t="n">
-        <v>240.1081112682183</v>
+        <v>241.6219084230326</v>
       </c>
       <c r="D139" t="n">
-        <v>236.5957456438558</v>
+        <v>237.9611083490254</v>
       </c>
       <c r="E139" t="n">
-        <v>237.9017486572266</v>
+        <v>239.9201354980469</v>
       </c>
       <c r="F139" t="n">
-        <v>7617600</v>
+        <v>7241300</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B140" t="n">
-        <v>240.9095376592209</v>
+        <v>240.4346190736229</v>
       </c>
       <c r="C140" t="n">
-        <v>241.6219084230326</v>
+        <v>242.7300393849503</v>
       </c>
       <c r="D140" t="n">
-        <v>237.9611083490254</v>
+        <v>240.0784336838334</v>
       </c>
       <c r="E140" t="n">
-        <v>239.9201354980469</v>
+        <v>241.8494720458984</v>
       </c>
       <c r="F140" t="n">
-        <v>7241300</v>
+        <v>7554200</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B141" t="n">
-        <v>240.4346190736229</v>
+        <v>242.9971782498834</v>
       </c>
       <c r="C141" t="n">
-        <v>242.7300393849503</v>
+        <v>244.580212658809</v>
       </c>
       <c r="D141" t="n">
-        <v>240.0784336838334</v>
+        <v>241.1568896154117</v>
       </c>
       <c r="E141" t="n">
-        <v>241.8494720458984</v>
+        <v>241.5328521728516</v>
       </c>
       <c r="F141" t="n">
-        <v>7554200</v>
+        <v>6314600</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B142" t="n">
-        <v>242.9971782498834</v>
+        <v>242.5123641523277</v>
       </c>
       <c r="C142" t="n">
-        <v>244.580212658809</v>
+        <v>244.5901147281089</v>
       </c>
       <c r="D142" t="n">
-        <v>241.1568896154117</v>
+        <v>239.3066957175141</v>
       </c>
       <c r="E142" t="n">
-        <v>241.5328521728516</v>
+        <v>240.4642944335938</v>
       </c>
       <c r="F142" t="n">
-        <v>6314600</v>
+        <v>6878700</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B143" t="n">
-        <v>242.5123641523277</v>
+        <v>240.0784329225297</v>
       </c>
       <c r="C143" t="n">
-        <v>244.5901147281089</v>
+        <v>240.9392230850874</v>
       </c>
       <c r="D143" t="n">
-        <v>239.3066957175141</v>
+        <v>237.9512242744999</v>
       </c>
       <c r="E143" t="n">
-        <v>240.4642944335938</v>
+        <v>238.4162445068359</v>
       </c>
       <c r="F143" t="n">
-        <v>6878700</v>
+        <v>4442400</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B144" t="n">
-        <v>240.0784175573595</v>
+        <v>238.2282554079276</v>
       </c>
       <c r="C144" t="n">
-        <v>240.9392076648261</v>
+        <v>238.2282554079276</v>
       </c>
       <c r="D144" t="n">
-        <v>237.9512090454724</v>
+        <v>233.5088027877857</v>
       </c>
       <c r="E144" t="n">
-        <v>238.4162292480469</v>
+        <v>235.8833770751953</v>
       </c>
       <c r="F144" t="n">
-        <v>4442400</v>
+        <v>6241100</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B145" t="n">
-        <v>238.2282554079276</v>
+        <v>234.1321342347395</v>
       </c>
       <c r="C145" t="n">
-        <v>238.2282554079276</v>
+        <v>238.7724329332046</v>
       </c>
       <c r="D145" t="n">
-        <v>233.5088027877857</v>
+        <v>231.4211667922781</v>
       </c>
       <c r="E145" t="n">
-        <v>235.8833770751953</v>
+        <v>238.7427520751953</v>
       </c>
       <c r="F145" t="n">
-        <v>6241100</v>
+        <v>8771100</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B146" t="n">
-        <v>234.1321342347395</v>
+        <v>238.7427511835681</v>
       </c>
       <c r="C146" t="n">
-        <v>238.7724329332046</v>
+        <v>241.612011492337</v>
       </c>
       <c r="D146" t="n">
-        <v>231.4211667922781</v>
+        <v>237.9907958579282</v>
       </c>
       <c r="E146" t="n">
-        <v>238.7427520751953</v>
+        <v>238.7526397705078</v>
       </c>
       <c r="F146" t="n">
-        <v>8771100</v>
+        <v>6216500</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B147" t="n">
-        <v>238.7427511835681</v>
+        <v>239.4353230782619</v>
       </c>
       <c r="C147" t="n">
-        <v>241.612011492337</v>
+        <v>239.6925622052984</v>
       </c>
       <c r="D147" t="n">
-        <v>237.9907958579282</v>
+        <v>235.3886718611059</v>
       </c>
       <c r="E147" t="n">
-        <v>238.7526397705078</v>
+        <v>235.9328460693359</v>
       </c>
       <c r="F147" t="n">
-        <v>6216500</v>
+        <v>7354500</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B148" t="n">
-        <v>239.4353230782619</v>
+        <v>235.1907903330984</v>
       </c>
       <c r="C148" t="n">
-        <v>239.6925622052984</v>
+        <v>235.8635765445355</v>
       </c>
       <c r="D148" t="n">
-        <v>235.3886718611059</v>
+        <v>232.6875890190388</v>
       </c>
       <c r="E148" t="n">
-        <v>235.9328460693359</v>
+        <v>235.4381408691406</v>
       </c>
       <c r="F148" t="n">
-        <v>7354500</v>
+        <v>7663600</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B149" t="n">
-        <v>235.1907903330984</v>
+        <v>232.5193972079424</v>
       </c>
       <c r="C149" t="n">
-        <v>235.8635765445355</v>
+        <v>239.6233125984258</v>
       </c>
       <c r="D149" t="n">
-        <v>232.6875890190388</v>
+        <v>230.7780548336423</v>
       </c>
       <c r="E149" t="n">
-        <v>235.4381408691406</v>
+        <v>237.5554656982422</v>
       </c>
       <c r="F149" t="n">
-        <v>7663600</v>
+        <v>10318700</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B150" t="n">
-        <v>232.5193972079424</v>
+        <v>237.3971547010872</v>
       </c>
       <c r="C150" t="n">
-        <v>239.6233125984258</v>
+        <v>237.8720635067345</v>
       </c>
       <c r="D150" t="n">
-        <v>230.7780548336423</v>
+        <v>234.2409594215431</v>
       </c>
       <c r="E150" t="n">
-        <v>237.5554656982422</v>
+        <v>236.1406097412109</v>
       </c>
       <c r="F150" t="n">
-        <v>10318700</v>
+        <v>6463500</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B151" t="n">
-        <v>237.3971547010872</v>
+        <v>234.9038500080299</v>
       </c>
       <c r="C151" t="n">
-        <v>237.8720635067345</v>
+        <v>235.6162207436799</v>
       </c>
       <c r="D151" t="n">
-        <v>234.2409594215431</v>
+        <v>229.6600157416919</v>
       </c>
       <c r="E151" t="n">
-        <v>236.1406097412109</v>
+        <v>232.0543670654297</v>
       </c>
       <c r="F151" t="n">
-        <v>6463500</v>
+        <v>8668900</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B152" t="n">
-        <v>234.9038654541874</v>
+        <v>231.8762966548944</v>
       </c>
       <c r="C152" t="n">
-        <v>235.6162362366795</v>
+        <v>233.0437839864675</v>
       </c>
       <c r="D152" t="n">
-        <v>229.6600308430398</v>
+        <v>229.5808763393496</v>
       </c>
       <c r="E152" t="n">
-        <v>232.0543823242188</v>
+        <v>231.6981964111328</v>
       </c>
       <c r="F152" t="n">
-        <v>8668900</v>
+        <v>8946300</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B153" t="n">
-        <v>231.8762966548944</v>
+        <v>232.321525670587</v>
       </c>
       <c r="C153" t="n">
-        <v>233.0437839864675</v>
+        <v>232.7667536363879</v>
       </c>
       <c r="D153" t="n">
-        <v>229.5808763393496</v>
+        <v>227.0974833184763</v>
       </c>
       <c r="E153" t="n">
-        <v>231.6981964111328</v>
+        <v>228.2451934814453</v>
       </c>
       <c r="F153" t="n">
-        <v>8946300</v>
+        <v>7810500</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B154" t="n">
-        <v>232.321525670587</v>
+        <v>226.9193941968888</v>
       </c>
       <c r="C154" t="n">
-        <v>232.7667536363879</v>
+        <v>227.2557873120845</v>
       </c>
       <c r="D154" t="n">
-        <v>227.0974833184763</v>
+        <v>222.3186650386415</v>
       </c>
       <c r="E154" t="n">
-        <v>228.2451934814453</v>
+        <v>223.7631988525391</v>
       </c>
       <c r="F154" t="n">
-        <v>7810500</v>
+        <v>11681200</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B155" t="n">
-        <v>226.9193787228735</v>
+        <v>223.7829810531976</v>
       </c>
       <c r="C155" t="n">
-        <v>227.2557718151299</v>
+        <v>225.0692069251634</v>
       </c>
       <c r="D155" t="n">
-        <v>222.3186498783577</v>
+        <v>221.4084218257834</v>
       </c>
       <c r="E155" t="n">
-        <v>223.76318359375</v>
+        <v>223.7038421630859</v>
       </c>
       <c r="F155" t="n">
-        <v>11681200</v>
+        <v>9003400</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B156" t="n">
-        <v>223.7829810531976</v>
+        <v>224.8416356959219</v>
       </c>
       <c r="C156" t="n">
-        <v>225.0692069251634</v>
+        <v>228.9377599403605</v>
       </c>
       <c r="D156" t="n">
-        <v>221.4084218257834</v>
+        <v>224.6239660179549</v>
       </c>
       <c r="E156" t="n">
-        <v>223.7038421630859</v>
+        <v>228.2055969238281</v>
       </c>
       <c r="F156" t="n">
-        <v>9003400</v>
+        <v>7097600</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B157" t="n">
-        <v>224.8416507297823</v>
+        <v>226.6027887018479</v>
       </c>
       <c r="C157" t="n">
-        <v>228.937775248105</v>
+        <v>227.5526214735122</v>
       </c>
       <c r="D157" t="n">
-        <v>224.623981037261</v>
+        <v>224.6140956793093</v>
       </c>
       <c r="E157" t="n">
-        <v>228.2056121826172</v>
+        <v>225.0890045166016</v>
       </c>
       <c r="F157" t="n">
-        <v>7097600</v>
+        <v>6067500</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B158" t="n">
-        <v>226.6027733404394</v>
+        <v>223.3773245484034</v>
       </c>
       <c r="C158" t="n">
-        <v>227.5526060477145</v>
+        <v>225.4946445162854</v>
       </c>
       <c r="D158" t="n">
-        <v>224.6140804527143</v>
+        <v>221.9723753264516</v>
       </c>
       <c r="E158" t="n">
-        <v>225.0889892578125</v>
+        <v>222.9518737792969</v>
       </c>
       <c r="F158" t="n">
-        <v>6067500</v>
+        <v>7897800</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B159" t="n">
-        <v>223.3773398363102</v>
+        <v>225.316553812185</v>
       </c>
       <c r="C159" t="n">
-        <v>225.4946599491012</v>
+        <v>228.5815840196301</v>
       </c>
       <c r="D159" t="n">
-        <v>221.972390518204</v>
+        <v>223.9709662459624</v>
       </c>
       <c r="E159" t="n">
-        <v>222.9518890380859</v>
+        <v>225.3759155273438</v>
       </c>
       <c r="F159" t="n">
-        <v>7897800</v>
+        <v>7179800</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B160" t="n">
-        <v>225.316553812185</v>
+        <v>223.1299896858621</v>
       </c>
       <c r="C160" t="n">
-        <v>228.5815840196301</v>
+        <v>226.2861851379911</v>
       </c>
       <c r="D160" t="n">
-        <v>223.9709662459624</v>
+        <v>222.4769806067155</v>
       </c>
       <c r="E160" t="n">
-        <v>225.3759155273438</v>
+        <v>224.9405975341797</v>
       </c>
       <c r="F160" t="n">
-        <v>7179800</v>
+        <v>7071100</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B161" t="n">
-        <v>223.1299745498951</v>
+        <v>225.534219851175</v>
       </c>
       <c r="C161" t="n">
-        <v>226.2861697879244</v>
+        <v>228.7102074345108</v>
       </c>
       <c r="D161" t="n">
-        <v>222.4769655150452</v>
+        <v>225.3957041523519</v>
       </c>
       <c r="E161" t="n">
-        <v>224.9405822753906</v>
+        <v>227.4140930175781</v>
       </c>
       <c r="F161" t="n">
-        <v>7071100</v>
+        <v>8157200</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B162" t="n">
-        <v>225.534219851175</v>
+        <v>226.6324494909732</v>
       </c>
       <c r="C162" t="n">
-        <v>228.7102074345108</v>
+        <v>227.3349316460146</v>
       </c>
       <c r="D162" t="n">
-        <v>225.3957041523519</v>
+        <v>224.6140757884101</v>
       </c>
       <c r="E162" t="n">
-        <v>227.4140930175781</v>
+        <v>224.7822723388672</v>
       </c>
       <c r="F162" t="n">
-        <v>8157200</v>
+        <v>6863600</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B163" t="n">
-        <v>226.6324494909732</v>
+        <v>223.12007375354</v>
       </c>
       <c r="C163" t="n">
-        <v>227.3349316460146</v>
+        <v>224.6635537914519</v>
       </c>
       <c r="D163" t="n">
-        <v>224.6140757884101</v>
+        <v>221.2105348477109</v>
       </c>
       <c r="E163" t="n">
-        <v>224.7822723388672</v>
+        <v>221.8239593505859</v>
       </c>
       <c r="F163" t="n">
-        <v>6863600</v>
+        <v>8215200</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B164" t="n">
-        <v>223.12007375354</v>
+        <v>223.0013599943453</v>
       </c>
       <c r="C164" t="n">
-        <v>224.6635537914519</v>
+        <v>224.1292778920903</v>
       </c>
       <c r="D164" t="n">
-        <v>221.2105348477109</v>
+        <v>222.5165474841354</v>
       </c>
       <c r="E164" t="n">
-        <v>221.8239593505859</v>
+        <v>223.15966796875</v>
       </c>
       <c r="F164" t="n">
-        <v>8215200</v>
+        <v>5556700</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B165" t="n">
-        <v>223.0013599943453</v>
+        <v>222.86284542864</v>
       </c>
       <c r="C165" t="n">
-        <v>224.1292778920903</v>
+        <v>223.9412902027537</v>
       </c>
       <c r="D165" t="n">
-        <v>222.5165474841354</v>
+        <v>220.5872173504634</v>
       </c>
       <c r="E165" t="n">
-        <v>223.15966796875</v>
+        <v>222.2395172119141</v>
       </c>
       <c r="F165" t="n">
-        <v>5556700</v>
+        <v>7982300</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B166" t="n">
-        <v>222.86284542864</v>
+        <v>222.3978024591847</v>
       </c>
       <c r="C166" t="n">
-        <v>223.9412902027537</v>
+        <v>222.3978024591847</v>
       </c>
       <c r="D166" t="n">
-        <v>220.5872173504634</v>
+        <v>218.2917897898664</v>
       </c>
       <c r="E166" t="n">
-        <v>222.2395172119141</v>
+        <v>220.15185546875</v>
       </c>
       <c r="F166" t="n">
-        <v>7982300</v>
+        <v>7269700</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B167" t="n">
-        <v>222.397817873641</v>
+        <v>220.5773139289545</v>
       </c>
       <c r="C167" t="n">
-        <v>222.397817873641</v>
+        <v>221.0027495995129</v>
       </c>
       <c r="D167" t="n">
-        <v>218.2918049197337</v>
+        <v>218.578717393272</v>
       </c>
       <c r="E167" t="n">
-        <v>220.1518707275391</v>
+        <v>218.9744873046875</v>
       </c>
       <c r="F167" t="n">
-        <v>7269700</v>
+        <v>5550600</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B168" t="n">
-        <v>220.5773139289545</v>
+        <v>218.9744932439037</v>
       </c>
       <c r="C168" t="n">
-        <v>221.0027495995129</v>
+        <v>220.9137130226623</v>
       </c>
       <c r="D168" t="n">
-        <v>218.578717393272</v>
+        <v>218.034549114472</v>
       </c>
       <c r="E168" t="n">
-        <v>218.9744873046875</v>
+        <v>219.0833129882812</v>
       </c>
       <c r="F168" t="n">
-        <v>5550600</v>
+        <v>6223200</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B169" t="n">
-        <v>218.9744932439037</v>
+        <v>220.6366899653626</v>
       </c>
       <c r="C169" t="n">
-        <v>220.9137130226623</v>
+        <v>225.2374041432973</v>
       </c>
       <c r="D169" t="n">
-        <v>218.034549114472</v>
+        <v>219.3009909603728</v>
       </c>
       <c r="E169" t="n">
-        <v>219.0833129882812</v>
+        <v>221.8833312988281</v>
       </c>
       <c r="F169" t="n">
-        <v>6223200</v>
+        <v>8632500</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B170" t="n">
-        <v>220.6366747923043</v>
+        <v>223.4268017505994</v>
       </c>
       <c r="C170" t="n">
-        <v>225.2373886538506</v>
+        <v>228.3540202522719</v>
       </c>
       <c r="D170" t="n">
-        <v>219.3009758791698</v>
+        <v>223.0508241008666</v>
       </c>
       <c r="E170" t="n">
-        <v>221.8833160400391</v>
+        <v>227.9780426025391</v>
       </c>
       <c r="F170" t="n">
-        <v>8632500</v>
+        <v>7464500</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B171" t="n">
-        <v>223.4268017505994</v>
+        <v>228.5518965755589</v>
       </c>
       <c r="C171" t="n">
-        <v>228.3540202522719</v>
+        <v>229.3038367743656</v>
       </c>
       <c r="D171" t="n">
-        <v>223.0508241008666</v>
+        <v>226.7314002434507</v>
       </c>
       <c r="E171" t="n">
-        <v>227.9780426025391</v>
+        <v>228.3540191650391</v>
       </c>
       <c r="F171" t="n">
-        <v>7464500</v>
+        <v>6974400</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B172" t="n">
-        <v>228.5519118475702</v>
+        <v>228.324343449484</v>
       </c>
       <c r="C172" t="n">
-        <v>229.3038520966222</v>
+        <v>229.6798195939985</v>
       </c>
       <c r="D172" t="n">
-        <v>226.7314153938151</v>
+        <v>224.0402302332647</v>
       </c>
       <c r="E172" t="n">
-        <v>228.3540344238281</v>
+        <v>224.307373046875</v>
       </c>
       <c r="F172" t="n">
-        <v>6974400</v>
+        <v>12167000</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B173" t="n">
-        <v>228.324343449484</v>
+        <v>224.3073719260098</v>
       </c>
       <c r="C173" t="n">
-        <v>229.6798195939985</v>
+        <v>227.2656747432453</v>
       </c>
       <c r="D173" t="n">
-        <v>224.0402302332647</v>
+        <v>223.466374045218</v>
       </c>
       <c r="E173" t="n">
-        <v>224.307373046875</v>
+        <v>226.4939422607422</v>
       </c>
       <c r="F173" t="n">
-        <v>12167000</v>
+        <v>10141600</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B174" t="n">
-        <v>224.3073719260098</v>
+        <v>226.5137209227187</v>
       </c>
       <c r="C174" t="n">
-        <v>227.2656747432453</v>
+        <v>228.4034825714771</v>
       </c>
       <c r="D174" t="n">
-        <v>223.466374045218</v>
+        <v>225.6232499676584</v>
       </c>
       <c r="E174" t="n">
-        <v>226.4939422607422</v>
+        <v>227.5624847412109</v>
       </c>
       <c r="F174" t="n">
-        <v>10141600</v>
+        <v>9677900</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B175" t="n">
-        <v>226.5137209227187</v>
+        <v>229.2345877493695</v>
       </c>
       <c r="C175" t="n">
-        <v>228.4034825714771</v>
+        <v>229.5413000019429</v>
       </c>
       <c r="D175" t="n">
-        <v>225.6232499676584</v>
+        <v>226.7412900911319</v>
       </c>
       <c r="E175" t="n">
-        <v>227.5624847412109</v>
+        <v>226.8897094726562</v>
       </c>
       <c r="F175" t="n">
-        <v>9677900</v>
+        <v>7353800</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B176" t="n">
-        <v>229.2345877493695</v>
+        <v>226.8897069691897</v>
       </c>
       <c r="C176" t="n">
-        <v>229.5413000019429</v>
+        <v>229.432462629467</v>
       </c>
       <c r="D176" t="n">
-        <v>226.7412900911319</v>
+        <v>224.9405835372236</v>
       </c>
       <c r="E176" t="n">
-        <v>226.8897094726562</v>
+        <v>229.2741546630859</v>
       </c>
       <c r="F176" t="n">
-        <v>7353800</v>
+        <v>5239000</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B177" t="n">
-        <v>226.8897069691897</v>
+        <v>230.5307110319731</v>
       </c>
       <c r="C177" t="n">
-        <v>229.432462629467</v>
+        <v>233.0042165151488</v>
       </c>
       <c r="D177" t="n">
-        <v>224.9405835372236</v>
+        <v>230.2536796256238</v>
       </c>
       <c r="E177" t="n">
-        <v>229.2741546630859</v>
+        <v>231.8565063476562</v>
       </c>
       <c r="F177" t="n">
-        <v>5239000</v>
+        <v>5462300</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,25 +5045,25 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B178" t="n">
-        <v>230.5307110319731</v>
+        <v>231.856506324529</v>
       </c>
       <c r="C178" t="n">
-        <v>233.0042165151488</v>
+        <v>232.0953339431715</v>
       </c>
       <c r="D178" t="n">
-        <v>230.2536796256238</v>
+        <v>227.9557463234551</v>
       </c>
       <c r="E178" t="n">
-        <v>231.8565063476562</v>
+        <v>229.0503387451172</v>
       </c>
       <c r="F178" t="n">
-        <v>5462300</v>
+        <v>6619600</v>
       </c>
       <c r="G178" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -5071,25 +5071,25 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B179" t="n">
-        <v>231.856506324529</v>
+        <v>228.8513234809034</v>
       </c>
       <c r="C179" t="n">
-        <v>232.0953339431715</v>
+        <v>231.7470457253588</v>
       </c>
       <c r="D179" t="n">
-        <v>227.9557463234551</v>
+        <v>227.896043373475</v>
       </c>
       <c r="E179" t="n">
-        <v>229.0503387451172</v>
+        <v>230.1548919677734</v>
       </c>
       <c r="F179" t="n">
-        <v>6619600</v>
+        <v>5835500</v>
       </c>
       <c r="G179" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B180" t="n">
-        <v>228.8513234809034</v>
+        <v>228.9010720691913</v>
       </c>
       <c r="C180" t="n">
-        <v>231.7470457253588</v>
+        <v>230.7320381891827</v>
       </c>
       <c r="D180" t="n">
-        <v>227.896043373475</v>
+        <v>228.6025413534768</v>
       </c>
       <c r="E180" t="n">
-        <v>230.1548919677734</v>
+        <v>229.6672973632812</v>
       </c>
       <c r="F180" t="n">
-        <v>5835500</v>
+        <v>7193400</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B181" t="n">
-        <v>228.9010720691913</v>
+        <v>230.0951744973679</v>
       </c>
       <c r="C181" t="n">
-        <v>230.7320381891827</v>
+        <v>230.36385365377</v>
       </c>
       <c r="D181" t="n">
-        <v>228.6025413534768</v>
+        <v>223.4877626284344</v>
       </c>
       <c r="E181" t="n">
-        <v>229.6672973632812</v>
+        <v>224.2241363525391</v>
       </c>
       <c r="F181" t="n">
-        <v>7193400</v>
+        <v>13897700</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B182" t="n">
-        <v>230.0951744973679</v>
+        <v>222.1045945004449</v>
       </c>
       <c r="C182" t="n">
-        <v>230.36385365377</v>
+        <v>223.3385143974124</v>
       </c>
       <c r="D182" t="n">
-        <v>223.4877626284344</v>
+        <v>219.7561761055088</v>
       </c>
       <c r="E182" t="n">
-        <v>224.2241363525391</v>
+        <v>222.4130706787109</v>
       </c>
       <c r="F182" t="n">
-        <v>13897700</v>
+        <v>8041000</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B183" t="n">
-        <v>222.1045945004449</v>
+        <v>221.4876358909895</v>
       </c>
       <c r="C183" t="n">
-        <v>223.3385143974124</v>
+        <v>224.3933034528787</v>
       </c>
       <c r="D183" t="n">
-        <v>219.7561761055088</v>
+        <v>220.0845521676131</v>
       </c>
       <c r="E183" t="n">
-        <v>222.4130706787109</v>
+        <v>221.7961120605469</v>
       </c>
       <c r="F183" t="n">
-        <v>8041000</v>
+        <v>5669000</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B184" t="n">
-        <v>221.4876358909895</v>
+        <v>221.3582777644383</v>
       </c>
       <c r="C184" t="n">
-        <v>224.3933034528787</v>
+        <v>223.8261024020756</v>
       </c>
       <c r="D184" t="n">
-        <v>220.0845521676131</v>
+        <v>220.9104892689172</v>
       </c>
       <c r="E184" t="n">
-        <v>221.7961120605469</v>
+        <v>222.1444091796875</v>
       </c>
       <c r="F184" t="n">
-        <v>5669000</v>
+        <v>6507200</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B185" t="n">
-        <v>221.3582777644383</v>
+        <v>225.9754999423843</v>
       </c>
       <c r="C185" t="n">
-        <v>223.8261024020756</v>
+        <v>227.5477475509985</v>
       </c>
       <c r="D185" t="n">
-        <v>220.9104892689172</v>
+        <v>224.7913377117005</v>
       </c>
       <c r="E185" t="n">
-        <v>222.1444091796875</v>
+        <v>227.0502014160156</v>
       </c>
       <c r="F185" t="n">
-        <v>6507200</v>
+        <v>7274800</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B186" t="n">
-        <v>225.9754999423843</v>
+        <v>228.8712298379233</v>
       </c>
       <c r="C186" t="n">
-        <v>227.5477475509985</v>
+        <v>234.0656128776528</v>
       </c>
       <c r="D186" t="n">
-        <v>224.7913377117005</v>
+        <v>227.8761375342802</v>
       </c>
       <c r="E186" t="n">
-        <v>227.0502014160156</v>
+        <v>231.6276397705078</v>
       </c>
       <c r="F186" t="n">
-        <v>7274800</v>
+        <v>8034900</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B187" t="n">
-        <v>228.8712298379233</v>
+        <v>231.6276367875738</v>
       </c>
       <c r="C187" t="n">
-        <v>234.0656128776528</v>
+        <v>233.7969306933057</v>
       </c>
       <c r="D187" t="n">
-        <v>227.8761375342802</v>
+        <v>229.428476143926</v>
       </c>
       <c r="E187" t="n">
-        <v>231.6276397705078</v>
+        <v>231.0206298828125</v>
       </c>
       <c r="F187" t="n">
-        <v>8034900</v>
+        <v>7559800</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B188" t="n">
-        <v>231.6276367875738</v>
+        <v>231.2395468518091</v>
       </c>
       <c r="C188" t="n">
-        <v>233.7969306933057</v>
+        <v>236.5433904796373</v>
       </c>
       <c r="D188" t="n">
-        <v>229.428476143926</v>
+        <v>229.2792138627353</v>
       </c>
       <c r="E188" t="n">
-        <v>231.0206298828125</v>
+        <v>235.8368682861328</v>
       </c>
       <c r="F188" t="n">
-        <v>7559800</v>
+        <v>8354500</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B189" t="n">
-        <v>231.2395468518091</v>
+        <v>237.6777986497502</v>
       </c>
       <c r="C189" t="n">
-        <v>236.5433904796373</v>
+        <v>239.7475772433621</v>
       </c>
       <c r="D189" t="n">
-        <v>229.2792138627353</v>
+        <v>235.886629497679</v>
       </c>
       <c r="E189" t="n">
-        <v>235.8368682861328</v>
+        <v>237.3195648193359</v>
       </c>
       <c r="F189" t="n">
-        <v>8354500</v>
+        <v>8350800</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B190" t="n">
-        <v>237.6777986497502</v>
+        <v>238.822141602048</v>
       </c>
       <c r="C190" t="n">
-        <v>239.7475772433621</v>
+        <v>240.4142952862894</v>
       </c>
       <c r="D190" t="n">
-        <v>235.886629497679</v>
+        <v>236.971269397276</v>
       </c>
       <c r="E190" t="n">
-        <v>237.3195648193359</v>
+        <v>237.1603393554688</v>
       </c>
       <c r="F190" t="n">
-        <v>8350800</v>
+        <v>7399000</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B191" t="n">
-        <v>238.822141602048</v>
+        <v>238.8221408093525</v>
       </c>
       <c r="C191" t="n">
-        <v>240.4142952862894</v>
+        <v>239.7276784040579</v>
       </c>
       <c r="D191" t="n">
-        <v>236.971269397276</v>
+        <v>236.354316272482</v>
       </c>
       <c r="E191" t="n">
-        <v>237.1603393554688</v>
+        <v>239.6878662109375</v>
       </c>
       <c r="F191" t="n">
-        <v>7399000</v>
+        <v>6459400</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B192" t="n">
-        <v>238.8221408093525</v>
+        <v>237.8270530309927</v>
       </c>
       <c r="C192" t="n">
-        <v>239.7276784040579</v>
+        <v>238.3245991670408</v>
       </c>
       <c r="D192" t="n">
-        <v>236.354316272482</v>
+        <v>232.4336547382997</v>
       </c>
       <c r="E192" t="n">
-        <v>239.6878662109375</v>
+        <v>234.5034484863281</v>
       </c>
       <c r="F192" t="n">
-        <v>6459400</v>
+        <v>7732000</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B193" t="n">
-        <v>237.8270530309927</v>
+        <v>235.2099495568312</v>
       </c>
       <c r="C193" t="n">
-        <v>238.3245991670408</v>
+        <v>235.2099495568312</v>
       </c>
       <c r="D193" t="n">
-        <v>232.4336547382997</v>
+        <v>229.8862151458974</v>
       </c>
       <c r="E193" t="n">
-        <v>234.5034484863281</v>
+        <v>234.0257873535156</v>
       </c>
       <c r="F193" t="n">
-        <v>7732000</v>
+        <v>7718100</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B194" t="n">
-        <v>235.2099495568312</v>
+        <v>232.8814495345484</v>
       </c>
       <c r="C194" t="n">
-        <v>235.2099495568312</v>
+        <v>234.2745726796724</v>
       </c>
       <c r="D194" t="n">
-        <v>229.8862151458974</v>
+        <v>229.5677903566066</v>
       </c>
       <c r="E194" t="n">
-        <v>234.0257873535156</v>
+        <v>233.0506134033203</v>
       </c>
       <c r="F194" t="n">
-        <v>7718100</v>
+        <v>8548000</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B195" t="n">
-        <v>232.8814495345484</v>
+        <v>230.6424813960874</v>
       </c>
       <c r="C195" t="n">
-        <v>234.2745726796724</v>
+        <v>231.6077220970904</v>
       </c>
       <c r="D195" t="n">
-        <v>229.5677903566066</v>
+        <v>226.4830030630252</v>
       </c>
       <c r="E195" t="n">
-        <v>233.0506134033203</v>
+        <v>227.2691192626953</v>
       </c>
       <c r="F195" t="n">
-        <v>8548000</v>
+        <v>18989800</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B196" t="n">
-        <v>230.6424813960874</v>
+        <v>227.8263796240252</v>
       </c>
       <c r="C196" t="n">
-        <v>231.6077220970904</v>
+        <v>230.3141103803127</v>
       </c>
       <c r="D196" t="n">
-        <v>226.4830030630252</v>
+        <v>226.3834988221592</v>
       </c>
       <c r="E196" t="n">
-        <v>227.2691192626953</v>
+        <v>230.1548919677734</v>
       </c>
       <c r="F196" t="n">
-        <v>18989800</v>
+        <v>8518300</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B197" t="n">
-        <v>227.8263796240252</v>
+        <v>234.4835421454308</v>
       </c>
       <c r="C197" t="n">
-        <v>230.3141103803127</v>
+        <v>238.6231296371808</v>
       </c>
       <c r="D197" t="n">
-        <v>226.3834988221592</v>
+        <v>233.1998797966796</v>
       </c>
       <c r="E197" t="n">
-        <v>230.1548919677734</v>
+        <v>237.9066619873047</v>
       </c>
       <c r="F197" t="n">
-        <v>8518300</v>
+        <v>11802000</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B198" t="n">
-        <v>234.4835421454308</v>
+        <v>238.7126772290818</v>
       </c>
       <c r="C198" t="n">
-        <v>238.6231296371808</v>
+        <v>241.8472117165478</v>
       </c>
       <c r="D198" t="n">
-        <v>233.1998797966796</v>
+        <v>237.5782726810186</v>
       </c>
       <c r="E198" t="n">
-        <v>237.9066619873047</v>
+        <v>239.8172302246094</v>
       </c>
       <c r="F198" t="n">
-        <v>11802000</v>
+        <v>8139200</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B199" t="n">
-        <v>238.7126772290818</v>
+        <v>240.0859235854152</v>
       </c>
       <c r="C199" t="n">
-        <v>241.8472117165478</v>
+        <v>246.9719604825856</v>
       </c>
       <c r="D199" t="n">
-        <v>237.5782726810186</v>
+        <v>239.7077836523882</v>
       </c>
       <c r="E199" t="n">
-        <v>239.8172302246094</v>
+        <v>243.6782073974609</v>
       </c>
       <c r="F199" t="n">
-        <v>8139200</v>
+        <v>10130400</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B200" t="n">
-        <v>240.0859235854152</v>
+        <v>247.0515630057391</v>
       </c>
       <c r="C200" t="n">
-        <v>246.9719604825856</v>
+        <v>253.857990512684</v>
       </c>
       <c r="D200" t="n">
-        <v>239.7077836523882</v>
+        <v>246.6535169859773</v>
       </c>
       <c r="E200" t="n">
-        <v>243.6782073974609</v>
+        <v>253.4102020263672</v>
       </c>
       <c r="F200" t="n">
-        <v>10130400</v>
+        <v>16316800</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B201" t="n">
-        <v>247.0515630057391</v>
+        <v>251.9474045302274</v>
       </c>
       <c r="C201" t="n">
-        <v>253.857990512684</v>
+        <v>257.3109358669097</v>
       </c>
       <c r="D201" t="n">
-        <v>246.6535169859773</v>
+        <v>250.7930938975173</v>
       </c>
       <c r="E201" t="n">
-        <v>253.4102020263672</v>
+        <v>257.2413024902344</v>
       </c>
       <c r="F201" t="n">
-        <v>16316800</v>
+        <v>8608400</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B202" t="n">
-        <v>251.9474045302274</v>
+        <v>257.7288999793201</v>
       </c>
       <c r="C202" t="n">
-        <v>257.3109358669097</v>
+        <v>258.62447695588</v>
       </c>
       <c r="D202" t="n">
-        <v>250.7930938975173</v>
+        <v>251.9275101770222</v>
       </c>
       <c r="E202" t="n">
-        <v>257.2413024902344</v>
+        <v>252.7235870361328</v>
       </c>
       <c r="F202" t="n">
-        <v>8608400</v>
+        <v>8469500</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B203" t="n">
-        <v>257.7288999793201</v>
+        <v>252.0071226458085</v>
       </c>
       <c r="C203" t="n">
-        <v>258.62447695588</v>
+        <v>252.9524572852904</v>
       </c>
       <c r="D203" t="n">
-        <v>251.9275101770222</v>
+        <v>249.8477741968348</v>
       </c>
       <c r="E203" t="n">
-        <v>252.7235870361328</v>
+        <v>252.7335357666016</v>
       </c>
       <c r="F203" t="n">
-        <v>8469500</v>
+        <v>6516500</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B204" t="n">
-        <v>252.0071226458085</v>
+        <v>254.5247047293354</v>
       </c>
       <c r="C204" t="n">
-        <v>252.9524572852904</v>
+        <v>261.8087875806335</v>
       </c>
       <c r="D204" t="n">
-        <v>249.8477741968348</v>
+        <v>252.753441667793</v>
       </c>
       <c r="E204" t="n">
-        <v>252.7335357666016</v>
+        <v>261.7490844726562</v>
       </c>
       <c r="F204" t="n">
-        <v>6516500</v>
+        <v>7998700</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B205" t="n">
-        <v>254.5247047293354</v>
+        <v>258.9528582650781</v>
       </c>
       <c r="C205" t="n">
-        <v>261.8087875806335</v>
+        <v>260.0972082397536</v>
       </c>
       <c r="D205" t="n">
-        <v>252.753441667793</v>
+        <v>254.673943516207</v>
       </c>
       <c r="E205" t="n">
-        <v>261.7490844726562</v>
+        <v>258.0572509765625</v>
       </c>
       <c r="F205" t="n">
-        <v>7998700</v>
+        <v>6803700</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B206" t="n">
-        <v>258.9528582650781</v>
+        <v>263.5899938466549</v>
       </c>
       <c r="C206" t="n">
-        <v>260.0972082397536</v>
+        <v>268.1076906797339</v>
       </c>
       <c r="D206" t="n">
-        <v>254.673943516207</v>
+        <v>262.7540896546532</v>
       </c>
       <c r="E206" t="n">
-        <v>258.0572509765625</v>
+        <v>265.9284362792969</v>
       </c>
       <c r="F206" t="n">
-        <v>6803700</v>
+        <v>9089700</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B207" t="n">
-        <v>263.5899938466549</v>
+        <v>267.2817917945089</v>
       </c>
       <c r="C207" t="n">
-        <v>268.1076906797339</v>
+        <v>267.2817917945089</v>
       </c>
       <c r="D207" t="n">
-        <v>262.7540896546532</v>
+        <v>261.8386358221884</v>
       </c>
       <c r="E207" t="n">
-        <v>265.9284362792969</v>
+        <v>262.1072998046875</v>
       </c>
       <c r="F207" t="n">
-        <v>9089700</v>
+        <v>6769400</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B208" t="n">
-        <v>267.2817917945089</v>
+        <v>259.3508895364454</v>
       </c>
       <c r="C208" t="n">
-        <v>267.2817917945089</v>
+        <v>262.1570568783993</v>
       </c>
       <c r="D208" t="n">
-        <v>261.8386358221884</v>
+        <v>256.8631589924022</v>
       </c>
       <c r="E208" t="n">
-        <v>262.1072998046875</v>
+        <v>257.8283996582031</v>
       </c>
       <c r="F208" t="n">
-        <v>6769400</v>
+        <v>6426100</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B209" t="n">
-        <v>259.3508895364454</v>
+        <v>258.9130640253377</v>
       </c>
       <c r="C209" t="n">
-        <v>262.1570568783993</v>
+        <v>260.0176018849775</v>
       </c>
       <c r="D209" t="n">
-        <v>256.8631589924022</v>
+        <v>254.2659848771424</v>
       </c>
       <c r="E209" t="n">
-        <v>257.8283996582031</v>
+        <v>255.7188262939453</v>
       </c>
       <c r="F209" t="n">
-        <v>6426100</v>
+        <v>6534700</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B210" t="n">
-        <v>258.9130640253377</v>
+        <v>256.6840530111044</v>
       </c>
       <c r="C210" t="n">
-        <v>260.0176018849775</v>
+        <v>258.2562853735001</v>
       </c>
       <c r="D210" t="n">
-        <v>254.2659848771424</v>
+        <v>254.892868775476</v>
       </c>
       <c r="E210" t="n">
-        <v>255.7188262939453</v>
+        <v>256.5049133300781</v>
       </c>
       <c r="F210" t="n">
-        <v>6534700</v>
+        <v>5272200</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B211" t="n">
-        <v>256.6840530111044</v>
+        <v>254.2759347913044</v>
       </c>
       <c r="C211" t="n">
-        <v>258.2562853735001</v>
+        <v>255.1317299625397</v>
       </c>
       <c r="D211" t="n">
-        <v>254.892868775476</v>
+        <v>250.9025724938729</v>
       </c>
       <c r="E211" t="n">
-        <v>256.5049133300781</v>
+        <v>252.6041870117188</v>
       </c>
       <c r="F211" t="n">
-        <v>5272200</v>
+        <v>8770600</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B212" t="n">
-        <v>254.2759347913044</v>
+        <v>248.8626188136353</v>
       </c>
       <c r="C212" t="n">
-        <v>255.1317299625397</v>
+        <v>255.5695309055475</v>
       </c>
       <c r="D212" t="n">
-        <v>250.9025724938729</v>
+        <v>244.842452777813</v>
       </c>
       <c r="E212" t="n">
-        <v>252.6041870117188</v>
+        <v>245.8076934814453</v>
       </c>
       <c r="F212" t="n">
-        <v>8770600</v>
+        <v>10547300</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B213" t="n">
-        <v>248.8626188136353</v>
+        <v>247.6784538478382</v>
       </c>
       <c r="C213" t="n">
-        <v>255.5695309055475</v>
+        <v>252.3056419000621</v>
       </c>
       <c r="D213" t="n">
-        <v>244.842452777813</v>
+        <v>245.091223119708</v>
       </c>
       <c r="E213" t="n">
-        <v>245.8076934814453</v>
+        <v>248.7432098388672</v>
       </c>
       <c r="F213" t="n">
-        <v>10547300</v>
+        <v>11097600</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B214" t="n">
-        <v>247.6784538478382</v>
+        <v>251.350352994489</v>
       </c>
       <c r="C214" t="n">
-        <v>252.3056419000621</v>
+        <v>254.4052935535989</v>
       </c>
       <c r="D214" t="n">
-        <v>245.091223119708</v>
+        <v>250.7134945486414</v>
       </c>
       <c r="E214" t="n">
-        <v>248.7432098388672</v>
+        <v>251.7981414794922</v>
       </c>
       <c r="F214" t="n">
-        <v>11097600</v>
+        <v>10167700</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B215" t="n">
-        <v>251.350352994489</v>
+        <v>250.7731932271148</v>
       </c>
       <c r="C215" t="n">
-        <v>254.4052935535989</v>
+        <v>252.9325415941838</v>
       </c>
       <c r="D215" t="n">
-        <v>250.7134945486414</v>
+        <v>247.4097917368304</v>
       </c>
       <c r="E215" t="n">
-        <v>251.7981414794922</v>
+        <v>247.5988616943359</v>
       </c>
       <c r="F215" t="n">
-        <v>10167700</v>
+        <v>8114700</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B216" t="n">
-        <v>250.7731932271148</v>
+        <v>246.2355858738711</v>
       </c>
       <c r="C216" t="n">
-        <v>252.9325415941838</v>
+        <v>250.1064943021279</v>
       </c>
       <c r="D216" t="n">
-        <v>247.4097917368304</v>
+        <v>244.2852134745944</v>
       </c>
       <c r="E216" t="n">
-        <v>247.5988616943359</v>
+        <v>249.3800811767578</v>
       </c>
       <c r="F216" t="n">
-        <v>8114700</v>
+        <v>7793100</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B217" t="n">
-        <v>246.2355858738711</v>
+        <v>251.5195173574522</v>
       </c>
       <c r="C217" t="n">
-        <v>250.1064943021279</v>
+        <v>255.0322070489389</v>
       </c>
       <c r="D217" t="n">
-        <v>244.2852134745944</v>
+        <v>249.9771364820368</v>
       </c>
       <c r="E217" t="n">
-        <v>249.3800811767578</v>
+        <v>254.3754425048828</v>
       </c>
       <c r="F217" t="n">
-        <v>7793100</v>
+        <v>9100200</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B218" t="n">
-        <v>251.5195173574522</v>
+        <v>253.9873531958193</v>
       </c>
       <c r="C218" t="n">
-        <v>255.0322070489389</v>
+        <v>258.9230174724852</v>
       </c>
       <c r="D218" t="n">
-        <v>249.9771364820368</v>
+        <v>253.1713702566359</v>
       </c>
       <c r="E218" t="n">
-        <v>254.3754425048828</v>
+        <v>257.99755859375</v>
       </c>
       <c r="F218" t="n">
-        <v>9100200</v>
+        <v>8063300</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B219" t="n">
-        <v>253.9873531958193</v>
+        <v>260.1469668034143</v>
       </c>
       <c r="C219" t="n">
-        <v>258.9230174724852</v>
+        <v>262.41577598127</v>
       </c>
       <c r="D219" t="n">
-        <v>253.1713702566359</v>
+        <v>258.3358915701962</v>
       </c>
       <c r="E219" t="n">
-        <v>257.99755859375</v>
+        <v>262.1072998046875</v>
       </c>
       <c r="F219" t="n">
-        <v>8063300</v>
+        <v>6351800</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B220" t="n">
-        <v>260.1469668034143</v>
+        <v>261.2614678377304</v>
       </c>
       <c r="C220" t="n">
-        <v>262.41577598127</v>
+        <v>267.4807946322661</v>
       </c>
       <c r="D220" t="n">
-        <v>258.3358915701962</v>
+        <v>260.0673753138636</v>
       </c>
       <c r="E220" t="n">
-        <v>262.1072998046875</v>
+        <v>264.6448059082031</v>
       </c>
       <c r="F220" t="n">
-        <v>6351800</v>
+        <v>9647900</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B221" t="n">
-        <v>261.2614678377304</v>
+        <v>268.6749001082239</v>
       </c>
       <c r="C221" t="n">
-        <v>267.4807946322661</v>
+        <v>273.5508459255159</v>
       </c>
       <c r="D221" t="n">
-        <v>260.0673753138636</v>
+        <v>264.8736405295307</v>
       </c>
       <c r="E221" t="n">
-        <v>264.6448059082031</v>
+        <v>265.4209594726562</v>
       </c>
       <c r="F221" t="n">
-        <v>9647900</v>
+        <v>10491000</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B222" t="n">
-        <v>268.6749001082239</v>
+        <v>267.1822622796963</v>
       </c>
       <c r="C222" t="n">
-        <v>273.5508459255159</v>
+        <v>268.0181361041443</v>
       </c>
       <c r="D222" t="n">
-        <v>264.8736405295307</v>
+        <v>263.4904786297666</v>
       </c>
       <c r="E222" t="n">
-        <v>265.4209594726562</v>
+        <v>264.2268371582031</v>
       </c>
       <c r="F222" t="n">
-        <v>10491000</v>
+        <v>6105600</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B223" t="n">
-        <v>267.1822622796963</v>
+        <v>257.7587518734895</v>
       </c>
       <c r="C223" t="n">
-        <v>268.0181361041443</v>
+        <v>259.2414296518399</v>
       </c>
       <c r="D223" t="n">
-        <v>263.4904786297666</v>
+        <v>253.310688170632</v>
       </c>
       <c r="E223" t="n">
-        <v>264.2268371582031</v>
+        <v>254.5645141601562</v>
       </c>
       <c r="F223" t="n">
-        <v>6105600</v>
+        <v>8216500</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B224" t="n">
-        <v>257.7587518734895</v>
+        <v>254.7535759665547</v>
       </c>
       <c r="C224" t="n">
-        <v>259.2414296518399</v>
+        <v>257.2114550322676</v>
       </c>
       <c r="D224" t="n">
-        <v>253.310688170632</v>
+        <v>252.046908655097</v>
       </c>
       <c r="E224" t="n">
-        <v>254.5645141601562</v>
+        <v>255.0919036865234</v>
       </c>
       <c r="F224" t="n">
-        <v>8216500</v>
+        <v>6782100</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B225" t="n">
-        <v>254.7535759665547</v>
+        <v>253.7186719595458</v>
       </c>
       <c r="C225" t="n">
-        <v>257.2114550322676</v>
+        <v>256.4850271972422</v>
       </c>
       <c r="D225" t="n">
-        <v>252.046908655097</v>
+        <v>249.6785998577546</v>
       </c>
       <c r="E225" t="n">
-        <v>255.0919036865234</v>
+        <v>253.1614227294922</v>
       </c>
       <c r="F225" t="n">
-        <v>6782100</v>
+        <v>8136300</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B226" t="n">
-        <v>253.7186719595458</v>
+        <v>253.1614264806184</v>
       </c>
       <c r="C226" t="n">
-        <v>256.4850271972422</v>
+        <v>254.2659795008061</v>
       </c>
       <c r="D226" t="n">
-        <v>249.6785998577546</v>
+        <v>249.2109089785714</v>
       </c>
       <c r="E226" t="n">
-        <v>253.1614227294922</v>
+        <v>253.6788635253906</v>
       </c>
       <c r="F226" t="n">
-        <v>8136300</v>
+        <v>7362400</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B227" t="n">
-        <v>253.1614264806184</v>
+        <v>253.9972934738065</v>
       </c>
       <c r="C227" t="n">
-        <v>254.2659795008061</v>
+        <v>258.0473261663437</v>
       </c>
       <c r="D227" t="n">
-        <v>249.2109089785714</v>
+        <v>253.2211227437212</v>
       </c>
       <c r="E227" t="n">
-        <v>253.6788635253906</v>
+        <v>256.3258056640625</v>
       </c>
       <c r="F227" t="n">
-        <v>7362400</v>
+        <v>6472600</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B228" t="n">
-        <v>253.9972934738065</v>
+        <v>260.425593365904</v>
       </c>
       <c r="C228" t="n">
-        <v>258.0473261663437</v>
+        <v>260.8236242062839</v>
       </c>
       <c r="D228" t="n">
-        <v>253.2211227437212</v>
+        <v>254.0271572625725</v>
       </c>
       <c r="E228" t="n">
-        <v>256.3258056640625</v>
+        <v>255.7188262939453</v>
       </c>
       <c r="F228" t="n">
-        <v>6472600</v>
+        <v>6931800</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B229" t="n">
-        <v>260.425593365904</v>
+        <v>254.6341623817563</v>
       </c>
       <c r="C229" t="n">
-        <v>260.8236242062839</v>
+        <v>258.3259614136433</v>
       </c>
       <c r="D229" t="n">
-        <v>254.0271572625725</v>
+        <v>253.8679370762885</v>
       </c>
       <c r="E229" t="n">
-        <v>255.7188262939453</v>
+        <v>257.9677124023438</v>
       </c>
       <c r="F229" t="n">
-        <v>6931800</v>
+        <v>6532100</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B230" t="n">
-        <v>254.6341623817563</v>
+        <v>257.7886121067854</v>
       </c>
       <c r="C230" t="n">
-        <v>258.3259614136433</v>
+        <v>260.7141859356404</v>
       </c>
       <c r="D230" t="n">
-        <v>253.8679370762885</v>
+        <v>257.281105309594</v>
       </c>
       <c r="E230" t="n">
-        <v>257.9677124023438</v>
+        <v>260.5251159667969</v>
       </c>
       <c r="F230" t="n">
-        <v>6532100</v>
+        <v>8985100</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B231" t="n">
-        <v>257.7886121067854</v>
+        <v>259.9479684253454</v>
       </c>
       <c r="C231" t="n">
-        <v>260.7141859356404</v>
+        <v>262.853620890259</v>
       </c>
       <c r="D231" t="n">
-        <v>257.281105309594</v>
+        <v>257.0920280597301</v>
       </c>
       <c r="E231" t="n">
-        <v>260.5251159667969</v>
+        <v>258.5249633789062</v>
       </c>
       <c r="F231" t="n">
-        <v>8985100</v>
+        <v>5945900</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B232" t="n">
-        <v>259.9479684253454</v>
+        <v>254.7436088096904</v>
       </c>
       <c r="C232" t="n">
-        <v>262.853620890259</v>
+        <v>260.1270613743755</v>
       </c>
       <c r="D232" t="n">
-        <v>257.0920280597301</v>
+        <v>254.00723509927</v>
       </c>
       <c r="E232" t="n">
-        <v>258.5249633789062</v>
+        <v>259.5797424316406</v>
       </c>
       <c r="F232" t="n">
-        <v>5945900</v>
+        <v>4629300</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B233" t="n">
-        <v>254.7436088096904</v>
+        <v>260.4455042155265</v>
       </c>
       <c r="C233" t="n">
-        <v>260.1270613743755</v>
+        <v>261.3311205223152</v>
       </c>
       <c r="D233" t="n">
-        <v>254.00723509927</v>
+        <v>258.3756953399613</v>
       </c>
       <c r="E233" t="n">
-        <v>259.5797424316406</v>
+        <v>260.7937622070312</v>
       </c>
       <c r="F233" t="n">
-        <v>4629300</v>
+        <v>4852700</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B234" t="n">
-        <v>260.4455042155265</v>
+        <v>259.3707811439639</v>
       </c>
       <c r="C234" t="n">
-        <v>261.3311205223152</v>
+        <v>260.4255764680427</v>
       </c>
       <c r="D234" t="n">
-        <v>258.3756953399613</v>
+        <v>257.8881034534354</v>
       </c>
       <c r="E234" t="n">
-        <v>260.7937622070312</v>
+        <v>259.072265625</v>
       </c>
       <c r="F234" t="n">
-        <v>4852700</v>
+        <v>4998100</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B235" t="n">
-        <v>259.3707811439639</v>
+        <v>257.5995438259766</v>
       </c>
       <c r="C235" t="n">
-        <v>260.4255764680427</v>
+        <v>262.9829969172681</v>
       </c>
       <c r="D235" t="n">
-        <v>257.8881034534354</v>
+        <v>256.7437790079673</v>
       </c>
       <c r="E235" t="n">
-        <v>259.072265625</v>
+        <v>261.0823669433594</v>
       </c>
       <c r="F235" t="n">
-        <v>4998100</v>
+        <v>5515500</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B236" t="n">
-        <v>257.5995438259766</v>
+        <v>266.3563600087168</v>
       </c>
       <c r="C236" t="n">
-        <v>262.9829969172681</v>
+        <v>270.3964321763198</v>
       </c>
       <c r="D236" t="n">
-        <v>256.7437790079673</v>
+        <v>265.0229096495755</v>
       </c>
       <c r="E236" t="n">
-        <v>261.0823669433594</v>
+        <v>269.7794494628906</v>
       </c>
       <c r="F236" t="n">
-        <v>5515500</v>
+        <v>7838200</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B237" t="n">
-        <v>266.3563600087168</v>
+        <v>271.6601848020655</v>
       </c>
       <c r="C237" t="n">
-        <v>270.3964321763198</v>
+        <v>275.1131561312948</v>
       </c>
       <c r="D237" t="n">
-        <v>265.0229096495755</v>
+        <v>269.2321572777068</v>
       </c>
       <c r="E237" t="n">
-        <v>269.7794494628906</v>
+        <v>272.0681762695312</v>
       </c>
       <c r="F237" t="n">
-        <v>7838200</v>
+        <v>7728500</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B238" t="n">
-        <v>271.6601848020655</v>
+        <v>272.0582363321417</v>
       </c>
       <c r="C238" t="n">
-        <v>275.1131561312948</v>
+        <v>272.0582363321417</v>
       </c>
       <c r="D238" t="n">
-        <v>269.2321572777068</v>
+        <v>266.0578308105469</v>
       </c>
       <c r="E238" t="n">
-        <v>272.0681762695312</v>
+        <v>266.0578308105469</v>
       </c>
       <c r="F238" t="n">
-        <v>7728500</v>
+        <v>6475900</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B239" t="n">
-        <v>272.0582363321417</v>
+        <v>266.5155507786093</v>
       </c>
       <c r="C239" t="n">
-        <v>272.0582363321417</v>
+        <v>271.3218634751246</v>
       </c>
       <c r="D239" t="n">
-        <v>266.0578308105469</v>
+        <v>265.6896375517999</v>
       </c>
       <c r="E239" t="n">
-        <v>266.0578308105469</v>
+        <v>268.9137268066406</v>
       </c>
       <c r="F239" t="n">
-        <v>6475900</v>
+        <v>6186800</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B240" t="n">
-        <v>266.5155507786093</v>
+        <v>268.4161893708204</v>
       </c>
       <c r="C240" t="n">
-        <v>271.3218634751246</v>
+        <v>272.635401405727</v>
       </c>
       <c r="D240" t="n">
-        <v>265.6896375517999</v>
+        <v>267.2519483767422</v>
       </c>
       <c r="E240" t="n">
-        <v>268.9137268066406</v>
+        <v>271.7000122070312</v>
       </c>
       <c r="F240" t="n">
-        <v>6186800</v>
+        <v>5436100</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,25 +6683,25 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B241" t="n">
-        <v>268.4161893708204</v>
+        <v>271</v>
       </c>
       <c r="C241" t="n">
-        <v>272.635401405727</v>
+        <v>273.7999877929688</v>
       </c>
       <c r="D241" t="n">
-        <v>267.2519483767422</v>
+        <v>270.1799926757812</v>
       </c>
       <c r="E241" t="n">
-        <v>271.7000122070312</v>
+        <v>273.1400146484375</v>
       </c>
       <c r="F241" t="n">
-        <v>5436100</v>
+        <v>4687000</v>
       </c>
       <c r="G241" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -6709,25 +6709,25 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B242" t="n">
-        <v>271</v>
+        <v>271.9700012207031</v>
       </c>
       <c r="C242" t="n">
-        <v>273.7999877929688</v>
+        <v>272.9100036621094</v>
       </c>
       <c r="D242" t="n">
-        <v>270.1799926757812</v>
+        <v>269.5499877929688</v>
       </c>
       <c r="E242" t="n">
-        <v>273.1400146484375</v>
+        <v>270</v>
       </c>
       <c r="F242" t="n">
-        <v>4687000</v>
+        <v>7214100</v>
       </c>
       <c r="G242" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B243" t="n">
-        <v>271.9700012207031</v>
+        <v>268.4500122070312</v>
       </c>
       <c r="C243" t="n">
-        <v>272.9100036621094</v>
+        <v>268.4500122070312</v>
       </c>
       <c r="D243" t="n">
-        <v>269.5499877929688</v>
+        <v>263.8299865722656</v>
       </c>
       <c r="E243" t="n">
-        <v>270</v>
+        <v>265.7699890136719</v>
       </c>
       <c r="F243" t="n">
-        <v>7214100</v>
+        <v>7306200</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B244" t="n">
-        <v>268.4500122070312</v>
+        <v>265.7799987792969</v>
       </c>
       <c r="C244" t="n">
-        <v>268.4500122070312</v>
+        <v>268.3800048828125</v>
       </c>
       <c r="D244" t="n">
-        <v>263.8299865722656</v>
+        <v>264.2699890136719</v>
       </c>
       <c r="E244" t="n">
-        <v>265.7699890136719</v>
+        <v>268.0400085449219</v>
       </c>
       <c r="F244" t="n">
-        <v>7306200</v>
+        <v>5765600</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B245" t="n">
-        <v>265.7799987792969</v>
+        <v>267.1300048828125</v>
       </c>
       <c r="C245" t="n">
-        <v>268.3800048828125</v>
+        <v>267.7699890136719</v>
       </c>
       <c r="D245" t="n">
-        <v>264.2699890136719</v>
+        <v>265.1700134277344</v>
       </c>
       <c r="E245" t="n">
-        <v>268.0400085449219</v>
+        <v>265.8500061035156</v>
       </c>
       <c r="F245" t="n">
-        <v>5765600</v>
+        <v>7900100</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B246" t="n">
-        <v>267.1300048828125</v>
+        <v>270.8299865722656</v>
       </c>
       <c r="C246" t="n">
-        <v>267.7699890136719</v>
+        <v>271.9100036621094</v>
       </c>
       <c r="D246" t="n">
-        <v>265.1700134277344</v>
+        <v>267.0199890136719</v>
       </c>
       <c r="E246" t="n">
-        <v>265.8500061035156</v>
+        <v>271.1900024414062</v>
       </c>
       <c r="F246" t="n">
-        <v>7900100</v>
+        <v>6033600</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B247" t="n">
-        <v>270.8299865722656</v>
+        <v>274.739990234375</v>
       </c>
       <c r="C247" t="n">
-        <v>271.9100036621094</v>
+        <v>281.0700073242188</v>
       </c>
       <c r="D247" t="n">
-        <v>267.0199890136719</v>
+        <v>273.5299987792969</v>
       </c>
       <c r="E247" t="n">
-        <v>271.1900024414062</v>
+        <v>275.2099914550781</v>
       </c>
       <c r="F247" t="n">
-        <v>6033600</v>
+        <v>7910600</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B248" t="n">
-        <v>274.739990234375</v>
+        <v>277.3200073242188</v>
       </c>
       <c r="C248" t="n">
-        <v>281.0700073242188</v>
+        <v>278.8900146484375</v>
       </c>
       <c r="D248" t="n">
-        <v>273.5299987792969</v>
+        <v>273.1600036621094</v>
       </c>
       <c r="E248" t="n">
-        <v>275.2099914550781</v>
+        <v>278.4299926757812</v>
       </c>
       <c r="F248" t="n">
-        <v>7910600</v>
+        <v>5940300</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B249" t="n">
-        <v>277.3200073242188</v>
+        <v>275.1300048828125</v>
       </c>
       <c r="C249" t="n">
-        <v>278.8900146484375</v>
+        <v>277.7999877929688</v>
       </c>
       <c r="D249" t="n">
-        <v>273.1600036621094</v>
+        <v>274.75</v>
       </c>
       <c r="E249" t="n">
-        <v>278.4299926757812</v>
+        <v>275.2300109863281</v>
       </c>
       <c r="F249" t="n">
-        <v>5940300</v>
+        <v>4320100</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B250" t="n">
-        <v>275.1300048828125</v>
+        <v>271.2799987792969</v>
       </c>
       <c r="C250" t="n">
-        <v>277.7999877929688</v>
+        <v>271.989990234375</v>
       </c>
       <c r="D250" t="n">
-        <v>274.75</v>
+        <v>266.8800048828125</v>
       </c>
       <c r="E250" t="n">
-        <v>275.2300109863281</v>
+        <v>269.1199951171875</v>
       </c>
       <c r="F250" t="n">
-        <v>4320100</v>
+        <v>8084700</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B251" t="n">
-        <v>271.2799987792969</v>
+        <v>268.510009765625</v>
       </c>
       <c r="C251" t="n">
-        <v>271.989990234375</v>
+        <v>270.1000061035156</v>
       </c>
       <c r="D251" t="n">
-        <v>266.8800048828125</v>
+        <v>266.7300109863281</v>
       </c>
       <c r="E251" t="n">
-        <v>269.1199951171875</v>
+        <v>267.0799865722656</v>
       </c>
       <c r="F251" t="n">
-        <v>8084700</v>
+        <v>6124600</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B252" t="n">
-        <v>268.510009765625</v>
+        <v>270.2099914550781</v>
       </c>
       <c r="C252" t="n">
-        <v>270.1000061035156</v>
+        <v>271.2699890136719</v>
       </c>
       <c r="D252" t="n">
-        <v>266.7300109863281</v>
+        <v>265.7200012207031</v>
       </c>
       <c r="E252" t="n">
-        <v>267.0799865722656</v>
+        <v>266.3500061035156</v>
       </c>
       <c r="F252" t="n">
-        <v>6124600</v>
+        <v>4929500</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10971,37 +10971,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>266.35</v>
+      </c>
+      <c r="D2" t="n">
         <v>267.08</v>
       </c>
-      <c r="D2" t="n">
-        <v>269.12</v>
-      </c>
       <c r="E2" t="n">
-        <v>268.51</v>
+        <v>270.21</v>
       </c>
       <c r="F2" t="n">
-        <v>270.1</v>
+        <v>271.27</v>
       </c>
       <c r="G2" t="n">
-        <v>266.73</v>
+        <v>265.72</v>
       </c>
       <c r="H2" t="n">
-        <v>5967693</v>
+        <v>4844617</v>
       </c>
       <c r="I2" t="n">
-        <v>7781654</v>
+        <v>7760762</v>
       </c>
       <c r="J2" t="n">
-        <v>643635675136</v>
+        <v>641876492288</v>
       </c>
       <c r="K2" t="n">
-        <v>30.947855</v>
+        <v>30.97093</v>
       </c>
       <c r="L2" t="n">
-        <v>21.700588</v>
+        <v>21.393576</v>
       </c>
       <c r="M2" t="n">
-        <v>8.550000000000001</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="N2" t="n">
         <v>281.07</v>
@@ -11013,7 +11013,7 @@
         <v>0.235</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="R2" t="n">
         <v>0.21482</v>
@@ -11037,7 +11037,7 @@
         <v>35.284</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.569436</v>
+        <v>7.5487475</v>
       </c>
       <c r="Z2" t="n">
         <v>-0.008999999999999999</v>
@@ -11049,7 +11049,7 @@
         <v>97929003008</v>
       </c>
       <c r="AC2" t="n">
-        <v>671913738240</v>
+        <v>670154489856</v>
       </c>
       <c r="AD2" t="n">
         <v>34872000512</v>
@@ -11076,7 +11076,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-10 18:59:34</t>
+          <t>2026-09-11 19:03:10</t>
         </is>
       </c>
     </row>

--- a/data/JNJ_data.xlsx
+++ b/data/JNJ_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="B2" t="n">
-        <v>171.8766472653515</v>
+        <v>173.7934495446803</v>
       </c>
       <c r="C2" t="n">
-        <v>174.9083323610806</v>
+        <v>174.8594234144472</v>
       </c>
       <c r="D2" t="n">
-        <v>171.759296719517</v>
+        <v>172.8252628178507</v>
       </c>
       <c r="E2" t="n">
-        <v>174.5660400390625</v>
+        <v>174.1357269287109</v>
       </c>
       <c r="F2" t="n">
-        <v>5792500</v>
+        <v>7220200</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="B3" t="n">
-        <v>173.7934495446803</v>
+        <v>173.8423467178463</v>
       </c>
       <c r="C3" t="n">
-        <v>174.8594234144472</v>
+        <v>175.0452495247757</v>
       </c>
       <c r="D3" t="n">
-        <v>172.8252628178507</v>
+        <v>173.0306372750611</v>
       </c>
       <c r="E3" t="n">
-        <v>174.1357269287109</v>
+        <v>173.4902801513672</v>
       </c>
       <c r="F3" t="n">
-        <v>7220200</v>
+        <v>4768100</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="B4" t="n">
-        <v>173.8423314280924</v>
+        <v>173.6565210631614</v>
       </c>
       <c r="C4" t="n">
-        <v>175.0452341292242</v>
+        <v>173.7054071692859</v>
       </c>
       <c r="D4" t="n">
-        <v>173.0306220566984</v>
+        <v>171.7788230370183</v>
       </c>
       <c r="E4" t="n">
-        <v>173.4902648925781</v>
+        <v>172.5709838867188</v>
       </c>
       <c r="F4" t="n">
-        <v>4768100</v>
+        <v>7959300</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="B5" t="n">
-        <v>173.6565364179341</v>
+        <v>172.8154864182272</v>
       </c>
       <c r="C5" t="n">
-        <v>173.7054225283811</v>
+        <v>174.5758041940759</v>
       </c>
       <c r="D5" t="n">
-        <v>171.7788382257642</v>
+        <v>172.6981209566707</v>
       </c>
       <c r="E5" t="n">
-        <v>172.5709991455078</v>
+        <v>173.294677734375</v>
       </c>
       <c r="F5" t="n">
-        <v>7959300</v>
+        <v>6714900</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B6" t="n">
-        <v>172.815501634823</v>
+        <v>172.7078974682877</v>
       </c>
       <c r="C6" t="n">
-        <v>174.5758195656696</v>
+        <v>173.1186392474049</v>
       </c>
       <c r="D6" t="n">
-        <v>172.6981361629323</v>
+        <v>170.0380535202773</v>
       </c>
       <c r="E6" t="n">
-        <v>173.2946929931641</v>
+        <v>170.3216705322266</v>
       </c>
       <c r="F6" t="n">
-        <v>6714900</v>
+        <v>8200900</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B7" t="n">
-        <v>172.7078819957212</v>
+        <v>170.8399892159715</v>
       </c>
       <c r="C7" t="n">
-        <v>173.1186237380408</v>
+        <v>173.2555537932855</v>
       </c>
       <c r="D7" t="n">
-        <v>170.038038286897</v>
+        <v>169.5099618168128</v>
       </c>
       <c r="E7" t="n">
-        <v>170.3216552734375</v>
+        <v>172.3069305419922</v>
       </c>
       <c r="F7" t="n">
-        <v>8200900</v>
+        <v>25621000</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B8" t="n">
-        <v>170.8400043448543</v>
+        <v>172.2091158723778</v>
       </c>
       <c r="C8" t="n">
-        <v>173.2555691360807</v>
+        <v>172.7469973036919</v>
       </c>
       <c r="D8" t="n">
-        <v>169.5099768279138</v>
+        <v>170.2825318781694</v>
       </c>
       <c r="E8" t="n">
-        <v>172.3069458007812</v>
+        <v>170.3705596923828</v>
       </c>
       <c r="F8" t="n">
-        <v>25621000</v>
+        <v>7193900</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B9" t="n">
-        <v>172.2091312958323</v>
+        <v>171.0355829083302</v>
       </c>
       <c r="C9" t="n">
-        <v>172.7470127753203</v>
+        <v>173.0697433912989</v>
       </c>
       <c r="D9" t="n">
-        <v>170.2825471290745</v>
+        <v>170.9769076413454</v>
       </c>
       <c r="E9" t="n">
-        <v>170.3705749511719</v>
+        <v>172.6883392333984</v>
       </c>
       <c r="F9" t="n">
-        <v>7193900</v>
+        <v>8350400</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B10" t="n">
-        <v>171.0355980210813</v>
+        <v>172.2580322171388</v>
       </c>
       <c r="C10" t="n">
-        <v>173.0697586837889</v>
+        <v>173.0501781580241</v>
       </c>
       <c r="D10" t="n">
-        <v>170.9769227489119</v>
+        <v>171.8668538263927</v>
       </c>
       <c r="E10" t="n">
-        <v>172.6883544921875</v>
+        <v>172.7959136962891</v>
       </c>
       <c r="F10" t="n">
-        <v>8350400</v>
+        <v>6676800</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B11" t="n">
-        <v>172.2580322171388</v>
+        <v>173.2946701929729</v>
       </c>
       <c r="C11" t="n">
-        <v>173.0501781580241</v>
+        <v>174.4682202999683</v>
       </c>
       <c r="D11" t="n">
-        <v>171.8668538263927</v>
+        <v>172.0331071855151</v>
       </c>
       <c r="E11" t="n">
-        <v>172.7959136962891</v>
+        <v>173.81298828125</v>
       </c>
       <c r="F11" t="n">
-        <v>6676800</v>
+        <v>8475000</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B12" t="n">
-        <v>173.2946549796862</v>
+        <v>174.663806775199</v>
       </c>
       <c r="C12" t="n">
-        <v>174.4682049836574</v>
+        <v>175.9449330497278</v>
       </c>
       <c r="D12" t="n">
-        <v>172.0330920829792</v>
+        <v>173.4120181311941</v>
       </c>
       <c r="E12" t="n">
-        <v>173.8129730224609</v>
+        <v>175.7493438720703</v>
       </c>
       <c r="F12" t="n">
-        <v>8475000</v>
+        <v>8634400</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B13" t="n">
-        <v>174.6638219397404</v>
+        <v>175.8667353595665</v>
       </c>
       <c r="C13" t="n">
-        <v>175.9449483254981</v>
+        <v>177.8617693123808</v>
       </c>
       <c r="D13" t="n">
-        <v>173.4120331870535</v>
+        <v>175.837397722209</v>
       </c>
       <c r="E13" t="n">
-        <v>175.7493591308594</v>
+        <v>177.6172790527344</v>
       </c>
       <c r="F13" t="n">
-        <v>8634400</v>
+        <v>8597100</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B14" t="n">
-        <v>175.8667202511636</v>
+        <v>177.6955105019011</v>
       </c>
       <c r="C14" t="n">
-        <v>177.861754032588</v>
+        <v>181.8909715434583</v>
       </c>
       <c r="D14" t="n">
-        <v>175.8373826163265</v>
+        <v>177.0794052199421</v>
       </c>
       <c r="E14" t="n">
-        <v>177.6172637939453</v>
+        <v>181.3335266113281</v>
       </c>
       <c r="F14" t="n">
-        <v>8597100</v>
+        <v>11569000</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B15" t="n">
-        <v>177.6954955492426</v>
+        <v>181.9007297071846</v>
       </c>
       <c r="C15" t="n">
-        <v>181.8909562377616</v>
+        <v>182.4483854305311</v>
       </c>
       <c r="D15" t="n">
-        <v>177.0793903191274</v>
+        <v>179.8567949816596</v>
       </c>
       <c r="E15" t="n">
-        <v>181.3335113525391</v>
+        <v>181.9496307373047</v>
       </c>
       <c r="F15" t="n">
-        <v>11569000</v>
+        <v>13063800</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B16" t="n">
-        <v>181.9007144524965</v>
+        <v>180.1306211004154</v>
       </c>
       <c r="C16" t="n">
-        <v>182.4483701299151</v>
+        <v>182.4777212984756</v>
       </c>
       <c r="D16" t="n">
-        <v>179.8567798983815</v>
+        <v>180.0328190411216</v>
       </c>
       <c r="E16" t="n">
-        <v>181.9496154785156</v>
+        <v>181.8811645507812</v>
       </c>
       <c r="F16" t="n">
-        <v>13063800</v>
+        <v>7728100</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B17" t="n">
-        <v>180.1306211004154</v>
+        <v>182.9373790605305</v>
       </c>
       <c r="C17" t="n">
-        <v>182.4777212984756</v>
+        <v>185.5974341276275</v>
       </c>
       <c r="D17" t="n">
-        <v>180.0328190411216</v>
+        <v>182.7906908821062</v>
       </c>
       <c r="E17" t="n">
-        <v>181.8811645507812</v>
+        <v>184.4825592041016</v>
       </c>
       <c r="F17" t="n">
-        <v>7728100</v>
+        <v>8675100</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B18" t="n">
-        <v>182.9373790605305</v>
+        <v>183.8566452365672</v>
       </c>
       <c r="C18" t="n">
-        <v>185.5974341276275</v>
+        <v>185.7343283333897</v>
       </c>
       <c r="D18" t="n">
-        <v>182.7906908821062</v>
+        <v>183.2405251076493</v>
       </c>
       <c r="E18" t="n">
-        <v>184.4825592041016</v>
+        <v>184.0131225585938</v>
       </c>
       <c r="F18" t="n">
-        <v>8675100</v>
+        <v>5806100</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B19" t="n">
-        <v>183.8566604823808</v>
+        <v>179.7198804430833</v>
       </c>
       <c r="C19" t="n">
-        <v>185.7343437349051</v>
+        <v>185.0595386501542</v>
       </c>
       <c r="D19" t="n">
-        <v>183.2405403023728</v>
+        <v>178.9081710978327</v>
       </c>
       <c r="E19" t="n">
-        <v>184.0131378173828</v>
+        <v>184.7270355224609</v>
       </c>
       <c r="F19" t="n">
-        <v>5806100</v>
+        <v>8776800</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B20" t="n">
-        <v>179.7198952882722</v>
+        <v>184.7074643396089</v>
       </c>
       <c r="C20" t="n">
-        <v>185.0595539364086</v>
+        <v>186.0277174802343</v>
       </c>
       <c r="D20" t="n">
-        <v>178.908185875973</v>
+        <v>184.1206967723854</v>
       </c>
       <c r="E20" t="n">
-        <v>184.72705078125</v>
+        <v>185.5093994140625</v>
       </c>
       <c r="F20" t="n">
-        <v>8776800</v>
+        <v>5751200</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B21" t="n">
-        <v>184.707479532436</v>
+        <v>185.8125748295944</v>
       </c>
       <c r="C21" t="n">
-        <v>186.0277327816568</v>
+        <v>187.8662987309212</v>
       </c>
       <c r="D21" t="n">
-        <v>184.1207119169489</v>
+        <v>185.5485212028525</v>
       </c>
       <c r="E21" t="n">
-        <v>185.5094146728516</v>
+        <v>186.8687744140625</v>
       </c>
       <c r="F21" t="n">
-        <v>5751200</v>
+        <v>7484800</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B22" t="n">
-        <v>185.8125748295944</v>
+        <v>187.7782713984262</v>
       </c>
       <c r="C22" t="n">
-        <v>187.8662987309212</v>
+        <v>187.8369615886886</v>
       </c>
       <c r="D22" t="n">
-        <v>185.5485212028525</v>
+        <v>185.6658871464611</v>
       </c>
       <c r="E22" t="n">
-        <v>186.8687744140625</v>
+        <v>186.5167083740234</v>
       </c>
       <c r="F22" t="n">
-        <v>7484800</v>
+        <v>9598000</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B23" t="n">
-        <v>187.7782713984262</v>
+        <v>185.6463385126197</v>
       </c>
       <c r="C23" t="n">
-        <v>187.8369615886886</v>
+        <v>187.0839423771316</v>
       </c>
       <c r="D23" t="n">
-        <v>185.6658871464611</v>
+        <v>185.1084569778533</v>
       </c>
       <c r="E23" t="n">
-        <v>186.5167083740234</v>
+        <v>186.6927490234375</v>
       </c>
       <c r="F23" t="n">
-        <v>9598000</v>
+        <v>7979500</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B24" t="n">
-        <v>185.646323339356</v>
+        <v>188.6682159172342</v>
       </c>
       <c r="C24" t="n">
-        <v>187.0839270863694</v>
+        <v>190.1155938776849</v>
       </c>
       <c r="D24" t="n">
-        <v>185.1084418485517</v>
+        <v>181.7833777150234</v>
       </c>
       <c r="E24" t="n">
-        <v>186.6927337646484</v>
+        <v>186.6438446044922</v>
       </c>
       <c r="F24" t="n">
-        <v>7979500</v>
+        <v>13613300</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B25" t="n">
-        <v>188.6682159172342</v>
+        <v>187.2599678902216</v>
       </c>
       <c r="C25" t="n">
-        <v>190.1155938776849</v>
+        <v>189.3039177190138</v>
       </c>
       <c r="D25" t="n">
-        <v>181.7833777150234</v>
+        <v>185.1280200754296</v>
       </c>
       <c r="E25" t="n">
-        <v>186.6438446044922</v>
+        <v>186.9568023681641</v>
       </c>
       <c r="F25" t="n">
-        <v>13613300</v>
+        <v>9473000</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B26" t="n">
-        <v>187.2599526066892</v>
+        <v>187.1230406678187</v>
       </c>
       <c r="C26" t="n">
-        <v>189.303902268661</v>
+        <v>188.7953604231518</v>
       </c>
       <c r="D26" t="n">
-        <v>185.1280049658996</v>
+        <v>186.2330926405801</v>
       </c>
       <c r="E26" t="n">
-        <v>186.956787109375</v>
+        <v>187.8858489990234</v>
       </c>
       <c r="F26" t="n">
-        <v>9473000</v>
+        <v>10611800</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B27" t="n">
-        <v>187.1230406678187</v>
+        <v>188.2574758352493</v>
       </c>
       <c r="C27" t="n">
-        <v>188.7953604231518</v>
+        <v>189.3332388090219</v>
       </c>
       <c r="D27" t="n">
-        <v>186.2330926405801</v>
+        <v>187.4555407234371</v>
       </c>
       <c r="E27" t="n">
-        <v>187.8858489990234</v>
+        <v>188.9616088867188</v>
       </c>
       <c r="F27" t="n">
-        <v>10611800</v>
+        <v>7764400</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B28" t="n">
-        <v>188.2574758352493</v>
+        <v>189.2354242017374</v>
       </c>
       <c r="C28" t="n">
-        <v>189.3332388090219</v>
+        <v>190.1938216550539</v>
       </c>
       <c r="D28" t="n">
-        <v>187.4555407234371</v>
+        <v>188.0912117995895</v>
       </c>
       <c r="E28" t="n">
-        <v>188.9616088867188</v>
+        <v>189.4505767822266</v>
       </c>
       <c r="F28" t="n">
-        <v>7764400</v>
+        <v>8034700</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B29" t="n">
-        <v>189.2354242017374</v>
+        <v>188.7562393006838</v>
       </c>
       <c r="C29" t="n">
-        <v>190.1938216550539</v>
+        <v>189.2843465750772</v>
       </c>
       <c r="D29" t="n">
-        <v>188.0912117995895</v>
+        <v>187.5435772620767</v>
       </c>
       <c r="E29" t="n">
-        <v>189.4505767822266</v>
+        <v>187.6511535644531</v>
       </c>
       <c r="F29" t="n">
-        <v>8034700</v>
+        <v>6716000</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B30" t="n">
-        <v>188.756223952035</v>
+        <v>187.768489042997</v>
       </c>
       <c r="C30" t="n">
-        <v>189.2843311834856</v>
+        <v>189.186529335124</v>
       </c>
       <c r="D30" t="n">
-        <v>187.5435620120352</v>
+        <v>187.553336455502</v>
       </c>
       <c r="E30" t="n">
-        <v>187.6511383056641</v>
+        <v>188.6877746582031</v>
       </c>
       <c r="F30" t="n">
-        <v>6716000</v>
+        <v>6343100</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B31" t="n">
-        <v>187.768489042997</v>
+        <v>188.3161623201141</v>
       </c>
       <c r="C31" t="n">
-        <v>189.186529335124</v>
+        <v>189.7244285069409</v>
       </c>
       <c r="D31" t="n">
-        <v>187.553336455502</v>
+        <v>187.3186379506951</v>
       </c>
       <c r="E31" t="n">
-        <v>188.6877746582031</v>
+        <v>188.2281494140625</v>
       </c>
       <c r="F31" t="n">
-        <v>6343100</v>
+        <v>8882500</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B32" t="n">
-        <v>188.3161470541903</v>
+        <v>187.9640678233363</v>
       </c>
       <c r="C32" t="n">
-        <v>189.7244131268554</v>
+        <v>188.0716441111252</v>
       </c>
       <c r="D32" t="n">
-        <v>187.318622765636</v>
+        <v>185.2453379201237</v>
       </c>
       <c r="E32" t="n">
-        <v>188.2281341552734</v>
+        <v>186.2037353515625</v>
       </c>
       <c r="F32" t="n">
-        <v>8882500</v>
+        <v>6903400</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B33" t="n">
-        <v>187.9640678233363</v>
+        <v>185.8027915483585</v>
       </c>
       <c r="C33" t="n">
-        <v>188.0716441111252</v>
+        <v>186.5949374675263</v>
       </c>
       <c r="D33" t="n">
-        <v>185.2453379201237</v>
+        <v>185.3529229810849</v>
       </c>
       <c r="E33" t="n">
-        <v>186.2037353515625</v>
+        <v>186.10595703125</v>
       </c>
       <c r="F33" t="n">
-        <v>6903400</v>
+        <v>7126000</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B34" t="n">
-        <v>185.8028067822911</v>
+        <v>185.0888771601165</v>
       </c>
       <c r="C34" t="n">
-        <v>186.5949527664067</v>
+        <v>185.3333673885486</v>
       </c>
       <c r="D34" t="n">
-        <v>185.3529381781329</v>
+        <v>182.5070609447738</v>
       </c>
       <c r="E34" t="n">
-        <v>186.1059722900391</v>
+        <v>182.8102264404297</v>
       </c>
       <c r="F34" t="n">
-        <v>7126000</v>
+        <v>8329500</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B35" t="n">
-        <v>185.0888617111332</v>
+        <v>182.5852901845839</v>
       </c>
       <c r="C35" t="n">
-        <v>185.3333519191582</v>
+        <v>182.9764834833836</v>
       </c>
       <c r="D35" t="n">
-        <v>182.5070457112893</v>
+        <v>180.5902565894498</v>
       </c>
       <c r="E35" t="n">
-        <v>182.8102111816406</v>
+        <v>182.4875030517578</v>
       </c>
       <c r="F35" t="n">
-        <v>8329500</v>
+        <v>10551100</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B36" t="n">
-        <v>182.5853054515495</v>
+        <v>182.9569151035874</v>
       </c>
       <c r="C36" t="n">
-        <v>182.9764987830591</v>
+        <v>185.2062280122887</v>
       </c>
       <c r="D36" t="n">
-        <v>180.5902716895996</v>
+        <v>182.7906635520636</v>
       </c>
       <c r="E36" t="n">
-        <v>182.4875183105469</v>
+        <v>184.8834991455078</v>
       </c>
       <c r="F36" t="n">
-        <v>10551100</v>
+        <v>7072500</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B37" t="n">
-        <v>182.9569302033718</v>
+        <v>183.3285602019948</v>
       </c>
       <c r="C37" t="n">
-        <v>185.2062432977132</v>
+        <v>185.3235939082472</v>
       </c>
       <c r="D37" t="n">
-        <v>182.7906786381269</v>
+        <v>182.6439756215902</v>
       </c>
       <c r="E37" t="n">
-        <v>184.8835144042969</v>
+        <v>184.7074737548828</v>
       </c>
       <c r="F37" t="n">
-        <v>7072500</v>
+        <v>8791700</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B38" t="n">
-        <v>183.3285450571186</v>
+        <v>184.834617119156</v>
       </c>
       <c r="C38" t="n">
-        <v>185.3235785985601</v>
+        <v>184.8639547534701</v>
       </c>
       <c r="D38" t="n">
-        <v>182.6439605332679</v>
+        <v>181.4313172362143</v>
       </c>
       <c r="E38" t="n">
-        <v>184.7074584960938</v>
+        <v>182.1549987792969</v>
       </c>
       <c r="F38" t="n">
-        <v>8791700</v>
+        <v>7542600</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B39" t="n">
-        <v>184.8346326024117</v>
+        <v>182.7124378793119</v>
       </c>
       <c r="C39" t="n">
-        <v>184.8639702391834</v>
+        <v>183.680624548461</v>
       </c>
       <c r="D39" t="n">
-        <v>181.4313324343818</v>
+        <v>181.5290986170187</v>
       </c>
       <c r="E39" t="n">
-        <v>182.1550140380859</v>
+        <v>182.7417755126953</v>
       </c>
       <c r="F39" t="n">
-        <v>7542600</v>
+        <v>7209400</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B40" t="n">
-        <v>182.7124378793119</v>
+        <v>182.5266206937376</v>
       </c>
       <c r="C40" t="n">
-        <v>183.680624548461</v>
+        <v>183.6903965454173</v>
       </c>
       <c r="D40" t="n">
-        <v>181.5290986170187</v>
+        <v>181.3139438128489</v>
       </c>
       <c r="E40" t="n">
-        <v>182.7417755126953</v>
+        <v>181.9007263183594</v>
       </c>
       <c r="F40" t="n">
-        <v>7209400</v>
+        <v>5049400</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B41" t="n">
-        <v>182.5266206937376</v>
+        <v>182.6439716214627</v>
       </c>
       <c r="C41" t="n">
-        <v>183.6903965454173</v>
+        <v>183.3872314530524</v>
       </c>
       <c r="D41" t="n">
-        <v>181.3139438128489</v>
+        <v>181.2846065725014</v>
       </c>
       <c r="E41" t="n">
-        <v>181.9007263183594</v>
+        <v>182.8493499755859</v>
       </c>
       <c r="F41" t="n">
-        <v>5049400</v>
+        <v>6767400</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B42" t="n">
-        <v>182.6439716214627</v>
+        <v>183.6024034971757</v>
       </c>
       <c r="C42" t="n">
-        <v>183.3872314530524</v>
+        <v>184.1989603040272</v>
       </c>
       <c r="D42" t="n">
-        <v>181.2846065725014</v>
+        <v>181.6073547007375</v>
       </c>
       <c r="E42" t="n">
-        <v>182.8493499755859</v>
+        <v>182.4581909179688</v>
       </c>
       <c r="F42" t="n">
-        <v>6767400</v>
+        <v>6959200</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B43" t="n">
-        <v>183.6023881426973</v>
+        <v>181.9007248187872</v>
       </c>
       <c r="C43" t="n">
-        <v>184.1989448996594</v>
+        <v>184.2673883725038</v>
       </c>
       <c r="D43" t="n">
-        <v>181.607339513103</v>
+        <v>181.0401144637998</v>
       </c>
       <c r="E43" t="n">
-        <v>182.4581756591797</v>
+        <v>184.2576141357422</v>
       </c>
       <c r="F43" t="n">
-        <v>6959200</v>
+        <v>5323800</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B44" t="n">
-        <v>181.9007248187872</v>
+        <v>185.2160176409071</v>
       </c>
       <c r="C44" t="n">
-        <v>184.2673883725038</v>
+        <v>189.6461794051158</v>
       </c>
       <c r="D44" t="n">
-        <v>181.0401144637998</v>
+        <v>184.8835145102268</v>
       </c>
       <c r="E44" t="n">
-        <v>184.2576141357422</v>
+        <v>189.5581665039062</v>
       </c>
       <c r="F44" t="n">
-        <v>5323800</v>
+        <v>7465600</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B45" t="n">
-        <v>185.2160176409071</v>
+        <v>189.0985363418636</v>
       </c>
       <c r="C45" t="n">
-        <v>189.6461794051158</v>
+        <v>191.24027328305</v>
       </c>
       <c r="D45" t="n">
-        <v>184.8835145102268</v>
+        <v>188.8149342225856</v>
       </c>
       <c r="E45" t="n">
-        <v>189.5581665039062</v>
+        <v>190.1058349609375</v>
       </c>
       <c r="F45" t="n">
-        <v>7465600</v>
+        <v>8803000</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B46" t="n">
-        <v>189.0985363418636</v>
+        <v>189.9297961094911</v>
       </c>
       <c r="C46" t="n">
-        <v>191.24027328305</v>
+        <v>191.6803395836668</v>
       </c>
       <c r="D46" t="n">
-        <v>188.8149342225856</v>
+        <v>189.1865362627468</v>
       </c>
       <c r="E46" t="n">
-        <v>190.1058349609375</v>
+        <v>190.9468688964844</v>
       </c>
       <c r="F46" t="n">
-        <v>8803000</v>
+        <v>8631600</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B47" t="n">
-        <v>189.9297961094911</v>
+        <v>190.7023809412554</v>
       </c>
       <c r="C47" t="n">
-        <v>191.6803395836668</v>
+        <v>192.8343286012861</v>
       </c>
       <c r="D47" t="n">
-        <v>189.1865362627468</v>
+        <v>189.2843405802947</v>
       </c>
       <c r="E47" t="n">
-        <v>190.9468688964844</v>
+        <v>191.6118774414062</v>
       </c>
       <c r="F47" t="n">
-        <v>8631600</v>
+        <v>8824800</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B48" t="n">
-        <v>190.7023657548931</v>
+        <v>192.6191743663224</v>
       </c>
       <c r="C48" t="n">
-        <v>192.8343132451486</v>
+        <v>195.8659966081333</v>
       </c>
       <c r="D48" t="n">
-        <v>189.2843255068563</v>
+        <v>191.5825233369659</v>
       </c>
       <c r="E48" t="n">
-        <v>191.6118621826172</v>
+        <v>195.1814270019531</v>
       </c>
       <c r="F48" t="n">
-        <v>8824800</v>
+        <v>13257000</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B49" t="n">
-        <v>192.619189424801</v>
+        <v>194.6240068730782</v>
       </c>
       <c r="C49" t="n">
-        <v>195.8660119204403</v>
+        <v>195.8855848784209</v>
       </c>
       <c r="D49" t="n">
-        <v>191.5825383144018</v>
+        <v>194.1545897867298</v>
       </c>
       <c r="E49" t="n">
-        <v>195.1814422607422</v>
+        <v>195.5921936035156</v>
       </c>
       <c r="F49" t="n">
-        <v>13257000</v>
+        <v>12468600</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B50" t="n">
-        <v>194.6239916898205</v>
+        <v>195.5921832139753</v>
       </c>
       <c r="C50" t="n">
-        <v>195.8855695967434</v>
+        <v>198.9954830235987</v>
       </c>
       <c r="D50" t="n">
-        <v>194.1545746400929</v>
+        <v>194.9858522212118</v>
       </c>
       <c r="E50" t="n">
-        <v>195.5921783447266</v>
+        <v>198.0468597412109</v>
       </c>
       <c r="F50" t="n">
-        <v>12468600</v>
+        <v>14690800</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B51" t="n">
-        <v>195.5921832139753</v>
+        <v>197.5480876884036</v>
       </c>
       <c r="C51" t="n">
-        <v>198.9954830235987</v>
+        <v>200.0027639999573</v>
       </c>
       <c r="D51" t="n">
-        <v>194.9858522212118</v>
+        <v>197.1275716942422</v>
       </c>
       <c r="E51" t="n">
-        <v>198.0468597412109</v>
+        <v>198.5945129394531</v>
       </c>
       <c r="F51" t="n">
-        <v>14690800</v>
+        <v>10612600</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B52" t="n">
-        <v>197.5481028667918</v>
+        <v>199.4648944074351</v>
       </c>
       <c r="C52" t="n">
-        <v>200.0027793669477</v>
+        <v>202.3792134580423</v>
       </c>
       <c r="D52" t="n">
-        <v>197.1275868403205</v>
+        <v>198.5162712230181</v>
       </c>
       <c r="E52" t="n">
-        <v>198.5945281982422</v>
+        <v>199.4062042236328</v>
       </c>
       <c r="F52" t="n">
-        <v>10612600</v>
+        <v>13189100</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B53" t="n">
-        <v>199.4649096707152</v>
+        <v>199.2204251313988</v>
       </c>
       <c r="C53" t="n">
-        <v>202.3792289443294</v>
+        <v>201.5772996022027</v>
       </c>
       <c r="D53" t="n">
-        <v>198.5162864137085</v>
+        <v>198.5260663138595</v>
       </c>
       <c r="E53" t="n">
-        <v>199.4062194824219</v>
+        <v>201.5088500976562</v>
       </c>
       <c r="F53" t="n">
-        <v>13189100</v>
+        <v>14803900</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,25 +1821,25 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B54" t="n">
-        <v>199.2204251313988</v>
+        <v>201.9320337594338</v>
       </c>
       <c r="C54" t="n">
-        <v>201.5772996022027</v>
+        <v>204.4318344688182</v>
       </c>
       <c r="D54" t="n">
-        <v>198.5260663138595</v>
+        <v>201.9320337594338</v>
       </c>
       <c r="E54" t="n">
-        <v>201.5088500976562</v>
+        <v>203.3984527587891</v>
       </c>
       <c r="F54" t="n">
-        <v>14803900</v>
+        <v>10275300</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -1847,25 +1847,25 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B55" t="n">
-        <v>201.9320337594338</v>
+        <v>203.2213139605992</v>
       </c>
       <c r="C55" t="n">
-        <v>204.4318344688182</v>
+        <v>204.5204108409229</v>
       </c>
       <c r="D55" t="n">
-        <v>201.9320337594338</v>
+        <v>202.6800173366119</v>
       </c>
       <c r="E55" t="n">
-        <v>203.3984527587891</v>
+        <v>204.2743682861328</v>
       </c>
       <c r="F55" t="n">
-        <v>10275300</v>
+        <v>6729000</v>
       </c>
       <c r="G55" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B56" t="n">
-        <v>203.2212987804707</v>
+        <v>203.723236152328</v>
       </c>
       <c r="C56" t="n">
-        <v>204.520395563755</v>
+        <v>204.1759610624769</v>
       </c>
       <c r="D56" t="n">
-        <v>202.6800021969169</v>
+        <v>201.390757529436</v>
       </c>
       <c r="E56" t="n">
-        <v>204.2743530273438</v>
+        <v>203.6445007324219</v>
       </c>
       <c r="F56" t="n">
-        <v>6729000</v>
+        <v>5638300</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B57" t="n">
-        <v>203.723236152328</v>
+        <v>203.2311644535453</v>
       </c>
       <c r="C57" t="n">
-        <v>204.1759610624769</v>
+        <v>204.4121657955886</v>
       </c>
       <c r="D57" t="n">
-        <v>201.390757529436</v>
+        <v>202.0895233154297</v>
       </c>
       <c r="E57" t="n">
-        <v>203.6445007324219</v>
+        <v>202.0895233154297</v>
       </c>
       <c r="F57" t="n">
-        <v>5638300</v>
+        <v>8473700</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B58" t="n">
-        <v>203.2311491085565</v>
+        <v>201.9910999780921</v>
       </c>
       <c r="C58" t="n">
-        <v>204.4121503614282</v>
+        <v>202.3552381514841</v>
       </c>
       <c r="D58" t="n">
-        <v>202.0895080566406</v>
+        <v>199.8849763223805</v>
       </c>
       <c r="E58" t="n">
-        <v>202.0895080566406</v>
+        <v>202.1682434082031</v>
       </c>
       <c r="F58" t="n">
-        <v>8473700</v>
+        <v>8393600</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B59" t="n">
-        <v>201.9910847326731</v>
+        <v>202.6406353348706</v>
       </c>
       <c r="C59" t="n">
-        <v>202.3552228785814</v>
+        <v>203.7429161551587</v>
       </c>
       <c r="D59" t="n">
-        <v>199.8849612359226</v>
+        <v>201.7450518785209</v>
       </c>
       <c r="E59" t="n">
-        <v>202.1682281494141</v>
+        <v>202.0796661376953</v>
       </c>
       <c r="F59" t="n">
-        <v>8393600</v>
+        <v>8363300</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B60" t="n">
-        <v>202.6406353348706</v>
+        <v>201.3513646031548</v>
       </c>
       <c r="C60" t="n">
-        <v>203.7429161551587</v>
+        <v>201.6170947448128</v>
       </c>
       <c r="D60" t="n">
-        <v>201.7450518785209</v>
+        <v>198.5169648220319</v>
       </c>
       <c r="E60" t="n">
-        <v>202.0796661376953</v>
+        <v>199.2747650146484</v>
       </c>
       <c r="F60" t="n">
-        <v>8363300</v>
+        <v>9049900</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B61" t="n">
-        <v>201.3513800209524</v>
+        <v>199.7668717489871</v>
       </c>
       <c r="C61" t="n">
-        <v>201.6171101829578</v>
+        <v>200.2294329646455</v>
       </c>
       <c r="D61" t="n">
-        <v>198.516980022795</v>
+        <v>197.6312241234294</v>
       </c>
       <c r="E61" t="n">
-        <v>199.2747802734375</v>
+        <v>198.7334899902344</v>
       </c>
       <c r="F61" t="n">
-        <v>9049900</v>
+        <v>7785300</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B62" t="n">
-        <v>199.7668717489871</v>
+        <v>199.4519359184436</v>
       </c>
       <c r="C62" t="n">
-        <v>200.2294329646455</v>
+        <v>200.0424290268597</v>
       </c>
       <c r="D62" t="n">
-        <v>197.6312241234294</v>
+        <v>197.8083734899551</v>
       </c>
       <c r="E62" t="n">
-        <v>198.7334899902344</v>
+        <v>198.4283905029297</v>
       </c>
       <c r="F62" t="n">
-        <v>7785300</v>
+        <v>7785700</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B63" t="n">
-        <v>199.4519359184436</v>
+        <v>199.7078130861464</v>
       </c>
       <c r="C63" t="n">
-        <v>200.0424290268597</v>
+        <v>202.2863341775681</v>
       </c>
       <c r="D63" t="n">
-        <v>197.8083734899551</v>
+        <v>196.7454662214423</v>
       </c>
       <c r="E63" t="n">
-        <v>198.4283905029297</v>
+        <v>196.794677734375</v>
       </c>
       <c r="F63" t="n">
-        <v>7785700</v>
+        <v>7509400</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B64" t="n">
-        <v>199.7078130861464</v>
+        <v>197.4146980881505</v>
       </c>
       <c r="C64" t="n">
-        <v>202.2863341775681</v>
+        <v>203.5264016771889</v>
       </c>
       <c r="D64" t="n">
-        <v>196.7454662214423</v>
+        <v>197.011184699407</v>
       </c>
       <c r="E64" t="n">
-        <v>196.794677734375</v>
+        <v>203.2705078125</v>
       </c>
       <c r="F64" t="n">
-        <v>7509400</v>
+        <v>11599800</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B65" t="n">
-        <v>197.4146980881505</v>
+        <v>204.608977678963</v>
       </c>
       <c r="C65" t="n">
-        <v>203.5264016771889</v>
+        <v>207.8961175457048</v>
       </c>
       <c r="D65" t="n">
-        <v>197.011184699407</v>
+        <v>204.5400935742317</v>
       </c>
       <c r="E65" t="n">
-        <v>203.2705078125</v>
+        <v>206.6855773925781</v>
       </c>
       <c r="F65" t="n">
-        <v>11599800</v>
+        <v>9009000</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B66" t="n">
-        <v>204.608977678963</v>
+        <v>206.951303914036</v>
       </c>
       <c r="C66" t="n">
-        <v>207.8961175457048</v>
+        <v>208.9098079752741</v>
       </c>
       <c r="D66" t="n">
-        <v>204.5400935742317</v>
+        <v>205.6522070875063</v>
       </c>
       <c r="E66" t="n">
-        <v>206.6855773925781</v>
+        <v>208.2307281494141</v>
       </c>
       <c r="F66" t="n">
-        <v>9009000</v>
+        <v>6922700</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B67" t="n">
-        <v>206.951303914036</v>
+        <v>207.0202168563343</v>
       </c>
       <c r="C67" t="n">
-        <v>208.9098079752741</v>
+        <v>211.7835972337083</v>
       </c>
       <c r="D67" t="n">
-        <v>205.6522070875063</v>
+        <v>205.7014173161141</v>
       </c>
       <c r="E67" t="n">
-        <v>208.2307281494141</v>
+        <v>210.7797393798828</v>
       </c>
       <c r="F67" t="n">
-        <v>6922700</v>
+        <v>8467000</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B68" t="n">
-        <v>207.0202168563343</v>
+        <v>210.6124287318692</v>
       </c>
       <c r="C68" t="n">
-        <v>211.7835972337083</v>
+        <v>211.3308687932753</v>
       </c>
       <c r="D68" t="n">
-        <v>205.7014173161141</v>
+        <v>205.5045828472482</v>
       </c>
       <c r="E68" t="n">
-        <v>210.7797393798828</v>
+        <v>205.9868316650391</v>
       </c>
       <c r="F68" t="n">
-        <v>8467000</v>
+        <v>9949800</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B69" t="n">
-        <v>210.6124287318692</v>
+        <v>206.0754116038892</v>
       </c>
       <c r="C69" t="n">
-        <v>211.3308687932753</v>
+        <v>208.1716990780921</v>
       </c>
       <c r="D69" t="n">
-        <v>205.5045828472482</v>
+        <v>205.1601404638689</v>
       </c>
       <c r="E69" t="n">
-        <v>205.9868316650391</v>
+        <v>207.0005340576172</v>
       </c>
       <c r="F69" t="n">
-        <v>9949800</v>
+        <v>8457600</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B70" t="n">
-        <v>206.0753964132944</v>
+        <v>206.478915988136</v>
       </c>
       <c r="C70" t="n">
-        <v>208.1716837329721</v>
+        <v>207.7189650641044</v>
       </c>
       <c r="D70" t="n">
-        <v>205.1601253407421</v>
+        <v>204.4712003216206</v>
       </c>
       <c r="E70" t="n">
-        <v>207.0005187988281</v>
+        <v>205.0124969482422</v>
       </c>
       <c r="F70" t="n">
-        <v>8457600</v>
+        <v>7499900</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B71" t="n">
-        <v>206.478915988136</v>
+        <v>204.2743601070968</v>
       </c>
       <c r="C71" t="n">
-        <v>207.7189650641044</v>
+        <v>205.927773818052</v>
       </c>
       <c r="D71" t="n">
-        <v>204.4712003216206</v>
+        <v>202.768580933452</v>
       </c>
       <c r="E71" t="n">
-        <v>205.0124969482422</v>
+        <v>203.1031951904297</v>
       </c>
       <c r="F71" t="n">
-        <v>7499900</v>
+        <v>24803900</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B72" t="n">
-        <v>204.2743601070968</v>
+        <v>202.8670125241163</v>
       </c>
       <c r="C72" t="n">
-        <v>205.927773818052</v>
+        <v>204.7861414522214</v>
       </c>
       <c r="D72" t="n">
-        <v>202.768580933452</v>
+        <v>202.2469804791725</v>
       </c>
       <c r="E72" t="n">
-        <v>203.1031951904297</v>
+        <v>204.0381774902344</v>
       </c>
       <c r="F72" t="n">
-        <v>24803900</v>
+        <v>8187800</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B73" t="n">
-        <v>202.8670125241163</v>
+        <v>201.7745885077481</v>
       </c>
       <c r="C73" t="n">
-        <v>204.7861414522214</v>
+        <v>203.2606801764464</v>
       </c>
       <c r="D73" t="n">
-        <v>202.2469804791725</v>
+        <v>200.0621268695276</v>
       </c>
       <c r="E73" t="n">
-        <v>204.0381774902344</v>
+        <v>202.5225524902344</v>
       </c>
       <c r="F73" t="n">
-        <v>8187800</v>
+        <v>7047300</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B74" t="n">
-        <v>201.7745733053134</v>
+        <v>202.739053555574</v>
       </c>
       <c r="C74" t="n">
-        <v>203.2606648620441</v>
+        <v>204.648346074342</v>
       </c>
       <c r="D74" t="n">
-        <v>200.062111796116</v>
+        <v>202.3158675938084</v>
       </c>
       <c r="E74" t="n">
-        <v>202.5225372314453</v>
+        <v>204.4908752441406</v>
       </c>
       <c r="F74" t="n">
-        <v>7047300</v>
+        <v>2376500</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B75" t="n">
-        <v>202.739053555574</v>
+        <v>204.2448234412372</v>
       </c>
       <c r="C75" t="n">
-        <v>204.648346074342</v>
+        <v>204.7467447953422</v>
       </c>
       <c r="D75" t="n">
-        <v>202.3158675938084</v>
+        <v>203.4378117532305</v>
       </c>
       <c r="E75" t="n">
-        <v>204.4908752441406</v>
+        <v>204.3432464599609</v>
       </c>
       <c r="F75" t="n">
-        <v>2376500</v>
+        <v>2316700</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B76" t="n">
-        <v>204.2448234412372</v>
+        <v>204.7074055853226</v>
       </c>
       <c r="C76" t="n">
-        <v>204.7467447953422</v>
+        <v>206.1541370088678</v>
       </c>
       <c r="D76" t="n">
-        <v>203.4378117532305</v>
+        <v>204.097224854962</v>
       </c>
       <c r="E76" t="n">
-        <v>204.3432464599609</v>
+        <v>204.2743682861328</v>
       </c>
       <c r="F76" t="n">
-        <v>2316700</v>
+        <v>4348900</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B77" t="n">
-        <v>204.7073902941868</v>
+        <v>204.2251366175628</v>
       </c>
       <c r="C77" t="n">
-        <v>206.1541216096647</v>
+        <v>204.4022950484963</v>
       </c>
       <c r="D77" t="n">
-        <v>204.0972096094051</v>
+        <v>203.2508178077831</v>
       </c>
       <c r="E77" t="n">
-        <v>204.2743530273438</v>
+        <v>203.6346435546875</v>
       </c>
       <c r="F77" t="n">
-        <v>4348900</v>
+        <v>3937400</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B78" t="n">
-        <v>204.2251519205988</v>
+        <v>203.6346662875698</v>
       </c>
       <c r="C78" t="n">
-        <v>204.4023103648072</v>
+        <v>204.2153231202547</v>
       </c>
       <c r="D78" t="n">
-        <v>203.2508330378112</v>
+        <v>203.1032059526835</v>
       </c>
       <c r="E78" t="n">
-        <v>203.6346588134766</v>
+        <v>203.6740264892578</v>
       </c>
       <c r="F78" t="n">
-        <v>3937400</v>
+        <v>4083800</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B79" t="n">
-        <v>203.6346662875698</v>
+        <v>203.5460790066363</v>
       </c>
       <c r="C79" t="n">
-        <v>204.2153231202547</v>
+        <v>204.1070481869595</v>
       </c>
       <c r="D79" t="n">
-        <v>203.1032059526835</v>
+        <v>200.4557702982002</v>
       </c>
       <c r="E79" t="n">
-        <v>203.6740264892578</v>
+        <v>204.0676879882812</v>
       </c>
       <c r="F79" t="n">
-        <v>4083800</v>
+        <v>6325500</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B80" t="n">
-        <v>203.5460790066363</v>
+        <v>202.6111241066418</v>
       </c>
       <c r="C80" t="n">
-        <v>204.1070481869595</v>
+        <v>202.6800232322651</v>
       </c>
       <c r="D80" t="n">
-        <v>200.4557702982002</v>
+        <v>197.7296480872701</v>
       </c>
       <c r="E80" t="n">
-        <v>204.0676879882812</v>
+        <v>201.0758209228516</v>
       </c>
       <c r="F80" t="n">
-        <v>6325500</v>
+        <v>9477000</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B81" t="n">
-        <v>202.6111087313451</v>
+        <v>201.3612227968269</v>
       </c>
       <c r="C81" t="n">
-        <v>202.68000785174</v>
+        <v>203.4378224562984</v>
       </c>
       <c r="D81" t="n">
-        <v>197.7296330824079</v>
+        <v>200.8888103027919</v>
       </c>
       <c r="E81" t="n">
-        <v>201.0758056640625</v>
+        <v>201.5482025146484</v>
       </c>
       <c r="F81" t="n">
-        <v>9477000</v>
+        <v>8107900</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B82" t="n">
-        <v>201.3612227968269</v>
+        <v>202.0107645526058</v>
       </c>
       <c r="C82" t="n">
-        <v>203.4378224562984</v>
+        <v>204.9632750752426</v>
       </c>
       <c r="D82" t="n">
-        <v>200.8888103027919</v>
+        <v>201.7844096173656</v>
       </c>
       <c r="E82" t="n">
-        <v>201.5482025146484</v>
+        <v>204.2054748535156</v>
       </c>
       <c r="F82" t="n">
-        <v>8107900</v>
+        <v>7545900</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B83" t="n">
-        <v>202.0107645526058</v>
+        <v>203.6543250611801</v>
       </c>
       <c r="C83" t="n">
-        <v>204.9632750752426</v>
+        <v>205.6718769031367</v>
       </c>
       <c r="D83" t="n">
-        <v>201.7844096173656</v>
+        <v>201.7253599471909</v>
       </c>
       <c r="E83" t="n">
-        <v>204.2054748535156</v>
+        <v>202.4930114746094</v>
       </c>
       <c r="F83" t="n">
-        <v>7545900</v>
+        <v>6557800</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B84" t="n">
-        <v>203.6543250611801</v>
+        <v>202.6504838830927</v>
       </c>
       <c r="C84" t="n">
-        <v>205.6718769031367</v>
+        <v>203.4279717120081</v>
       </c>
       <c r="D84" t="n">
-        <v>201.7253599471909</v>
+        <v>200.7805515444468</v>
       </c>
       <c r="E84" t="n">
-        <v>202.4930114746094</v>
+        <v>201.154541015625</v>
       </c>
       <c r="F84" t="n">
-        <v>6557800</v>
+        <v>6154300</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B85" t="n">
-        <v>202.6504838830927</v>
+        <v>202.2961890410606</v>
       </c>
       <c r="C85" t="n">
-        <v>203.4279717120081</v>
+        <v>206.5773204309254</v>
       </c>
       <c r="D85" t="n">
-        <v>200.7805515444468</v>
+        <v>200.6231026927027</v>
       </c>
       <c r="E85" t="n">
-        <v>201.154541015625</v>
+        <v>206.4001770019531</v>
       </c>
       <c r="F85" t="n">
-        <v>6154300</v>
+        <v>11794300</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B86" t="n">
-        <v>202.2961890410606</v>
+        <v>206.5871576245673</v>
       </c>
       <c r="C86" t="n">
-        <v>206.5773204309254</v>
+        <v>210.9962356455094</v>
       </c>
       <c r="D86" t="n">
-        <v>200.6231026927027</v>
+        <v>205.5537759744533</v>
       </c>
       <c r="E86" t="n">
-        <v>206.4001770019531</v>
+        <v>210.2679443359375</v>
       </c>
       <c r="F86" t="n">
-        <v>11794300</v>
+        <v>11379600</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B87" t="n">
-        <v>206.5871576245673</v>
+        <v>211.3308558190507</v>
       </c>
       <c r="C87" t="n">
-        <v>210.9962356455094</v>
+        <v>215.3954834155094</v>
       </c>
       <c r="D87" t="n">
-        <v>205.5537759744533</v>
+        <v>210.7600353199485</v>
       </c>
       <c r="E87" t="n">
-        <v>210.2679443359375</v>
+        <v>215.0903930664062</v>
       </c>
       <c r="F87" t="n">
-        <v>11379600</v>
+        <v>11858800</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B88" t="n">
-        <v>211.3308558190507</v>
+        <v>214.7754540862871</v>
       </c>
       <c r="C88" t="n">
-        <v>215.3954834155094</v>
+        <v>216.2713969640869</v>
       </c>
       <c r="D88" t="n">
-        <v>210.7600353199485</v>
+        <v>212.4921870786144</v>
       </c>
       <c r="E88" t="n">
-        <v>215.0903930664062</v>
+        <v>216.0942535400391</v>
       </c>
       <c r="F88" t="n">
-        <v>11858800</v>
+        <v>8492100</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B89" t="n">
-        <v>214.7754540862871</v>
+        <v>215.5726286297608</v>
       </c>
       <c r="C89" t="n">
-        <v>216.2713969640869</v>
+        <v>216.6256979258031</v>
       </c>
       <c r="D89" t="n">
-        <v>212.4921870786144</v>
+        <v>214.686881478726</v>
       </c>
       <c r="E89" t="n">
-        <v>216.0942535400391</v>
+        <v>215.1986541748047</v>
       </c>
       <c r="F89" t="n">
-        <v>8492100</v>
+        <v>10021500</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B90" t="n">
-        <v>215.5726286297608</v>
+        <v>213.6535174405211</v>
       </c>
       <c r="C90" t="n">
-        <v>216.6256979258031</v>
+        <v>215.2675560609527</v>
       </c>
       <c r="D90" t="n">
-        <v>214.686881478726</v>
+        <v>211.1045200795966</v>
       </c>
       <c r="E90" t="n">
-        <v>215.1986541748047</v>
+        <v>214.7557983398438</v>
       </c>
       <c r="F90" t="n">
-        <v>10021500</v>
+        <v>14057100</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B91" t="n">
-        <v>213.6535174405211</v>
+        <v>207.659916851811</v>
       </c>
       <c r="C91" t="n">
-        <v>215.2675560609527</v>
+        <v>215.2183369488501</v>
       </c>
       <c r="D91" t="n">
-        <v>211.1045200795966</v>
+        <v>207.1678317407877</v>
       </c>
       <c r="E91" t="n">
-        <v>214.7557983398438</v>
+        <v>214.5589447021484</v>
       </c>
       <c r="F91" t="n">
-        <v>14057100</v>
+        <v>14762900</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B92" t="n">
-        <v>207.659916851811</v>
+        <v>215.3069232717918</v>
       </c>
       <c r="C92" t="n">
-        <v>215.2183369488501</v>
+        <v>218.6530960134773</v>
       </c>
       <c r="D92" t="n">
-        <v>207.1678317407877</v>
+        <v>214.6475310263463</v>
       </c>
       <c r="E92" t="n">
-        <v>214.5589447021484</v>
+        <v>215.0313568115234</v>
       </c>
       <c r="F92" t="n">
-        <v>14762900</v>
+        <v>13160000</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B93" t="n">
-        <v>215.3069232717918</v>
+        <v>216.3206133966017</v>
       </c>
       <c r="C93" t="n">
-        <v>218.6530960134773</v>
+        <v>217.7082969855193</v>
       </c>
       <c r="D93" t="n">
-        <v>214.6475310263463</v>
+        <v>214.3916331931512</v>
       </c>
       <c r="E93" t="n">
-        <v>215.0313568115234</v>
+        <v>216.6552276611328</v>
       </c>
       <c r="F93" t="n">
-        <v>13160000</v>
+        <v>6950600</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B94" t="n">
-        <v>216.3206133966017</v>
+        <v>216.7241195858665</v>
       </c>
       <c r="C94" t="n">
-        <v>217.7082969855193</v>
+        <v>218.515301484998</v>
       </c>
       <c r="D94" t="n">
-        <v>214.3916331931512</v>
+        <v>216.5174372427288</v>
       </c>
       <c r="E94" t="n">
-        <v>216.6552276611328</v>
+        <v>217.9838562011719</v>
       </c>
       <c r="F94" t="n">
-        <v>6950600</v>
+        <v>6856700</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B95" t="n">
-        <v>216.7241347564745</v>
+        <v>218.4857986661137</v>
       </c>
       <c r="C95" t="n">
-        <v>218.5153167809881</v>
+        <v>221.9303945910299</v>
       </c>
       <c r="D95" t="n">
-        <v>216.5174523988691</v>
+        <v>217.2063743191241</v>
       </c>
       <c r="E95" t="n">
-        <v>217.9838714599609</v>
+        <v>220.8871765136719</v>
       </c>
       <c r="F95" t="n">
-        <v>6856700</v>
+        <v>8154100</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B96" t="n">
-        <v>218.4857986661137</v>
+        <v>222.8161377007139</v>
       </c>
       <c r="C96" t="n">
-        <v>221.9303945910299</v>
+        <v>224.9518003498371</v>
       </c>
       <c r="D96" t="n">
-        <v>217.2063743191241</v>
+        <v>222.5012110309432</v>
       </c>
       <c r="E96" t="n">
-        <v>220.8871765136719</v>
+        <v>224.1152496337891</v>
       </c>
       <c r="F96" t="n">
-        <v>8154100</v>
+        <v>9026500</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B97" t="n">
-        <v>222.8161377007139</v>
+        <v>225.1879747271155</v>
       </c>
       <c r="C97" t="n">
-        <v>224.9518003498371</v>
+        <v>226.3591396349424</v>
       </c>
       <c r="D97" t="n">
-        <v>222.5012110309432</v>
+        <v>223.4853645338204</v>
       </c>
       <c r="E97" t="n">
-        <v>224.1152496337891</v>
+        <v>223.6920318603516</v>
       </c>
       <c r="F97" t="n">
-        <v>9026500</v>
+        <v>9645300</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B98" t="n">
-        <v>225.1879747271155</v>
+        <v>224.6466859457881</v>
       </c>
       <c r="C98" t="n">
-        <v>226.3591396349424</v>
+        <v>224.8828922015737</v>
       </c>
       <c r="D98" t="n">
-        <v>223.4853645338204</v>
+        <v>221.7630744488117</v>
       </c>
       <c r="E98" t="n">
-        <v>223.6920318603516</v>
+        <v>223.6526794433594</v>
       </c>
       <c r="F98" t="n">
-        <v>9645300</v>
+        <v>11045500</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B99" t="n">
-        <v>224.6466859457881</v>
+        <v>224.7057483906486</v>
       </c>
       <c r="C99" t="n">
-        <v>224.8828922015737</v>
+        <v>227.530312073188</v>
       </c>
       <c r="D99" t="n">
-        <v>221.7630744488117</v>
+        <v>223.6526790631295</v>
       </c>
       <c r="E99" t="n">
-        <v>223.6526794433594</v>
+        <v>227.0972747802734</v>
       </c>
       <c r="F99" t="n">
-        <v>11045500</v>
+        <v>8187500</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B100" t="n">
-        <v>224.7057483906486</v>
+        <v>227.8354016268972</v>
       </c>
       <c r="C100" t="n">
-        <v>227.530312073188</v>
+        <v>231.4768283686728</v>
       </c>
       <c r="D100" t="n">
-        <v>223.6526790631295</v>
+        <v>226.8315438166281</v>
       </c>
       <c r="E100" t="n">
-        <v>227.0972747802734</v>
+        <v>229.4100799560547</v>
       </c>
       <c r="F100" t="n">
-        <v>8187500</v>
+        <v>9346600</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B101" t="n">
-        <v>227.8353864728449</v>
+        <v>231.2799860551316</v>
       </c>
       <c r="C101" t="n">
-        <v>231.4768129724177</v>
+        <v>232.0968490845446</v>
       </c>
       <c r="D101" t="n">
-        <v>226.8315287293456</v>
+        <v>229.252597941833</v>
       </c>
       <c r="E101" t="n">
-        <v>229.4100646972656</v>
+        <v>230.7583770751953</v>
       </c>
       <c r="F101" t="n">
-        <v>9346600</v>
+        <v>8641400</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B102" t="n">
-        <v>231.2800013484118</v>
+        <v>231.2799897072634</v>
       </c>
       <c r="C102" t="n">
-        <v>232.0968644318395</v>
+        <v>235.787490883202</v>
       </c>
       <c r="D102" t="n">
-        <v>229.2526131010531</v>
+        <v>231.2701534117819</v>
       </c>
       <c r="E102" t="n">
-        <v>230.7583923339844</v>
+        <v>234.0258178710938</v>
       </c>
       <c r="F102" t="n">
-        <v>8641400</v>
+        <v>10267500</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B103" t="n">
-        <v>231.2799897072634</v>
+        <v>235.1773306195327</v>
       </c>
       <c r="C103" t="n">
-        <v>235.787490883202</v>
+        <v>237.1259835185858</v>
       </c>
       <c r="D103" t="n">
-        <v>231.2701534117819</v>
+        <v>234.2128329577192</v>
       </c>
       <c r="E103" t="n">
-        <v>234.0258178710938</v>
+        <v>236.1910247802734</v>
       </c>
       <c r="F103" t="n">
-        <v>10267500</v>
+        <v>8274000</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B104" t="n">
-        <v>235.1773154262319</v>
+        <v>236.4468956382332</v>
       </c>
       <c r="C104" t="n">
-        <v>237.125968199395</v>
+        <v>236.9291444528193</v>
       </c>
       <c r="D104" t="n">
-        <v>234.2128178267284</v>
+        <v>233.2877026206608</v>
       </c>
       <c r="E104" t="n">
-        <v>236.1910095214844</v>
+        <v>234.8623809814453</v>
       </c>
       <c r="F104" t="n">
-        <v>8274000</v>
+        <v>9378500</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B105" t="n">
-        <v>236.4468956382332</v>
+        <v>236.1811524926561</v>
       </c>
       <c r="C105" t="n">
-        <v>236.9291444528193</v>
+        <v>236.6929251843698</v>
       </c>
       <c r="D105" t="n">
-        <v>233.2877026206608</v>
+        <v>234.1144041521209</v>
       </c>
       <c r="E105" t="n">
-        <v>234.8623809814453</v>
+        <v>234.5769653320312</v>
       </c>
       <c r="F105" t="n">
-        <v>9378500</v>
+        <v>6723300</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B106" t="n">
-        <v>236.1811678557945</v>
+        <v>235.551283100246</v>
       </c>
       <c r="C106" t="n">
-        <v>236.6929405807981</v>
+        <v>237.4408880102699</v>
       </c>
       <c r="D106" t="n">
-        <v>234.1144193808212</v>
+        <v>233.6419905821425</v>
       </c>
       <c r="E106" t="n">
-        <v>234.5769805908203</v>
+        <v>237.0472259521484</v>
       </c>
       <c r="F106" t="n">
-        <v>6723300</v>
+        <v>6803900</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B107" t="n">
-        <v>235.5512982627408</v>
+        <v>236.6732379543034</v>
       </c>
       <c r="C107" t="n">
-        <v>237.4409032943991</v>
+        <v>242.4503270560588</v>
       </c>
       <c r="D107" t="n">
-        <v>233.6420056217357</v>
+        <v>235.8858988159272</v>
       </c>
       <c r="E107" t="n">
-        <v>237.0472412109375</v>
+        <v>240.6788177490234</v>
       </c>
       <c r="F107" t="n">
-        <v>6803900</v>
+        <v>10254300</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B108" t="n">
-        <v>236.6732529591429</v>
+        <v>240.7181753030812</v>
       </c>
       <c r="C108" t="n">
-        <v>242.4503424271597</v>
+        <v>241.0724771605951</v>
       </c>
       <c r="D108" t="n">
-        <v>235.8859137708501</v>
+        <v>238.7695225953774</v>
       </c>
       <c r="E108" t="n">
-        <v>240.6788330078125</v>
+        <v>239.5962219238281</v>
       </c>
       <c r="F108" t="n">
-        <v>10254300</v>
+        <v>13268500</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B109" t="n">
-        <v>240.7181753030812</v>
+        <v>240.2654886197458</v>
       </c>
       <c r="C109" t="n">
-        <v>241.0724771605951</v>
+        <v>240.6197905114409</v>
       </c>
       <c r="D109" t="n">
-        <v>238.7695225953774</v>
+        <v>238.0412542373971</v>
       </c>
       <c r="E109" t="n">
-        <v>239.5962219238281</v>
+        <v>239.4781494140625</v>
       </c>
       <c r="F109" t="n">
-        <v>13268500</v>
+        <v>12703000</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B110" t="n">
-        <v>240.2654886197458</v>
+        <v>239.389564336343</v>
       </c>
       <c r="C110" t="n">
-        <v>240.6197905114409</v>
+        <v>241.1905976005163</v>
       </c>
       <c r="D110" t="n">
-        <v>238.0412542373971</v>
+        <v>238.9762146553066</v>
       </c>
       <c r="E110" t="n">
-        <v>239.4781494140625</v>
+        <v>241.1118621826172</v>
       </c>
       <c r="F110" t="n">
-        <v>12703000</v>
+        <v>8129700</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B111" t="n">
-        <v>239.389564336343</v>
+        <v>240.7477067024548</v>
       </c>
       <c r="C111" t="n">
-        <v>241.1905976005163</v>
+        <v>243.0506763566235</v>
       </c>
       <c r="D111" t="n">
-        <v>238.9762146553066</v>
+        <v>240.4032561468311</v>
       </c>
       <c r="E111" t="n">
-        <v>241.1118621826172</v>
+        <v>243.00146484375</v>
       </c>
       <c r="F111" t="n">
-        <v>8129700</v>
+        <v>7553900</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B112" t="n">
-        <v>240.7477218197236</v>
+        <v>242.5684367756451</v>
       </c>
       <c r="C112" t="n">
-        <v>243.0506916185027</v>
+        <v>242.9719501723976</v>
       </c>
       <c r="D112" t="n">
-        <v>240.4032712424708</v>
+        <v>236.4764206746478</v>
       </c>
       <c r="E112" t="n">
-        <v>243.0014801025391</v>
+        <v>238.6514434814453</v>
       </c>
       <c r="F112" t="n">
-        <v>7553900</v>
+        <v>13565800</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B113" t="n">
-        <v>242.5684367756451</v>
+        <v>239.7733870753068</v>
       </c>
       <c r="C113" t="n">
-        <v>242.9719501723976</v>
+        <v>242.9030410566114</v>
       </c>
       <c r="D113" t="n">
-        <v>236.4764206746478</v>
+        <v>238.7596929857211</v>
       </c>
       <c r="E113" t="n">
-        <v>238.6514434814453</v>
+        <v>241.9483947753906</v>
       </c>
       <c r="F113" t="n">
-        <v>13565800</v>
+        <v>9622700</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,25 +3381,25 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B114" t="n">
-        <v>239.7734021969262</v>
+        <v>242.7498308706833</v>
       </c>
       <c r="C114" t="n">
-        <v>242.9030563756065</v>
+        <v>244.6296889736104</v>
       </c>
       <c r="D114" t="n">
-        <v>238.7597080434106</v>
+        <v>241.9484024234396</v>
       </c>
       <c r="E114" t="n">
-        <v>241.9484100341797</v>
+        <v>243.6699676513672</v>
       </c>
       <c r="F114" t="n">
-        <v>9622700</v>
+        <v>7246300</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -3407,25 +3407,25 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B115" t="n">
-        <v>242.7498156695138</v>
+        <v>242.2650193059668</v>
       </c>
       <c r="C115" t="n">
-        <v>244.6296736547229</v>
+        <v>244.6296899211394</v>
       </c>
       <c r="D115" t="n">
-        <v>241.9483872724562</v>
+        <v>241.1371014204259</v>
       </c>
       <c r="E115" t="n">
-        <v>243.6699523925781</v>
+        <v>242.5717315673828</v>
       </c>
       <c r="F115" t="n">
-        <v>7246300</v>
+        <v>7698200</v>
       </c>
       <c r="G115" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B116" t="n">
-        <v>242.2650040664713</v>
+        <v>242.5123742558835</v>
       </c>
       <c r="C116" t="n">
-        <v>244.629674532896</v>
+        <v>242.8685596523689</v>
       </c>
       <c r="D116" t="n">
-        <v>241.1370862518812</v>
+        <v>239.4551250760139</v>
       </c>
       <c r="E116" t="n">
-        <v>242.5717163085938</v>
+        <v>240.8897552490234</v>
       </c>
       <c r="F116" t="n">
-        <v>7698200</v>
+        <v>7172600</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B117" t="n">
-        <v>242.5123588943122</v>
+        <v>241.4438165545137</v>
       </c>
       <c r="C117" t="n">
-        <v>242.8685442682355</v>
+        <v>246.3017849576054</v>
       </c>
       <c r="D117" t="n">
-        <v>239.4551099080992</v>
+        <v>239.9300324032001</v>
       </c>
       <c r="E117" t="n">
-        <v>240.8897399902344</v>
+        <v>245.7971801757812</v>
       </c>
       <c r="F117" t="n">
-        <v>7172600</v>
+        <v>16428600</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B118" t="n">
-        <v>241.4438165545137</v>
+        <v>246.549124695673</v>
       </c>
       <c r="C118" t="n">
-        <v>246.3017849576054</v>
+        <v>249.0424223461303</v>
       </c>
       <c r="D118" t="n">
-        <v>239.9300324032001</v>
+        <v>244.2537044562187</v>
       </c>
       <c r="E118" t="n">
-        <v>245.7971801757812</v>
+        <v>245.9257965087891</v>
       </c>
       <c r="F118" t="n">
-        <v>16428600</v>
+        <v>9042400</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B119" t="n">
-        <v>246.549124695673</v>
+        <v>243.8480592687475</v>
       </c>
       <c r="C119" t="n">
-        <v>249.0424223461303</v>
+        <v>245.2530085028214</v>
       </c>
       <c r="D119" t="n">
-        <v>244.2537044562187</v>
+        <v>241.7703087256774</v>
       </c>
       <c r="E119" t="n">
-        <v>245.9257965087891</v>
+        <v>244.1349792480469</v>
       </c>
       <c r="F119" t="n">
-        <v>9042400</v>
+        <v>6178700</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B120" t="n">
-        <v>243.8480592687475</v>
+        <v>243.1455911306439</v>
       </c>
       <c r="C120" t="n">
-        <v>245.2530085028214</v>
+        <v>243.9569081828458</v>
       </c>
       <c r="D120" t="n">
-        <v>241.7703087256774</v>
+        <v>240.6028202250193</v>
       </c>
       <c r="E120" t="n">
-        <v>244.1349792480469</v>
+        <v>242.7003631591797</v>
       </c>
       <c r="F120" t="n">
-        <v>6178700</v>
+        <v>5768000</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B121" t="n">
-        <v>243.145575843863</v>
+        <v>240.0586607026203</v>
       </c>
       <c r="C121" t="n">
-        <v>243.9568928450567</v>
+        <v>240.4247346856854</v>
       </c>
       <c r="D121" t="n">
-        <v>240.6028050981046</v>
+        <v>233.4296538825942</v>
       </c>
       <c r="E121" t="n">
-        <v>242.7003479003906</v>
+        <v>237.0904541015625</v>
       </c>
       <c r="F121" t="n">
-        <v>5768000</v>
+        <v>9375400</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B122" t="n">
-        <v>240.0586452528019</v>
+        <v>235.5964438849938</v>
       </c>
       <c r="C122" t="n">
-        <v>240.424719212307</v>
+        <v>238.238145912047</v>
       </c>
       <c r="D122" t="n">
-        <v>233.4296388594088</v>
+        <v>232.9349495870229</v>
       </c>
       <c r="E122" t="n">
-        <v>237.0904388427734</v>
+        <v>237.8522796630859</v>
       </c>
       <c r="F122" t="n">
-        <v>9375400</v>
+        <v>7179800</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B123" t="n">
-        <v>235.596428770922</v>
+        <v>238.3172853623119</v>
       </c>
       <c r="C123" t="n">
-        <v>238.2381306285037</v>
+        <v>241.5031614171852</v>
       </c>
       <c r="D123" t="n">
-        <v>232.9349346436922</v>
+        <v>237.496079785725</v>
       </c>
       <c r="E123" t="n">
-        <v>237.8522644042969</v>
+        <v>240.0190582275391</v>
       </c>
       <c r="F123" t="n">
-        <v>7179800</v>
+        <v>7844000</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B124" t="n">
-        <v>238.3173005129137</v>
+        <v>239.732151823879</v>
       </c>
       <c r="C124" t="n">
-        <v>241.5031767703235</v>
+        <v>242.4035346970428</v>
       </c>
       <c r="D124" t="n">
-        <v>237.4960948841201</v>
+        <v>238.2678408210546</v>
       </c>
       <c r="E124" t="n">
-        <v>240.0190734863281</v>
+        <v>241.1272125244141</v>
       </c>
       <c r="F124" t="n">
-        <v>7844000</v>
+        <v>7214100</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B125" t="n">
-        <v>239.732151823879</v>
+        <v>240.2960869196001</v>
       </c>
       <c r="C125" t="n">
-        <v>242.4035346970428</v>
+        <v>241.1074039007698</v>
       </c>
       <c r="D125" t="n">
-        <v>238.2678408210546</v>
+        <v>238.802095160397</v>
       </c>
       <c r="E125" t="n">
-        <v>241.1272125244141</v>
+        <v>240.4148254394531</v>
       </c>
       <c r="F125" t="n">
-        <v>7214100</v>
+        <v>6933200</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B126" t="n">
-        <v>240.2960869196001</v>
+        <v>238.9010440853151</v>
       </c>
       <c r="C126" t="n">
-        <v>241.1074039007698</v>
+        <v>241.8098736554103</v>
       </c>
       <c r="D126" t="n">
-        <v>238.802095160397</v>
+        <v>237.7533339953824</v>
       </c>
       <c r="E126" t="n">
-        <v>240.4148254394531</v>
+        <v>239.4748840332031</v>
       </c>
       <c r="F126" t="n">
-        <v>6933200</v>
+        <v>7710200</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B127" t="n">
-        <v>238.9010593075404</v>
+        <v>241.6218975517249</v>
       </c>
       <c r="C127" t="n">
-        <v>241.8098890629796</v>
+        <v>242.9872622066995</v>
       </c>
       <c r="D127" t="n">
-        <v>237.7533491444783</v>
+        <v>238.9406111728678</v>
       </c>
       <c r="E127" t="n">
-        <v>239.4748992919922</v>
+        <v>238.9604034423828</v>
       </c>
       <c r="F127" t="n">
-        <v>7710200</v>
+        <v>6415300</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B128" t="n">
-        <v>241.6219129804633</v>
+        <v>241.3349607287423</v>
       </c>
       <c r="C128" t="n">
-        <v>242.9872777226232</v>
+        <v>242.4628785296478</v>
       </c>
       <c r="D128" t="n">
-        <v>238.940626430393</v>
+        <v>239.1088059824489</v>
       </c>
       <c r="E128" t="n">
-        <v>238.9604187011719</v>
+        <v>240.6127014160156</v>
       </c>
       <c r="F128" t="n">
-        <v>6415300</v>
+        <v>7571500</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B129" t="n">
-        <v>241.3349760333344</v>
+        <v>240.99857884995</v>
       </c>
       <c r="C129" t="n">
-        <v>242.4628939057684</v>
+        <v>241.5526416415011</v>
       </c>
       <c r="D129" t="n">
-        <v>239.1088211458664</v>
+        <v>234.7059805370448</v>
       </c>
       <c r="E129" t="n">
-        <v>240.6127166748047</v>
+        <v>235.5865478515625</v>
       </c>
       <c r="F129" t="n">
-        <v>7571500</v>
+        <v>7281800</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B130" t="n">
-        <v>240.99857884995</v>
+        <v>235.349078713635</v>
       </c>
       <c r="C130" t="n">
-        <v>241.5526416415011</v>
+        <v>236.5759427839531</v>
       </c>
       <c r="D130" t="n">
-        <v>234.7059805370448</v>
+        <v>232.9250465260699</v>
       </c>
       <c r="E130" t="n">
-        <v>235.5865478515625</v>
+        <v>234.7653350830078</v>
       </c>
       <c r="F130" t="n">
-        <v>7281800</v>
+        <v>6811500</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B131" t="n">
-        <v>235.349094010365</v>
+        <v>235.814102878936</v>
       </c>
       <c r="C131" t="n">
-        <v>236.5759581604242</v>
+        <v>236.7243510378414</v>
       </c>
       <c r="D131" t="n">
-        <v>232.9250616652477</v>
+        <v>233.80561773863</v>
       </c>
       <c r="E131" t="n">
-        <v>234.7653503417969</v>
+        <v>235.0819549560547</v>
       </c>
       <c r="F131" t="n">
-        <v>6811500</v>
+        <v>7511500</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B132" t="n">
-        <v>235.814102878936</v>
+        <v>234.3201136195421</v>
       </c>
       <c r="C132" t="n">
-        <v>236.7243510378414</v>
+        <v>235.764632308021</v>
       </c>
       <c r="D132" t="n">
-        <v>233.80561773863</v>
+        <v>232.0148047922595</v>
       </c>
       <c r="E132" t="n">
-        <v>235.0819549560547</v>
+        <v>232.8755798339844</v>
       </c>
       <c r="F132" t="n">
-        <v>7511500</v>
+        <v>17156600</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B133" t="n">
-        <v>234.3201136195421</v>
+        <v>234.884060828395</v>
       </c>
       <c r="C133" t="n">
-        <v>235.764632308021</v>
+        <v>235.7844203946137</v>
       </c>
       <c r="D133" t="n">
-        <v>232.0148047922595</v>
+        <v>231.7674501417346</v>
       </c>
       <c r="E133" t="n">
-        <v>232.8755798339844</v>
+        <v>232.925048828125</v>
       </c>
       <c r="F133" t="n">
-        <v>17156600</v>
+        <v>7313700</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B134" t="n">
-        <v>234.884060828395</v>
+        <v>231.6586126149741</v>
       </c>
       <c r="C134" t="n">
-        <v>235.7844203946137</v>
+        <v>233.4989011687466</v>
       </c>
       <c r="D134" t="n">
-        <v>231.7674501417346</v>
+        <v>229.7787546189723</v>
       </c>
       <c r="E134" t="n">
-        <v>232.925048828125</v>
+        <v>232.7766418457031</v>
       </c>
       <c r="F134" t="n">
-        <v>7313700</v>
+        <v>9046200</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B135" t="n">
-        <v>231.6586126149741</v>
+        <v>234.2904343153693</v>
       </c>
       <c r="C135" t="n">
-        <v>233.4989011687466</v>
+        <v>238.9010520004889</v>
       </c>
       <c r="D135" t="n">
-        <v>229.7787546189723</v>
+        <v>233.2317667584392</v>
       </c>
       <c r="E135" t="n">
-        <v>232.7766418457031</v>
+        <v>237.3872528076172</v>
       </c>
       <c r="F135" t="n">
-        <v>9046200</v>
+        <v>6456400</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B136" t="n">
-        <v>234.2904343153693</v>
+        <v>237.4565300874115</v>
       </c>
       <c r="C136" t="n">
-        <v>238.9010520004889</v>
+        <v>239.0890376929306</v>
       </c>
       <c r="D136" t="n">
-        <v>233.2317667584392</v>
+        <v>236.3978624775069</v>
       </c>
       <c r="E136" t="n">
-        <v>237.3872528076172</v>
+        <v>236.70458984375</v>
       </c>
       <c r="F136" t="n">
-        <v>6456400</v>
+        <v>5171400</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B137" t="n">
-        <v>237.4565300874115</v>
+        <v>238.6339116976677</v>
       </c>
       <c r="C137" t="n">
-        <v>239.0890376929306</v>
+        <v>240.1081112682183</v>
       </c>
       <c r="D137" t="n">
-        <v>236.3978624775069</v>
+        <v>236.5957456438558</v>
       </c>
       <c r="E137" t="n">
-        <v>236.70458984375</v>
+        <v>237.9017486572266</v>
       </c>
       <c r="F137" t="n">
-        <v>5171400</v>
+        <v>7617600</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B138" t="n">
-        <v>238.6339116976677</v>
+        <v>240.9095376592209</v>
       </c>
       <c r="C138" t="n">
-        <v>240.1081112682183</v>
+        <v>241.6219084230326</v>
       </c>
       <c r="D138" t="n">
-        <v>236.5957456438558</v>
+        <v>237.9611083490254</v>
       </c>
       <c r="E138" t="n">
-        <v>237.9017486572266</v>
+        <v>239.9201354980469</v>
       </c>
       <c r="F138" t="n">
-        <v>7617600</v>
+        <v>7241300</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B139" t="n">
-        <v>240.9095376592209</v>
+        <v>240.4346190736229</v>
       </c>
       <c r="C139" t="n">
-        <v>241.6219084230326</v>
+        <v>242.7300393849503</v>
       </c>
       <c r="D139" t="n">
-        <v>237.9611083490254</v>
+        <v>240.0784336838334</v>
       </c>
       <c r="E139" t="n">
-        <v>239.9201354980469</v>
+        <v>241.8494720458984</v>
       </c>
       <c r="F139" t="n">
-        <v>7241300</v>
+        <v>7554200</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B140" t="n">
-        <v>240.4346190736229</v>
+        <v>242.9971782498834</v>
       </c>
       <c r="C140" t="n">
-        <v>242.7300393849503</v>
+        <v>244.580212658809</v>
       </c>
       <c r="D140" t="n">
-        <v>240.0784336838334</v>
+        <v>241.1568896154117</v>
       </c>
       <c r="E140" t="n">
-        <v>241.8494720458984</v>
+        <v>241.5328521728516</v>
       </c>
       <c r="F140" t="n">
-        <v>7554200</v>
+        <v>6314600</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B141" t="n">
-        <v>242.9971782498834</v>
+        <v>242.5123641523277</v>
       </c>
       <c r="C141" t="n">
-        <v>244.580212658809</v>
+        <v>244.5901147281089</v>
       </c>
       <c r="D141" t="n">
-        <v>241.1568896154117</v>
+        <v>239.3066957175141</v>
       </c>
       <c r="E141" t="n">
-        <v>241.5328521728516</v>
+        <v>240.4642944335938</v>
       </c>
       <c r="F141" t="n">
-        <v>6314600</v>
+        <v>6878700</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B142" t="n">
-        <v>242.5123641523277</v>
+        <v>240.0784175573595</v>
       </c>
       <c r="C142" t="n">
-        <v>244.5901147281089</v>
+        <v>240.9392076648261</v>
       </c>
       <c r="D142" t="n">
-        <v>239.3066957175141</v>
+        <v>237.9512090454724</v>
       </c>
       <c r="E142" t="n">
-        <v>240.4642944335938</v>
+        <v>238.4162292480469</v>
       </c>
       <c r="F142" t="n">
-        <v>6878700</v>
+        <v>4442400</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B143" t="n">
-        <v>240.0784329225297</v>
+        <v>238.2282554079276</v>
       </c>
       <c r="C143" t="n">
-        <v>240.9392230850874</v>
+        <v>238.2282554079276</v>
       </c>
       <c r="D143" t="n">
-        <v>237.9512242744999</v>
+        <v>233.5088027877857</v>
       </c>
       <c r="E143" t="n">
-        <v>238.4162445068359</v>
+        <v>235.8833770751953</v>
       </c>
       <c r="F143" t="n">
-        <v>4442400</v>
+        <v>6241100</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B144" t="n">
-        <v>238.2282554079276</v>
+        <v>234.1321342347395</v>
       </c>
       <c r="C144" t="n">
-        <v>238.2282554079276</v>
+        <v>238.7724329332046</v>
       </c>
       <c r="D144" t="n">
-        <v>233.5088027877857</v>
+        <v>231.4211667922781</v>
       </c>
       <c r="E144" t="n">
-        <v>235.8833770751953</v>
+        <v>238.7427520751953</v>
       </c>
       <c r="F144" t="n">
-        <v>6241100</v>
+        <v>8771100</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B145" t="n">
-        <v>234.1321342347395</v>
+        <v>238.7427511835681</v>
       </c>
       <c r="C145" t="n">
-        <v>238.7724329332046</v>
+        <v>241.612011492337</v>
       </c>
       <c r="D145" t="n">
-        <v>231.4211667922781</v>
+        <v>237.9907958579282</v>
       </c>
       <c r="E145" t="n">
-        <v>238.7427520751953</v>
+        <v>238.7526397705078</v>
       </c>
       <c r="F145" t="n">
-        <v>8771100</v>
+        <v>6216500</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B146" t="n">
-        <v>238.7427511835681</v>
+        <v>239.4353230782619</v>
       </c>
       <c r="C146" t="n">
-        <v>241.612011492337</v>
+        <v>239.6925622052984</v>
       </c>
       <c r="D146" t="n">
-        <v>237.9907958579282</v>
+        <v>235.3886718611059</v>
       </c>
       <c r="E146" t="n">
-        <v>238.7526397705078</v>
+        <v>235.9328460693359</v>
       </c>
       <c r="F146" t="n">
-        <v>6216500</v>
+        <v>7354500</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B147" t="n">
-        <v>239.4353230782619</v>
+        <v>235.1907903330984</v>
       </c>
       <c r="C147" t="n">
-        <v>239.6925622052984</v>
+        <v>235.8635765445355</v>
       </c>
       <c r="D147" t="n">
-        <v>235.3886718611059</v>
+        <v>232.6875890190388</v>
       </c>
       <c r="E147" t="n">
-        <v>235.9328460693359</v>
+        <v>235.4381408691406</v>
       </c>
       <c r="F147" t="n">
-        <v>7354500</v>
+        <v>7663600</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B148" t="n">
-        <v>235.1907903330984</v>
+        <v>232.5193972079424</v>
       </c>
       <c r="C148" t="n">
-        <v>235.8635765445355</v>
+        <v>239.6233125984258</v>
       </c>
       <c r="D148" t="n">
-        <v>232.6875890190388</v>
+        <v>230.7780548336423</v>
       </c>
       <c r="E148" t="n">
-        <v>235.4381408691406</v>
+        <v>237.5554656982422</v>
       </c>
       <c r="F148" t="n">
-        <v>7663600</v>
+        <v>10318700</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B149" t="n">
-        <v>232.5193972079424</v>
+        <v>237.3971547010872</v>
       </c>
       <c r="C149" t="n">
-        <v>239.6233125984258</v>
+        <v>237.8720635067345</v>
       </c>
       <c r="D149" t="n">
-        <v>230.7780548336423</v>
+        <v>234.2409594215431</v>
       </c>
       <c r="E149" t="n">
-        <v>237.5554656982422</v>
+        <v>236.1406097412109</v>
       </c>
       <c r="F149" t="n">
-        <v>10318700</v>
+        <v>6463500</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B150" t="n">
-        <v>237.3971547010872</v>
+        <v>234.9038654541874</v>
       </c>
       <c r="C150" t="n">
-        <v>237.8720635067345</v>
+        <v>235.6162362366795</v>
       </c>
       <c r="D150" t="n">
-        <v>234.2409594215431</v>
+        <v>229.6600308430398</v>
       </c>
       <c r="E150" t="n">
-        <v>236.1406097412109</v>
+        <v>232.0543823242188</v>
       </c>
       <c r="F150" t="n">
-        <v>6463500</v>
+        <v>8668900</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B151" t="n">
-        <v>234.9038500080299</v>
+        <v>231.8762966548944</v>
       </c>
       <c r="C151" t="n">
-        <v>235.6162207436799</v>
+        <v>233.0437839864675</v>
       </c>
       <c r="D151" t="n">
-        <v>229.6600157416919</v>
+        <v>229.5808763393496</v>
       </c>
       <c r="E151" t="n">
-        <v>232.0543670654297</v>
+        <v>231.6981964111328</v>
       </c>
       <c r="F151" t="n">
-        <v>8668900</v>
+        <v>8946300</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B152" t="n">
-        <v>231.8762966548944</v>
+        <v>232.321525670587</v>
       </c>
       <c r="C152" t="n">
-        <v>233.0437839864675</v>
+        <v>232.7667536363879</v>
       </c>
       <c r="D152" t="n">
-        <v>229.5808763393496</v>
+        <v>227.0974833184763</v>
       </c>
       <c r="E152" t="n">
-        <v>231.6981964111328</v>
+        <v>228.2451934814453</v>
       </c>
       <c r="F152" t="n">
-        <v>8946300</v>
+        <v>7810500</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B153" t="n">
-        <v>232.321525670587</v>
+        <v>226.9193787228735</v>
       </c>
       <c r="C153" t="n">
-        <v>232.7667536363879</v>
+        <v>227.2557718151299</v>
       </c>
       <c r="D153" t="n">
-        <v>227.0974833184763</v>
+        <v>222.3186498783577</v>
       </c>
       <c r="E153" t="n">
-        <v>228.2451934814453</v>
+        <v>223.76318359375</v>
       </c>
       <c r="F153" t="n">
-        <v>7810500</v>
+        <v>11681200</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B154" t="n">
-        <v>226.9193941968888</v>
+        <v>223.7829810531976</v>
       </c>
       <c r="C154" t="n">
-        <v>227.2557873120845</v>
+        <v>225.0692069251634</v>
       </c>
       <c r="D154" t="n">
-        <v>222.3186650386415</v>
+        <v>221.4084218257834</v>
       </c>
       <c r="E154" t="n">
-        <v>223.7631988525391</v>
+        <v>223.7038421630859</v>
       </c>
       <c r="F154" t="n">
-        <v>11681200</v>
+        <v>9003400</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B155" t="n">
-        <v>223.7829810531976</v>
+        <v>224.8416507297823</v>
       </c>
       <c r="C155" t="n">
-        <v>225.0692069251634</v>
+        <v>228.937775248105</v>
       </c>
       <c r="D155" t="n">
-        <v>221.4084218257834</v>
+        <v>224.623981037261</v>
       </c>
       <c r="E155" t="n">
-        <v>223.7038421630859</v>
+        <v>228.2056121826172</v>
       </c>
       <c r="F155" t="n">
-        <v>9003400</v>
+        <v>7097600</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B156" t="n">
-        <v>224.8416356959219</v>
+        <v>226.6027733404394</v>
       </c>
       <c r="C156" t="n">
-        <v>228.9377599403605</v>
+        <v>227.5526060477145</v>
       </c>
       <c r="D156" t="n">
-        <v>224.6239660179549</v>
+        <v>224.6140804527143</v>
       </c>
       <c r="E156" t="n">
-        <v>228.2055969238281</v>
+        <v>225.0889892578125</v>
       </c>
       <c r="F156" t="n">
-        <v>7097600</v>
+        <v>6067500</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B157" t="n">
-        <v>226.6027887018479</v>
+        <v>223.3773398363102</v>
       </c>
       <c r="C157" t="n">
-        <v>227.5526214735122</v>
+        <v>225.4946599491012</v>
       </c>
       <c r="D157" t="n">
-        <v>224.6140956793093</v>
+        <v>221.972390518204</v>
       </c>
       <c r="E157" t="n">
-        <v>225.0890045166016</v>
+        <v>222.9518890380859</v>
       </c>
       <c r="F157" t="n">
-        <v>6067500</v>
+        <v>7897800</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B158" t="n">
-        <v>223.3773245484034</v>
+        <v>225.316553812185</v>
       </c>
       <c r="C158" t="n">
-        <v>225.4946445162854</v>
+        <v>228.5815840196301</v>
       </c>
       <c r="D158" t="n">
-        <v>221.9723753264516</v>
+        <v>223.9709662459624</v>
       </c>
       <c r="E158" t="n">
-        <v>222.9518737792969</v>
+        <v>225.3759155273438</v>
       </c>
       <c r="F158" t="n">
-        <v>7897800</v>
+        <v>7179800</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B159" t="n">
-        <v>225.316553812185</v>
+        <v>223.1299745498951</v>
       </c>
       <c r="C159" t="n">
-        <v>228.5815840196301</v>
+        <v>226.2861697879244</v>
       </c>
       <c r="D159" t="n">
-        <v>223.9709662459624</v>
+        <v>222.4769655150452</v>
       </c>
       <c r="E159" t="n">
-        <v>225.3759155273438</v>
+        <v>224.9405822753906</v>
       </c>
       <c r="F159" t="n">
-        <v>7179800</v>
+        <v>7071100</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B160" t="n">
-        <v>223.1299896858621</v>
+        <v>225.534219851175</v>
       </c>
       <c r="C160" t="n">
-        <v>226.2861851379911</v>
+        <v>228.7102074345108</v>
       </c>
       <c r="D160" t="n">
-        <v>222.4769806067155</v>
+        <v>225.3957041523519</v>
       </c>
       <c r="E160" t="n">
-        <v>224.9405975341797</v>
+        <v>227.4140930175781</v>
       </c>
       <c r="F160" t="n">
-        <v>7071100</v>
+        <v>8157200</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B161" t="n">
-        <v>225.534219851175</v>
+        <v>226.6324494909732</v>
       </c>
       <c r="C161" t="n">
-        <v>228.7102074345108</v>
+        <v>227.3349316460146</v>
       </c>
       <c r="D161" t="n">
-        <v>225.3957041523519</v>
+        <v>224.6140757884101</v>
       </c>
       <c r="E161" t="n">
-        <v>227.4140930175781</v>
+        <v>224.7822723388672</v>
       </c>
       <c r="F161" t="n">
-        <v>8157200</v>
+        <v>6863600</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B162" t="n">
-        <v>226.6324494909732</v>
+        <v>223.12007375354</v>
       </c>
       <c r="C162" t="n">
-        <v>227.3349316460146</v>
+        <v>224.6635537914519</v>
       </c>
       <c r="D162" t="n">
-        <v>224.6140757884101</v>
+        <v>221.2105348477109</v>
       </c>
       <c r="E162" t="n">
-        <v>224.7822723388672</v>
+        <v>221.8239593505859</v>
       </c>
       <c r="F162" t="n">
-        <v>6863600</v>
+        <v>8215200</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B163" t="n">
-        <v>223.12007375354</v>
+        <v>223.0013599943453</v>
       </c>
       <c r="C163" t="n">
-        <v>224.6635537914519</v>
+        <v>224.1292778920903</v>
       </c>
       <c r="D163" t="n">
-        <v>221.2105348477109</v>
+        <v>222.5165474841354</v>
       </c>
       <c r="E163" t="n">
-        <v>221.8239593505859</v>
+        <v>223.15966796875</v>
       </c>
       <c r="F163" t="n">
-        <v>8215200</v>
+        <v>5556700</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B164" t="n">
-        <v>223.0013599943453</v>
+        <v>222.86284542864</v>
       </c>
       <c r="C164" t="n">
-        <v>224.1292778920903</v>
+        <v>223.9412902027537</v>
       </c>
       <c r="D164" t="n">
-        <v>222.5165474841354</v>
+        <v>220.5872173504634</v>
       </c>
       <c r="E164" t="n">
-        <v>223.15966796875</v>
+        <v>222.2395172119141</v>
       </c>
       <c r="F164" t="n">
-        <v>5556700</v>
+        <v>7982300</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B165" t="n">
-        <v>222.86284542864</v>
+        <v>222.397817873641</v>
       </c>
       <c r="C165" t="n">
-        <v>223.9412902027537</v>
+        <v>222.397817873641</v>
       </c>
       <c r="D165" t="n">
-        <v>220.5872173504634</v>
+        <v>218.2918049197337</v>
       </c>
       <c r="E165" t="n">
-        <v>222.2395172119141</v>
+        <v>220.1518707275391</v>
       </c>
       <c r="F165" t="n">
-        <v>7982300</v>
+        <v>7269700</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B166" t="n">
-        <v>222.3978024591847</v>
+        <v>220.5773139289545</v>
       </c>
       <c r="C166" t="n">
-        <v>222.3978024591847</v>
+        <v>221.0027495995129</v>
       </c>
       <c r="D166" t="n">
-        <v>218.2917897898664</v>
+        <v>218.578717393272</v>
       </c>
       <c r="E166" t="n">
-        <v>220.15185546875</v>
+        <v>218.9744873046875</v>
       </c>
       <c r="F166" t="n">
-        <v>7269700</v>
+        <v>5550600</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B167" t="n">
-        <v>220.5773139289545</v>
+        <v>218.9744932439037</v>
       </c>
       <c r="C167" t="n">
-        <v>221.0027495995129</v>
+        <v>220.9137130226623</v>
       </c>
       <c r="D167" t="n">
-        <v>218.578717393272</v>
+        <v>218.034549114472</v>
       </c>
       <c r="E167" t="n">
-        <v>218.9744873046875</v>
+        <v>219.0833129882812</v>
       </c>
       <c r="F167" t="n">
-        <v>5550600</v>
+        <v>6223200</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B168" t="n">
-        <v>218.9744932439037</v>
+        <v>220.6366747923043</v>
       </c>
       <c r="C168" t="n">
-        <v>220.9137130226623</v>
+        <v>225.2373886538506</v>
       </c>
       <c r="D168" t="n">
-        <v>218.034549114472</v>
+        <v>219.3009758791698</v>
       </c>
       <c r="E168" t="n">
-        <v>219.0833129882812</v>
+        <v>221.8833160400391</v>
       </c>
       <c r="F168" t="n">
-        <v>6223200</v>
+        <v>8632500</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B169" t="n">
-        <v>220.6366899653626</v>
+        <v>223.4268017505994</v>
       </c>
       <c r="C169" t="n">
-        <v>225.2374041432973</v>
+        <v>228.3540202522719</v>
       </c>
       <c r="D169" t="n">
-        <v>219.3009909603728</v>
+        <v>223.0508241008666</v>
       </c>
       <c r="E169" t="n">
-        <v>221.8833312988281</v>
+        <v>227.9780426025391</v>
       </c>
       <c r="F169" t="n">
-        <v>8632500</v>
+        <v>7464500</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B170" t="n">
-        <v>223.4268017505994</v>
+        <v>228.5519118475702</v>
       </c>
       <c r="C170" t="n">
-        <v>228.3540202522719</v>
+        <v>229.3038520966222</v>
       </c>
       <c r="D170" t="n">
-        <v>223.0508241008666</v>
+        <v>226.7314153938151</v>
       </c>
       <c r="E170" t="n">
-        <v>227.9780426025391</v>
+        <v>228.3540344238281</v>
       </c>
       <c r="F170" t="n">
-        <v>7464500</v>
+        <v>6974400</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B171" t="n">
-        <v>228.5518965755589</v>
+        <v>228.324343449484</v>
       </c>
       <c r="C171" t="n">
-        <v>229.3038367743656</v>
+        <v>229.6798195939985</v>
       </c>
       <c r="D171" t="n">
-        <v>226.7314002434507</v>
+        <v>224.0402302332647</v>
       </c>
       <c r="E171" t="n">
-        <v>228.3540191650391</v>
+        <v>224.307373046875</v>
       </c>
       <c r="F171" t="n">
-        <v>6974400</v>
+        <v>12167000</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B172" t="n">
-        <v>228.324343449484</v>
+        <v>224.3073719260098</v>
       </c>
       <c r="C172" t="n">
-        <v>229.6798195939985</v>
+        <v>227.2656747432453</v>
       </c>
       <c r="D172" t="n">
-        <v>224.0402302332647</v>
+        <v>223.466374045218</v>
       </c>
       <c r="E172" t="n">
-        <v>224.307373046875</v>
+        <v>226.4939422607422</v>
       </c>
       <c r="F172" t="n">
-        <v>12167000</v>
+        <v>10141600</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B173" t="n">
-        <v>224.3073719260098</v>
+        <v>226.5137209227187</v>
       </c>
       <c r="C173" t="n">
-        <v>227.2656747432453</v>
+        <v>228.4034825714771</v>
       </c>
       <c r="D173" t="n">
-        <v>223.466374045218</v>
+        <v>225.6232499676584</v>
       </c>
       <c r="E173" t="n">
-        <v>226.4939422607422</v>
+        <v>227.5624847412109</v>
       </c>
       <c r="F173" t="n">
-        <v>10141600</v>
+        <v>9677900</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B174" t="n">
-        <v>226.5137209227187</v>
+        <v>229.2345877493695</v>
       </c>
       <c r="C174" t="n">
-        <v>228.4034825714771</v>
+        <v>229.5413000019429</v>
       </c>
       <c r="D174" t="n">
-        <v>225.6232499676584</v>
+        <v>226.7412900911319</v>
       </c>
       <c r="E174" t="n">
-        <v>227.5624847412109</v>
+        <v>226.8897094726562</v>
       </c>
       <c r="F174" t="n">
-        <v>9677900</v>
+        <v>7353800</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B175" t="n">
-        <v>229.2345877493695</v>
+        <v>226.8897069691897</v>
       </c>
       <c r="C175" t="n">
-        <v>229.5413000019429</v>
+        <v>229.432462629467</v>
       </c>
       <c r="D175" t="n">
-        <v>226.7412900911319</v>
+        <v>224.9405835372236</v>
       </c>
       <c r="E175" t="n">
-        <v>226.8897094726562</v>
+        <v>229.2741546630859</v>
       </c>
       <c r="F175" t="n">
-        <v>7353800</v>
+        <v>5239000</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B176" t="n">
-        <v>226.8897069691897</v>
+        <v>230.5307110319731</v>
       </c>
       <c r="C176" t="n">
-        <v>229.432462629467</v>
+        <v>233.0042165151488</v>
       </c>
       <c r="D176" t="n">
-        <v>224.9405835372236</v>
+        <v>230.2536796256238</v>
       </c>
       <c r="E176" t="n">
-        <v>229.2741546630859</v>
+        <v>231.8565063476562</v>
       </c>
       <c r="F176" t="n">
-        <v>5239000</v>
+        <v>5462300</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,25 +5019,25 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B177" t="n">
-        <v>230.5307110319731</v>
+        <v>231.856506324529</v>
       </c>
       <c r="C177" t="n">
-        <v>233.0042165151488</v>
+        <v>232.0953339431715</v>
       </c>
       <c r="D177" t="n">
-        <v>230.2536796256238</v>
+        <v>227.9557463234551</v>
       </c>
       <c r="E177" t="n">
-        <v>231.8565063476562</v>
+        <v>229.0503387451172</v>
       </c>
       <c r="F177" t="n">
-        <v>5462300</v>
+        <v>6619600</v>
       </c>
       <c r="G177" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -5045,25 +5045,25 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B178" t="n">
-        <v>231.856506324529</v>
+        <v>228.8513234809034</v>
       </c>
       <c r="C178" t="n">
-        <v>232.0953339431715</v>
+        <v>231.7470457253588</v>
       </c>
       <c r="D178" t="n">
-        <v>227.9557463234551</v>
+        <v>227.896043373475</v>
       </c>
       <c r="E178" t="n">
-        <v>229.0503387451172</v>
+        <v>230.1548919677734</v>
       </c>
       <c r="F178" t="n">
-        <v>6619600</v>
+        <v>5835500</v>
       </c>
       <c r="G178" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B179" t="n">
-        <v>228.8513234809034</v>
+        <v>228.9010720691913</v>
       </c>
       <c r="C179" t="n">
-        <v>231.7470457253588</v>
+        <v>230.7320381891827</v>
       </c>
       <c r="D179" t="n">
-        <v>227.896043373475</v>
+        <v>228.6025413534768</v>
       </c>
       <c r="E179" t="n">
-        <v>230.1548919677734</v>
+        <v>229.6672973632812</v>
       </c>
       <c r="F179" t="n">
-        <v>5835500</v>
+        <v>7193400</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B180" t="n">
-        <v>228.9010720691913</v>
+        <v>230.0951744973679</v>
       </c>
       <c r="C180" t="n">
-        <v>230.7320381891827</v>
+        <v>230.36385365377</v>
       </c>
       <c r="D180" t="n">
-        <v>228.6025413534768</v>
+        <v>223.4877626284344</v>
       </c>
       <c r="E180" t="n">
-        <v>229.6672973632812</v>
+        <v>224.2241363525391</v>
       </c>
       <c r="F180" t="n">
-        <v>7193400</v>
+        <v>13897700</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B181" t="n">
-        <v>230.0951744973679</v>
+        <v>222.1045945004449</v>
       </c>
       <c r="C181" t="n">
-        <v>230.36385365377</v>
+        <v>223.3385143974124</v>
       </c>
       <c r="D181" t="n">
-        <v>223.4877626284344</v>
+        <v>219.7561761055088</v>
       </c>
       <c r="E181" t="n">
-        <v>224.2241363525391</v>
+        <v>222.4130706787109</v>
       </c>
       <c r="F181" t="n">
-        <v>13897700</v>
+        <v>8041000</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B182" t="n">
-        <v>222.1045945004449</v>
+        <v>221.4876358909895</v>
       </c>
       <c r="C182" t="n">
-        <v>223.3385143974124</v>
+        <v>224.3933034528787</v>
       </c>
       <c r="D182" t="n">
-        <v>219.7561761055088</v>
+        <v>220.0845521676131</v>
       </c>
       <c r="E182" t="n">
-        <v>222.4130706787109</v>
+        <v>221.7961120605469</v>
       </c>
       <c r="F182" t="n">
-        <v>8041000</v>
+        <v>5669000</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B183" t="n">
-        <v>221.4876358909895</v>
+        <v>221.3582777644383</v>
       </c>
       <c r="C183" t="n">
-        <v>224.3933034528787</v>
+        <v>223.8261024020756</v>
       </c>
       <c r="D183" t="n">
-        <v>220.0845521676131</v>
+        <v>220.9104892689172</v>
       </c>
       <c r="E183" t="n">
-        <v>221.7961120605469</v>
+        <v>222.1444091796875</v>
       </c>
       <c r="F183" t="n">
-        <v>5669000</v>
+        <v>6507200</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B184" t="n">
-        <v>221.3582777644383</v>
+        <v>225.9754999423843</v>
       </c>
       <c r="C184" t="n">
-        <v>223.8261024020756</v>
+        <v>227.5477475509985</v>
       </c>
       <c r="D184" t="n">
-        <v>220.9104892689172</v>
+        <v>224.7913377117005</v>
       </c>
       <c r="E184" t="n">
-        <v>222.1444091796875</v>
+        <v>227.0502014160156</v>
       </c>
       <c r="F184" t="n">
-        <v>6507200</v>
+        <v>7274800</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B185" t="n">
-        <v>225.9754999423843</v>
+        <v>228.8712298379233</v>
       </c>
       <c r="C185" t="n">
-        <v>227.5477475509985</v>
+        <v>234.0656128776528</v>
       </c>
       <c r="D185" t="n">
-        <v>224.7913377117005</v>
+        <v>227.8761375342802</v>
       </c>
       <c r="E185" t="n">
-        <v>227.0502014160156</v>
+        <v>231.6276397705078</v>
       </c>
       <c r="F185" t="n">
-        <v>7274800</v>
+        <v>8034900</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B186" t="n">
-        <v>228.8712298379233</v>
+        <v>231.6276367875738</v>
       </c>
       <c r="C186" t="n">
-        <v>234.0656128776528</v>
+        <v>233.7969306933057</v>
       </c>
       <c r="D186" t="n">
-        <v>227.8761375342802</v>
+        <v>229.428476143926</v>
       </c>
       <c r="E186" t="n">
-        <v>231.6276397705078</v>
+        <v>231.0206298828125</v>
       </c>
       <c r="F186" t="n">
-        <v>8034900</v>
+        <v>7559800</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B187" t="n">
-        <v>231.6276367875738</v>
+        <v>231.2395468518091</v>
       </c>
       <c r="C187" t="n">
-        <v>233.7969306933057</v>
+        <v>236.5433904796373</v>
       </c>
       <c r="D187" t="n">
-        <v>229.428476143926</v>
+        <v>229.2792138627353</v>
       </c>
       <c r="E187" t="n">
-        <v>231.0206298828125</v>
+        <v>235.8368682861328</v>
       </c>
       <c r="F187" t="n">
-        <v>7559800</v>
+        <v>8354500</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B188" t="n">
-        <v>231.2395468518091</v>
+        <v>237.6777986497502</v>
       </c>
       <c r="C188" t="n">
-        <v>236.5433904796373</v>
+        <v>239.7475772433621</v>
       </c>
       <c r="D188" t="n">
-        <v>229.2792138627353</v>
+        <v>235.886629497679</v>
       </c>
       <c r="E188" t="n">
-        <v>235.8368682861328</v>
+        <v>237.3195648193359</v>
       </c>
       <c r="F188" t="n">
-        <v>8354500</v>
+        <v>8350800</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B189" t="n">
-        <v>237.6777986497502</v>
+        <v>238.822141602048</v>
       </c>
       <c r="C189" t="n">
-        <v>239.7475772433621</v>
+        <v>240.4142952862894</v>
       </c>
       <c r="D189" t="n">
-        <v>235.886629497679</v>
+        <v>236.971269397276</v>
       </c>
       <c r="E189" t="n">
-        <v>237.3195648193359</v>
+        <v>237.1603393554688</v>
       </c>
       <c r="F189" t="n">
-        <v>8350800</v>
+        <v>7399000</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B190" t="n">
-        <v>238.822141602048</v>
+        <v>238.8221408093525</v>
       </c>
       <c r="C190" t="n">
-        <v>240.4142952862894</v>
+        <v>239.7276784040579</v>
       </c>
       <c r="D190" t="n">
-        <v>236.971269397276</v>
+        <v>236.354316272482</v>
       </c>
       <c r="E190" t="n">
-        <v>237.1603393554688</v>
+        <v>239.6878662109375</v>
       </c>
       <c r="F190" t="n">
-        <v>7399000</v>
+        <v>6459400</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B191" t="n">
-        <v>238.8221408093525</v>
+        <v>237.8270530309927</v>
       </c>
       <c r="C191" t="n">
-        <v>239.7276784040579</v>
+        <v>238.3245991670408</v>
       </c>
       <c r="D191" t="n">
-        <v>236.354316272482</v>
+        <v>232.4336547382997</v>
       </c>
       <c r="E191" t="n">
-        <v>239.6878662109375</v>
+        <v>234.5034484863281</v>
       </c>
       <c r="F191" t="n">
-        <v>6459400</v>
+        <v>7732000</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B192" t="n">
-        <v>237.8270530309927</v>
+        <v>235.2099495568312</v>
       </c>
       <c r="C192" t="n">
-        <v>238.3245991670408</v>
+        <v>235.2099495568312</v>
       </c>
       <c r="D192" t="n">
-        <v>232.4336547382997</v>
+        <v>229.8862151458974</v>
       </c>
       <c r="E192" t="n">
-        <v>234.5034484863281</v>
+        <v>234.0257873535156</v>
       </c>
       <c r="F192" t="n">
-        <v>7732000</v>
+        <v>7718100</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B193" t="n">
-        <v>235.2099495568312</v>
+        <v>232.8814495345484</v>
       </c>
       <c r="C193" t="n">
-        <v>235.2099495568312</v>
+        <v>234.2745726796724</v>
       </c>
       <c r="D193" t="n">
-        <v>229.8862151458974</v>
+        <v>229.5677903566066</v>
       </c>
       <c r="E193" t="n">
-        <v>234.0257873535156</v>
+        <v>233.0506134033203</v>
       </c>
       <c r="F193" t="n">
-        <v>7718100</v>
+        <v>8548000</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B194" t="n">
-        <v>232.8814495345484</v>
+        <v>230.6424813960874</v>
       </c>
       <c r="C194" t="n">
-        <v>234.2745726796724</v>
+        <v>231.6077220970904</v>
       </c>
       <c r="D194" t="n">
-        <v>229.5677903566066</v>
+        <v>226.4830030630252</v>
       </c>
       <c r="E194" t="n">
-        <v>233.0506134033203</v>
+        <v>227.2691192626953</v>
       </c>
       <c r="F194" t="n">
-        <v>8548000</v>
+        <v>18989800</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B195" t="n">
-        <v>230.6424813960874</v>
+        <v>227.8263796240252</v>
       </c>
       <c r="C195" t="n">
-        <v>231.6077220970904</v>
+        <v>230.3141103803127</v>
       </c>
       <c r="D195" t="n">
-        <v>226.4830030630252</v>
+        <v>226.3834988221592</v>
       </c>
       <c r="E195" t="n">
-        <v>227.2691192626953</v>
+        <v>230.1548919677734</v>
       </c>
       <c r="F195" t="n">
-        <v>18989800</v>
+        <v>8518300</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B196" t="n">
-        <v>227.8263796240252</v>
+        <v>234.4835421454308</v>
       </c>
       <c r="C196" t="n">
-        <v>230.3141103803127</v>
+        <v>238.6231296371808</v>
       </c>
       <c r="D196" t="n">
-        <v>226.3834988221592</v>
+        <v>233.1998797966796</v>
       </c>
       <c r="E196" t="n">
-        <v>230.1548919677734</v>
+        <v>237.9066619873047</v>
       </c>
       <c r="F196" t="n">
-        <v>8518300</v>
+        <v>11802000</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B197" t="n">
-        <v>234.4835421454308</v>
+        <v>238.7126772290818</v>
       </c>
       <c r="C197" t="n">
-        <v>238.6231296371808</v>
+        <v>241.8472117165478</v>
       </c>
       <c r="D197" t="n">
-        <v>233.1998797966796</v>
+        <v>237.5782726810186</v>
       </c>
       <c r="E197" t="n">
-        <v>237.9066619873047</v>
+        <v>239.8172302246094</v>
       </c>
       <c r="F197" t="n">
-        <v>11802000</v>
+        <v>8139200</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B198" t="n">
-        <v>238.7126772290818</v>
+        <v>240.0859235854152</v>
       </c>
       <c r="C198" t="n">
-        <v>241.8472117165478</v>
+        <v>246.9719604825856</v>
       </c>
       <c r="D198" t="n">
-        <v>237.5782726810186</v>
+        <v>239.7077836523882</v>
       </c>
       <c r="E198" t="n">
-        <v>239.8172302246094</v>
+        <v>243.6782073974609</v>
       </c>
       <c r="F198" t="n">
-        <v>8139200</v>
+        <v>10130400</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B199" t="n">
-        <v>240.0859235854152</v>
+        <v>247.0515630057391</v>
       </c>
       <c r="C199" t="n">
-        <v>246.9719604825856</v>
+        <v>253.857990512684</v>
       </c>
       <c r="D199" t="n">
-        <v>239.7077836523882</v>
+        <v>246.6535169859773</v>
       </c>
       <c r="E199" t="n">
-        <v>243.6782073974609</v>
+        <v>253.4102020263672</v>
       </c>
       <c r="F199" t="n">
-        <v>10130400</v>
+        <v>16316800</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B200" t="n">
-        <v>247.0515630057391</v>
+        <v>251.9474045302274</v>
       </c>
       <c r="C200" t="n">
-        <v>253.857990512684</v>
+        <v>257.3109358669097</v>
       </c>
       <c r="D200" t="n">
-        <v>246.6535169859773</v>
+        <v>250.7930938975173</v>
       </c>
       <c r="E200" t="n">
-        <v>253.4102020263672</v>
+        <v>257.2413024902344</v>
       </c>
       <c r="F200" t="n">
-        <v>16316800</v>
+        <v>8608400</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B201" t="n">
-        <v>251.9474045302274</v>
+        <v>257.7288999793201</v>
       </c>
       <c r="C201" t="n">
-        <v>257.3109358669097</v>
+        <v>258.62447695588</v>
       </c>
       <c r="D201" t="n">
-        <v>250.7930938975173</v>
+        <v>251.9275101770222</v>
       </c>
       <c r="E201" t="n">
-        <v>257.2413024902344</v>
+        <v>252.7235870361328</v>
       </c>
       <c r="F201" t="n">
-        <v>8608400</v>
+        <v>8469500</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B202" t="n">
-        <v>257.7288999793201</v>
+        <v>252.0071226458085</v>
       </c>
       <c r="C202" t="n">
-        <v>258.62447695588</v>
+        <v>252.9524572852904</v>
       </c>
       <c r="D202" t="n">
-        <v>251.9275101770222</v>
+        <v>249.8477741968348</v>
       </c>
       <c r="E202" t="n">
-        <v>252.7235870361328</v>
+        <v>252.7335357666016</v>
       </c>
       <c r="F202" t="n">
-        <v>8469500</v>
+        <v>6516500</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B203" t="n">
-        <v>252.0071226458085</v>
+        <v>254.5247047293354</v>
       </c>
       <c r="C203" t="n">
-        <v>252.9524572852904</v>
+        <v>261.8087875806335</v>
       </c>
       <c r="D203" t="n">
-        <v>249.8477741968348</v>
+        <v>252.753441667793</v>
       </c>
       <c r="E203" t="n">
-        <v>252.7335357666016</v>
+        <v>261.7490844726562</v>
       </c>
       <c r="F203" t="n">
-        <v>6516500</v>
+        <v>7998700</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B204" t="n">
-        <v>254.5247047293354</v>
+        <v>258.9528582650781</v>
       </c>
       <c r="C204" t="n">
-        <v>261.8087875806335</v>
+        <v>260.0972082397536</v>
       </c>
       <c r="D204" t="n">
-        <v>252.753441667793</v>
+        <v>254.673943516207</v>
       </c>
       <c r="E204" t="n">
-        <v>261.7490844726562</v>
+        <v>258.0572509765625</v>
       </c>
       <c r="F204" t="n">
-        <v>7998700</v>
+        <v>6803700</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B205" t="n">
-        <v>258.9528582650781</v>
+        <v>263.5899938466549</v>
       </c>
       <c r="C205" t="n">
-        <v>260.0972082397536</v>
+        <v>268.1076906797339</v>
       </c>
       <c r="D205" t="n">
-        <v>254.673943516207</v>
+        <v>262.7540896546532</v>
       </c>
       <c r="E205" t="n">
-        <v>258.0572509765625</v>
+        <v>265.9284362792969</v>
       </c>
       <c r="F205" t="n">
-        <v>6803700</v>
+        <v>9089700</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B206" t="n">
-        <v>263.5899938466549</v>
+        <v>267.2817917945089</v>
       </c>
       <c r="C206" t="n">
-        <v>268.1076906797339</v>
+        <v>267.2817917945089</v>
       </c>
       <c r="D206" t="n">
-        <v>262.7540896546532</v>
+        <v>261.8386358221884</v>
       </c>
       <c r="E206" t="n">
-        <v>265.9284362792969</v>
+        <v>262.1072998046875</v>
       </c>
       <c r="F206" t="n">
-        <v>9089700</v>
+        <v>6769400</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B207" t="n">
-        <v>267.2817917945089</v>
+        <v>259.3508895364454</v>
       </c>
       <c r="C207" t="n">
-        <v>267.2817917945089</v>
+        <v>262.1570568783993</v>
       </c>
       <c r="D207" t="n">
-        <v>261.8386358221884</v>
+        <v>256.8631589924022</v>
       </c>
       <c r="E207" t="n">
-        <v>262.1072998046875</v>
+        <v>257.8283996582031</v>
       </c>
       <c r="F207" t="n">
-        <v>6769400</v>
+        <v>6426100</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B208" t="n">
-        <v>259.3508895364454</v>
+        <v>258.9130640253377</v>
       </c>
       <c r="C208" t="n">
-        <v>262.1570568783993</v>
+        <v>260.0176018849775</v>
       </c>
       <c r="D208" t="n">
-        <v>256.8631589924022</v>
+        <v>254.2659848771424</v>
       </c>
       <c r="E208" t="n">
-        <v>257.8283996582031</v>
+        <v>255.7188262939453</v>
       </c>
       <c r="F208" t="n">
-        <v>6426100</v>
+        <v>6534700</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B209" t="n">
-        <v>258.9130640253377</v>
+        <v>256.6840530111044</v>
       </c>
       <c r="C209" t="n">
-        <v>260.0176018849775</v>
+        <v>258.2562853735001</v>
       </c>
       <c r="D209" t="n">
-        <v>254.2659848771424</v>
+        <v>254.892868775476</v>
       </c>
       <c r="E209" t="n">
-        <v>255.7188262939453</v>
+        <v>256.5049133300781</v>
       </c>
       <c r="F209" t="n">
-        <v>6534700</v>
+        <v>5272200</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B210" t="n">
-        <v>256.6840530111044</v>
+        <v>254.2759347913044</v>
       </c>
       <c r="C210" t="n">
-        <v>258.2562853735001</v>
+        <v>255.1317299625397</v>
       </c>
       <c r="D210" t="n">
-        <v>254.892868775476</v>
+        <v>250.9025724938729</v>
       </c>
       <c r="E210" t="n">
-        <v>256.5049133300781</v>
+        <v>252.6041870117188</v>
       </c>
       <c r="F210" t="n">
-        <v>5272200</v>
+        <v>8770600</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B211" t="n">
-        <v>254.2759347913044</v>
+        <v>248.8626188136353</v>
       </c>
       <c r="C211" t="n">
-        <v>255.1317299625397</v>
+        <v>255.5695309055475</v>
       </c>
       <c r="D211" t="n">
-        <v>250.9025724938729</v>
+        <v>244.842452777813</v>
       </c>
       <c r="E211" t="n">
-        <v>252.6041870117188</v>
+        <v>245.8076934814453</v>
       </c>
       <c r="F211" t="n">
-        <v>8770600</v>
+        <v>10547300</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B212" t="n">
-        <v>248.8626188136353</v>
+        <v>247.6784538478382</v>
       </c>
       <c r="C212" t="n">
-        <v>255.5695309055475</v>
+        <v>252.3056419000621</v>
       </c>
       <c r="D212" t="n">
-        <v>244.842452777813</v>
+        <v>245.091223119708</v>
       </c>
       <c r="E212" t="n">
-        <v>245.8076934814453</v>
+        <v>248.7432098388672</v>
       </c>
       <c r="F212" t="n">
-        <v>10547300</v>
+        <v>11097600</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B213" t="n">
-        <v>247.6784538478382</v>
+        <v>251.350352994489</v>
       </c>
       <c r="C213" t="n">
-        <v>252.3056419000621</v>
+        <v>254.4052935535989</v>
       </c>
       <c r="D213" t="n">
-        <v>245.091223119708</v>
+        <v>250.7134945486414</v>
       </c>
       <c r="E213" t="n">
-        <v>248.7432098388672</v>
+        <v>251.7981414794922</v>
       </c>
       <c r="F213" t="n">
-        <v>11097600</v>
+        <v>10167700</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B214" t="n">
-        <v>251.350352994489</v>
+        <v>250.7731932271148</v>
       </c>
       <c r="C214" t="n">
-        <v>254.4052935535989</v>
+        <v>252.9325415941838</v>
       </c>
       <c r="D214" t="n">
-        <v>250.7134945486414</v>
+        <v>247.4097917368304</v>
       </c>
       <c r="E214" t="n">
-        <v>251.7981414794922</v>
+        <v>247.5988616943359</v>
       </c>
       <c r="F214" t="n">
-        <v>10167700</v>
+        <v>8114700</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B215" t="n">
-        <v>250.7731932271148</v>
+        <v>246.2355858738711</v>
       </c>
       <c r="C215" t="n">
-        <v>252.9325415941838</v>
+        <v>250.1064943021279</v>
       </c>
       <c r="D215" t="n">
-        <v>247.4097917368304</v>
+        <v>244.2852134745944</v>
       </c>
       <c r="E215" t="n">
-        <v>247.5988616943359</v>
+        <v>249.3800811767578</v>
       </c>
       <c r="F215" t="n">
-        <v>8114700</v>
+        <v>7793100</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B216" t="n">
-        <v>246.2355858738711</v>
+        <v>251.5195173574522</v>
       </c>
       <c r="C216" t="n">
-        <v>250.1064943021279</v>
+        <v>255.0322070489389</v>
       </c>
       <c r="D216" t="n">
-        <v>244.2852134745944</v>
+        <v>249.9771364820368</v>
       </c>
       <c r="E216" t="n">
-        <v>249.3800811767578</v>
+        <v>254.3754425048828</v>
       </c>
       <c r="F216" t="n">
-        <v>7793100</v>
+        <v>9100200</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B217" t="n">
-        <v>251.5195173574522</v>
+        <v>253.9873531958193</v>
       </c>
       <c r="C217" t="n">
-        <v>255.0322070489389</v>
+        <v>258.9230174724852</v>
       </c>
       <c r="D217" t="n">
-        <v>249.9771364820368</v>
+        <v>253.1713702566359</v>
       </c>
       <c r="E217" t="n">
-        <v>254.3754425048828</v>
+        <v>257.99755859375</v>
       </c>
       <c r="F217" t="n">
-        <v>9100200</v>
+        <v>8063300</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B218" t="n">
-        <v>253.9873531958193</v>
+        <v>260.1469668034143</v>
       </c>
       <c r="C218" t="n">
-        <v>258.9230174724852</v>
+        <v>262.41577598127</v>
       </c>
       <c r="D218" t="n">
-        <v>253.1713702566359</v>
+        <v>258.3358915701962</v>
       </c>
       <c r="E218" t="n">
-        <v>257.99755859375</v>
+        <v>262.1072998046875</v>
       </c>
       <c r="F218" t="n">
-        <v>8063300</v>
+        <v>6351800</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B219" t="n">
-        <v>260.1469668034143</v>
+        <v>261.2614678377304</v>
       </c>
       <c r="C219" t="n">
-        <v>262.41577598127</v>
+        <v>267.4807946322661</v>
       </c>
       <c r="D219" t="n">
-        <v>258.3358915701962</v>
+        <v>260.0673753138636</v>
       </c>
       <c r="E219" t="n">
-        <v>262.1072998046875</v>
+        <v>264.6448059082031</v>
       </c>
       <c r="F219" t="n">
-        <v>6351800</v>
+        <v>9647900</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B220" t="n">
-        <v>261.2614678377304</v>
+        <v>268.6749001082239</v>
       </c>
       <c r="C220" t="n">
-        <v>267.4807946322661</v>
+        <v>273.5508459255159</v>
       </c>
       <c r="D220" t="n">
-        <v>260.0673753138636</v>
+        <v>264.8736405295307</v>
       </c>
       <c r="E220" t="n">
-        <v>264.6448059082031</v>
+        <v>265.4209594726562</v>
       </c>
       <c r="F220" t="n">
-        <v>9647900</v>
+        <v>10491000</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B221" t="n">
-        <v>268.6749001082239</v>
+        <v>267.1822622796963</v>
       </c>
       <c r="C221" t="n">
-        <v>273.5508459255159</v>
+        <v>268.0181361041443</v>
       </c>
       <c r="D221" t="n">
-        <v>264.8736405295307</v>
+        <v>263.4904786297666</v>
       </c>
       <c r="E221" t="n">
-        <v>265.4209594726562</v>
+        <v>264.2268371582031</v>
       </c>
       <c r="F221" t="n">
-        <v>10491000</v>
+        <v>6105600</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B222" t="n">
-        <v>267.1822622796963</v>
+        <v>257.7587518734895</v>
       </c>
       <c r="C222" t="n">
-        <v>268.0181361041443</v>
+        <v>259.2414296518399</v>
       </c>
       <c r="D222" t="n">
-        <v>263.4904786297666</v>
+        <v>253.310688170632</v>
       </c>
       <c r="E222" t="n">
-        <v>264.2268371582031</v>
+        <v>254.5645141601562</v>
       </c>
       <c r="F222" t="n">
-        <v>6105600</v>
+        <v>8216500</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B223" t="n">
-        <v>257.7587518734895</v>
+        <v>254.7535759665547</v>
       </c>
       <c r="C223" t="n">
-        <v>259.2414296518399</v>
+        <v>257.2114550322676</v>
       </c>
       <c r="D223" t="n">
-        <v>253.310688170632</v>
+        <v>252.046908655097</v>
       </c>
       <c r="E223" t="n">
-        <v>254.5645141601562</v>
+        <v>255.0919036865234</v>
       </c>
       <c r="F223" t="n">
-        <v>8216500</v>
+        <v>6782100</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B224" t="n">
-        <v>254.7535759665547</v>
+        <v>253.7186719595458</v>
       </c>
       <c r="C224" t="n">
-        <v>257.2114550322676</v>
+        <v>256.4850271972422</v>
       </c>
       <c r="D224" t="n">
-        <v>252.046908655097</v>
+        <v>249.6785998577546</v>
       </c>
       <c r="E224" t="n">
-        <v>255.0919036865234</v>
+        <v>253.1614227294922</v>
       </c>
       <c r="F224" t="n">
-        <v>6782100</v>
+        <v>8136300</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B225" t="n">
-        <v>253.7186719595458</v>
+        <v>253.1614264806184</v>
       </c>
       <c r="C225" t="n">
-        <v>256.4850271972422</v>
+        <v>254.2659795008061</v>
       </c>
       <c r="D225" t="n">
-        <v>249.6785998577546</v>
+        <v>249.2109089785714</v>
       </c>
       <c r="E225" t="n">
-        <v>253.1614227294922</v>
+        <v>253.6788635253906</v>
       </c>
       <c r="F225" t="n">
-        <v>8136300</v>
+        <v>7362400</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B226" t="n">
-        <v>253.1614264806184</v>
+        <v>253.9972934738065</v>
       </c>
       <c r="C226" t="n">
-        <v>254.2659795008061</v>
+        <v>258.0473261663437</v>
       </c>
       <c r="D226" t="n">
-        <v>249.2109089785714</v>
+        <v>253.2211227437212</v>
       </c>
       <c r="E226" t="n">
-        <v>253.6788635253906</v>
+        <v>256.3258056640625</v>
       </c>
       <c r="F226" t="n">
-        <v>7362400</v>
+        <v>6472600</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B227" t="n">
-        <v>253.9972934738065</v>
+        <v>260.425593365904</v>
       </c>
       <c r="C227" t="n">
-        <v>258.0473261663437</v>
+        <v>260.8236242062839</v>
       </c>
       <c r="D227" t="n">
-        <v>253.2211227437212</v>
+        <v>254.0271572625725</v>
       </c>
       <c r="E227" t="n">
-        <v>256.3258056640625</v>
+        <v>255.7188262939453</v>
       </c>
       <c r="F227" t="n">
-        <v>6472600</v>
+        <v>6931800</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B228" t="n">
-        <v>260.425593365904</v>
+        <v>254.6341623817563</v>
       </c>
       <c r="C228" t="n">
-        <v>260.8236242062839</v>
+        <v>258.3259614136433</v>
       </c>
       <c r="D228" t="n">
-        <v>254.0271572625725</v>
+        <v>253.8679370762885</v>
       </c>
       <c r="E228" t="n">
-        <v>255.7188262939453</v>
+        <v>257.9677124023438</v>
       </c>
       <c r="F228" t="n">
-        <v>6931800</v>
+        <v>6532100</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B229" t="n">
-        <v>254.6341623817563</v>
+        <v>257.7886121067854</v>
       </c>
       <c r="C229" t="n">
-        <v>258.3259614136433</v>
+        <v>260.7141859356404</v>
       </c>
       <c r="D229" t="n">
-        <v>253.8679370762885</v>
+        <v>257.281105309594</v>
       </c>
       <c r="E229" t="n">
-        <v>257.9677124023438</v>
+        <v>260.5251159667969</v>
       </c>
       <c r="F229" t="n">
-        <v>6532100</v>
+        <v>8985100</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B230" t="n">
-        <v>257.7886121067854</v>
+        <v>259.9479684253454</v>
       </c>
       <c r="C230" t="n">
-        <v>260.7141859356404</v>
+        <v>262.853620890259</v>
       </c>
       <c r="D230" t="n">
-        <v>257.281105309594</v>
+        <v>257.0920280597301</v>
       </c>
       <c r="E230" t="n">
-        <v>260.5251159667969</v>
+        <v>258.5249633789062</v>
       </c>
       <c r="F230" t="n">
-        <v>8985100</v>
+        <v>5945900</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B231" t="n">
-        <v>259.9479684253454</v>
+        <v>254.7436088096904</v>
       </c>
       <c r="C231" t="n">
-        <v>262.853620890259</v>
+        <v>260.1270613743755</v>
       </c>
       <c r="D231" t="n">
-        <v>257.0920280597301</v>
+        <v>254.00723509927</v>
       </c>
       <c r="E231" t="n">
-        <v>258.5249633789062</v>
+        <v>259.5797424316406</v>
       </c>
       <c r="F231" t="n">
-        <v>5945900</v>
+        <v>4629300</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B232" t="n">
-        <v>254.7436088096904</v>
+        <v>260.4455042155265</v>
       </c>
       <c r="C232" t="n">
-        <v>260.1270613743755</v>
+        <v>261.3311205223152</v>
       </c>
       <c r="D232" t="n">
-        <v>254.00723509927</v>
+        <v>258.3756953399613</v>
       </c>
       <c r="E232" t="n">
-        <v>259.5797424316406</v>
+        <v>260.7937622070312</v>
       </c>
       <c r="F232" t="n">
-        <v>4629300</v>
+        <v>4852700</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B233" t="n">
-        <v>260.4455042155265</v>
+        <v>259.3707811439639</v>
       </c>
       <c r="C233" t="n">
-        <v>261.3311205223152</v>
+        <v>260.4255764680427</v>
       </c>
       <c r="D233" t="n">
-        <v>258.3756953399613</v>
+        <v>257.8881034534354</v>
       </c>
       <c r="E233" t="n">
-        <v>260.7937622070312</v>
+        <v>259.072265625</v>
       </c>
       <c r="F233" t="n">
-        <v>4852700</v>
+        <v>4998100</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B234" t="n">
-        <v>259.3707811439639</v>
+        <v>257.5995438259766</v>
       </c>
       <c r="C234" t="n">
-        <v>260.4255764680427</v>
+        <v>262.9829969172681</v>
       </c>
       <c r="D234" t="n">
-        <v>257.8881034534354</v>
+        <v>256.7437790079673</v>
       </c>
       <c r="E234" t="n">
-        <v>259.072265625</v>
+        <v>261.0823669433594</v>
       </c>
       <c r="F234" t="n">
-        <v>4998100</v>
+        <v>5515500</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B235" t="n">
-        <v>257.5995438259766</v>
+        <v>266.3563600087168</v>
       </c>
       <c r="C235" t="n">
-        <v>262.9829969172681</v>
+        <v>270.3964321763198</v>
       </c>
       <c r="D235" t="n">
-        <v>256.7437790079673</v>
+        <v>265.0229096495755</v>
       </c>
       <c r="E235" t="n">
-        <v>261.0823669433594</v>
+        <v>269.7794494628906</v>
       </c>
       <c r="F235" t="n">
-        <v>5515500</v>
+        <v>7838200</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B236" t="n">
-        <v>266.3563600087168</v>
+        <v>271.6601848020655</v>
       </c>
       <c r="C236" t="n">
-        <v>270.3964321763198</v>
+        <v>275.1131561312948</v>
       </c>
       <c r="D236" t="n">
-        <v>265.0229096495755</v>
+        <v>269.2321572777068</v>
       </c>
       <c r="E236" t="n">
-        <v>269.7794494628906</v>
+        <v>272.0681762695312</v>
       </c>
       <c r="F236" t="n">
-        <v>7838200</v>
+        <v>7728500</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B237" t="n">
-        <v>271.6601848020655</v>
+        <v>272.0582363321417</v>
       </c>
       <c r="C237" t="n">
-        <v>275.1131561312948</v>
+        <v>272.0582363321417</v>
       </c>
       <c r="D237" t="n">
-        <v>269.2321572777068</v>
+        <v>266.0578308105469</v>
       </c>
       <c r="E237" t="n">
-        <v>272.0681762695312</v>
+        <v>266.0578308105469</v>
       </c>
       <c r="F237" t="n">
-        <v>7728500</v>
+        <v>6475900</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B238" t="n">
-        <v>272.0582363321417</v>
+        <v>266.5155507786093</v>
       </c>
       <c r="C238" t="n">
-        <v>272.0582363321417</v>
+        <v>271.3218634751246</v>
       </c>
       <c r="D238" t="n">
-        <v>266.0578308105469</v>
+        <v>265.6896375517999</v>
       </c>
       <c r="E238" t="n">
-        <v>266.0578308105469</v>
+        <v>268.9137268066406</v>
       </c>
       <c r="F238" t="n">
-        <v>6475900</v>
+        <v>6186800</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B239" t="n">
-        <v>266.5155507786093</v>
+        <v>268.4161893708204</v>
       </c>
       <c r="C239" t="n">
-        <v>271.3218634751246</v>
+        <v>272.635401405727</v>
       </c>
       <c r="D239" t="n">
-        <v>265.6896375517999</v>
+        <v>267.2519483767422</v>
       </c>
       <c r="E239" t="n">
-        <v>268.9137268066406</v>
+        <v>271.7000122070312</v>
       </c>
       <c r="F239" t="n">
-        <v>6186800</v>
+        <v>5436100</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,25 +6657,25 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B240" t="n">
-        <v>268.4161893708204</v>
+        <v>271</v>
       </c>
       <c r="C240" t="n">
-        <v>272.635401405727</v>
+        <v>273.7999877929688</v>
       </c>
       <c r="D240" t="n">
-        <v>267.2519483767422</v>
+        <v>270.1799926757812</v>
       </c>
       <c r="E240" t="n">
-        <v>271.7000122070312</v>
+        <v>273.1400146484375</v>
       </c>
       <c r="F240" t="n">
-        <v>5436100</v>
+        <v>4687000</v>
       </c>
       <c r="G240" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="H240" t="n">
         <v>0</v>
@@ -6683,25 +6683,25 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B241" t="n">
-        <v>271</v>
+        <v>271.9700012207031</v>
       </c>
       <c r="C241" t="n">
-        <v>273.7999877929688</v>
+        <v>272.9100036621094</v>
       </c>
       <c r="D241" t="n">
-        <v>270.1799926757812</v>
+        <v>269.5499877929688</v>
       </c>
       <c r="E241" t="n">
-        <v>273.1400146484375</v>
+        <v>270</v>
       </c>
       <c r="F241" t="n">
-        <v>4687000</v>
+        <v>7214100</v>
       </c>
       <c r="G241" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B242" t="n">
-        <v>271.9700012207031</v>
+        <v>268.4500122070312</v>
       </c>
       <c r="C242" t="n">
-        <v>272.9100036621094</v>
+        <v>268.4500122070312</v>
       </c>
       <c r="D242" t="n">
-        <v>269.5499877929688</v>
+        <v>263.8299865722656</v>
       </c>
       <c r="E242" t="n">
-        <v>270</v>
+        <v>265.7699890136719</v>
       </c>
       <c r="F242" t="n">
-        <v>7214100</v>
+        <v>7306200</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B243" t="n">
-        <v>268.4500122070312</v>
+        <v>265.7799987792969</v>
       </c>
       <c r="C243" t="n">
-        <v>268.4500122070312</v>
+        <v>268.3800048828125</v>
       </c>
       <c r="D243" t="n">
-        <v>263.8299865722656</v>
+        <v>264.2699890136719</v>
       </c>
       <c r="E243" t="n">
-        <v>265.7699890136719</v>
+        <v>268.0400085449219</v>
       </c>
       <c r="F243" t="n">
-        <v>7306200</v>
+        <v>5765600</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B244" t="n">
-        <v>265.7799987792969</v>
+        <v>267.1300048828125</v>
       </c>
       <c r="C244" t="n">
-        <v>268.3800048828125</v>
+        <v>267.7699890136719</v>
       </c>
       <c r="D244" t="n">
-        <v>264.2699890136719</v>
+        <v>265.1700134277344</v>
       </c>
       <c r="E244" t="n">
-        <v>268.0400085449219</v>
+        <v>265.8500061035156</v>
       </c>
       <c r="F244" t="n">
-        <v>5765600</v>
+        <v>7900100</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B245" t="n">
-        <v>267.1300048828125</v>
+        <v>270.8299865722656</v>
       </c>
       <c r="C245" t="n">
-        <v>267.7699890136719</v>
+        <v>271.9100036621094</v>
       </c>
       <c r="D245" t="n">
-        <v>265.1700134277344</v>
+        <v>267.0199890136719</v>
       </c>
       <c r="E245" t="n">
-        <v>265.8500061035156</v>
+        <v>271.1900024414062</v>
       </c>
       <c r="F245" t="n">
-        <v>7900100</v>
+        <v>6033600</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B246" t="n">
-        <v>270.8299865722656</v>
+        <v>274.739990234375</v>
       </c>
       <c r="C246" t="n">
-        <v>271.9100036621094</v>
+        <v>281.0700073242188</v>
       </c>
       <c r="D246" t="n">
-        <v>267.0199890136719</v>
+        <v>273.5299987792969</v>
       </c>
       <c r="E246" t="n">
-        <v>271.1900024414062</v>
+        <v>275.2099914550781</v>
       </c>
       <c r="F246" t="n">
-        <v>6033600</v>
+        <v>7910600</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B247" t="n">
-        <v>274.739990234375</v>
+        <v>277.3200073242188</v>
       </c>
       <c r="C247" t="n">
-        <v>281.0700073242188</v>
+        <v>278.8900146484375</v>
       </c>
       <c r="D247" t="n">
-        <v>273.5299987792969</v>
+        <v>273.1600036621094</v>
       </c>
       <c r="E247" t="n">
-        <v>275.2099914550781</v>
+        <v>278.4299926757812</v>
       </c>
       <c r="F247" t="n">
-        <v>7910600</v>
+        <v>5940300</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B248" t="n">
-        <v>277.3200073242188</v>
+        <v>275.1300048828125</v>
       </c>
       <c r="C248" t="n">
-        <v>278.8900146484375</v>
+        <v>277.7999877929688</v>
       </c>
       <c r="D248" t="n">
-        <v>273.1600036621094</v>
+        <v>274.75</v>
       </c>
       <c r="E248" t="n">
-        <v>278.4299926757812</v>
+        <v>275.2300109863281</v>
       </c>
       <c r="F248" t="n">
-        <v>5940300</v>
+        <v>4320100</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B249" t="n">
-        <v>275.1300048828125</v>
+        <v>271.2799987792969</v>
       </c>
       <c r="C249" t="n">
-        <v>277.7999877929688</v>
+        <v>271.989990234375</v>
       </c>
       <c r="D249" t="n">
-        <v>274.75</v>
+        <v>266.8800048828125</v>
       </c>
       <c r="E249" t="n">
-        <v>275.2300109863281</v>
+        <v>269.1199951171875</v>
       </c>
       <c r="F249" t="n">
-        <v>4320100</v>
+        <v>8084700</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B250" t="n">
-        <v>271.2799987792969</v>
+        <v>268.510009765625</v>
       </c>
       <c r="C250" t="n">
-        <v>271.989990234375</v>
+        <v>270.1000061035156</v>
       </c>
       <c r="D250" t="n">
-        <v>266.8800048828125</v>
+        <v>266.7300109863281</v>
       </c>
       <c r="E250" t="n">
-        <v>269.1199951171875</v>
+        <v>267.0799865722656</v>
       </c>
       <c r="F250" t="n">
-        <v>8084700</v>
+        <v>6124600</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B251" t="n">
-        <v>268.510009765625</v>
+        <v>270.2099914550781</v>
       </c>
       <c r="C251" t="n">
-        <v>270.1000061035156</v>
+        <v>271.2699890136719</v>
       </c>
       <c r="D251" t="n">
-        <v>266.7300109863281</v>
+        <v>265.7200012207031</v>
       </c>
       <c r="E251" t="n">
-        <v>267.0799865722656</v>
+        <v>266.3500061035156</v>
       </c>
       <c r="F251" t="n">
-        <v>6124600</v>
+        <v>4929500</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B252" t="n">
-        <v>270.2099914550781</v>
+        <v>268.0299987792969</v>
       </c>
       <c r="C252" t="n">
-        <v>271.2699890136719</v>
+        <v>270.3999938964844</v>
       </c>
       <c r="D252" t="n">
-        <v>265.7200012207031</v>
+        <v>265.25</v>
       </c>
       <c r="E252" t="n">
-        <v>266.3500061035156</v>
+        <v>265.5799865722656</v>
       </c>
       <c r="F252" t="n">
-        <v>4929500</v>
+        <v>4701200</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -7371,7 +7371,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2407400000</v>
+        <v>2407939000</v>
       </c>
       <c r="C19" t="n">
         <v>2406922000</v>
@@ -7411,7 +7411,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11.13</v>
+        <v>11.131511</v>
       </c>
       <c r="C21" t="n">
         <v>5.843978</v>
@@ -10971,37 +10971,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>265.58</v>
+      </c>
+      <c r="D2" t="n">
         <v>266.35</v>
       </c>
-      <c r="D2" t="n">
-        <v>267.08</v>
-      </c>
       <c r="E2" t="n">
-        <v>270.21</v>
+        <v>268.03</v>
       </c>
       <c r="F2" t="n">
-        <v>271.27</v>
+        <v>270.385</v>
       </c>
       <c r="G2" t="n">
-        <v>265.72</v>
+        <v>265.25</v>
       </c>
       <c r="H2" t="n">
-        <v>4844617</v>
+        <v>4389477</v>
       </c>
       <c r="I2" t="n">
-        <v>7760762</v>
+        <v>7686738</v>
       </c>
       <c r="J2" t="n">
-        <v>641876492288</v>
+        <v>640020840448</v>
       </c>
       <c r="K2" t="n">
-        <v>30.97093</v>
+        <v>30.881392</v>
       </c>
       <c r="L2" t="n">
-        <v>21.393576</v>
+        <v>21.331726</v>
       </c>
       <c r="M2" t="n">
-        <v>8.630000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="N2" t="n">
         <v>281.07</v>
@@ -11013,7 +11013,7 @@
         <v>0.235</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="R2" t="n">
         <v>0.21482</v>
@@ -11037,7 +11037,7 @@
         <v>35.284</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.5487475</v>
+        <v>7.526924</v>
       </c>
       <c r="Z2" t="n">
         <v>-0.008999999999999999</v>
@@ -11049,7 +11049,7 @@
         <v>97929003008</v>
       </c>
       <c r="AC2" t="n">
-        <v>670154489856</v>
+        <v>668298838016</v>
       </c>
       <c r="AD2" t="n">
         <v>34872000512</v>
@@ -11076,7 +11076,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-11 19:03:10</t>
+          <t>2026-09-12 21:47:14</t>
         </is>
       </c>
     </row>
